--- a/data/adult_login_required_webtoons_v2.xlsx
+++ b/data/adult_login_required_webtoons_v2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK53"/>
+  <dimension ref="A1:AK54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -634,7 +634,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-22 11:40:58</t>
+          <t>2026-06-29 13:06:01</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -754,7 +754,7 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2026-06-22 12:22:39</t>
+          <t>2026-06-29 13:48:27</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-06-22 11:40:59</t>
+          <t>2026-06-29 13:06:01</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -910,7 +910,7 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2026-06-22 12:22:39</t>
+          <t>2026-06-29 13:48:27</t>
         </is>
       </c>
     </row>
@@ -945,7 +945,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-06-22 11:40:59</t>
+          <t>2026-06-29 13:06:02</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2026-06-22 12:22:39</t>
+          <t>2026-06-29 13:48:27</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-06-22 11:41:00</t>
+          <t>2026-06-29 13:06:02</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2026-06-22 12:22:39</t>
+          <t>2026-06-29 13:48:27</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-22 11:41:00</t>
+          <t>2026-06-29 13:06:03</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2026-06-22 12:22:39</t>
+          <t>2026-06-29 13:48:27</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-22 11:41:01</t>
+          <t>2026-06-29 13:06:03</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2026-06-22 12:22:39</t>
+          <t>2026-06-29 13:48:27</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-06-22 11:41:02</t>
+          <t>2026-06-29 13:06:05</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2026-06-22 12:22:39</t>
+          <t>2026-06-29 13:48:27</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-06-22 11:41:02</t>
+          <t>2026-06-29 13:06:05</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2026-06-22 12:22:39</t>
+          <t>2026-06-29 13:48:27</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-06-22 11:41:02</t>
+          <t>2026-06-29 13:06:05</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2026-06-22 12:22:39</t>
+          <t>2026-06-29 13:48:27</t>
         </is>
       </c>
     </row>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-06-22 11:41:03</t>
+          <t>2026-06-29 13:06:05</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2026-06-22 12:22:39</t>
+          <t>2026-06-29 13:48:27</t>
         </is>
       </c>
     </row>
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-06-22 11:41:03</t>
+          <t>2026-06-29 13:06:06</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2026-06-22 12:22:39</t>
+          <t>2026-06-29 13:48:27</t>
         </is>
       </c>
     </row>
@@ -2341,26 +2341,26 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>축살</t>
+          <t>화분</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=840184&amp;tab=tue</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=851671&amp;tab=tue</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>840184</t>
+          <t>851671</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-06-22 11:41:03</t>
+          <t>2026-06-29 13:06:06</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -2388,21 +2388,21 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>축살</t>
+          <t>화분</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>축살 (총 51화/미완결)</t>
+          <t>화분 (총 5화/미완결)</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>총 51화/미완결</t>
+          <t>총 5화/미완결</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -2411,30 +2411,30 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>평점 9.9 | 장성준 장성준 | 2026.05.11. | 총51화/미완결 | 전화 무료</t>
+          <t>평점 10.0 | 쿼시 쿼시 | 2026.06.15. | 총5화/미완결 | 1화 무료</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>평점 9.9 | 장성준 장성준 | 2026.05.11. | 총51화/미완결 | 전화 무료</t>
+          <t>평점 10.0 | 쿼시 쿼시 | 2026.06.15. | 총5화/미완결 | 1화 무료</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=12763164</t>
+          <t>https://series.naver.com/comic/detail.series?productNo=14284647</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>12763164</t>
+          <t>14284647</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>축살 (총 51화/미완결)
+          <t>화분 (총 5화/미완결)
 평점
-9.9 | 장성준 장성준 | 2026.05.11. | 총51화/미완결 | 전화 무료
-귀신이 나온다는 이유로 아무도 찾지 않는 버려진 마을이 된 타악리...그곳을 미스테리X파일 제작팀이 관심을 갖고 찾아간다. 그러나 기다리는 것은 당시 사건으로 죽은 귀신과, 염매라는 사악한 주술을 통해 살아 있는 악귀가 ..</t>
+10.0 | 쿼시 쿼시 | 2026.06.15. | 총5화/미완결 | 1화 무료
+버림받는 것이 무서운 여자와 그런 그녀가 무섭게 느껴지는 남자. 오래된 인연으로 시작된 사랑은 다정함의 얼굴을 한 집착이 되어, 두 사람의 일상과 마음을 서서히 갉아먹어 간다.우리 사랑은, 어디서부터 잘못된거지..?</t>
         </is>
       </c>
       <c r="Y13" t="b">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>2026-06-22 12:22:39</t>
+          <t>2026-06-29 13:48:27</t>
         </is>
       </c>
     </row>
@@ -2497,7 +2497,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-06-22 11:41:04</t>
+          <t>2026-06-29 13:06:06</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -2637,7 +2637,7 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>2026-06-22 12:22:39</t>
+          <t>2026-06-29 13:48:27</t>
         </is>
       </c>
     </row>
@@ -2653,26 +2653,26 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>화분</t>
+          <t>포 더 퀸덤</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=851671&amp;tab=tue</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=812414&amp;tab=tue</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>851671</t>
+          <t>812414</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-06-22 11:41:04</t>
+          <t>2026-06-29 13:06:07</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -2700,21 +2700,21 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>화분</t>
+          <t>포 더 퀸덤</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>화분 (총 5화/미완결)</t>
+          <t>포 더 퀸덤 (총 128화/미완결)</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>총 5화/미완결</t>
+          <t>총 128화/미완결</t>
         </is>
       </c>
       <c r="R15" t="n">
-        <v>5</v>
+        <v>128</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -2723,181 +2723,25 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>평점 10.0 | 쿼시 쿼시 | 2026.06.15. | 총5화/미완결 | 1화 무료</t>
+          <t>평점 9.0 | 로즈옹 로즈옹 | 2026.06.15. | 총128화/미완결 | 123화 무료</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>평점 10.0 | 쿼시 쿼시 | 2026.06.15. | 총5화/미완결 | 1화 무료</t>
+          <t>평점 9.0 | 로즈옹 로즈옹 | 2026.06.15. | 총128화/미완결 | 123화 무료</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=14284647</t>
+          <t>https://series.naver.com/comic/detail.series?productNo=9895056</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>14284647</t>
+          <t>9895056</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
-        <is>
-          <t>화분 (총 5화/미완결)
-평점
-10.0 | 쿼시 쿼시 | 2026.06.15. | 총5화/미완결 | 1화 무료
-버림받는 것이 무서운 여자와 그런 그녀가 무섭게 느껴지는 남자. 오래된 인연으로 시작된 사랑은 다정함의 얼굴을 한 집착이 되어, 두 사람의 일상과 마음을 서서히 갉아먹어 간다.우리 사랑은, 어디서부터 잘못된거지..?</t>
-        </is>
-      </c>
-      <c r="Y15" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>105</v>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>review_needed</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>non_compilation_but_download_not_ok</t>
-        </is>
-      </c>
-      <c r="AE15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF15" t="inlineStr"/>
-      <c r="AG15" t="inlineStr"/>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>2026-06-22 12:22:39</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>tue</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>화</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>79</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>포 더 퀸덤</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=812414&amp;tab=tue</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>812414</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>2026-06-22 11:41:05</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="b">
-        <v>1</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>tue</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>tue</t>
-        </is>
-      </c>
-      <c r="N16" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>포 더 퀸덤</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>포 더 퀸덤 (총 128화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>총 128화/미완결</t>
-        </is>
-      </c>
-      <c r="R16" t="n">
-        <v>128</v>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>평점 9.0 | 로즈옹 로즈옹 | 2026.06.15. | 총128화/미완결 | 123화 무료</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>평점 9.0 | 로즈옹 로즈옹 | 2026.06.15. | 총128화/미완결 | 123화 무료</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=9895056</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>9895056</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
         <is>
           <t>포 더 퀸덤 (총 128화/미완결)
 평점
@@ -2905,6 +2749,162 @@
 악마 아벨은 인간 여자 연리에게 사랑하는 형, 카인을 잃고 만다.분노에 가득 차 연리를 찾아간 아벨은 사랑에 빠지는 금총알을 맞게 되면서, 연리에게 끓어오르는 사랑을 느끼게 되는데…그는 과연 형제의 복수를 택할 것인가..</t>
         </is>
       </c>
+      <c r="Y15" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>non_compilation_but_download_not_ok</t>
+        </is>
+      </c>
+      <c r="AE15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>2026-06-29 13:48:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>tue</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>화</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>100</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>연애 못하면 사망</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=834175&amp;tab=tue</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>834175</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-06-29 13:06:07</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="b">
+        <v>1</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>tue</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>tue</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>연애 못하면 사망</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>연애 못하면 사망 (총 85화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>총 85화/미완결</t>
+        </is>
+      </c>
+      <c r="R16" t="n">
+        <v>85</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>평점 10.0 | 홍치 홍치 | 2026.06.15. | 총85화/미완결 | 80화 무료</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>평점 10.0 | 홍치 홍치 | 2026.06.15. | 총85화/미완결 | 80화 무료</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=11845281</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>11845281</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>연애 못하면 사망 (총 85화/미완결)
+평점
+10.0 | 홍치 홍치 | 2026.06.15. | 총85화/미완결 | 80화 무료
+111세 덕순 F&amp;B의 회장 김덕순은 죽기 직전 마지막 소원으로 첫사랑 왕종열과의 불꽃 같은 사랑을 하게 해달라 빌고 25세 김도희라는 여자의 몸에서 깨어난다. 그러나 마지막 소원을 이루기 위해 종열을 향해 달려가던 덕순..</t>
+        </is>
+      </c>
       <c r="Y16" t="b">
         <v>0</v>
       </c>
@@ -2912,31 +2912,37 @@
         <v>1</v>
       </c>
       <c r="AA16" t="n">
-        <v>105</v>
+        <v>145</v>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+          <t>title_contains,author_exact_or_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>review_needed</t>
+          <t>matched</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>non_compilation_but_download_not_ok</t>
+          <t>first_non_compilation_numeric_download</t>
         </is>
       </c>
       <c r="AE16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF16" t="inlineStr"/>
-      <c r="AG16" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>37만</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>370000</v>
+      </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>not_found</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
@@ -2949,7 +2955,7 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>2026-06-22 12:22:39</t>
+          <t>2026-06-29 13:48:27</t>
         </is>
       </c>
     </row>
@@ -2965,7 +2971,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2984,7 +2990,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-06-22 11:41:06</t>
+          <t>2026-06-29 13:06:08</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -3105,7 +3111,7 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>2026-06-22 12:22:39</t>
+          <t>2026-06-29 13:48:27</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3146,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-06-22 11:41:06</t>
+          <t>2026-06-29 13:06:08</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -3261,7 +3267,7 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>2026-06-22 12:22:39</t>
+          <t>2026-06-29 13:48:27</t>
         </is>
       </c>
     </row>
@@ -3277,7 +3283,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3296,7 +3302,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-06-22 11:41:06</t>
+          <t>2026-06-29 13:06:08</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
@@ -3423,7 +3429,7 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>2026-06-22 12:22:39</t>
+          <t>2026-06-29 13:48:27</t>
         </is>
       </c>
     </row>
@@ -3439,7 +3445,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3458,7 +3464,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-06-22 11:41:07</t>
+          <t>2026-06-29 13:06:09</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -3579,7 +3585,7 @@
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>2026-06-22 12:22:39</t>
+          <t>2026-06-29 13:48:27</t>
         </is>
       </c>
     </row>
@@ -3614,7 +3620,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-06-22 11:41:07</t>
+          <t>2026-06-29 13:06:09</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
@@ -3741,7 +3747,7 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>2026-06-22 12:22:39</t>
+          <t>2026-06-29 13:48:27</t>
         </is>
       </c>
     </row>
@@ -3757,7 +3763,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3776,7 +3782,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-06-22 11:41:07</t>
+          <t>2026-06-29 13:06:09</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
@@ -3897,7 +3903,7 @@
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>2026-06-22 12:22:39</t>
+          <t>2026-06-29 13:48:27</t>
         </is>
       </c>
     </row>
@@ -3913,7 +3919,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3932,7 +3938,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-06-22 11:41:08</t>
+          <t>2026-06-29 13:06:10</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
@@ -4053,7 +4059,7 @@
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>2026-06-22 12:22:39</t>
+          <t>2026-06-29 13:48:27</t>
         </is>
       </c>
     </row>
@@ -4088,7 +4094,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-06-22 11:41:10</t>
+          <t>2026-06-29 13:06:11</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -4209,7 +4215,7 @@
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>2026-06-22 12:22:39</t>
+          <t>2026-06-29 13:48:27</t>
         </is>
       </c>
     </row>
@@ -4225,26 +4231,26 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>당신의 살인을 위하여</t>
+          <t>당신에게 얽힌 채</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=836066&amp;tab=thu</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=849879&amp;tab=thu</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>836066</t>
+          <t>849879</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-06-22 11:41:11</t>
+          <t>2026-06-29 13:06:12</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -4272,21 +4278,21 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>당신의 살인을 위하여</t>
+          <t>당신에게 얽힌 채</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>당신의 살인을 위하여 (총 70화/미완결)</t>
+          <t>당신에게 얽힌 채 (총 10화/미완결)</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>총 70화/미완결</t>
+          <t>총 10화/미완결</t>
         </is>
       </c>
       <c r="R25" t="n">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -4295,181 +4301,25 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>평점 9.9 | 세윤 징크 | 2026.06.17. | 총70화/미완결 | 전화 무료</t>
+          <t>평점 10.0 | Nicole Knight, 유다 danah789 | 2026.06.17. | 총10화/미완결 | 5화 무료</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>평점 9.9 | 세윤 징크 | 2026.06.17. | 총70화/미완결 | 전화 무료</t>
+          <t>평점 10.0 | Nicole Knight, 유다 danah789 | 2026.06.17. | 총10화/미완결 | 5화 무료</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=12161861</t>
+          <t>https://series.naver.com/comic/detail.series?productNo=14041685</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>12161861</t>
+          <t>14041685</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
-        <is>
-          <t>당신의 살인을 위하여 (총 70화/미완결)
-평점
-9.9 | 세윤 징크 | 2026.06.17. | 총70화/미완결 | 전화 무료
-자신을 억누르고 사는 초등학교 교사 고기정은 학부모에게 시달리다 근처 변호사를 찾아간다.그러나 찾아간 변호사 오인섭은 연쇄살인마였는데..</t>
-        </is>
-      </c>
-      <c r="Y25" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>105</v>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>review_needed</t>
-        </is>
-      </c>
-      <c r="AD25" t="inlineStr">
-        <is>
-          <t>non_compilation_but_download_not_ok</t>
-        </is>
-      </c>
-      <c r="AE25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF25" t="inlineStr"/>
-      <c r="AG25" t="inlineStr"/>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>2026-06-22 12:22:39</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>thu</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>목</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>34</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>당신에게 얽힌 채</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=849879&amp;tab=thu</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>849879</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>2026-06-22 11:41:11</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="b">
-        <v>1</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>thu</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>thu</t>
-        </is>
-      </c>
-      <c r="N26" t="n">
-        <v>1</v>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>당신에게 얽힌 채</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>당신에게 얽힌 채 (총 10화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>총 10화/미완결</t>
-        </is>
-      </c>
-      <c r="R26" t="n">
-        <v>10</v>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>평점 10.0 | Nicole Knight, 유다 danah789 | 2026.06.17. | 총10화/미완결 | 5화 무료</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>평점 10.0 | Nicole Knight, 유다 danah789 | 2026.06.17. | 총10화/미완결 | 5화 무료</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=14041685</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>14041685</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
         <is>
           <t>당신에게 얽힌 채 (총 10화/미완결)
 평점
@@ -4477,155 +4327,155 @@
 상속자가 아닌 복종하는 존재로 길러진 에이바 모레티. 뉴욕에서 가장 강력한 마피아 가문의 막내딸인 그녀는 ‘집안의 사고뭉치’라는 오명을 벗고 자신의 자리를 찾기 위해 분투한다.그러던 어느 날 밤, 낯선 남자와 보낸 뜨..</t>
         </is>
       </c>
-      <c r="Y26" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z26" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA26" t="n">
+      <c r="Y25" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA25" t="n">
         <v>105</v>
       </c>
-      <c r="AB26" t="inlineStr">
+      <c r="AB25" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
+      <c r="AC25" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD26" t="inlineStr">
+      <c r="AD25" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF26" t="inlineStr"/>
-      <c r="AG26" t="inlineStr"/>
-      <c r="AH26" t="inlineStr">
+      <c r="AE25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI26" t="inlineStr">
+      <c r="AI25" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>2026-06-22 12:22:39</t>
+      <c r="AJ25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>2026-06-29 13:48:27</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="C27" t="n">
-        <v>76</v>
-      </c>
-      <c r="D27" t="inlineStr">
+      <c r="C26" t="n">
+        <v>74</v>
+      </c>
+      <c r="D26" t="inlineStr">
         <is>
           <t>휴먼 웨어러블</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=845460&amp;tab=thu</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>845460</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>2026-06-22 11:41:13</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="b">
-        <v>1</v>
-      </c>
-      <c r="J27" t="inlineStr">
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-06-29 13:06:14</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="b">
+        <v>1</v>
+      </c>
+      <c r="J26" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="N27" t="n">
-        <v>1</v>
-      </c>
-      <c r="O27" t="inlineStr">
+      <c r="N26" t="n">
+        <v>1</v>
+      </c>
+      <c r="O26" t="inlineStr">
         <is>
           <t>휴먼 웨어러블</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>휴먼 웨어러블 (총 30화/미완결)</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>총 30화/미완결</t>
         </is>
       </c>
-      <c r="R27" t="n">
+      <c r="R26" t="n">
         <v>30</v>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>평점 9.9 | 쥬타인 쥬타인 | 2026.06.03. | 총30화/미완결 | 27화 무료</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>평점 9.9 | 쥬타인 쥬타인 | 2026.06.03. | 총30화/미완결 | 27화 무료</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13481722</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>13481722</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>휴먼 웨어러블 (총 30화/미완결)
 평점
@@ -4633,6 +4483,162 @@
 꿈의 무대, 패션 서바이벌 &lt;휴먼 웨어러블&gt;.고아 출신이지만 명문 ‘순백패션예술학교’를 거쳐 올라온 학생들.이 무대에서 인생 역전의 주인공이 탄생한다—…그런데 무언가, 이상하게 흘러가기 시작했다.</t>
         </is>
       </c>
+      <c r="Y26" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>non_compilation_but_download_not_ok</t>
+        </is>
+      </c>
+      <c r="AE26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>2026-06-29 13:48:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>thu</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>102</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>운명해주세요</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=835004&amp;tab=thu</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>835004</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-06-29 13:06:14</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="b">
+        <v>1</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>thu</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>thu</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>운명해주세요</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>운명해주세요 (총 53화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>총 53화/미완결</t>
+        </is>
+      </c>
+      <c r="R27" t="n">
+        <v>53</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>평점 10.0 | 노뱀 노뱀 | 2025.12.24. | 총53화/미완결 | 전화 무료</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>평점 10.0 | 노뱀 노뱀 | 2025.12.24. | 총53화/미완결 | 전화 무료</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=11990945</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>11990945</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>운명해주세요 (총 53화/미완결)
+평점
+10.0 | 노뱀 노뱀 | 2025.12.24. | 총53화/미완결 | 전화 무료
+무수한 고난을 알코올의 힘으로 씩씩하게 이겨내는 청년 백수 해솔.그런 해솔의 앞에 13년 만에 나타난 수상한 속내의 하현.둘 중 하나가 죽어야만 살 수 있는 해솔과 하현의 저세상 로맨스!</t>
+        </is>
+      </c>
       <c r="Y27" t="b">
         <v>0</v>
       </c>
@@ -4649,27 +4655,33 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>review_needed</t>
+          <t>matched</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>non_compilation_but_download_not_ok</t>
+          <t>first_non_compilation_numeric_download</t>
         </is>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
-      <c r="AG27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>12.7만</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>127000</v>
+      </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>not_found</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>reused_existing_product_no</t>
+          <t>searched_series</t>
         </is>
       </c>
       <c r="AJ27" t="b">
@@ -4677,7 +4689,7 @@
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>2026-06-22 12:22:39</t>
+          <t>2026-06-29 13:48:27</t>
         </is>
       </c>
     </row>
@@ -4693,7 +4705,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4712,7 +4724,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-06-22 11:41:14</t>
+          <t>2026-06-29 13:06:15</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
@@ -4833,7 +4845,7 @@
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>2026-06-22 12:22:39</t>
+          <t>2026-06-29 13:48:27</t>
         </is>
       </c>
     </row>
@@ -4868,7 +4880,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-06-22 11:41:15</t>
+          <t>2026-06-29 13:06:15</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
@@ -4995,7 +5007,7 @@
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>2026-06-22 12:22:39</t>
+          <t>2026-06-29 13:48:27</t>
         </is>
       </c>
     </row>
@@ -5030,7 +5042,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-06-22 11:41:15</t>
+          <t>2026-06-29 13:06:15</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
@@ -5151,7 +5163,7 @@
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>2026-06-22 12:22:39</t>
+          <t>2026-06-29 13:48:27</t>
         </is>
       </c>
     </row>
@@ -5186,7 +5198,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-06-22 11:41:15</t>
+          <t>2026-06-29 13:06:15</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
@@ -5307,7 +5319,7 @@
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>2026-06-22 12:22:39</t>
+          <t>2026-06-29 13:48:27</t>
         </is>
       </c>
     </row>
@@ -5342,7 +5354,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-06-22 11:41:16</t>
+          <t>2026-06-29 13:06:16</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
@@ -5463,7 +5475,7 @@
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>2026-06-22 12:22:39</t>
+          <t>2026-06-29 13:48:27</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5510,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-06-22 11:41:16</t>
+          <t>2026-06-29 13:06:16</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
@@ -5625,7 +5637,7 @@
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>2026-06-22 12:22:39</t>
+          <t>2026-06-29 13:48:27</t>
         </is>
       </c>
     </row>
@@ -5660,7 +5672,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-06-22 11:41:17</t>
+          <t>2026-06-29 13:06:17</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
@@ -5787,7 +5799,7 @@
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>2026-06-22 12:22:39</t>
+          <t>2026-06-29 13:48:27</t>
         </is>
       </c>
     </row>
@@ -5803,7 +5815,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5822,7 +5834,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-06-22 11:41:18</t>
+          <t>2026-06-29 13:06:17</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
@@ -5943,7 +5955,7 @@
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>2026-06-22 12:22:39</t>
+          <t>2026-06-29 13:48:27</t>
         </is>
       </c>
     </row>
@@ -5959,7 +5971,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5978,7 +5990,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-06-22 11:41:18</t>
+          <t>2026-06-29 13:06:17</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
@@ -6099,7 +6111,7 @@
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>2026-06-22 12:22:39</t>
+          <t>2026-06-29 13:48:27</t>
         </is>
       </c>
     </row>
@@ -6115,26 +6127,26 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>완벽한 게 다인</t>
+          <t>나의 모르는 여자친구</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=841767&amp;tab=fri</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=841923&amp;tab=fri</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>841767</t>
+          <t>841923</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-06-22 11:41:20</t>
+          <t>2026-06-29 13:06:19</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
@@ -6162,21 +6174,21 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>완벽한 게 다인</t>
+          <t>나의 모르는 여자친구</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>완벽한 게 다인 (총 46화/미완결)</t>
+          <t>나의 모르는 여자친구 (총 41화/미완결)</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>총 46화/미완결</t>
+          <t>총 41화/미완결</t>
         </is>
       </c>
       <c r="R37" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -6185,26 +6197,26 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>평점 10.0 | 은솔 재림 | 2026.06.04. | 총46화/미완결 | 41화 무료</t>
+          <t>평점 9.9 | 이정빈 이정빈 | 2026.06.04. | 총41화/미완결 | 36화 무료</t>
         </is>
       </c>
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr">
         <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=13009203</t>
+          <t>https://series.naver.com/comic/detail.series?productNo=13025901</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>13009203</t>
+          <t>13025901</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>완벽한 게 다인 (총 46화/미완결)
+          <t>나의 모르는 여자친구 (총 41화/미완결)
 평점
-10.0 | 은솔 재림 | 2026.06.04. | 총46화/미완결 | 41화 무료
-매사에 열심히, 열정적인 학창시절을 살아온 대학 새내기 김다인은 성적, 교우관계, 스펙 모든 것이 완벽한 캠퍼스 라이프를 꿈꾼다.하지만 다인은 자신과 이름이 같지만 자신과 다르게 '완벽한 외모와 인성을 겸비한' 강다인..</t>
+9.9 | 이정빈 이정빈 | 2026.06.04. | 총41화/미완결 | 36화 무료
+눈 떠보니 아이돌의 여자친구가 되어있다?! 평범한 삶을 추구하는 대학생 ‘해나’는 인기 아이돌 ‘은하‘와의 거짓 열애설로 일상에 금이 갈 위기를 맞는다.</t>
         </is>
       </c>
       <c r="Y37" t="b">
@@ -6236,11 +6248,11 @@
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>25.8만</t>
+          <t>7.8만</t>
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>258000</v>
+        <v>78000</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6257,7 +6269,7 @@
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>2026-06-22 12:22:39</t>
+          <t>2026-06-29 13:48:27</t>
         </is>
       </c>
     </row>
@@ -6292,7 +6304,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-06-22 11:41:21</t>
+          <t>2026-06-29 13:06:19</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -6412,7 +6424,7 @@
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>2026-06-22 12:22:39</t>
+          <t>2026-06-29 13:48:27</t>
         </is>
       </c>
     </row>
@@ -6447,7 +6459,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-06-22 11:41:21</t>
+          <t>2026-06-29 13:06:19</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
@@ -6568,7 +6580,7 @@
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>2026-06-22 12:22:39</t>
+          <t>2026-06-29 13:48:27</t>
         </is>
       </c>
     </row>
@@ -6584,7 +6596,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -6603,7 +6615,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-06-22 11:41:21</t>
+          <t>2026-06-29 13:06:19</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
@@ -6724,7 +6736,7 @@
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>2026-06-22 12:22:39</t>
+          <t>2026-06-29 13:48:27</t>
         </is>
       </c>
     </row>
@@ -6759,7 +6771,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-06-22 11:41:21</t>
+          <t>2026-06-29 13:06:19</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -6880,7 +6892,7 @@
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>2026-06-22 12:22:39</t>
+          <t>2026-06-29 13:48:27</t>
         </is>
       </c>
     </row>
@@ -6896,7 +6908,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6915,7 +6927,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-06-22 11:41:23</t>
+          <t>2026-06-29 13:06:20</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
@@ -7036,7 +7048,7 @@
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>2026-06-22 12:22:39</t>
+          <t>2026-06-29 13:48:27</t>
         </is>
       </c>
     </row>
@@ -7052,7 +7064,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -7071,7 +7083,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-06-22 11:41:23</t>
+          <t>2026-06-29 13:06:20</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
@@ -7192,7 +7204,7 @@
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>2026-06-22 12:22:39</t>
+          <t>2026-06-29 13:48:27</t>
         </is>
       </c>
     </row>
@@ -7208,7 +7220,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -7227,7 +7239,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-06-22 11:41:23</t>
+          <t>2026-06-29 13:06:20</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
@@ -7348,42 +7360,42 @@
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>2026-06-22 12:22:39</t>
+          <t>2026-06-29 13:48:27</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>sat</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>토</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2회차 환관이 남성을 되찾음</t>
+          <t>데스루프</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=832566&amp;tab=sun</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=852086&amp;tab=sat</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>832566</t>
+          <t>852086</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-06-22 11:41:26</t>
+          <t>2026-06-29 13:06:21</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
@@ -7398,61 +7410,217 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>1</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>데스루프</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>데스루프 (총 6화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>총 6화/미완결</t>
+        </is>
+      </c>
+      <c r="R45" t="n">
+        <v>6</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>평점 8.3 | 은삼 은삼 | 2026.06.26. | 총6화/미완결 | 1화 무료</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>평점 8.3 | 은삼 은삼 | 2026.06.26. | 총6화/미완결 | 1화 무료</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=14366954</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>14366954</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>데스루프 (총 6화/미완결)
+평점
+8.3 | 은삼 은삼 | 2026.06.26. | 총6화/미완결 | 1화 무료
+정신을 차려 보니 지하 창고에 갇힌 주인공 홍연화.연화는 자신을 가둔 남성에게 여러 번 끔찍한 죽음을 맞이하지만, 계속해서 시간이 반복된다.겨우 그곳을 빠져나오지만 그녀 앞에 마주한 것은 끔찍하게 생긴 괴물.과연 그녀..</t>
+        </is>
+      </c>
+      <c r="Y45" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z45" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>non_compilation_but_download_not_ok</t>
+        </is>
+      </c>
+      <c r="AE45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="inlineStr"/>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>searched_series</t>
+        </is>
+      </c>
+      <c r="AJ45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>2026-06-29 13:48:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>4</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2회차 환관이 남성을 되찾음</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=832566&amp;tab=sun</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>832566</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-06-29 13:06:23</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="b">
+        <v>1</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="N45" t="n">
-        <v>1</v>
-      </c>
-      <c r="O45" t="inlineStr">
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>1</v>
+      </c>
+      <c r="O46" t="inlineStr">
         <is>
           <t>2회차 환관이 남성을 되찾음</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>2회차 환관이 남성을 되찾음 (총 93화/미완결)</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="Q46" t="inlineStr">
         <is>
           <t>총 93화/미완결</t>
         </is>
       </c>
-      <c r="R45" t="n">
+      <c r="R46" t="n">
         <v>93</v>
       </c>
-      <c r="S45" t="inlineStr">
+      <c r="S46" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr">
+      <c r="T46" t="inlineStr">
         <is>
           <t>평점 9.6 | LICO, 노빠꾸맨 포스 스튜디오 | 2026.06.13. | 총93화/미완결 | 89화 무료</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="U46" t="inlineStr">
         <is>
           <t>평점 9.6 | LICO, 노빠꾸맨 포스 스튜디오 | 2026.06.13. | 총93화/미완결 | 89화 무료</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr">
+      <c r="V46" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=11636787</t>
         </is>
       </c>
-      <c r="W45" t="inlineStr">
+      <c r="W46" t="inlineStr">
         <is>
           <t>11636787</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>2회차 환관이 남성을 되찾음 (총 93화/미완결)
 평점
@@ -7460,310 +7628,310 @@
 제국의 국정을 마음대로 주무르는 비선실세 환관, 이철수.절대 권력에 돈 많고, 무공까지 강하지만.. 그게 무슨 의미가 있지? '그걸' 못하는데!!환생대법을 통해, 고자가 되기 전으로 회귀한 철수의 목표는 하나다.알파메일이 되..</t>
         </is>
       </c>
-      <c r="Y45" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z45" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA45" t="n">
+      <c r="Y46" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA46" t="n">
         <v>105</v>
       </c>
-      <c r="AB45" t="inlineStr">
+      <c r="AB46" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
+      <c r="AC46" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD45" t="inlineStr">
+      <c r="AD46" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF45" t="inlineStr"/>
-      <c r="AG45" t="inlineStr"/>
-      <c r="AH45" t="inlineStr">
+      <c r="AE46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="inlineStr"/>
+      <c r="AH46" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI45" t="inlineStr">
+      <c r="AI46" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>2026-06-22 12:22:39</t>
+      <c r="AJ46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>2026-06-29 13:48:27</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C46" t="n">
-        <v>5</v>
-      </c>
-      <c r="D46" t="inlineStr">
+      <c r="C47" t="n">
+        <v>6</v>
+      </c>
+      <c r="D47" t="inlineStr">
         <is>
           <t>시루/24/1km</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=850068&amp;tab=sun</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>850068</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>2026-06-22 11:41:26</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="b">
-        <v>1</v>
-      </c>
-      <c r="J46" t="inlineStr">
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-06-29 13:06:23</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="b">
+        <v>1</v>
+      </c>
+      <c r="J47" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr">
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="N46" t="n">
-        <v>1</v>
-      </c>
-      <c r="O46" t="inlineStr">
+      <c r="N47" t="n">
+        <v>1</v>
+      </c>
+      <c r="O47" t="inlineStr">
         <is>
           <t>19금 시루/24/1km</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>19금 시루/24/1km (총 12화/미완결)</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="Q47" t="inlineStr">
         <is>
           <t>총 12화/미완결</t>
         </is>
       </c>
-      <c r="R46" t="n">
+      <c r="R47" t="n">
         <v>12</v>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="S47" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr">
+      <c r="T47" t="inlineStr">
         <is>
           <t>평점 10.0 | 6M 941 | 2026.06.13. | 총12화/미완결 | 7화 무료</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="U47" t="inlineStr">
         <is>
           <t>평점 10.0 | 6M 941 | 2026.06.13. | 총12화/미완결 | 7화 무료</t>
         </is>
       </c>
-      <c r="V46" t="inlineStr">
+      <c r="V47" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14081030</t>
         </is>
       </c>
-      <c r="W46" t="inlineStr">
+      <c r="W47" t="inlineStr">
         <is>
           <t>14081030</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>19금 시루/24/1km (총 12화/미완결)
 평점
 10.0 | 6M 941 | 2026.06.13. | 총12화/미완결 | 7화 무료</t>
         </is>
       </c>
-      <c r="Y46" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z46" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA46" t="n">
+      <c r="Y47" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z47" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA47" t="n">
         <v>105</v>
       </c>
-      <c r="AB46" t="inlineStr">
+      <c r="AB47" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
+      <c r="AC47" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD46" t="inlineStr">
+      <c r="AD47" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF46" t="inlineStr"/>
-      <c r="AG46" t="inlineStr"/>
-      <c r="AH46" t="inlineStr">
+      <c r="AE47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="inlineStr"/>
+      <c r="AH47" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI46" t="inlineStr">
+      <c r="AI47" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>2026-06-22 12:22:39</t>
+      <c r="AJ47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>2026-06-29 13:48:27</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C47" t="n">
-        <v>10</v>
-      </c>
-      <c r="D47" t="inlineStr">
+      <c r="C48" t="n">
+        <v>8</v>
+      </c>
+      <c r="D48" t="inlineStr">
         <is>
           <t>어린 아내와 나쁜 짓</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=851385&amp;tab=sun</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>851385</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>2026-06-22 11:41:26</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="b">
-        <v>1</v>
-      </c>
-      <c r="J47" t="inlineStr">
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026-06-29 13:06:23</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="b">
+        <v>1</v>
+      </c>
+      <c r="J48" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr">
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="N47" t="n">
-        <v>1</v>
-      </c>
-      <c r="O47" t="inlineStr">
+      <c r="N48" t="n">
+        <v>1</v>
+      </c>
+      <c r="O48" t="inlineStr">
         <is>
           <t>어린 아내와 나쁜 짓</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>어린 아내와 나쁜 짓 (총 8화/미완결)</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="Q48" t="inlineStr">
         <is>
           <t>총 8화/미완결</t>
         </is>
       </c>
-      <c r="R47" t="n">
+      <c r="R48" t="n">
         <v>8</v>
       </c>
-      <c r="S47" t="inlineStr">
+      <c r="S48" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T47" t="inlineStr">
+      <c r="T48" t="inlineStr">
         <is>
           <t>평점 9.9 | 이리와, 무멘 83 | 2026.06.13. | 총8화/미완결 | 2화 무료</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="U48" t="inlineStr">
         <is>
           <t>평점 9.9 | 이리와, 무멘 83 | 2026.06.13. | 총8화/미완결 | 2화 무료</t>
         </is>
       </c>
-      <c r="V47" t="inlineStr">
+      <c r="V48" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14245757</t>
         </is>
       </c>
-      <c r="W47" t="inlineStr">
+      <c r="W48" t="inlineStr">
         <is>
           <t>14245757</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
+      <c r="X48" t="inlineStr">
         <is>
           <t>어린 아내와 나쁜 짓 (총 8화/미완결)
 평점
@@ -7771,155 +7939,155 @@
 절망의 끝에서 나를 구원해준 남자, 범도건.작고 지켜야할 애기님이라며 내 고백을 짓밞았던 그때와는 다르게...이 남자, 남편 역할을 해도 너무 잘한다.낮에는 세상 든든한 보호자이던 그가 밤만 되면 맹수처럼 집착하며 나를 ..</t>
         </is>
       </c>
-      <c r="Y47" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z47" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA47" t="n">
+      <c r="Y48" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z48" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA48" t="n">
         <v>105</v>
       </c>
-      <c r="AB47" t="inlineStr">
+      <c r="AB48" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
+      <c r="AC48" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD47" t="inlineStr">
+      <c r="AD48" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF47" t="inlineStr"/>
-      <c r="AG47" t="inlineStr"/>
-      <c r="AH47" t="inlineStr">
+      <c r="AE48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="inlineStr"/>
+      <c r="AH48" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI47" t="inlineStr">
+      <c r="AI48" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>2026-06-22 12:22:39</t>
+      <c r="AJ48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>2026-06-29 13:48:27</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C48" t="n">
+      <c r="C49" t="n">
         <v>12</v>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>유쾌한 신</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=846053&amp;tab=sun</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>846053</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>2026-06-22 11:41:26</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="b">
-        <v>1</v>
-      </c>
-      <c r="J48" t="inlineStr">
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-06-29 13:06:23</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="b">
+        <v>1</v>
+      </c>
+      <c r="J49" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr">
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
         <is>
           <t>wed,sun</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>wed,sun</t>
         </is>
       </c>
-      <c r="N48" t="n">
+      <c r="N49" t="n">
         <v>2</v>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>당신의 유쾌한 주말</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="P49" t="inlineStr">
         <is>
           <t>당신의 유쾌한 주말 (총 19화/미완결)</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
+      <c r="Q49" t="inlineStr">
         <is>
           <t>총 19화/미완결</t>
         </is>
       </c>
-      <c r="R48" t="n">
+      <c r="R49" t="n">
         <v>19</v>
       </c>
-      <c r="S48" t="inlineStr">
+      <c r="S49" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr">
+      <c r="T49" t="inlineStr">
         <is>
           <t>평점 9.4 | 김수영 김수영 | 2010.04.20. | 총19화/미완결</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="U49" t="inlineStr">
         <is>
           <t>평점 9.4 | 김수영 김수영 | 2010.04.20. | 총19화/미완결</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr">
+      <c r="V49" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=57402</t>
         </is>
       </c>
-      <c r="W48" t="inlineStr">
+      <c r="W49" t="inlineStr">
         <is>
           <t>57402</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
+      <c r="X49" t="inlineStr">
         <is>
           <t>당신의 유쾌한 주말 (총 19화/미완결)
 평점
@@ -7927,161 +8095,161 @@
 화창한 토욜 인형을 잔뜩 가지고 나온 남자는 오는 손님 쫓고 가는 손님은 거들 떠 보지도 않는다. 사실 이 남자는 인형 만들기에 빠져 연재가 짤린 만화가였으니...</t>
         </is>
       </c>
-      <c r="Y48" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z48" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA48" t="n">
+      <c r="Y49" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z49" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA49" t="n">
         <v>30</v>
       </c>
-      <c r="AB48" t="inlineStr">
+      <c r="AB49" t="inlineStr">
         <is>
           <t>bonus_total_episode_info,bonus_rank_2</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
+      <c r="AC49" t="inlineStr">
         <is>
           <t>matched</t>
         </is>
       </c>
-      <c r="AD48" t="inlineStr">
+      <c r="AD49" t="inlineStr">
         <is>
           <t>first_non_compilation_numeric_download</t>
         </is>
       </c>
-      <c r="AE48" t="n">
+      <c r="AE49" t="n">
         <v>2</v>
       </c>
-      <c r="AF48" t="inlineStr">
+      <c r="AF49" t="inlineStr">
         <is>
           <t>3.8천</t>
         </is>
       </c>
-      <c r="AG48" t="n">
+      <c r="AG49" t="n">
         <v>3800</v>
       </c>
-      <c r="AH48" t="inlineStr">
+      <c r="AH49" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="AI48" t="inlineStr">
+      <c r="AI49" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>2026-06-22 12:22:39</t>
+      <c r="AJ49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>2026-06-29 13:48:27</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C49" t="n">
+      <c r="C50" t="n">
         <v>44</v>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>서바이브</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=838594&amp;tab=sun</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>838594</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>2026-06-22 11:41:27</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="b">
-        <v>1</v>
-      </c>
-      <c r="J49" t="inlineStr">
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2026-06-29 13:06:24</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="b">
+        <v>1</v>
+      </c>
+      <c r="J50" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr">
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="N49" t="n">
+      <c r="N50" t="n">
         <v>2</v>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>연금술 무인도 서바이브</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="P50" t="inlineStr">
         <is>
           <t>연금술 무인도 서바이브 (총 42화/완결)</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="Q50" t="inlineStr">
         <is>
           <t>총 42화/완결</t>
         </is>
       </c>
-      <c r="R49" t="n">
+      <c r="R50" t="n">
         <v>42</v>
       </c>
-      <c r="S49" t="inlineStr">
+      <c r="S50" t="inlineStr">
         <is>
           <t>완결</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr">
+      <c r="T50" t="inlineStr">
         <is>
           <t>평점 9.9 | 호시 렌지,이구치 콘 호시 렌지 | 2025.02.24. | 총42화/완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr">
+      <c r="U50" t="inlineStr">
         <is>
           <t>평점 9.9 | 호시 렌지,이구치 콘 호시 렌지 | 2025.02.24. | 총42화/완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr">
+      <c r="V50" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=10375934</t>
         </is>
       </c>
-      <c r="W49" t="inlineStr">
+      <c r="W50" t="inlineStr">
         <is>
           <t>10375934</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
+      <c r="X50" t="inlineStr">
         <is>
           <t>연금술 무인도 서바이브 (총 42화/완결)
 평점
@@ -8089,161 +8257,161 @@
 항행 중 사고를 당한 연금술사 니코, 요리사 진, 포로남 셋이 표착한 곳은…… 지도에도 표시돼 있지 않은 무인도였다! 「무인도에서 처음으로 해야 할 일은?」, 「물 확보는 어떻게?」, 「식량 수집의 포인트는?」 살아남기 ..</t>
         </is>
       </c>
-      <c r="Y49" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z49" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA49" t="n">
+      <c r="Y50" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z50" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA50" t="n">
         <v>100</v>
       </c>
-      <c r="AB49" t="inlineStr">
+      <c r="AB50" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_2</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
+      <c r="AC50" t="inlineStr">
         <is>
           <t>matched</t>
         </is>
       </c>
-      <c r="AD49" t="inlineStr">
+      <c r="AD50" t="inlineStr">
         <is>
           <t>first_non_compilation_numeric_download</t>
         </is>
       </c>
-      <c r="AE49" t="n">
+      <c r="AE50" t="n">
         <v>2</v>
       </c>
-      <c r="AF49" t="inlineStr">
+      <c r="AF50" t="inlineStr">
         <is>
           <t>5.6천</t>
         </is>
       </c>
-      <c r="AG49" t="n">
+      <c r="AG50" t="n">
         <v>5600</v>
       </c>
-      <c r="AH49" t="inlineStr">
+      <c r="AH50" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="AI49" t="inlineStr">
+      <c r="AI50" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>2026-06-22 12:22:39</t>
+      <c r="AJ50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>2026-06-29 13:48:27</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C50" t="n">
+      <c r="C51" t="n">
         <v>46</v>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>화스트 페이스</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=847905&amp;tab=sun</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>847905</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>2026-06-22 11:41:28</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="b">
-        <v>1</v>
-      </c>
-      <c r="J50" t="inlineStr">
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2026-06-29 13:06:24</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="b">
+        <v>1</v>
+      </c>
+      <c r="J51" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr">
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="N50" t="n">
-        <v>1</v>
-      </c>
-      <c r="O50" t="inlineStr">
+      <c r="N51" t="n">
+        <v>1</v>
+      </c>
+      <c r="O51" t="inlineStr">
         <is>
           <t>화스트 페이스</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="P51" t="inlineStr">
         <is>
           <t>화스트 페이스 (총 24화/미완결)</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
+      <c r="Q51" t="inlineStr">
         <is>
           <t>총 24화/미완결</t>
         </is>
       </c>
-      <c r="R50" t="n">
+      <c r="R51" t="n">
         <v>24</v>
       </c>
-      <c r="S50" t="inlineStr">
+      <c r="S51" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr">
+      <c r="T51" t="inlineStr">
         <is>
           <t>평점 9.9 | NO_Teamkill NO_Teamkill | 2026.06.13. | 총24화/미완결 | 20화 무료</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr">
+      <c r="U51" t="inlineStr">
         <is>
           <t>평점 9.9 | NO_Teamkill NO_Teamkill | 2026.06.13. | 총24화/미완결 | 20화 무료</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr">
+      <c r="V51" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13750354</t>
         </is>
       </c>
-      <c r="W50" t="inlineStr">
+      <c r="W51" t="inlineStr">
         <is>
           <t>13750354</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
+      <c r="X51" t="inlineStr">
         <is>
           <t>화스트 페이스 (총 24화/미완결)
 평점
@@ -8251,155 +8419,155 @@
 화스트 페이스! 상황 발생! 상황 발생!현재 적 대규모 도발로 인해 준전시상태 돌입!전 병력 전투 장비 구비하고 즉각 출동 준비할 수 있도록!제1부 화스트페이스!제2부 20XX년 XX월 XX일 21시44분!제3부 발령권자 군단장!..</t>
         </is>
       </c>
-      <c r="Y50" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z50" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA50" t="n">
+      <c r="Y51" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z51" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA51" t="n">
         <v>105</v>
       </c>
-      <c r="AB50" t="inlineStr">
+      <c r="AB51" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
+      <c r="AC51" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD50" t="inlineStr">
+      <c r="AD51" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF50" t="inlineStr"/>
-      <c r="AG50" t="inlineStr"/>
-      <c r="AH50" t="inlineStr">
+      <c r="AE51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="inlineStr"/>
+      <c r="AH51" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI50" t="inlineStr">
+      <c r="AI51" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>2026-06-22 12:22:39</t>
+      <c r="AJ51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>2026-06-29 13:48:27</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C51" t="n">
+      <c r="C52" t="n">
         <v>79</v>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>사내 계약 연애</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=842148&amp;tab=sun</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>842148</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>2026-06-22 11:41:29</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="b">
-        <v>1</v>
-      </c>
-      <c r="J51" t="inlineStr">
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2026-06-29 13:06:25</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="b">
+        <v>1</v>
+      </c>
+      <c r="J52" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr">
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="N51" t="n">
-        <v>1</v>
-      </c>
-      <c r="O51" t="inlineStr">
+      <c r="N52" t="n">
+        <v>1</v>
+      </c>
+      <c r="O52" t="inlineStr">
         <is>
           <t>사내 계약 연애</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="P52" t="inlineStr">
         <is>
           <t>사내 계약 연애 (총 48화/미완결)</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="Q52" t="inlineStr">
         <is>
           <t>총 48화/미완결</t>
         </is>
       </c>
-      <c r="R51" t="n">
+      <c r="R52" t="n">
         <v>48</v>
       </c>
-      <c r="S51" t="inlineStr">
+      <c r="S52" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr">
+      <c r="T52" t="inlineStr">
         <is>
           <t>평점 9.9 | 최무탁, 미리엄 울 | 2026.06.13. | 총48화/미완결 | 42화 무료</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr">
+      <c r="U52" t="inlineStr">
         <is>
           <t>평점 9.9 | 최무탁, 미리엄 울 | 2026.06.13. | 총48화/미완결 | 42화 무료</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr">
+      <c r="V52" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13046250</t>
         </is>
       </c>
-      <c r="W51" t="inlineStr">
+      <c r="W52" t="inlineStr">
         <is>
           <t>13046250</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
+      <c r="X52" t="inlineStr">
         <is>
           <t>사내 계약 연애 (총 48화/미완결)
 평점
@@ -8407,161 +8575,161 @@
 예쁘고 잘생긴 것, '미'를 애정하는 서윤.그리고 그런 그녀가 더 애정하는 것은바로 미의 남녀가 서로를 사랑스럽게 탐하는 19금 만화책!그런데 이 미적 추구미에 도달하는 남자가가장 가까이에 그녀의 직속 상사로 있었으니.....</t>
         </is>
       </c>
-      <c r="Y51" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z51" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA51" t="n">
+      <c r="Y52" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z52" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA52" t="n">
         <v>105</v>
       </c>
-      <c r="AB51" t="inlineStr">
+      <c r="AB52" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
+      <c r="AC52" t="inlineStr">
         <is>
           <t>matched</t>
         </is>
       </c>
-      <c r="AD51" t="inlineStr">
+      <c r="AD52" t="inlineStr">
         <is>
           <t>first_non_compilation_numeric_download</t>
         </is>
       </c>
-      <c r="AE51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF51" t="inlineStr">
+      <c r="AE52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF52" t="inlineStr">
         <is>
           <t>51.5만</t>
         </is>
       </c>
-      <c r="AG51" t="n">
+      <c r="AG52" t="n">
         <v>515000</v>
       </c>
-      <c r="AH51" t="inlineStr">
+      <c r="AH52" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="AI51" t="inlineStr">
+      <c r="AI52" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>2026-06-22 12:22:39</t>
+      <c r="AJ52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>2026-06-29 13:48:27</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C52" t="n">
-        <v>80</v>
-      </c>
-      <c r="D52" t="inlineStr">
+      <c r="C53" t="n">
+        <v>83</v>
+      </c>
+      <c r="D53" t="inlineStr">
         <is>
           <t>나는 참지 못한다</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=823476&amp;tab=sun</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>823476</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>2026-06-22 11:41:29</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="b">
-        <v>1</v>
-      </c>
-      <c r="J52" t="inlineStr">
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2026-06-29 13:06:25</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="b">
+        <v>1</v>
+      </c>
+      <c r="J53" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr">
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="N52" t="n">
-        <v>1</v>
-      </c>
-      <c r="O52" t="inlineStr">
+      <c r="N53" t="n">
+        <v>1</v>
+      </c>
+      <c r="O53" t="inlineStr">
         <is>
           <t>나는 참지 못한다</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
+      <c r="P53" t="inlineStr">
         <is>
           <t>나는 참지 못한다 (총 115화/미완결)</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
+      <c r="Q53" t="inlineStr">
         <is>
           <t>총 115화/미완결</t>
         </is>
       </c>
-      <c r="R52" t="n">
+      <c r="R53" t="n">
         <v>115</v>
       </c>
-      <c r="S52" t="inlineStr">
+      <c r="S53" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr">
+      <c r="T53" t="inlineStr">
         <is>
           <t>평점 10.0 | 성현 성현 | 2026.06.13. | 총115화/미완결 | 111화 무료</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr">
+      <c r="U53" t="inlineStr">
         <is>
           <t>평점 10.0 | 성현 성현 | 2026.06.13. | 총115화/미완결 | 111화 무료</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr">
+      <c r="V53" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=10970308</t>
         </is>
       </c>
-      <c r="W52" t="inlineStr">
+      <c r="W53" t="inlineStr">
         <is>
           <t>10970308</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>나는 참지 못한다 (총 115화/미완결)
 평점
@@ -8569,155 +8737,155 @@
 평범한 회사원 김연지는 교통사고 이후 변화를 겪게 된다.스트레스가 폭발하면 아무것도 참지 못하는 상태가 되고 만다.계속 일어나는 통제불능 사건들, 자신에게 접근하는 의문의 남성 민성훈.사건은 커지고 일상은 꼬여만 가..</t>
         </is>
       </c>
-      <c r="Y52" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z52" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA52" t="n">
+      <c r="Y53" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z53" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA53" t="n">
         <v>105</v>
       </c>
-      <c r="AB52" t="inlineStr">
+      <c r="AB53" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
+      <c r="AC53" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD52" t="inlineStr">
+      <c r="AD53" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF52" t="inlineStr"/>
-      <c r="AG52" t="inlineStr"/>
-      <c r="AH52" t="inlineStr">
+      <c r="AE53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="inlineStr"/>
+      <c r="AH53" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI52" t="inlineStr">
+      <c r="AI53" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>2026-06-22 12:22:39</t>
+      <c r="AJ53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>2026-06-29 13:48:27</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+    <row r="54">
+      <c r="A54" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C53" t="n">
-        <v>88</v>
-      </c>
-      <c r="D53" t="inlineStr">
+      <c r="C54" t="n">
+        <v>91</v>
+      </c>
+      <c r="D54" t="inlineStr">
         <is>
           <t>죽거나 혹은 사랑에 빠지거나</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=819696&amp;tab=sun</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>819696</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>2026-06-22 11:41:29</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="b">
-        <v>1</v>
-      </c>
-      <c r="J53" t="inlineStr">
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2026-06-29 13:06:26</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="b">
+        <v>1</v>
+      </c>
+      <c r="J54" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr">
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="N53" t="n">
-        <v>1</v>
-      </c>
-      <c r="O53" t="inlineStr">
+      <c r="N54" t="n">
+        <v>1</v>
+      </c>
+      <c r="O54" t="inlineStr">
         <is>
           <t>죽거나 혹은 사랑에 빠지거나</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr">
+      <c r="P54" t="inlineStr">
         <is>
           <t>죽거나 혹은 사랑에 빠지거나 (총 128화/미완결)</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr">
+      <c r="Q54" t="inlineStr">
         <is>
           <t>총 128화/미완결</t>
         </is>
       </c>
-      <c r="R53" t="n">
+      <c r="R54" t="n">
         <v>128</v>
       </c>
-      <c r="S53" t="inlineStr">
+      <c r="S54" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T53" t="inlineStr">
+      <c r="T54" t="inlineStr">
         <is>
           <t>평점 9.8 | 허니비 허니비 | 2026.06.13. | 총128화/미완결 | 122화 무료</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr">
+      <c r="U54" t="inlineStr">
         <is>
           <t>평점 9.8 | 허니비 허니비 | 2026.06.13. | 총128화/미완결 | 122화 무료</t>
         </is>
       </c>
-      <c r="V53" t="inlineStr">
+      <c r="V54" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=10555314</t>
         </is>
       </c>
-      <c r="W53" t="inlineStr">
+      <c r="W54" t="inlineStr">
         <is>
           <t>10555314</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
+      <c r="X54" t="inlineStr">
         <is>
           <t>죽거나 혹은 사랑에 빠지거나 (총 128화/미완결)
 평점
@@ -8725,51 +8893,51 @@
 아름다운 도시 루베른에서 일어나는 의문의 연쇄살인 사건. 조용하고 눈에 띄지 않는 이자벨라에게 살인마의 초대장이 전달되는데.. 목숨을 건 15일간의 내기. 절대 어떤 쾌락과 환상에도 사랑에 빠져서는 안 된다.</t>
         </is>
       </c>
-      <c r="Y53" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z53" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA53" t="n">
+      <c r="Y54" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z54" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA54" t="n">
         <v>105</v>
       </c>
-      <c r="AB53" t="inlineStr">
+      <c r="AB54" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
+      <c r="AC54" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD53" t="inlineStr">
+      <c r="AD54" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE53" t="n">
+      <c r="AE54" t="n">
         <v>2</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
-      <c r="AG53" t="inlineStr"/>
-      <c r="AH53" t="inlineStr">
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="inlineStr"/>
+      <c r="AH54" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI53" t="inlineStr">
+      <c r="AI54" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>2026-06-22 12:22:39</t>
+      <c r="AJ54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>2026-06-29 13:48:27</t>
         </is>
       </c>
     </row>

--- a/data/adult_login_required_webtoons_v2.xlsx
+++ b/data/adult_login_required_webtoons_v2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK50"/>
+  <dimension ref="A1:AK49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -615,26 +615,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>그린스킨</t>
+          <t>신체</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=851187&amp;tab=mon</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=844058&amp;tab=mon</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>851187</t>
+          <t>844058</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-20 12:20:08</t>
+          <t>2026-07-27 12:19:44</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -662,48 +662,203 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
+          <t>19금 신체</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>19금 신체 (총 44화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>총 44화/미완결</t>
+        </is>
+      </c>
+      <c r="R2" t="n">
+        <v>44</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>평점 9.8 | 엄세윤 정썸머 | 2026.07.26. | 총44화/미완결 | 39화 무료</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>평점 9.8 | 엄세윤 정썸머 | 2026.07.26. | 총44화/미완결 | 39화 무료</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=13285897</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>13285897</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>19금 신체 (총 44화/미완결)
+평점
+9.8 | 엄세윤 정썸머 | 2026.07.26. | 총44화/미완결 | 39화 무료</t>
+        </is>
+      </c>
+      <c r="Y2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>non_compilation_but_download_not_ok</t>
+        </is>
+      </c>
+      <c r="AE2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>searched_series</t>
+        </is>
+      </c>
+      <c r="AJ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>2026-07-27 13:10:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>그린스킨</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=851187&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>851187</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:19:45</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>그린스킨</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>그린스킨 (총 12화/미완결)</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>총 12화/미완결</t>
         </is>
       </c>
-      <c r="R2" t="n">
+      <c r="R3" t="n">
         <v>12</v>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>평점 8.8 | 승기사, 흙수저 파김치 | 2026.07.19. | 총12화/미완결 | 8화 무료</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>평점 8.8 | 승기사, 흙수저 파김치 | 2026.07.19. | 총12화/미완결 | 8화 무료</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14212275</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>14212275</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>그린스킨 (총 12화/미완결)
 평점
@@ -711,155 +866,155 @@
 이세계에서 10년을 버텼다. 하지만 돌아온 건 배신과 죽음. 다시눈을 뜬 순간, 나는 인간이 아닌 고블린이 되어 있었다</t>
         </is>
       </c>
-      <c r="Y2" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA2" t="n">
+      <c r="Y3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA3" t="n">
         <v>105</v>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr">
+      <c r="AE3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>searched_series</t>
-        </is>
-      </c>
-      <c r="AJ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:58:13</t>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>2026-07-27 13:10:46</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>mon</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>월</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C4" t="n">
         <v>26</v>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>망플루언서</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=850526&amp;tab=mon</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>850526</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:20:08</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:19:45</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
         <is>
           <t>mon</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>mon</t>
         </is>
       </c>
-      <c r="N3" t="n">
-        <v>1</v>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>망플루언서</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>망플루언서 (총 12화/미완결)</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>총 12화/미완결</t>
         </is>
       </c>
-      <c r="R3" t="n">
+      <c r="R4" t="n">
         <v>12</v>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>평점 10.0 | 망순 망순 | 2026.06.14. | 총12화/미완결 | 6화 무료</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>평점 10.0 | 망순 망순 | 2026.06.14. | 총12화/미완결 | 6화 무료</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14140191</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>14140191</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>망플루언서 (총 12화/미완결)
 평점
@@ -867,155 +1022,155 @@
 대중의 관심을 먹고 사는 빛나는 직업 '인플루언서!'보여지는 모습과 달리 그들의 숨겨진 추악한 비밀들을 폭로하는 유명 렉카 너튜브 채널 '셀럽 쓰레기통'그 채널을 운영하는 두 여자, 선미와 주원의 이야기."거짓으로 돈을 ..</t>
         </is>
       </c>
-      <c r="Y3" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA3" t="n">
+      <c r="Y4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA4" t="n">
         <v>105</v>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr">
+      <c r="AE4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="AI4" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:58:13</t>
+      <c r="AJ4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>2026-07-27 13:10:46</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>mon</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>월</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>44</v>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="C5" t="n">
+        <v>46</v>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>피폐물을 힐링물로 만드는 방법</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=826381&amp;tab=mon</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>826381</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:20:08</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="b">
-        <v>1</v>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:19:46</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
         <is>
           <t>mon</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>mon</t>
         </is>
       </c>
-      <c r="N4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>피폐물을 힐링물로 만드는 방법</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>피폐물을 힐링물로 만드는 방법 (총 84화/미완결)</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>총 84화/미완결</t>
         </is>
       </c>
-      <c r="R4" t="n">
+      <c r="R5" t="n">
         <v>84</v>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>평점 9.9 | 류호, 황도톨 양담 | 2026.06.14. | 총84화/미완결 | 78화 무료</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>평점 9.9 | 류호, 황도톨 양담 | 2026.06.14. | 총84화/미완결 | 78화 무료</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=11152272</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>11152272</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>피폐물을 힐링물로 만드는 방법 (총 84화/미완결)
 평점
@@ -1023,161 +1178,161 @@
 [살아생전 즐겨보던 소설에 환생했다.] 너무 진부하다구요? 아닐 걸요!왜냐면 그 소설이... 19금 피폐물이거든요...! ̗̀(ꀬ⏖ꀬ∴)예쁘고 상냥한 여주인공의 동생으로 환생했지만, 언니의 새드엔딩을 지켜볼 수 없었던 레나티..</t>
         </is>
       </c>
-      <c r="Y4" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA4" t="n">
+      <c r="Y5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA5" t="n">
         <v>105</v>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>matched</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>first_non_compilation_numeric_download</t>
         </is>
       </c>
-      <c r="AE4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF4" t="inlineStr">
+      <c r="AE5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" t="inlineStr">
         <is>
           <t>216.7만</t>
         </is>
       </c>
-      <c r="AG4" t="n">
+      <c r="AG5" t="n">
         <v>2167000</v>
       </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AH5" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
+      <c r="AI5" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:58:13</t>
+      <c r="AJ5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>2026-07-27 13:10:46</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>mon</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>월</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>58</v>
-      </c>
-      <c r="D5" t="inlineStr">
+      <c r="C6" t="n">
+        <v>61</v>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>페일 블루 아이즈</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=849898&amp;tab=mon</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>849898</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:20:09</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="b">
-        <v>1</v>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:19:46</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
         <is>
           <t>mon</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>mon</t>
         </is>
       </c>
-      <c r="N5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>페일 블루 아이즈</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>페일 블루 아이즈 (총 13화/미완결)</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>총 13화/미완결</t>
         </is>
       </c>
-      <c r="R5" t="n">
+      <c r="R6" t="n">
         <v>13</v>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>평점 9.9 | LICO, 피숙혜 당도삼십 | 2026.06.14. | 총13화/미완결 | 9화 무료</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>평점 9.9 | LICO, 피숙혜 당도삼십 | 2026.06.14. | 총13화/미완결 | 9화 무료</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14051143</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>14051143</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>페일 블루 아이즈 (총 13화/미완결)
 평점
@@ -1185,155 +1340,311 @@
 주은은 자신을 늘 외롭게 만드는 가족을 떠나 홀연히 영국으로 향한다. 그곳에서 만난 창백한 푸른눈의 남자, 에덴. 조악한 문신으로 온몸을 뒤덮은, 쓰레기 같은 펑크를 노래하는, 주변의 모든 여자를 열병에 들끓게 만드는, 하..</t>
         </is>
       </c>
-      <c r="Y5" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA5" t="n">
+      <c r="Y6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA6" t="n">
         <v>105</v>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr">
+      <c r="AE6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AI6" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:58:13</t>
+      <c r="AJ6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>2026-07-27 13:10:46</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>78</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>누가 죄인인가</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=846782&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>846782</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:19:47</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>누가 죄인인가</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>누가 죄인인가 (총 31화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>총 31화/미완결</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>31</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>평점 10.0 | 이승우 이승우 | 2026.07.26. | 총31화/미완결 | 24화 무료</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>평점 10.0 | 이승우 이승우 | 2026.07.26. | 총31화/미완결 | 24화 무료</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=13634954</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>13634954</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>누가 죄인인가 (총 31화/미완결)
+평점
+10.0 | 이승우 이승우 | 2026.07.26. | 총31화/미완결 | 24화 무료
+"나의 아버지는 악마로 만들어졌다."연쇄살인마 '허욱열'의 딸로서 30년간 지옥 같은 삶을 살아온 일류 청부업자 '허예주' 오늘날 허욱열의 무고가 밝혀지게 되지만 이들은 여전히 지옥 속에 살고 있고 예주는자신과 같이 지옥 ..</t>
+        </is>
+      </c>
+      <c r="Y7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>non_compilation_but_download_not_ok</t>
+        </is>
+      </c>
+      <c r="AE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>searched_series</t>
+        </is>
+      </c>
+      <c r="AJ7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>2026-07-27 13:10:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C8" t="n">
         <v>3</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>오! 나의 교주님</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=841624&amp;tab=tue</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>841624</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:20:10</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:19:48</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
         <is>
           <t>tue,fri</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>tue,fri</t>
         </is>
       </c>
-      <c r="N6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>오! 나의 교주님</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>오! 나의 교주님 (총 94화/미완결)</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>총 94화/미완결</t>
         </is>
       </c>
-      <c r="R6" t="n">
+      <c r="R8" t="n">
         <v>94</v>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>평점 9.4 | 김꿀빨, 김완두 김꿀빨, 김완두 | 2026.06.18. | 총94화/미완결 | 89화 무료</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>평점 9.4 | 김꿀빨, 김완두 김꿀빨, 김완두 | 2026.06.18. | 총94화/미완결 | 89화 무료</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=12998643</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>12998643</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>오! 나의 교주님 (총 94화/미완결)
 평점
@@ -1341,310 +1652,310 @@
 사이비 종교 ‘진천교’에서 태어나 평생을 그곳에서 살아온 한성민. 그는 결국 모든 것을 잃고 홀로 탈출한다.수년 후, 성인이 된 그는 다시 진천교에 잠입해 처절한 복수를 시작하려 한다.“오, 나의 교주님. 제가 보내드릴게..</t>
         </is>
       </c>
-      <c r="Y6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA6" t="n">
+      <c r="Y8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA8" t="n">
         <v>105</v>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr">
+      <c r="AE8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:58:13</t>
+      <c r="AJ8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>2026-07-27 13:10:46</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C9" t="n">
         <v>7</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>예쁨 컬렉션</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=844519&amp;tab=tue</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>844519</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:20:10</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:19:48</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>19금 예쁨 컬렉션</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>19금 예쁨 컬렉션 (총 35화/미완결)</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>총 35화/미완결</t>
         </is>
       </c>
-      <c r="R7" t="n">
+      <c r="R9" t="n">
         <v>35</v>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>평점 9.9 | 김이연 김이연 | 2026.06.15. | 총35화/미완결 | 30화 무료</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>평점 9.9 | 김이연 김이연 | 2026.06.15. | 총35화/미완결 | 30화 무료</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13365963</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>13365963</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>19금 예쁨 컬렉션 (총 35화/미완결)
 평점
 9.9 | 김이연 김이연 | 2026.06.15. | 총35화/미완결 | 30화 무료</t>
         </is>
       </c>
-      <c r="Y7" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA7" t="n">
+      <c r="Y9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA9" t="n">
         <v>105</v>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr">
+      <c r="AE9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AI9" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:58:13</t>
+      <c r="AJ9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>2026-07-27 13:10:46</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>10</v>
-      </c>
-      <c r="D8" t="inlineStr">
+      <c r="C10" t="n">
+        <v>9</v>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>포그랜드</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=843116&amp;tab=tue</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>843116</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:20:10</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="b">
-        <v>1</v>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:19:48</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="N8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>포그랜드</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>포그랜드 (총 44화/미완결)</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>총 44화/미완결</t>
         </is>
       </c>
-      <c r="R8" t="n">
+      <c r="R10" t="n">
         <v>44</v>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>평점 10.0 | POGO POGO | 2026.06.15. | 총44화/미완결 | 38화 무료</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>평점 10.0 | POGO POGO | 2026.06.15. | 총44화/미완결 | 38화 무료</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13177080</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>13177080</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>포그랜드 (총 44화/미완결)
 평점
@@ -1652,155 +1963,155 @@
 존재만으로도 미스터리한 국제 교도소 포그랜드.죄수 교화 목적으로 파견된 과학교사 단테 강은 한순간의 폭동 속에 포그랜드에 갇히게 된다.탈출하는 방법은 영도자가 되는 길 뿐.무너진 이성과 신성을 목도하라!단테의 아홉 ..</t>
         </is>
       </c>
-      <c r="Y8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA8" t="n">
+      <c r="Y10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA10" t="n">
         <v>105</v>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="inlineStr">
+      <c r="AE10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AI10" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:58:13</t>
+      <c r="AJ10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>2026-07-27 13:10:46</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>28</v>
-      </c>
-      <c r="D9" t="inlineStr">
+      <c r="C11" t="n">
+        <v>25</v>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>분신</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=845407&amp;tab=tue</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>845407</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:20:11</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="b">
-        <v>1</v>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:19:48</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J11" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="inlineStr">
         <is>
           <t>분신으로 자동사냥 [독점]</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>분신으로 자동사냥 [독점] (총 176화/완결)</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>총 176화/완결</t>
         </is>
       </c>
-      <c r="R9" t="n">
+      <c r="R11" t="n">
         <v>176</v>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>완결</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>평점 9.7 | 차씨 오팔 | 2025.12.27. | 총176화/완결 | 7화 무료</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>평점 9.7 | 차씨 오팔 | 2025.12.27. | 총176화/완결 | 7화 무료</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=8833786</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>8833786</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>분신으로 자동사냥 [독점] (총 176화/완결)
 평점
@@ -1808,161 +2119,161 @@
 일해야 하고, 공부도 해야 하고, 밥도 먹어야 하고.‘왜 사람은 한 번에 한 가지 일밖에 못 하는 걸까.’상우는 항상 자신의 몸이 두 개였으면 좋겠다고 생각했다...그랬더니 몸이 두 개가 되었다.</t>
         </is>
       </c>
-      <c r="Y9" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA9" t="n">
+      <c r="Y11" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA11" t="n">
         <v>105</v>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>matched</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>first_non_compilation_numeric_download</t>
         </is>
       </c>
-      <c r="AE9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF9" t="inlineStr">
+      <c r="AE11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF11" t="inlineStr">
         <is>
           <t>1,022만</t>
         </is>
       </c>
-      <c r="AG9" t="n">
+      <c r="AG11" t="n">
         <v>10220000</v>
       </c>
-      <c r="AH9" t="inlineStr">
+      <c r="AH11" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
+      <c r="AI11" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:58:13</t>
+      <c r="AJ11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>2026-07-27 13:10:46</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>29</v>
-      </c>
-      <c r="D10" t="inlineStr">
+      <c r="C12" t="n">
+        <v>30</v>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>나쁜남자가 돼라!</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=847491&amp;tab=tue</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>847491</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:20:11</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="b">
-        <v>1</v>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:19:49</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J12" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="inlineStr">
         <is>
           <t>나쁜남자가 돼라!</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>나쁜남자가 돼라! (총 28화/미완결)</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>총 28화/미완결</t>
         </is>
       </c>
-      <c r="R10" t="n">
+      <c r="R12" t="n">
         <v>28</v>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>평점 9.9 | 이연 자개 | 2026.06.15. | 총28화/미완결 | 20화 무료</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>평점 9.9 | 이연 자개 | 2026.06.15. | 총28화/미완결 | 20화 무료</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13704125</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>13704125</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>나쁜남자가 돼라! (총 28화/미완결)
 평점
@@ -1970,155 +2281,155 @@
 구남친에 대한 트라우마로 나쁜남자 취향을 가지게 된 수연은 현재의 남자친구에게 약간의 불만을 느끼지만 잘 지내고 있다.그러던 어느 날, 남자친구의 몸에 수연의 취향 그 자체인 '나쁜 남자'가 빙의하는데…이 저주. 풀어줘..</t>
         </is>
       </c>
-      <c r="Y10" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA10" t="n">
+      <c r="Y12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA12" t="n">
         <v>105</v>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="inlineStr"/>
-      <c r="AH10" t="inlineStr">
+      <c r="AE12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
+      <c r="AI12" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:58:13</t>
+      <c r="AJ12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>2026-07-27 13:10:46</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>38</v>
-      </c>
-      <c r="D11" t="inlineStr">
+      <c r="C13" t="n">
+        <v>45</v>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>화분</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=851671&amp;tab=tue</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>851671</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:20:11</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="b">
-        <v>1</v>
-      </c>
-      <c r="J11" t="inlineStr">
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:19:49</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="N11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" t="inlineStr">
+      <c r="N13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" t="inlineStr">
         <is>
           <t>화분</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>화분 (총 5화/미완결)</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>총 5화/미완결</t>
         </is>
       </c>
-      <c r="R11" t="n">
+      <c r="R13" t="n">
         <v>5</v>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>평점 10.0 | 쿼시 쿼시 | 2026.06.15. | 총5화/미완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>평점 10.0 | 쿼시 쿼시 | 2026.06.15. | 총5화/미완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14284647</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>14284647</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>화분 (총 5화/미완결)
 평점
@@ -2126,155 +2437,155 @@
 버림받는 것이 무서운 여자와 그런 그녀가 무섭게 느껴지는 남자. 오래된 인연으로 시작된 사랑은 다정함의 얼굴을 한 집착이 되어, 두 사람의 일상과 마음을 서서히 갉아먹어 간다.우리 사랑은, 어디서부터 잘못된거지..?</t>
         </is>
       </c>
-      <c r="Y11" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA11" t="n">
+      <c r="Y13" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA13" t="n">
         <v>105</v>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD13" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF11" t="inlineStr"/>
-      <c r="AG11" t="inlineStr"/>
-      <c r="AH11" t="inlineStr">
+      <c r="AE13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
+      <c r="AI13" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:58:13</t>
+      <c r="AJ13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>2026-07-27 13:10:46</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>53</v>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C14" t="n">
+        <v>54</v>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>원수의 아기를 가졌다</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=846110&amp;tab=tue</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>846110</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:20:11</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="b">
-        <v>1</v>
-      </c>
-      <c r="J12" t="inlineStr">
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:19:49</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="b">
+        <v>1</v>
+      </c>
+      <c r="J14" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="N12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" t="inlineStr">
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>원수의 아기를 가졌다</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>원수의 아기를 가졌다 (총 30화/미완결)</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>총 30화/미완결</t>
         </is>
       </c>
-      <c r="R12" t="n">
+      <c r="R14" t="n">
         <v>30</v>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>평점 9.7 | 미니바라기, 안지 이삼 | 2026.06.15. | 총30화/미완결 | 25화 무료</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>평점 9.7 | 미니바라기, 안지 이삼 | 2026.06.15. | 총30화/미완결 | 25화 무료</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13567690</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>13567690</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>원수의 아기를 가졌다 (총 30화/미완결)
 평점
@@ -2282,155 +2593,155 @@
 서로를 끔찍하게 혐오하는 두 가문 버몬테와 템네스.클로델은 강제 화해를 위한 희생양이 되어 템네스 공작 카이안의 신부가 된다.“템네스의 환영을 받지 못하는 신부로군. 주제를 알고 제 발로 걸어들어오라지.”오랜 반목을 ..</t>
         </is>
       </c>
-      <c r="Y12" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA12" t="n">
+      <c r="Y14" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA14" t="n">
         <v>105</v>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AC14" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AD14" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="inlineStr"/>
-      <c r="AH12" t="inlineStr">
+      <c r="AE14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
+      <c r="AI14" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:58:13</t>
+      <c r="AJ14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>2026-07-27 13:10:46</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>76</v>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C15" t="n">
+        <v>78</v>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>포 더 퀸덤</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=812414&amp;tab=tue</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>812414</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:20:12</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="b">
-        <v>1</v>
-      </c>
-      <c r="J13" t="inlineStr">
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:19:50</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="b">
+        <v>1</v>
+      </c>
+      <c r="J15" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="N13" t="n">
-        <v>1</v>
-      </c>
-      <c r="O13" t="inlineStr">
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t>포 더 퀸덤</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>포 더 퀸덤 (총 128화/미완결)</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>총 128화/미완결</t>
         </is>
       </c>
-      <c r="R13" t="n">
+      <c r="R15" t="n">
         <v>128</v>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>평점 9.0 | 로즈옹 로즈옹 | 2026.06.15. | 총128화/미완결 | 123화 무료</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>평점 9.0 | 로즈옹 로즈옹 | 2026.06.15. | 총128화/미완결 | 123화 무료</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=9895056</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>9895056</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>포 더 퀸덤 (총 128화/미완결)
 평점
@@ -2438,155 +2749,155 @@
 악마 아벨은 인간 여자 연리에게 사랑하는 형, 카인을 잃고 만다.분노에 가득 차 연리를 찾아간 아벨은 사랑에 빠지는 금총알을 맞게 되면서, 연리에게 끓어오르는 사랑을 느끼게 되는데…그는 과연 형제의 복수를 택할 것인가..</t>
         </is>
       </c>
-      <c r="Y13" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA13" t="n">
+      <c r="Y15" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA15" t="n">
         <v>105</v>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
+      <c r="AC15" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD13" t="inlineStr">
+      <c r="AD15" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE13" t="n">
+      <c r="AE15" t="n">
         <v>2</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="inlineStr"/>
-      <c r="AH13" t="inlineStr">
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI13" t="inlineStr">
+      <c r="AI15" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:58:13</t>
+      <c r="AJ15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>2026-07-27 13:10:46</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>8</v>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="C16" t="n">
+        <v>9</v>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>썰:관계주의</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=834033&amp;tab=wed</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>834033</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:20:14</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="b">
-        <v>1</v>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:19:51</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="b">
+        <v>1</v>
+      </c>
+      <c r="J16" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="N14" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" t="inlineStr">
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>썰:관계주의</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>썰:관계주의 (총 87화/미완결)</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>총 87화/미완결</t>
         </is>
       </c>
-      <c r="R14" t="n">
+      <c r="R16" t="n">
         <v>87</v>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>평점 10.0 | 이삼 장버들 | 2026.06.16. | 총87화/미완결 | 83화 무료</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>평점 10.0 | 이삼 장버들 | 2026.06.16. | 총87화/미완결 | 83화 무료</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=11802777</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>11802777</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>썰:관계주의 (총 87화/미완결)
 평점
@@ -2594,155 +2905,155 @@
 여러 상가가 들어서 있는 강남의 유명타워. 이야기는 유명타워의 한 피부과 안내 데스크 직원 강지영으로부터 시작된다. 동료이자 유부남 의사와 만남을 이어가던 지영은 그에게 또 다른 불륜 상대가 있음을 눈치 채는데 그 상..</t>
         </is>
       </c>
-      <c r="Y14" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA14" t="n">
+      <c r="Y16" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA16" t="n">
         <v>105</v>
       </c>
-      <c r="AB14" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
+      <c r="AC16" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD14" t="inlineStr">
+      <c r="AD16" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="inlineStr"/>
-      <c r="AH14" t="inlineStr">
+      <c r="AE16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI14" t="inlineStr">
+      <c r="AI16" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:58:13</t>
+      <c r="AJ16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>2026-07-27 13:10:46</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="C17" t="n">
         <v>10</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>싸이코패스 in 무림</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=846109&amp;tab=wed</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>846109</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:20:14</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="b">
-        <v>1</v>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:19:51</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="b">
+        <v>1</v>
+      </c>
+      <c r="J17" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="N15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O15" t="inlineStr">
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="inlineStr">
         <is>
           <t>싸이코패스 in 무림[독점]</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>싸이코패스 in 무림[독점] (총 32화/미완결)</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>총 32화/미완결</t>
         </is>
       </c>
-      <c r="R15" t="n">
+      <c r="R17" t="n">
         <v>32</v>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>평점 9.8 | 김언, 곤붕 송범규 | 2026.06.16. | 총32화/미완결 | 26화 무료</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>평점 9.8 | 김언, 곤붕 송범규 | 2026.06.16. | 총32화/미완결 | 26화 무료</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13566546</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>13566546</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>싸이코패스 in 무림[독점] (총 32화/미완결)
 평점
@@ -2750,317 +3061,317 @@
 [진정한 강자들의 세상, 무림 온라인에 오신 걸 환영합니다.]무림에 떨어진 희대의 싸이코패스.음모와 악의가 가득한 무림에 동봉수, 그의 무정한 이빨이 드리운다.</t>
         </is>
       </c>
-      <c r="Y15" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA15" t="n">
+      <c r="Y17" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA17" t="n">
         <v>105</v>
       </c>
-      <c r="AB15" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
+      <c r="AC17" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD15" t="inlineStr">
+      <c r="AD17" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF15" t="inlineStr"/>
-      <c r="AG15" t="inlineStr"/>
-      <c r="AH15" t="inlineStr">
+      <c r="AE17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI15" t="inlineStr">
+      <c r="AI17" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:58:13</t>
+      <c r="AJ17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>2026-07-27 13:10:46</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="C16" t="n">
-        <v>13</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>유쾌한 신</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=846053&amp;tab=wed</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>846053</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:20:14</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="b">
-        <v>1</v>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="C18" t="n">
+        <v>31</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>끝장</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=844588&amp;tab=wed</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>844588</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:19:52</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>wed,sun</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>wed,sun</t>
-        </is>
-      </c>
-      <c r="N16" t="n">
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>wed</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>wed</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
         <v>2</v>
       </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>당신의 유쾌한 주말</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>당신의 유쾌한 주말 (총 19화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>총 19화/미완결</t>
-        </is>
-      </c>
-      <c r="R16" t="n">
-        <v>19</v>
-      </c>
-      <c r="S16" t="inlineStr">
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>떨어지면 끝장</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>떨어지면 끝장 (총 70화/완결)</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>총 70화/완결</t>
+        </is>
+      </c>
+      <c r="R18" t="n">
+        <v>70</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>완결</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>평점 9.7 | Keiko Suenobu Keiko Suenobu | 2024.04.12. | 총70화/완결 | 3화 무료</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>평점 9.7 | Keiko Suenobu Keiko Suenobu | 2024.04.12. | 총70화/완결 | 3화 무료</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=6039213</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>6039213</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>떨어지면 끝장 (총 70화/완결)
+평점
+9.7 | Keiko Suenobu Keiko Suenobu | 2024.04.12. | 총70화/완결 | 3화 무료
+“떨어지면 끝장이야.”그토록 바라던 신축 초고층 아파트에 입주하게 된 주부 아스미.같은 아파트에 거주하며 아이들 유치원도 같은 세 명의 맘 친구가 생긴다.행복 가득한 새로운 생활이 펼쳐지리라 기대했지만, 어떤 인물과..</t>
+        </is>
+      </c>
+      <c r="Y18" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_2</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>first_non_compilation_numeric_download</t>
+        </is>
+      </c>
+      <c r="AE18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>3.9만</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>39000</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>2026-07-27 13:10:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>wed</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>32</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>표절의혹</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=846106&amp;tab=wed</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>846106</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:19:52</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="b">
+        <v>1</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>wed</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>wed</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>표절의혹</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>표절의혹 (총 29화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>총 29화/미완결</t>
+        </is>
+      </c>
+      <c r="R19" t="n">
+        <v>29</v>
+      </c>
+      <c r="S19" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>평점 9.4 | 김수영 김수영 | 2010.04.20. | 총19화/미완결</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>평점 9.4 | 김수영 김수영 | 2010.04.20. | 총19화/미완결</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=57402</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>57402</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>당신의 유쾌한 주말 (총 19화/미완결)
-평점
-9.4 | 김수영 김수영 | 2010.04.20. | 총19화/미완결
-화창한 토욜 인형을 잔뜩 가지고 나온 남자는 오는 손님 쫓고 가는 손님은 거들 떠 보지도 않는다. 사실 이 남자는 인형 만들기에 빠져 연재가 짤린 만화가였으니...</t>
-        </is>
-      </c>
-      <c r="Y16" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>30</v>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>bonus_total_episode_info,bonus_rank_2</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>matched</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>first_non_compilation_numeric_download</t>
-        </is>
-      </c>
-      <c r="AE16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>3.8천</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>3800</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:58:13</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>wed</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>수</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>32</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>표절의혹</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=846106&amp;tab=wed</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>846106</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:20:15</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="b">
-        <v>1</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>wed</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>wed</t>
-        </is>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>표절의혹</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>표절의혹 (총 29화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>총 29화/미완결</t>
-        </is>
-      </c>
-      <c r="R17" t="n">
-        <v>29</v>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>평점 9.4 | 김칸비 황영찬 | 2026.06.16. | 총29화/미완결 | 24화 무료</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>평점 9.4 | 김칸비 황영찬 | 2026.06.16. | 총29화/미완결 | 24화 무료</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13575121</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>13575121</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>표절의혹 (총 29화/미완결)
 평점
@@ -3068,317 +3379,155 @@
 살인사건 피해자들의 시신을 예술품처럼 사고파는 인간성을 잃은 자들, 그리고 그런 예술 살인을 저지르는 ‘자학’이라는 연쇄살인마가 세간의 화제가 되고 있다. 한 예술가는 이 상황에 분노해 자학을 추적하기 시작하는데.....</t>
         </is>
       </c>
-      <c r="Y17" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA17" t="n">
+      <c r="Y19" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA19" t="n">
         <v>105</v>
       </c>
-      <c r="AB17" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
+      <c r="AC19" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD17" t="inlineStr">
+      <c r="AD19" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF17" t="inlineStr"/>
-      <c r="AG17" t="inlineStr"/>
-      <c r="AH17" t="inlineStr">
+      <c r="AE19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI17" t="inlineStr">
+      <c r="AI19" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:58:13</t>
+      <c r="AJ19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>2026-07-27 13:10:46</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>34</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>끝장</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=844588&amp;tab=wed</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>844588</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:20:15</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="b">
-        <v>1</v>
-      </c>
-      <c r="J18" t="inlineStr">
+      <c r="C20" t="n">
+        <v>83</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>일곱 번째 의뢰인</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=850210&amp;tab=wed</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>850210</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:19:53</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="b">
+        <v>1</v>
+      </c>
+      <c r="J20" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="N18" t="n">
-        <v>2</v>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>떨어지면 끝장</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>떨어지면 끝장 (총 70화/완결)</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>총 70화/완결</t>
-        </is>
-      </c>
-      <c r="R18" t="n">
-        <v>70</v>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>완결</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>평점 9.7 | Keiko Suenobu Keiko Suenobu | 2024.04.12. | 총70화/완결 | 3화 무료</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>평점 9.7 | Keiko Suenobu Keiko Suenobu | 2024.04.12. | 총70화/완결 | 3화 무료</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=6039213</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>6039213</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>떨어지면 끝장 (총 70화/완결)
-평점
-9.7 | Keiko Suenobu Keiko Suenobu | 2024.04.12. | 총70화/완결 | 3화 무료
-“떨어지면 끝장이야.”그토록 바라던 신축 초고층 아파트에 입주하게 된 주부 아스미.같은 아파트에 거주하며 아이들 유치원도 같은 세 명의 맘 친구가 생긴다.행복 가득한 새로운 생활이 펼쳐지리라 기대했지만, 어떤 인물과..</t>
-        </is>
-      </c>
-      <c r="Y18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_2</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>matched</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>first_non_compilation_numeric_download</t>
-        </is>
-      </c>
-      <c r="AE18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>3.9만</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>39000</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:58:13</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>wed</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>수</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>84</v>
-      </c>
-      <c r="D19" t="inlineStr">
+      <c r="N20" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" t="inlineStr">
         <is>
           <t>일곱 번째 의뢰인</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=850210&amp;tab=wed</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>850210</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:20:17</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="b">
-        <v>1</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>wed</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>wed</t>
-        </is>
-      </c>
-      <c r="N19" t="n">
-        <v>1</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>일곱 번째 의뢰인</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>일곱 번째 의뢰인 (총 14화/미완결)</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>총 14화/미완결</t>
         </is>
       </c>
-      <c r="R19" t="n">
+      <c r="R20" t="n">
         <v>14</v>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>평점 10.0 | 함영서 함영서 | 2026.06.16. | 총14화/미완결 | 9화 무료</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>평점 10.0 | 함영서 함영서 | 2026.06.16. | 총14화/미완결 | 9화 무료</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14102285</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>14102285</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>일곱 번째 의뢰인 (총 14화/미완결)
 평점
@@ -3386,155 +3535,155 @@
 어린 탐정 맥스는 아무도 주목하지 않는 도박 업자의 죽음을 조사하라는 의뢰를 받는다. 의뢰인이 용의자로 지목한 도박 업자의 아내 제인. 맥스는 그녀를 향한 의심과 이끌림 사이에서 갈등하는데. 제인은 결백한가, 살인자인..</t>
         </is>
       </c>
-      <c r="Y19" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA19" t="n">
+      <c r="Y20" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA20" t="n">
         <v>105</v>
       </c>
-      <c r="AB19" t="inlineStr">
+      <c r="AB20" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
+      <c r="AC20" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD19" t="inlineStr">
+      <c r="AD20" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF19" t="inlineStr"/>
-      <c r="AG19" t="inlineStr"/>
-      <c r="AH19" t="inlineStr">
+      <c r="AE20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI19" t="inlineStr">
+      <c r="AI20" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:58:13</t>
+      <c r="AJ20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>2026-07-27 13:10:46</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="C21" t="n">
         <v>5</v>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>소꿉친구 컴플렉스</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=822640&amp;tab=thu</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>822640</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:20:18</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="b">
-        <v>1</v>
-      </c>
-      <c r="J20" t="inlineStr">
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:19:54</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J21" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="N20" t="n">
-        <v>1</v>
-      </c>
-      <c r="O20" t="inlineStr">
+      <c r="N21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" t="inlineStr">
         <is>
           <t>소꿉친구 컴플렉스</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>소꿉친구 컴플렉스 (총 80화/미완결)</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>총 80화/미완결</t>
         </is>
       </c>
-      <c r="R20" t="n">
+      <c r="R21" t="n">
         <v>80</v>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>평점 9.8 | 은하이 은하이 | 2026.06.17. | 총80화/미완결 | 76화 무료</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>평점 9.8 | 은하이 은하이 | 2026.06.17. | 총80화/미완결 | 76화 무료</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=10851069</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>10851069</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>소꿉친구 컴플렉스 (총 80화/미완결)
 평점
@@ -3542,155 +3691,155 @@
 20살에 20년지기, 평생을 함께한 소꿉친구 하늘과 민철.그런 소꿉친구의 알고 싶지 않은 은밀한 사정을 알아버렸다?!서로를 이성으로 생각한 적이 결코 없는 두사람이지만,오해가 오해를 낳고 착각이 착각을 낳는 상황들 속에..</t>
         </is>
       </c>
-      <c r="Y20" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA20" t="n">
+      <c r="Y21" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA21" t="n">
         <v>105</v>
       </c>
-      <c r="AB20" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
+      <c r="AC21" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD20" t="inlineStr">
+      <c r="AD21" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE20" t="n">
+      <c r="AE21" t="n">
         <v>3</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
-      <c r="AG20" t="inlineStr"/>
-      <c r="AH20" t="inlineStr">
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI20" t="inlineStr">
+      <c r="AI21" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:58:13</t>
+      <c r="AJ21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>2026-07-27 13:10:46</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="C21" t="n">
-        <v>25</v>
-      </c>
-      <c r="D21" t="inlineStr">
+      <c r="C22" t="n">
+        <v>12</v>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>럭키비치</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=852498&amp;tab=thu</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>852498</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:20:19</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="b">
-        <v>1</v>
-      </c>
-      <c r="J21" t="inlineStr">
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:19:55</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="b">
+        <v>1</v>
+      </c>
+      <c r="J22" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
         <is>
           <t>thu,sun</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>thu,sun</t>
         </is>
       </c>
-      <c r="N21" t="n">
-        <v>1</v>
-      </c>
-      <c r="O21" t="inlineStr">
+      <c r="N22" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" t="inlineStr">
         <is>
           <t>럭키비치</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>럭키비치 (총 8화/미완결)</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>총 8화/미완결</t>
         </is>
       </c>
-      <c r="R21" t="n">
+      <c r="R22" t="n">
         <v>8</v>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>평점 10.0 | MAJOR, 약수 약수 | 2026.07.18. | 총8화/미완결 | 3화 무료</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>평점 10.0 | MAJOR, 약수 약수 | 2026.07.18. | 총8화/미완결 | 3화 무료</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14424733</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>14424733</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>럭키비치 (총 8화/미완결)
 평점
@@ -3698,155 +3847,155 @@
 “그거 알아? 기는 놈 위에 나는 썅X 있는 거?”불우한 환경과 폐쇄적인 바닷가 촌에서 자라온 소녀 '정임'은,그칠줄 모르는 주변의 부조리와 권태 속에서 결국 폭발,퇴폐업을 하는 고모의 불경한 쌈짓돈을 훔쳐 서울로 상경한..</t>
         </is>
       </c>
-      <c r="Y21" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA21" t="n">
+      <c r="Y22" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA22" t="n">
         <v>105</v>
       </c>
-      <c r="AB21" t="inlineStr">
+      <c r="AB22" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
+      <c r="AC22" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD21" t="inlineStr">
+      <c r="AD22" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF21" t="inlineStr"/>
-      <c r="AG21" t="inlineStr"/>
-      <c r="AH21" t="inlineStr">
+      <c r="AE22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>searched_series</t>
-        </is>
-      </c>
-      <c r="AJ21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:58:13</t>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>2026-07-27 13:10:46</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="C22" t="n">
-        <v>49</v>
-      </c>
-      <c r="D22" t="inlineStr">
+      <c r="C23" t="n">
+        <v>54</v>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>당신에게 얽힌 채</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=849879&amp;tab=thu</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>849879</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:20:20</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="b">
-        <v>1</v>
-      </c>
-      <c r="J22" t="inlineStr">
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:19:56</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="b">
+        <v>1</v>
+      </c>
+      <c r="J23" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="N22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O22" t="inlineStr">
+      <c r="N23" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" t="inlineStr">
         <is>
           <t>당신에게 얽힌 채</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>당신에게 얽힌 채 (총 10화/미완결)</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>총 10화/미완결</t>
         </is>
       </c>
-      <c r="R22" t="n">
+      <c r="R23" t="n">
         <v>10</v>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>평점 10.0 | Nicole Knight, 유다 danah789 | 2026.06.17. | 총10화/미완결 | 5화 무료</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>평점 10.0 | Nicole Knight, 유다 danah789 | 2026.06.17. | 총10화/미완결 | 5화 무료</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14041685</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>14041685</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>당신에게 얽힌 채 (총 10화/미완결)
 평점
@@ -3854,155 +4003,313 @@
 상속자가 아닌 복종하는 존재로 길러진 에이바 모레티. 뉴욕에서 가장 강력한 마피아 가문의 막내딸인 그녀는 ‘집안의 사고뭉치’라는 오명을 벗고 자신의 자리를 찾기 위해 분투한다.그러던 어느 날 밤, 낯선 남자와 보낸 뜨..</t>
         </is>
       </c>
-      <c r="Y22" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z22" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA22" t="n">
+      <c r="Y23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA23" t="n">
         <v>105</v>
       </c>
-      <c r="AB22" t="inlineStr">
+      <c r="AB23" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
+      <c r="AC23" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD22" t="inlineStr">
+      <c r="AD23" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF22" t="inlineStr"/>
-      <c r="AG22" t="inlineStr"/>
-      <c r="AH22" t="inlineStr">
+      <c r="AE23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI22" t="inlineStr">
+      <c r="AI23" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:58:13</t>
+      <c r="AJ23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>2026-07-27 13:10:46</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="C23" t="n">
-        <v>70</v>
-      </c>
-      <c r="D23" t="inlineStr">
+      <c r="C24" t="n">
+        <v>71</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>첫눈에 반한 건 아니지만</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=830637&amp;tab=thu</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>830637</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:19:56</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="b">
+        <v>1</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>thu</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>thu</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>첫눈에 반한 건 아니지만</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>첫눈에 반한 건 아니지만 (총 68화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>총 68화/미완결</t>
+        </is>
+      </c>
+      <c r="R24" t="n">
+        <v>68</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>평점 9.9 | 아임 아임 | 2026.06.03. | 총68화/미완결 | 63화 무료</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=11573054</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>11573054</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>첫눈에 반한 건 아니지만 (총 68화/미완결)
+평점
+9.9 | 아임 아임 | 2026.06.03. | 총68화/미완결 | 63화 무료
+결혼을 전제로 선을 본 서은재. 그 상대인 윤시우는 안 좋은 소문이 무성한 남자였기에은재는 그를 경계하고 거절하려고 한다.하지만 첫눈에 반했다는 그의 열열한 구애에 끝내는 마음을 빼앗기고 마는데...은재는 시우에게 푹 ..</t>
+        </is>
+      </c>
+      <c r="Y24" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>145</v>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>title_contains,author_exact_or_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>first_non_compilation_numeric_download</t>
+        </is>
+      </c>
+      <c r="AE24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>90.6만</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>906000</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>2026-07-27 13:10:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>thu</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>77</v>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>휴먼 웨어러블</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=845460&amp;tab=thu</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>845460</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:20:21</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="b">
-        <v>1</v>
-      </c>
-      <c r="J23" t="inlineStr">
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:19:56</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="b">
+        <v>1</v>
+      </c>
+      <c r="J25" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="N23" t="n">
-        <v>1</v>
-      </c>
-      <c r="O23" t="inlineStr">
+      <c r="N25" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" t="inlineStr">
         <is>
           <t>휴먼 웨어러블</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>휴먼 웨어러블 (총 30화/미완결)</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>총 30화/미완결</t>
         </is>
       </c>
-      <c r="R23" t="n">
+      <c r="R25" t="n">
         <v>30</v>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>평점 9.9 | 쥬타인 쥬타인 | 2026.06.03. | 총30화/미완결 | 27화 무료</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>평점 9.9 | 쥬타인 쥬타인 | 2026.06.03. | 총30화/미완결 | 27화 무료</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13481722</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>13481722</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>휴먼 웨어러블 (총 30화/미완결)
 평점
@@ -4010,155 +4317,155 @@
 꿈의 무대, 패션 서바이벌 &lt;휴먼 웨어러블&gt;.고아 출신이지만 명문 ‘순백패션예술학교’를 거쳐 올라온 학생들.이 무대에서 인생 역전의 주인공이 탄생한다—…그런데 무언가, 이상하게 흘러가기 시작했다.</t>
         </is>
       </c>
-      <c r="Y23" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z23" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA23" t="n">
+      <c r="Y25" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA25" t="n">
         <v>105</v>
       </c>
-      <c r="AB23" t="inlineStr">
+      <c r="AB25" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
+      <c r="AC25" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD23" t="inlineStr">
+      <c r="AD25" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF23" t="inlineStr"/>
-      <c r="AG23" t="inlineStr"/>
-      <c r="AH23" t="inlineStr">
+      <c r="AE25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI23" t="inlineStr">
+      <c r="AI25" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:58:13</t>
+      <c r="AJ25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>2026-07-27 13:10:46</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="C26" t="n">
         <v>2</v>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>오! 나의 교주님</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=841624&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>841624</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:20:23</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="b">
-        <v>1</v>
-      </c>
-      <c r="J24" t="inlineStr">
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:19:57</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="b">
+        <v>1</v>
+      </c>
+      <c r="J26" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
         <is>
           <t>tue,fri</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>tue,fri</t>
         </is>
       </c>
-      <c r="N24" t="n">
-        <v>1</v>
-      </c>
-      <c r="O24" t="inlineStr">
+      <c r="N26" t="n">
+        <v>1</v>
+      </c>
+      <c r="O26" t="inlineStr">
         <is>
           <t>오! 나의 교주님</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>오! 나의 교주님 (총 94화/미완결)</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>총 94화/미완결</t>
         </is>
       </c>
-      <c r="R24" t="n">
+      <c r="R26" t="n">
         <v>94</v>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>평점 9.4 | 김꿀빨, 김완두 김꿀빨, 김완두 | 2026.06.18. | 총94화/미완결 | 89화 무료</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>평점 9.4 | 김꿀빨, 김완두 김꿀빨, 김완두 | 2026.06.18. | 총94화/미완결 | 89화 무료</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=12998643</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>12998643</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>오! 나의 교주님 (총 94화/미완결)
 평점
@@ -4166,155 +4473,155 @@
 사이비 종교 ‘진천교’에서 태어나 평생을 그곳에서 살아온 한성민. 그는 결국 모든 것을 잃고 홀로 탈출한다.수년 후, 성인이 된 그는 다시 진천교에 잠입해 처절한 복수를 시작하려 한다.“오, 나의 교주님. 제가 보내드릴게..</t>
         </is>
       </c>
-      <c r="Y24" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z24" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA24" t="n">
+      <c r="Y26" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA26" t="n">
         <v>105</v>
       </c>
-      <c r="AB24" t="inlineStr">
+      <c r="AB26" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
+      <c r="AC26" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD24" t="inlineStr">
+      <c r="AD26" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF24" t="inlineStr"/>
-      <c r="AG24" t="inlineStr"/>
-      <c r="AH24" t="inlineStr">
+      <c r="AE26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI24" t="inlineStr">
+      <c r="AI26" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:58:13</t>
+      <c r="AJ26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>2026-07-27 13:10:46</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C25" t="n">
+      <c r="C27" t="n">
         <v>8</v>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>두 얼굴</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=845646&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>845646</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:20:23</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="b">
-        <v>1</v>
-      </c>
-      <c r="J25" t="inlineStr">
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:19:58</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="b">
+        <v>1</v>
+      </c>
+      <c r="J27" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="N25" t="n">
-        <v>1</v>
-      </c>
-      <c r="O25" t="inlineStr">
+      <c r="N27" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" t="inlineStr">
         <is>
           <t>두 얼굴의 대표님</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>두 얼굴의 대표님 (총 126화/완결)</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>총 126화/완결</t>
         </is>
       </c>
-      <c r="R25" t="n">
+      <c r="R27" t="n">
         <v>126</v>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>완결</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>평점 6.2 | 1M, KuaiKan, YY 1M, KuaiKan, YY | 2022.10.02. | 총126화/완결 | 3화 무료</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>평점 6.2 | 1M, KuaiKan, YY 1M, KuaiKan, YY | 2022.10.02. | 총126화/완결 | 3화 무료</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=6489984</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>6489984</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>두 얼굴의 대표님 (총 126화/완결)
 평점
@@ -4322,161 +4629,161 @@
 재벌가의 사생아로 태어난 소원은 일찍 엄마를 잃고, 가족들의 멸시 속에서 살아왔다.그러다 언니에게 약혼자까지 뺏기게 되자, 실의에 빠진 소원은 유학을 떠나게 되고, 그곳에서 평범한 남편을 만나 결혼을 하게 된다.1년 후 ..</t>
         </is>
       </c>
-      <c r="Y25" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA25" t="n">
+      <c r="Y27" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA27" t="n">
         <v>105</v>
       </c>
-      <c r="AB25" t="inlineStr">
+      <c r="AB27" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
+      <c r="AC27" t="inlineStr">
         <is>
           <t>matched</t>
         </is>
       </c>
-      <c r="AD25" t="inlineStr">
+      <c r="AD27" t="inlineStr">
         <is>
           <t>first_non_compilation_numeric_download</t>
         </is>
       </c>
-      <c r="AE25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF25" t="inlineStr">
+      <c r="AE27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF27" t="inlineStr">
         <is>
           <t>157.5만</t>
         </is>
       </c>
-      <c r="AG25" t="n">
+      <c r="AG27" t="n">
         <v>1575000</v>
       </c>
-      <c r="AH25" t="inlineStr">
+      <c r="AH27" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="AI25" t="inlineStr">
+      <c r="AI27" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:58:13</t>
+      <c r="AJ27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>2026-07-27 13:10:46</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C26" t="n">
+      <c r="C28" t="n">
         <v>10</v>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>네가 사는 그 집</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=842465&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>842465</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:20:23</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="b">
-        <v>1</v>
-      </c>
-      <c r="J26" t="inlineStr">
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:19:58</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="b">
+        <v>1</v>
+      </c>
+      <c r="J28" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="N26" t="n">
-        <v>1</v>
-      </c>
-      <c r="O26" t="inlineStr">
+      <c r="N28" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" t="inlineStr">
         <is>
           <t>네가 사는 그 집</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>네가 사는 그 집 (총 47화/미완결)</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>총 47화/미완결</t>
         </is>
       </c>
-      <c r="R26" t="n">
+      <c r="R28" t="n">
         <v>47</v>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>평점 9.7 | 석우 해바다 | 2026.06.18. | 총47화/미완결 | 41화 무료</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>평점 9.7 | 석우 해바다 | 2026.06.18. | 총47화/미완결 | 41화 무료</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13090391</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>13090391</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>네가 사는 그 집 (총 47화/미완결)
 평점
@@ -4484,155 +4791,155 @@
 찢어지게 가난한 집에서 두 아이를 키우며 힘겹게 살아가던 30대 화린.어느날, 자기 첫사랑이었던 부유한 선배와 결혼해 행복하게 사는 친구와 몸이 바뀐다.하지만 부러워하던 삶을 얻은 기쁨도 잠시,그 집의 추악한 비밀이 드..</t>
         </is>
       </c>
-      <c r="Y26" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z26" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA26" t="n">
+      <c r="Y28" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA28" t="n">
         <v>105</v>
       </c>
-      <c r="AB26" t="inlineStr">
+      <c r="AB28" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
+      <c r="AC28" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD26" t="inlineStr">
+      <c r="AD28" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF26" t="inlineStr"/>
-      <c r="AG26" t="inlineStr"/>
-      <c r="AH26" t="inlineStr">
+      <c r="AE28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI26" t="inlineStr">
+      <c r="AI28" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:58:13</t>
+      <c r="AJ28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>2026-07-27 13:10:46</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C27" t="n">
-        <v>12</v>
-      </c>
-      <c r="D27" t="inlineStr">
+      <c r="C29" t="n">
+        <v>11</v>
+      </c>
+      <c r="D29" t="inlineStr">
         <is>
           <t>그리디</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=845919&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>845919</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:20:23</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="b">
-        <v>1</v>
-      </c>
-      <c r="J27" t="inlineStr">
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:19:58</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="b">
+        <v>1</v>
+      </c>
+      <c r="J29" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="N27" t="n">
-        <v>1</v>
-      </c>
-      <c r="O27" t="inlineStr">
+      <c r="N29" t="n">
+        <v>1</v>
+      </c>
+      <c r="O29" t="inlineStr">
         <is>
           <t>그리디</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>그리디 (총 31화/미완결)</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>총 31화/미완결</t>
         </is>
       </c>
-      <c r="R27" t="n">
+      <c r="R29" t="n">
         <v>31</v>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>평점 9.9 | 영하 랑라리 | 2026.06.18. | 총31화/미완결 | 25화 무료</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>평점 9.9 | 영하 랑라리 | 2026.06.18. | 총31화/미완결 | 25화 무료</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13530624</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>13530624</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>그리디 (총 31화/미완결)
 평점
@@ -4640,155 +4947,155 @@
 파혼했다. 십년지기 친구와 내가 파혼한 남자가 찍힌 청첩장 한 장.한유주는 그걸 끝으로 서른하나에 사랑도 우정도 다 버렸다. 남은 건 칼럼 한 줄에도 이름을 걸 수 없는 5년짜리 패션지 주니어 에디터 신세뿐.일도 사랑도, 마..</t>
         </is>
       </c>
-      <c r="Y27" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA27" t="n">
+      <c r="Y29" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA29" t="n">
         <v>105</v>
       </c>
-      <c r="AB27" t="inlineStr">
+      <c r="AB29" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
+      <c r="AC29" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD27" t="inlineStr">
+      <c r="AD29" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF27" t="inlineStr"/>
-      <c r="AG27" t="inlineStr"/>
-      <c r="AH27" t="inlineStr">
+      <c r="AE29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI27" t="inlineStr">
+      <c r="AI29" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:58:13</t>
+      <c r="AJ29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>2026-07-27 13:10:46</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C28" t="n">
-        <v>33</v>
-      </c>
-      <c r="D28" t="inlineStr">
+      <c r="C30" t="n">
+        <v>34</v>
+      </c>
+      <c r="D30" t="inlineStr">
         <is>
           <t>로맨스 저주</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=834035&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>834035</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:20:24</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="b">
-        <v>1</v>
-      </c>
-      <c r="J28" t="inlineStr">
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:19:59</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="b">
+        <v>1</v>
+      </c>
+      <c r="J30" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="N28" t="n">
-        <v>1</v>
-      </c>
-      <c r="O28" t="inlineStr">
+      <c r="N30" t="n">
+        <v>1</v>
+      </c>
+      <c r="O30" t="inlineStr">
         <is>
           <t>로맨스 저주</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>로맨스 저주 (총 92화/미완결)</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>총 92화/미완결</t>
         </is>
       </c>
-      <c r="R28" t="n">
+      <c r="R30" t="n">
         <v>92</v>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>평점 9.9 | 다원 다원 | 2026.06.18. | 총92화/미완결 | 85화 무료</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>평점 9.9 | 다원 다원 | 2026.06.18. | 총92화/미완결 | 85화 무료</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="V30" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=11824393</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>11824393</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>로맨스 저주 (총 92화/미완결)
 평점
@@ -4796,155 +5103,155 @@
 희수는 타인을 저주하는 글을 쓰면 현실이 되는 신비한 노트를 택배로 받는다.심지어 저주를 할 때마다 현금이 나온다!희수는 짝사랑하던 남자 현우를 저주해 자신과의 로맨스를 강요한다.하지만 뜻대로 되지 않고, 일이 꼬여..</t>
         </is>
       </c>
-      <c r="Y28" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z28" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA28" t="n">
+      <c r="Y30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA30" t="n">
         <v>105</v>
       </c>
-      <c r="AB28" t="inlineStr">
+      <c r="AB30" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
+      <c r="AC30" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD28" t="inlineStr">
+      <c r="AD30" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE28" t="n">
+      <c r="AE30" t="n">
         <v>2</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
-      <c r="AG28" t="inlineStr"/>
-      <c r="AH28" t="inlineStr">
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
+      <c r="AH30" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI28" t="inlineStr">
+      <c r="AI30" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:58:13</t>
+      <c r="AJ30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>2026-07-27 13:10:46</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C29" t="n">
-        <v>41</v>
-      </c>
-      <c r="D29" t="inlineStr">
+      <c r="C31" t="n">
+        <v>43</v>
+      </c>
+      <c r="D31" t="inlineStr">
         <is>
           <t>사자의 서</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=823737&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>823737</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:20:24</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="b">
-        <v>1</v>
-      </c>
-      <c r="J29" t="inlineStr">
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:19:59</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="b">
+        <v>1</v>
+      </c>
+      <c r="J31" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr">
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="N29" t="n">
+      <c r="N31" t="n">
         <v>2</v>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>사자의서 [도시정벌 레거시]</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>사자의서 [도시정벌 레거시] (총 219화/완결)</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>총 219화/완결</t>
         </is>
       </c>
-      <c r="R29" t="n">
+      <c r="R31" t="n">
         <v>219</v>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>완결</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>평점 9.2 | 신형빈 신형빈 | 2019.11.06. | 총219화/완결 | 5화 무료</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>평점 9.2 | 신형빈 신형빈 | 2019.11.06. | 총219화/완결 | 5화 무료</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="V31" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=2737090</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="W31" t="inlineStr">
         <is>
           <t>2737090</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>사자의서 [도시정벌 레거시] (총 219화/완결)
 평점
@@ -4952,161 +5259,161 @@
 죽음(死)에서 돌아 온 자. 그가 써내려가는 피의 역사에 도시(都市)가 깨어난다.</t>
         </is>
       </c>
-      <c r="Y29" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA29" t="n">
+      <c r="Y31" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA31" t="n">
         <v>100</v>
       </c>
-      <c r="AB29" t="inlineStr">
+      <c r="AB31" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_2</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
+      <c r="AC31" t="inlineStr">
         <is>
           <t>matched</t>
         </is>
       </c>
-      <c r="AD29" t="inlineStr">
+      <c r="AD31" t="inlineStr">
         <is>
           <t>first_non_compilation_numeric_download</t>
         </is>
       </c>
-      <c r="AE29" t="n">
+      <c r="AE31" t="n">
         <v>2</v>
       </c>
-      <c r="AF29" t="inlineStr">
+      <c r="AF31" t="inlineStr">
         <is>
           <t>121.3만</t>
         </is>
       </c>
-      <c r="AG29" t="n">
+      <c r="AG31" t="n">
         <v>1213000</v>
       </c>
-      <c r="AH29" t="inlineStr">
+      <c r="AH31" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="AI29" t="inlineStr">
+      <c r="AI31" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:58:13</t>
+      <c r="AJ31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>2026-07-27 13:10:46</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C30" t="n">
-        <v>56</v>
-      </c>
-      <c r="D30" t="inlineStr">
+      <c r="C32" t="n">
+        <v>57</v>
+      </c>
+      <c r="D32" t="inlineStr">
         <is>
           <t>박제</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=846363&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>846363</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:20:25</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="b">
-        <v>1</v>
-      </c>
-      <c r="J30" t="inlineStr">
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:19:59</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="b">
+        <v>1</v>
+      </c>
+      <c r="J32" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr">
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="N30" t="n">
+      <c r="N32" t="n">
         <v>2</v>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>박제하는 시간</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>박제하는 시간 (총 28화/완결)</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>총 28화/완결</t>
         </is>
       </c>
-      <c r="R30" t="n">
+      <c r="R32" t="n">
         <v>28</v>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>완결</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>평점 10.0 | 이언 | 2024.07.19. | 총28화/완결 | 5화 무료</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>평점 10.0 | 이언 | 2024.07.19. | 총28화/완결 | 5화 무료</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=10632769</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>10632769</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>박제하는 시간 (총 28화/완결)
 평점
@@ -5114,161 +5421,161 @@
 박제사 ‘도연’은 죽은 연인의 시체를 빼돌린다.이 과정을 목격한 작가 ‘이명’은 침묵의 대가로 도연의 삶을 소재로 요구해 온다.일주일간의 취재를 허락한 도연. 죽은 연인과 꼭 닮은 이명의 모습에 혼란을 느낀다.숲속의 ..</t>
         </is>
       </c>
-      <c r="Y30" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA30" t="n">
+      <c r="Y32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA32" t="n">
         <v>100</v>
       </c>
-      <c r="AB30" t="inlineStr">
+      <c r="AB32" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_2</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
+      <c r="AC32" t="inlineStr">
         <is>
           <t>matched</t>
         </is>
       </c>
-      <c r="AD30" t="inlineStr">
+      <c r="AD32" t="inlineStr">
         <is>
           <t>first_non_compilation_numeric_download</t>
         </is>
       </c>
-      <c r="AE30" t="n">
+      <c r="AE32" t="n">
         <v>2</v>
       </c>
-      <c r="AF30" t="inlineStr">
+      <c r="AF32" t="inlineStr">
         <is>
           <t>7.2만</t>
         </is>
       </c>
-      <c r="AG30" t="n">
+      <c r="AG32" t="n">
         <v>72000</v>
       </c>
-      <c r="AH30" t="inlineStr">
+      <c r="AH32" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="AI30" t="inlineStr">
+      <c r="AI32" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:58:13</t>
+      <c r="AJ32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>2026-07-27 13:10:46</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C31" t="n">
+      <c r="C33" t="n">
         <v>70</v>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>죽여주는 캐스팅</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=843866&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>843866</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:20:25</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="b">
-        <v>1</v>
-      </c>
-      <c r="J31" t="inlineStr">
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:20:00</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="b">
+        <v>1</v>
+      </c>
+      <c r="J33" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr">
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="N31" t="n">
-        <v>1</v>
-      </c>
-      <c r="O31" t="inlineStr">
+      <c r="N33" t="n">
+        <v>1</v>
+      </c>
+      <c r="O33" t="inlineStr">
         <is>
           <t>죽여주는 캐스팅 [독점]</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>죽여주는 캐스팅 [독점] (총 42화/미완결)</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>총 42화/미완결</t>
         </is>
       </c>
-      <c r="R31" t="n">
+      <c r="R33" t="n">
         <v>42</v>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>평점 9.6 | 영춘 하보 | 2026.06.18. | 총42화/미완결 | 36화 무료</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>평점 9.6 | 영춘 하보 | 2026.06.18. | 총42화/미완결 | 36화 무료</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="V33" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13253015</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
+      <c r="W33" t="inlineStr">
         <is>
           <t>13253015</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>죽여주는 캐스팅 [독점] (총 42화/미완결)
 평점
@@ -5276,155 +5583,155 @@
 영화감상 동호회에서 만난 혜수와 강호.성공한 배우를 꿈꾸는 강호는 오디션과 술자리에 몰두하며 혜수에게 기대어 살아간다.그런 강호를 이해하고자 혜수는 연기 수업을 시작하고 점차 자신의 길을 걷기 시작한다.하지만 강..</t>
         </is>
       </c>
-      <c r="Y31" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z31" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA31" t="n">
+      <c r="Y33" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA33" t="n">
         <v>105</v>
       </c>
-      <c r="AB31" t="inlineStr">
+      <c r="AB33" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
+      <c r="AC33" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD31" t="inlineStr">
+      <c r="AD33" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF31" t="inlineStr"/>
-      <c r="AG31" t="inlineStr"/>
-      <c r="AH31" t="inlineStr">
+      <c r="AE33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI31" t="inlineStr">
+      <c r="AI33" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:58:13</t>
+      <c r="AJ33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>2026-07-27 13:10:46</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C32" t="n">
+      <c r="C34" t="n">
         <v>72</v>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>사탄의 순애</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=845378&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>845378</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:20:25</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="b">
-        <v>1</v>
-      </c>
-      <c r="J32" t="inlineStr">
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:20:00</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="b">
+        <v>1</v>
+      </c>
+      <c r="J34" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr">
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="N32" t="n">
-        <v>1</v>
-      </c>
-      <c r="O32" t="inlineStr">
+      <c r="N34" t="n">
+        <v>1</v>
+      </c>
+      <c r="O34" t="inlineStr">
         <is>
           <t>사탄의 순애 [독점]</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>사탄의 순애 [독점] (총 35화/미완결)</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>총 35화/미완결</t>
         </is>
       </c>
-      <c r="R32" t="n">
+      <c r="R34" t="n">
         <v>35</v>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>평점 9.8 | 용현 카모모 | 2026.06.18. | 총35화/미완결 | 28화 무료</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>평점 9.8 | 용현 카모모 | 2026.06.18. | 총35화/미완결 | 28화 무료</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
+      <c r="V34" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13451638</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr">
+      <c r="W34" t="inlineStr">
         <is>
           <t>13451638</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>사탄의 순애 [독점] (총 35화/미완결)
 평점
@@ -5432,468 +5739,310 @@
 초식동물계 대표주자 호구남 백은우 VS 육식동물계 대표주자 차도녀 범호연.정반대의 두 사람은 어쩌다 사귀게 됐을까?“백은우. 나한테 취업해라. 내 애인인 척 딱 1년. 그럼 10억이야.”업계에서 악마로 소문난 아티스트 레..</t>
         </is>
       </c>
-      <c r="Y32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z32" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA32" t="n">
+      <c r="Y34" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA34" t="n">
         <v>105</v>
       </c>
-      <c r="AB32" t="inlineStr">
+      <c r="AB34" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
+      <c r="AC34" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD32" t="inlineStr">
+      <c r="AD34" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF32" t="inlineStr"/>
-      <c r="AG32" t="inlineStr"/>
-      <c r="AH32" t="inlineStr">
+      <c r="AE34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI32" t="inlineStr">
+      <c r="AI34" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:58:13</t>
+      <c r="AJ34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>2026-07-27 13:10:46</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>fri</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>금</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>116</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>둘뿐인 교실</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=840278&amp;tab=fri</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>840278</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:20:27</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="b">
-        <v>1</v>
-      </c>
-      <c r="J33" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>토</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>4</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>만취남녀</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=846883&amp;tab=sat</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>846883</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:20:02</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="b">
+        <v>1</v>
+      </c>
+      <c r="J35" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>fri</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>fri</t>
-        </is>
-      </c>
-      <c r="N33" t="n">
-        <v>1</v>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>둘뿐인 교실</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>둘뿐인 교실 (총 56화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>총 56화/미완결</t>
-        </is>
-      </c>
-      <c r="R33" t="n">
-        <v>56</v>
-      </c>
-      <c r="S33" t="inlineStr">
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>19금 만취남녀</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>19금 만취남녀 (총 26화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>총 26화/미완결</t>
+        </is>
+      </c>
+      <c r="R35" t="n">
+        <v>26</v>
+      </c>
+      <c r="S35" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>평점 10.0 | 종달 도요 | 2026.06.04. | 총56화/미완결 | 49화 무료</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=12773241</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>12773241</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>둘뿐인 교실 (총 56화/미완결)
-평점
-10.0 | 종달 도요 | 2026.06.04. | 총56화/미완결 | 49화 무료
-깡시골에서 지내는 민지.유일하게 친하게 지내는 동네 오빠 지훈에게는 장렬하게 차이고 친구는 아무도 없다.외로움에 시달리던 와중 도시에서 유진이 전학오게 되는데….</t>
-        </is>
-      </c>
-      <c r="Y33" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z33" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>145</v>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>title_contains,author_exact_or_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>matched</t>
-        </is>
-      </c>
-      <c r="AD33" t="inlineStr">
-        <is>
-          <t>first_non_compilation_numeric_download</t>
-        </is>
-      </c>
-      <c r="AE33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>3.7만</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>37000</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:58:13</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>토</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>4</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>만취남녀</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=846883&amp;tab=sat</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>846883</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:20:27</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="b">
-        <v>1</v>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="N34" t="n">
-        <v>1</v>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>19금 만취남녀</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>19금 만취남녀 (총 26화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>총 26화/미완결</t>
-        </is>
-      </c>
-      <c r="R34" t="n">
-        <v>26</v>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>평점 9.7 | 금 금 | 2026.06.12. | 총26화/미완결 | 21화 무료</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>평점 9.7 | 금 금 | 2026.06.12. | 총26화/미완결 | 21화 무료</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
+      <c r="V35" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13646371</t>
         </is>
       </c>
-      <c r="W34" t="inlineStr">
+      <c r="W35" t="inlineStr">
         <is>
           <t>13646371</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>19금 만취남녀 (총 26화/미완결)
 평점
 9.7 | 금 금 | 2026.06.12. | 총26화/미완결 | 21화 무료</t>
         </is>
       </c>
-      <c r="Y34" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z34" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA34" t="n">
+      <c r="Y35" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA35" t="n">
         <v>105</v>
       </c>
-      <c r="AB34" t="inlineStr">
+      <c r="AB35" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
+      <c r="AC35" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD34" t="inlineStr">
+      <c r="AD35" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF34" t="inlineStr"/>
-      <c r="AG34" t="inlineStr"/>
-      <c r="AH34" t="inlineStr">
+      <c r="AE35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI34" t="inlineStr">
+      <c r="AI35" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:58:13</t>
+      <c r="AJ35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>2026-07-27 13:10:46</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>토</t>
         </is>
       </c>
-      <c r="C35" t="n">
+      <c r="C36" t="n">
         <v>5</v>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>시든 꽃에 눈물을</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=827190&amp;tab=sat</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>827190</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:20:27</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="b">
-        <v>1</v>
-      </c>
-      <c r="J35" t="inlineStr">
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:20:02</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="b">
+        <v>1</v>
+      </c>
+      <c r="J36" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr">
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="N35" t="n">
-        <v>1</v>
-      </c>
-      <c r="O35" t="inlineStr">
+      <c r="N36" t="n">
+        <v>1</v>
+      </c>
+      <c r="O36" t="inlineStr">
         <is>
           <t>시든 꽃에 눈물을</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>시든 꽃에 눈물을 (총 106화/미완결)</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>총 106화/미완결</t>
         </is>
       </c>
-      <c r="R35" t="n">
+      <c r="R36" t="n">
         <v>106</v>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>평점 9.8 | 개 개 | 2026.06.12. | 총106화/미완결 | 100화 무료</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>평점 9.8 | 개 개 | 2026.06.12. | 총106화/미완결 | 100화 무료</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr">
+      <c r="V36" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=11253061</t>
         </is>
       </c>
-      <c r="W35" t="inlineStr">
+      <c r="W36" t="inlineStr">
         <is>
           <t>11253061</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>시든 꽃에 눈물을 (총 106화/미완결)
 평점
@@ -5901,155 +6050,155 @@
 남편이 불륜을 저질렀다. 엄청난 빚을 떠안기고, 아이를 잃게 한 것으로 모자라, 한참 어린 여자와 제 눈앞에서 몸을 섞었다. 상처 입은 삶은 볼품 없이 시들어 버려질 예정이었다. 그런데-, "어른의 사랑을 가르쳐 주세요."나해..</t>
         </is>
       </c>
-      <c r="Y35" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z35" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA35" t="n">
+      <c r="Y36" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA36" t="n">
         <v>105</v>
       </c>
-      <c r="AB35" t="inlineStr">
+      <c r="AB36" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
+      <c r="AC36" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD35" t="inlineStr">
+      <c r="AD36" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE35" t="n">
+      <c r="AE36" t="n">
         <v>4</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
-      <c r="AG35" t="inlineStr"/>
-      <c r="AH35" t="inlineStr">
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI35" t="inlineStr">
+      <c r="AI36" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:58:13</t>
+      <c r="AJ36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>2026-07-27 13:10:46</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>토</t>
         </is>
       </c>
-      <c r="C36" t="n">
-        <v>11</v>
-      </c>
-      <c r="D36" t="inlineStr">
+      <c r="C37" t="n">
+        <v>10</v>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>둘째에게</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=845711&amp;tab=sat</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>845711</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:20:27</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="b">
-        <v>1</v>
-      </c>
-      <c r="J36" t="inlineStr">
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:20:02</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="b">
+        <v>1</v>
+      </c>
+      <c r="J37" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr">
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="N36" t="n">
-        <v>1</v>
-      </c>
-      <c r="O36" t="inlineStr">
+      <c r="N37" t="n">
+        <v>1</v>
+      </c>
+      <c r="O37" t="inlineStr">
         <is>
           <t>둘째에게</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>둘째에게 (총 32화/미완결)</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>총 32화/미완결</t>
         </is>
       </c>
-      <c r="R36" t="n">
+      <c r="R37" t="n">
         <v>32</v>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="T37" t="inlineStr">
         <is>
           <t>평점 10.0 | 고태호 고태호 | 2026.06.12. | 총32화/미완결 | 27화 무료</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>평점 10.0 | 고태호 고태호 | 2026.06.12. | 총32화/미완결 | 27화 무료</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr">
+      <c r="V37" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13512084</t>
         </is>
       </c>
-      <c r="W36" t="inlineStr">
+      <c r="W37" t="inlineStr">
         <is>
           <t>13512084</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>둘째에게 (총 32화/미완결)
 평점
@@ -6057,155 +6206,155 @@
 슬럼프에 시달리고 있는 작가 '이류진'은 자신의 팬이자 조직폭력배 '둘째'와 우연히 엮이게 되고, 슬럼프를 극복하고 싶은 작가와 글쓰는 법을 배우고 싶어하는 조폭은 필요로 인해 서로 교류를 하게 된다.그렇게 교류를 하며 ..</t>
         </is>
       </c>
-      <c r="Y36" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z36" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA36" t="n">
+      <c r="Y37" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA37" t="n">
         <v>105</v>
       </c>
-      <c r="AB36" t="inlineStr">
+      <c r="AB37" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
+      <c r="AC37" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD36" t="inlineStr">
+      <c r="AD37" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF36" t="inlineStr"/>
-      <c r="AG36" t="inlineStr"/>
-      <c r="AH36" t="inlineStr">
+      <c r="AE37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="inlineStr"/>
+      <c r="AH37" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI36" t="inlineStr">
+      <c r="AI37" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:58:13</t>
+      <c r="AJ37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>2026-07-27 13:10:46</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>토</t>
         </is>
       </c>
-      <c r="C37" t="n">
+      <c r="C38" t="n">
         <v>16</v>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>데이워커</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=828880&amp;tab=sat</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>828880</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:20:28</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="b">
-        <v>1</v>
-      </c>
-      <c r="J37" t="inlineStr">
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:20:02</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="b">
+        <v>1</v>
+      </c>
+      <c r="J38" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr">
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="N37" t="n">
-        <v>1</v>
-      </c>
-      <c r="O37" t="inlineStr">
+      <c r="N38" t="n">
+        <v>1</v>
+      </c>
+      <c r="O38" t="inlineStr">
         <is>
           <t>데이워커</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>데이워커 (총 94화/미완결)</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
+      <c r="Q38" t="inlineStr">
         <is>
           <t>총 94화/미완결</t>
         </is>
       </c>
-      <c r="R37" t="n">
+      <c r="R38" t="n">
         <v>94</v>
       </c>
-      <c r="S37" t="inlineStr">
+      <c r="S38" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr">
+      <c r="T38" t="inlineStr">
         <is>
           <t>평점 9.6 | MUTE MUTE | 2026.06.12. | 총94화/미완결 | 89화 무료</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="U38" t="inlineStr">
         <is>
           <t>평점 9.6 | MUTE MUTE | 2026.06.12. | 총94화/미완결 | 89화 무료</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr">
+      <c r="V38" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=11433164</t>
         </is>
       </c>
-      <c r="W37" t="inlineStr">
+      <c r="W38" t="inlineStr">
         <is>
           <t>11433164</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>데이워커 (총 94화/미완결)
 평점
@@ -6213,162 +6362,6 @@
 국정원 블랙요원 '수혁'은 한국에 약물을 밀매하는 조직 '나나야구미'의 수장 암살 임무를 받는다.그러나 그 수장은 '안나'란 이름의 싸움과는 연관 없을 법한 매력적인 여자였는데... 이 임무 뭔가 이상하다.자신을 배신한 국정..</t>
         </is>
       </c>
-      <c r="Y37" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z37" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>105</v>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>review_needed</t>
-        </is>
-      </c>
-      <c r="AD37" t="inlineStr">
-        <is>
-          <t>non_compilation_but_download_not_ok</t>
-        </is>
-      </c>
-      <c r="AE37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF37" t="inlineStr"/>
-      <c r="AG37" t="inlineStr"/>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:58:13</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>토</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>35</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>시한복권</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=839588&amp;tab=sat</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>839588</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:20:28</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="b">
-        <v>1</v>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="N38" t="n">
-        <v>1</v>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>시한복권</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>시한복권 (총 55화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>총 55화/미완결</t>
-        </is>
-      </c>
-      <c r="R38" t="n">
-        <v>55</v>
-      </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>평점 10.0 | 세모 네모 | 2026.05.29. | 총55화/미완결 | 51화 무료</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>평점 10.0 | 세모 네모 | 2026.05.29. | 총55화/미완결 | 51화 무료</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=12681116</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>12681116</t>
-        </is>
-      </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>시한복권 (총 55화/미완결)
-평점
-10.0 | 세모 네모 | 2026.05.29. | 총55화/미완결 | 51화 무료
-완벽한 가족에서 소외된 송준은 집안으로부터 독립을 위해 매일 복권을 구매한다.송준은 소원대로 5억짜리 즉석 복권이 당첨되고 완벽한 가족에게 당첨 사실을 기꺼이 알린다.그런데 보잘것없어 보이는 5억짜리 복권에 목숨..</t>
-        </is>
-      </c>
       <c r="Y38" t="b">
         <v>0</v>
       </c>
@@ -6413,7 +6406,7 @@
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>2026-07-20 12:58:13</t>
+          <t>2026-07-27 13:10:46</t>
         </is>
       </c>
     </row>
@@ -6448,7 +6441,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-07-20 12:20:28</t>
+          <t>2026-07-27 12:20:03</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
@@ -6569,7 +6562,7 @@
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>2026-07-20 12:58:13</t>
+          <t>2026-07-27 13:10:46</t>
         </is>
       </c>
     </row>
@@ -6585,7 +6578,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -6604,7 +6597,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-20 12:20:29</t>
+          <t>2026-07-27 12:20:03</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
@@ -6725,7 +6718,7 @@
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>2026-07-20 12:58:13</t>
+          <t>2026-07-27 13:10:46</t>
         </is>
       </c>
     </row>
@@ -6741,7 +6734,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6760,7 +6753,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-07-20 12:20:32</t>
+          <t>2026-07-27 12:20:06</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -6881,7 +6874,7 @@
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>2026-07-20 12:58:13</t>
+          <t>2026-07-27 13:10:46</t>
         </is>
       </c>
     </row>
@@ -6897,7 +6890,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6916,7 +6909,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-07-20 12:20:32</t>
+          <t>2026-07-27 12:20:06</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
@@ -7037,7 +7030,7 @@
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>2026-07-20 12:58:13</t>
+          <t>2026-07-27 13:10:46</t>
         </is>
       </c>
     </row>
@@ -7072,7 +7065,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-07-20 12:20:32</t>
+          <t>2026-07-27 12:20:06</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
@@ -7192,7 +7185,7 @@
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>2026-07-20 12:58:13</t>
+          <t>2026-07-27 13:10:46</t>
         </is>
       </c>
     </row>
@@ -7208,26 +7201,26 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>유쾌한 신</t>
+          <t>럭키비치</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=846053&amp;tab=sun</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=852498&amp;tab=sun</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>846053</t>
+          <t>852498</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-07-20 12:20:32</t>
+          <t>2026-07-27 12:20:06</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
@@ -7242,34 +7235,34 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>wed,sun</t>
+          <t>thu,sun</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>wed,sun</t>
+          <t>thu,sun</t>
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>당신의 유쾌한 주말</t>
+          <t>럭키비치</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>당신의 유쾌한 주말 (총 19화/미완결)</t>
+          <t>럭키비치 (총 8화/미완결)</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>총 19화/미완결</t>
+          <t>총 8화/미완결</t>
         </is>
       </c>
       <c r="R44" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -7278,187 +7271,25 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>평점 9.4 | 김수영 김수영 | 2010.04.20. | 총19화/미완결</t>
+          <t>평점 10.0 | MAJOR, 약수 약수 | 2026.07.18. | 총8화/미완결 | 3화 무료</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>평점 9.4 | 김수영 김수영 | 2010.04.20. | 총19화/미완결</t>
+          <t>평점 10.0 | MAJOR, 약수 약수 | 2026.07.18. | 총8화/미완결 | 3화 무료</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=57402</t>
+          <t>https://series.naver.com/comic/detail.series?productNo=14424733</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>57402</t>
+          <t>14424733</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
-        <is>
-          <t>당신의 유쾌한 주말 (총 19화/미완결)
-평점
-9.4 | 김수영 김수영 | 2010.04.20. | 총19화/미완결
-화창한 토욜 인형을 잔뜩 가지고 나온 남자는 오는 손님 쫓고 가는 손님은 거들 떠 보지도 않는다. 사실 이 남자는 인형 만들기에 빠져 연재가 짤린 만화가였으니...</t>
-        </is>
-      </c>
-      <c r="Y44" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z44" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>30</v>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>bonus_total_episode_info,bonus_rank_2</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>matched</t>
-        </is>
-      </c>
-      <c r="AD44" t="inlineStr">
-        <is>
-          <t>first_non_compilation_numeric_download</t>
-        </is>
-      </c>
-      <c r="AE44" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF44" t="inlineStr">
-        <is>
-          <t>3.8천</t>
-        </is>
-      </c>
-      <c r="AG44" t="n">
-        <v>3800</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:58:13</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>20</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>럭키비치</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=852498&amp;tab=sun</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>852498</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:20:32</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="b">
-        <v>1</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>thu,sun</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>thu,sun</t>
-        </is>
-      </c>
-      <c r="N45" t="n">
-        <v>1</v>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>럭키비치</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>럭키비치 (총 8화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>총 8화/미완결</t>
-        </is>
-      </c>
-      <c r="R45" t="n">
-        <v>8</v>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>평점 10.0 | MAJOR, 약수 약수 | 2026.07.18. | 총8화/미완결 | 3화 무료</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>평점 10.0 | MAJOR, 약수 약수 | 2026.07.18. | 총8화/미완결 | 3화 무료</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=14424733</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>14424733</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr">
         <is>
           <t>럭키비치 (총 8화/미완결)
 평점
@@ -7466,155 +7297,155 @@
 “그거 알아? 기는 놈 위에 나는 썅X 있는 거?”불우한 환경과 폐쇄적인 바닷가 촌에서 자라온 소녀 '정임'은,그칠줄 모르는 주변의 부조리와 권태 속에서 결국 폭발,퇴폐업을 하는 고모의 불경한 쌈짓돈을 훔쳐 서울로 상경한..</t>
         </is>
       </c>
-      <c r="Y45" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z45" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA45" t="n">
+      <c r="Y44" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z44" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA44" t="n">
         <v>105</v>
       </c>
-      <c r="AB45" t="inlineStr">
+      <c r="AB44" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
+      <c r="AC44" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD45" t="inlineStr">
+      <c r="AD44" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF45" t="inlineStr"/>
-      <c r="AG45" t="inlineStr"/>
-      <c r="AH45" t="inlineStr">
+      <c r="AE44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="inlineStr"/>
+      <c r="AH44" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>searched_series</t>
-        </is>
-      </c>
-      <c r="AJ45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:58:13</t>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>2026-07-27 13:10:46</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C46" t="n">
-        <v>45</v>
-      </c>
-      <c r="D46" t="inlineStr">
+      <c r="C45" t="n">
+        <v>44</v>
+      </c>
+      <c r="D45" t="inlineStr">
         <is>
           <t>서바이브</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=838594&amp;tab=sun</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>838594</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:20:33</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="b">
-        <v>1</v>
-      </c>
-      <c r="J46" t="inlineStr">
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:20:07</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="b">
+        <v>1</v>
+      </c>
+      <c r="J45" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr">
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="N46" t="n">
+      <c r="N45" t="n">
         <v>2</v>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>연금술 무인도 서바이브</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>연금술 무인도 서바이브 (총 42화/완결)</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="Q45" t="inlineStr">
         <is>
           <t>총 42화/완결</t>
         </is>
       </c>
-      <c r="R46" t="n">
+      <c r="R45" t="n">
         <v>42</v>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="S45" t="inlineStr">
         <is>
           <t>완결</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr">
+      <c r="T45" t="inlineStr">
         <is>
           <t>평점 9.9 | 호시 렌지,이구치 콘 호시 렌지 | 2025.02.24. | 총42화/완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="U45" t="inlineStr">
         <is>
           <t>평점 9.9 | 호시 렌지,이구치 콘 호시 렌지 | 2025.02.24. | 총42화/완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="V46" t="inlineStr">
+      <c r="V45" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=10375934</t>
         </is>
       </c>
-      <c r="W46" t="inlineStr">
+      <c r="W45" t="inlineStr">
         <is>
           <t>10375934</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
+      <c r="X45" t="inlineStr">
         <is>
           <t>연금술 무인도 서바이브 (총 42화/완결)
 평점
@@ -7622,161 +7453,161 @@
 항행 중 사고를 당한 연금술사 니코, 요리사 진, 포로남 셋이 표착한 곳은…… 지도에도 표시돼 있지 않은 무인도였다! 「무인도에서 처음으로 해야 할 일은?」, 「물 확보는 어떻게?」, 「식량 수집의 포인트는?」 살아남기 ..</t>
         </is>
       </c>
-      <c r="Y46" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z46" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA46" t="n">
+      <c r="Y45" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z45" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA45" t="n">
         <v>100</v>
       </c>
-      <c r="AB46" t="inlineStr">
+      <c r="AB45" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_2</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
+      <c r="AC45" t="inlineStr">
         <is>
           <t>matched</t>
         </is>
       </c>
-      <c r="AD46" t="inlineStr">
+      <c r="AD45" t="inlineStr">
         <is>
           <t>first_non_compilation_numeric_download</t>
         </is>
       </c>
-      <c r="AE46" t="n">
+      <c r="AE45" t="n">
         <v>2</v>
       </c>
-      <c r="AF46" t="inlineStr">
+      <c r="AF45" t="inlineStr">
         <is>
           <t>5.6천</t>
         </is>
       </c>
-      <c r="AG46" t="n">
+      <c r="AG45" t="n">
         <v>5600</v>
       </c>
-      <c r="AH46" t="inlineStr">
+      <c r="AH45" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="AI46" t="inlineStr">
+      <c r="AI45" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:58:13</t>
+      <c r="AJ45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>2026-07-27 13:10:46</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C47" t="n">
-        <v>49</v>
-      </c>
-      <c r="D47" t="inlineStr">
+      <c r="C46" t="n">
+        <v>47</v>
+      </c>
+      <c r="D46" t="inlineStr">
         <is>
           <t>화스트 페이스</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=847905&amp;tab=sun</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>847905</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:20:33</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="b">
-        <v>1</v>
-      </c>
-      <c r="J47" t="inlineStr">
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:20:07</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="b">
+        <v>1</v>
+      </c>
+      <c r="J46" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr">
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="N47" t="n">
-        <v>1</v>
-      </c>
-      <c r="O47" t="inlineStr">
+      <c r="N46" t="n">
+        <v>1</v>
+      </c>
+      <c r="O46" t="inlineStr">
         <is>
           <t>화스트 페이스</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>화스트 페이스 (총 24화/미완결)</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="Q46" t="inlineStr">
         <is>
           <t>총 24화/미완결</t>
         </is>
       </c>
-      <c r="R47" t="n">
+      <c r="R46" t="n">
         <v>24</v>
       </c>
-      <c r="S47" t="inlineStr">
+      <c r="S46" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T47" t="inlineStr">
+      <c r="T46" t="inlineStr">
         <is>
           <t>평점 9.9 | NO_Teamkill NO_Teamkill | 2026.06.13. | 총24화/미완결 | 20화 무료</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="U46" t="inlineStr">
         <is>
           <t>평점 9.9 | NO_Teamkill NO_Teamkill | 2026.06.13. | 총24화/미완결 | 20화 무료</t>
         </is>
       </c>
-      <c r="V47" t="inlineStr">
+      <c r="V46" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13750354</t>
         </is>
       </c>
-      <c r="W47" t="inlineStr">
+      <c r="W46" t="inlineStr">
         <is>
           <t>13750354</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>화스트 페이스 (총 24화/미완결)
 평점
@@ -7784,155 +7615,155 @@
 화스트 페이스! 상황 발생! 상황 발생!현재 적 대규모 도발로 인해 준전시상태 돌입!전 병력 전투 장비 구비하고 즉각 출동 준비할 수 있도록!제1부 화스트페이스!제2부 20XX년 XX월 XX일 21시44분!제3부 발령권자 군단장!..</t>
         </is>
       </c>
-      <c r="Y47" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z47" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA47" t="n">
+      <c r="Y46" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA46" t="n">
         <v>105</v>
       </c>
-      <c r="AB47" t="inlineStr">
+      <c r="AB46" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
+      <c r="AC46" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD47" t="inlineStr">
+      <c r="AD46" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF47" t="inlineStr"/>
-      <c r="AG47" t="inlineStr"/>
-      <c r="AH47" t="inlineStr">
+      <c r="AE46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="inlineStr"/>
+      <c r="AH46" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI47" t="inlineStr">
+      <c r="AI46" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:58:13</t>
+      <c r="AJ46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>2026-07-27 13:10:46</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C48" t="n">
+      <c r="C47" t="n">
         <v>80</v>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>나는 참지 못한다</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=823476&amp;tab=sun</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>823476</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:20:34</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="b">
-        <v>1</v>
-      </c>
-      <c r="J48" t="inlineStr">
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:20:08</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="b">
+        <v>1</v>
+      </c>
+      <c r="J47" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr">
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="N48" t="n">
-        <v>1</v>
-      </c>
-      <c r="O48" t="inlineStr">
+      <c r="N47" t="n">
+        <v>1</v>
+      </c>
+      <c r="O47" t="inlineStr">
         <is>
           <t>나는 참지 못한다</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>나는 참지 못한다 (총 115화/미완결)</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
+      <c r="Q47" t="inlineStr">
         <is>
           <t>총 115화/미완결</t>
         </is>
       </c>
-      <c r="R48" t="n">
+      <c r="R47" t="n">
         <v>115</v>
       </c>
-      <c r="S48" t="inlineStr">
+      <c r="S47" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr">
+      <c r="T47" t="inlineStr">
         <is>
           <t>평점 10.0 | 성현 성현 | 2026.06.13. | 총115화/미완결 | 111화 무료</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="U47" t="inlineStr">
         <is>
           <t>평점 10.0 | 성현 성현 | 2026.06.13. | 총115화/미완결 | 111화 무료</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr">
+      <c r="V47" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=10970308</t>
         </is>
       </c>
-      <c r="W48" t="inlineStr">
+      <c r="W47" t="inlineStr">
         <is>
           <t>10970308</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>나는 참지 못한다 (총 115화/미완결)
 평점
@@ -7940,155 +7771,155 @@
 평범한 회사원 김연지는 교통사고 이후 변화를 겪게 된다.스트레스가 폭발하면 아무것도 참지 못하는 상태가 되고 만다.계속 일어나는 통제불능 사건들, 자신에게 접근하는 의문의 남성 민성훈.사건은 커지고 일상은 꼬여만 가..</t>
         </is>
       </c>
-      <c r="Y48" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z48" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA48" t="n">
+      <c r="Y47" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z47" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA47" t="n">
         <v>105</v>
       </c>
-      <c r="AB48" t="inlineStr">
+      <c r="AB47" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
+      <c r="AC47" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD48" t="inlineStr">
+      <c r="AD47" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE48" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF48" t="inlineStr"/>
-      <c r="AG48" t="inlineStr"/>
-      <c r="AH48" t="inlineStr">
+      <c r="AE47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="inlineStr"/>
+      <c r="AH47" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI48" t="inlineStr">
+      <c r="AI47" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:58:13</t>
+      <c r="AJ47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>2026-07-27 13:10:46</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C49" t="n">
-        <v>82</v>
-      </c>
-      <c r="D49" t="inlineStr">
+      <c r="C48" t="n">
+        <v>81</v>
+      </c>
+      <c r="D48" t="inlineStr">
         <is>
           <t>사내 계약 연애</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=842148&amp;tab=sun</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>842148</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:20:34</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="b">
-        <v>1</v>
-      </c>
-      <c r="J49" t="inlineStr">
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:20:08</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="b">
+        <v>1</v>
+      </c>
+      <c r="J48" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr">
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="N49" t="n">
-        <v>1</v>
-      </c>
-      <c r="O49" t="inlineStr">
+      <c r="N48" t="n">
+        <v>1</v>
+      </c>
+      <c r="O48" t="inlineStr">
         <is>
           <t>사내 계약 연애</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>사내 계약 연애 (총 48화/미완결)</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="Q48" t="inlineStr">
         <is>
           <t>총 48화/미완결</t>
         </is>
       </c>
-      <c r="R49" t="n">
+      <c r="R48" t="n">
         <v>48</v>
       </c>
-      <c r="S49" t="inlineStr">
+      <c r="S48" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr">
+      <c r="T48" t="inlineStr">
         <is>
           <t>평점 9.9 | 최무탁, 미리엄 울 | 2026.06.13. | 총48화/미완결 | 42화 무료</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr">
+      <c r="U48" t="inlineStr">
         <is>
           <t>평점 9.9 | 최무탁, 미리엄 울 | 2026.06.13. | 총48화/미완결 | 42화 무료</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr">
+      <c r="V48" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13046250</t>
         </is>
       </c>
-      <c r="W49" t="inlineStr">
+      <c r="W48" t="inlineStr">
         <is>
           <t>13046250</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
+      <c r="X48" t="inlineStr">
         <is>
           <t>사내 계약 연애 (총 48화/미완결)
 평점
@@ -8096,161 +7927,161 @@
 예쁘고 잘생긴 것, '미'를 애정하는 서윤.그리고 그런 그녀가 더 애정하는 것은바로 미의 남녀가 서로를 사랑스럽게 탐하는 19금 만화책!그런데 이 미적 추구미에 도달하는 남자가가장 가까이에 그녀의 직속 상사로 있었으니.....</t>
         </is>
       </c>
-      <c r="Y49" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z49" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA49" t="n">
+      <c r="Y48" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z48" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA48" t="n">
         <v>105</v>
       </c>
-      <c r="AB49" t="inlineStr">
+      <c r="AB48" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
+      <c r="AC48" t="inlineStr">
         <is>
           <t>matched</t>
         </is>
       </c>
-      <c r="AD49" t="inlineStr">
+      <c r="AD48" t="inlineStr">
         <is>
           <t>first_non_compilation_numeric_download</t>
         </is>
       </c>
-      <c r="AE49" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF49" t="inlineStr">
+      <c r="AE48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF48" t="inlineStr">
         <is>
           <t>51.5만</t>
         </is>
       </c>
-      <c r="AG49" t="n">
+      <c r="AG48" t="n">
         <v>515000</v>
       </c>
-      <c r="AH49" t="inlineStr">
+      <c r="AH48" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="AI49" t="inlineStr">
+      <c r="AI48" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:58:13</t>
+      <c r="AJ48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>2026-07-27 13:10:46</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C50" t="n">
-        <v>87</v>
-      </c>
-      <c r="D50" t="inlineStr">
+      <c r="C49" t="n">
+        <v>86</v>
+      </c>
+      <c r="D49" t="inlineStr">
         <is>
           <t>죽거나 혹은 사랑에 빠지거나</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=819696&amp;tab=sun</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>819696</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:20:35</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="b">
-        <v>1</v>
-      </c>
-      <c r="J50" t="inlineStr">
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:20:08</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="b">
+        <v>1</v>
+      </c>
+      <c r="J49" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr">
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="N50" t="n">
-        <v>1</v>
-      </c>
-      <c r="O50" t="inlineStr">
+      <c r="N49" t="n">
+        <v>1</v>
+      </c>
+      <c r="O49" t="inlineStr">
         <is>
           <t>죽거나 혹은 사랑에 빠지거나</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="P49" t="inlineStr">
         <is>
           <t>죽거나 혹은 사랑에 빠지거나 (총 128화/미완결)</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
+      <c r="Q49" t="inlineStr">
         <is>
           <t>총 128화/미완결</t>
         </is>
       </c>
-      <c r="R50" t="n">
+      <c r="R49" t="n">
         <v>128</v>
       </c>
-      <c r="S50" t="inlineStr">
+      <c r="S49" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr">
+      <c r="T49" t="inlineStr">
         <is>
           <t>평점 9.8 | 허니비 허니비 | 2026.06.13. | 총128화/미완결 | 122화 무료</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr">
+      <c r="U49" t="inlineStr">
         <is>
           <t>평점 9.8 | 허니비 허니비 | 2026.06.13. | 총128화/미완결 | 122화 무료</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr">
+      <c r="V49" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=10555314</t>
         </is>
       </c>
-      <c r="W50" t="inlineStr">
+      <c r="W49" t="inlineStr">
         <is>
           <t>10555314</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
+      <c r="X49" t="inlineStr">
         <is>
           <t>죽거나 혹은 사랑에 빠지거나 (총 128화/미완결)
 평점
@@ -8258,51 +8089,51 @@
 아름다운 도시 루베른에서 일어나는 의문의 연쇄살인 사건. 조용하고 눈에 띄지 않는 이자벨라에게 살인마의 초대장이 전달되는데.. 목숨을 건 15일간의 내기. 절대 어떤 쾌락과 환상에도 사랑에 빠져서는 안 된다.</t>
         </is>
       </c>
-      <c r="Y50" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z50" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA50" t="n">
+      <c r="Y49" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z49" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA49" t="n">
         <v>105</v>
       </c>
-      <c r="AB50" t="inlineStr">
+      <c r="AB49" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
+      <c r="AC49" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD50" t="inlineStr">
+      <c r="AD49" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE50" t="n">
+      <c r="AE49" t="n">
         <v>2</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
-      <c r="AG50" t="inlineStr"/>
-      <c r="AH50" t="inlineStr">
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="inlineStr"/>
+      <c r="AH49" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI50" t="inlineStr">
+      <c r="AI49" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:58:13</t>
+      <c r="AJ49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>2026-07-27 13:10:46</t>
         </is>
       </c>
     </row>

--- a/data/adult_login_required_webtoons_v2.xlsx
+++ b/data/adult_login_required_webtoons_v2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK49"/>
+  <dimension ref="A1:AK48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -634,7 +634,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-27 12:19:44</t>
+          <t>2026-08-03 11:55:49</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -746,7 +746,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>searched_series</t>
+          <t>reused_existing_product_no</t>
         </is>
       </c>
       <c r="AJ2" t="b">
@@ -754,7 +754,7 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2026-07-27 13:10:46</t>
+          <t>2026-08-03 12:36:11</t>
         </is>
       </c>
     </row>
@@ -789,7 +789,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-27 12:19:45</t>
+          <t>2026-08-03 11:55:50</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -910,7 +910,7 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2026-07-27 13:10:46</t>
+          <t>2026-08-03 12:36:11</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-27 12:19:45</t>
+          <t>2026-08-03 11:55:50</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2026-07-27 13:10:46</t>
+          <t>2026-08-03 12:36:11</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-27 12:19:46</t>
+          <t>2026-08-03 11:55:51</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2026-07-27 13:10:46</t>
+          <t>2026-08-03 12:36:11</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-27 12:19:46</t>
+          <t>2026-08-03 11:55:51</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2026-07-27 13:10:46</t>
+          <t>2026-08-03 12:36:11</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-27 12:19:47</t>
+          <t>2026-08-03 11:55:52</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>searched_series</t>
+          <t>reused_existing_product_no</t>
         </is>
       </c>
       <c r="AJ7" t="b">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2026-07-27 13:10:46</t>
+          <t>2026-08-03 12:36:11</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-07-27 12:19:48</t>
+          <t>2026-08-03 11:55:53</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2026-07-27 13:10:46</t>
+          <t>2026-08-03 12:36:11</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-07-27 12:19:48</t>
+          <t>2026-08-03 11:55:53</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2026-07-27 13:10:46</t>
+          <t>2026-08-03 12:36:11</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-07-27 12:19:48</t>
+          <t>2026-08-03 11:55:53</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2026-07-27 13:10:46</t>
+          <t>2026-08-03 12:36:11</t>
         </is>
       </c>
     </row>
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-07-27 12:19:48</t>
+          <t>2026-08-03 11:55:53</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2026-07-27 13:10:46</t>
+          <t>2026-08-03 12:36:11</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-07-27 12:19:49</t>
+          <t>2026-08-03 11:55:54</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2026-07-27 13:10:46</t>
+          <t>2026-08-03 12:36:11</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-07-27 12:19:49</t>
+          <t>2026-08-03 11:55:54</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>2026-07-27 13:10:46</t>
+          <t>2026-08-03 12:36:11</t>
         </is>
       </c>
     </row>
@@ -2497,7 +2497,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-07-27 12:19:49</t>
+          <t>2026-08-03 11:55:54</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -2637,7 +2637,7 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>2026-07-27 13:10:46</t>
+          <t>2026-08-03 12:36:11</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-07-27 12:19:50</t>
+          <t>2026-08-03 11:55:55</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>2026-07-27 13:10:46</t>
+          <t>2026-08-03 12:36:11</t>
         </is>
       </c>
     </row>
@@ -2809,26 +2809,26 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>썰:관계주의</t>
+          <t>싸이코패스 in 무림</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=834033&amp;tab=wed</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=846109&amp;tab=wed</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>834033</t>
+          <t>846109</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-07-27 12:19:51</t>
+          <t>2026-08-03 11:55:57</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -2856,48 +2856,204 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
+          <t>싸이코패스 in 무림[독점]</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>싸이코패스 in 무림[독점] (총 32화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>총 32화/미완결</t>
+        </is>
+      </c>
+      <c r="R16" t="n">
+        <v>32</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>평점 9.8 | 김언, 곤붕 송범규 | 2026.06.16. | 총32화/미완결 | 26화 무료</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>평점 9.8 | 김언, 곤붕 송범규 | 2026.06.16. | 총32화/미완결 | 26화 무료</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=13566546</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>13566546</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>싸이코패스 in 무림[독점] (총 32화/미완결)
+평점
+9.8 | 김언, 곤붕 송범규 | 2026.06.16. | 총32화/미완결 | 26화 무료
+[진정한 강자들의 세상, 무림 온라인에 오신 걸 환영합니다.]무림에 떨어진 희대의 싸이코패스.음모와 악의가 가득한 무림에 동봉수, 그의 무정한 이빨이 드리운다.</t>
+        </is>
+      </c>
+      <c r="Y16" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>non_compilation_but_download_not_ok</t>
+        </is>
+      </c>
+      <c r="AE16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:36:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>wed</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>10</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>썰:관계주의</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=834033&amp;tab=wed</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>834033</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-08-03 11:55:57</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="b">
+        <v>1</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>wed</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>wed</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>썰:관계주의</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
         <is>
           <t>썰:관계주의 (총 87화/미완결)</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>총 87화/미완결</t>
         </is>
       </c>
-      <c r="R16" t="n">
+      <c r="R17" t="n">
         <v>87</v>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>평점 10.0 | 이삼 장버들 | 2026.06.16. | 총87화/미완결 | 83화 무료</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>평점 10.0 | 이삼 장버들 | 2026.06.16. | 총87화/미완결 | 83화 무료</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=11802777</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>11802777</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>썰:관계주의 (총 87화/미완결)
 평점
@@ -2905,162 +3061,6 @@
 여러 상가가 들어서 있는 강남의 유명타워. 이야기는 유명타워의 한 피부과 안내 데스크 직원 강지영으로부터 시작된다. 동료이자 유부남 의사와 만남을 이어가던 지영은 그에게 또 다른 불륜 상대가 있음을 눈치 채는데 그 상..</t>
         </is>
       </c>
-      <c r="Y16" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>105</v>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>review_needed</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>non_compilation_but_download_not_ok</t>
-        </is>
-      </c>
-      <c r="AE16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF16" t="inlineStr"/>
-      <c r="AG16" t="inlineStr"/>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>2026-07-27 13:10:46</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>wed</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>수</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>10</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>싸이코패스 in 무림</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=846109&amp;tab=wed</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>846109</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>2026-07-27 12:19:51</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="b">
-        <v>1</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>wed</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>wed</t>
-        </is>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>싸이코패스 in 무림[독점]</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>싸이코패스 in 무림[독점] (총 32화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>총 32화/미완결</t>
-        </is>
-      </c>
-      <c r="R17" t="n">
-        <v>32</v>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>평점 9.8 | 김언, 곤붕 송범규 | 2026.06.16. | 총32화/미완결 | 26화 무료</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>평점 9.8 | 김언, 곤붕 송범규 | 2026.06.16. | 총32화/미완결 | 26화 무료</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=13566546</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>13566546</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>싸이코패스 in 무림[독점] (총 32화/미완결)
-평점
-9.8 | 김언, 곤붕 송범규 | 2026.06.16. | 총32화/미완결 | 26화 무료
-[진정한 강자들의 세상, 무림 온라인에 오신 걸 환영합니다.]무림에 떨어진 희대의 싸이코패스.음모와 악의가 가득한 무림에 동봉수, 그의 무정한 이빨이 드리운다.</t>
-        </is>
-      </c>
       <c r="Y17" t="b">
         <v>0</v>
       </c>
@@ -3105,7 +3105,7 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>2026-07-27 13:10:46</t>
+          <t>2026-08-03 12:36:11</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3121,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-07-27 12:19:52</t>
+          <t>2026-08-03 11:55:57</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>2026-07-27 13:10:46</t>
+          <t>2026-08-03 12:36:11</t>
         </is>
       </c>
     </row>
@@ -3302,7 +3302,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-07-27 12:19:52</t>
+          <t>2026-08-03 11:55:57</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>2026-07-27 13:10:46</t>
+          <t>2026-08-03 12:36:11</t>
         </is>
       </c>
     </row>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-07-27 12:19:53</t>
+          <t>2026-08-03 11:55:59</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>2026-07-27 13:10:46</t>
+          <t>2026-08-03 12:36:11</t>
         </is>
       </c>
     </row>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-07-27 12:19:54</t>
+          <t>2026-08-03 11:56:00</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>2026-07-27 13:10:46</t>
+          <t>2026-08-03 12:36:11</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-07-27 12:19:55</t>
+          <t>2026-08-03 11:56:00</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>2026-07-27 13:10:46</t>
+          <t>2026-08-03 12:36:11</t>
         </is>
       </c>
     </row>
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-07-27 12:19:56</t>
+          <t>2026-08-03 11:56:02</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>2026-07-27 13:10:46</t>
+          <t>2026-08-03 12:36:11</t>
         </is>
       </c>
     </row>
@@ -4063,26 +4063,26 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>첫눈에 반한 건 아니지만</t>
+          <t>휴먼 웨어러블</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=830637&amp;tab=thu</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=845460&amp;tab=thu</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>830637</t>
+          <t>845460</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-07-27 12:19:56</t>
+          <t>2026-08-03 11:56:03</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -4110,21 +4110,21 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>첫눈에 반한 건 아니지만</t>
+          <t>휴먼 웨어러블</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>첫눈에 반한 건 아니지만 (총 68화/미완결)</t>
+          <t>휴먼 웨어러블 (총 30화/미완결)</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>총 68화/미완결</t>
+          <t>총 30화/미완결</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -4133,183 +4133,25 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>평점 9.9 | 아임 아임 | 2026.06.03. | 총68화/미완결 | 63화 무료</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr"/>
+          <t>평점 9.9 | 쥬타인 쥬타인 | 2026.06.03. | 총30화/미완결 | 27화 무료</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>평점 9.9 | 쥬타인 쥬타인 | 2026.06.03. | 총30화/미완결 | 27화 무료</t>
+        </is>
+      </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=11573054</t>
+          <t>https://series.naver.com/comic/detail.series?productNo=13481722</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>11573054</t>
+          <t>13481722</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
-        <is>
-          <t>첫눈에 반한 건 아니지만 (총 68화/미완결)
-평점
-9.9 | 아임 아임 | 2026.06.03. | 총68화/미완결 | 63화 무료
-결혼을 전제로 선을 본 서은재. 그 상대인 윤시우는 안 좋은 소문이 무성한 남자였기에은재는 그를 경계하고 거절하려고 한다.하지만 첫눈에 반했다는 그의 열열한 구애에 끝내는 마음을 빼앗기고 마는데...은재는 시우에게 푹 ..</t>
-        </is>
-      </c>
-      <c r="Y24" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z24" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>145</v>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>title_contains,author_exact_or_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>matched</t>
-        </is>
-      </c>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>first_non_compilation_numeric_download</t>
-        </is>
-      </c>
-      <c r="AE24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>90.6만</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>906000</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>2026-07-27 13:10:46</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>thu</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>목</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>77</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>휴먼 웨어러블</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=845460&amp;tab=thu</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>845460</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>2026-07-27 12:19:56</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="b">
-        <v>1</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>thu</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>thu</t>
-        </is>
-      </c>
-      <c r="N25" t="n">
-        <v>1</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>휴먼 웨어러블</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>휴먼 웨어러블 (총 30화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>총 30화/미완결</t>
-        </is>
-      </c>
-      <c r="R25" t="n">
-        <v>30</v>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>평점 9.9 | 쥬타인 쥬타인 | 2026.06.03. | 총30화/미완결 | 27화 무료</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>평점 9.9 | 쥬타인 쥬타인 | 2026.06.03. | 총30화/미완결 | 27화 무료</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=13481722</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>13481722</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
         <is>
           <t>휴먼 웨어러블 (총 30화/미완결)
 평점
@@ -4317,155 +4159,155 @@
 꿈의 무대, 패션 서바이벌 &lt;휴먼 웨어러블&gt;.고아 출신이지만 명문 ‘순백패션예술학교’를 거쳐 올라온 학생들.이 무대에서 인생 역전의 주인공이 탄생한다—…그런데 무언가, 이상하게 흘러가기 시작했다.</t>
         </is>
       </c>
-      <c r="Y25" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA25" t="n">
+      <c r="Y24" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA24" t="n">
         <v>105</v>
       </c>
-      <c r="AB25" t="inlineStr">
+      <c r="AB24" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
+      <c r="AC24" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD25" t="inlineStr">
+      <c r="AD24" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF25" t="inlineStr"/>
-      <c r="AG25" t="inlineStr"/>
-      <c r="AH25" t="inlineStr">
+      <c r="AE24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI25" t="inlineStr">
+      <c r="AI24" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>2026-07-27 13:10:46</t>
+      <c r="AJ24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:36:11</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C26" t="n">
+      <c r="C25" t="n">
         <v>2</v>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>오! 나의 교주님</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=841624&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>841624</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>2026-07-27 12:19:57</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="b">
-        <v>1</v>
-      </c>
-      <c r="J26" t="inlineStr">
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-08-03 11:56:03</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="b">
+        <v>1</v>
+      </c>
+      <c r="J25" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
         <is>
           <t>tue,fri</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>tue,fri</t>
         </is>
       </c>
-      <c r="N26" t="n">
-        <v>1</v>
-      </c>
-      <c r="O26" t="inlineStr">
+      <c r="N25" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" t="inlineStr">
         <is>
           <t>오! 나의 교주님</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>오! 나의 교주님 (총 94화/미완결)</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>총 94화/미완결</t>
         </is>
       </c>
-      <c r="R26" t="n">
+      <c r="R25" t="n">
         <v>94</v>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>평점 9.4 | 김꿀빨, 김완두 김꿀빨, 김완두 | 2026.06.18. | 총94화/미완결 | 89화 무료</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>평점 9.4 | 김꿀빨, 김완두 김꿀빨, 김완두 | 2026.06.18. | 총94화/미완결 | 89화 무료</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=12998643</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>12998643</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>오! 나의 교주님 (총 94화/미완결)
 평점
@@ -4473,155 +4315,155 @@
 사이비 종교 ‘진천교’에서 태어나 평생을 그곳에서 살아온 한성민. 그는 결국 모든 것을 잃고 홀로 탈출한다.수년 후, 성인이 된 그는 다시 진천교에 잠입해 처절한 복수를 시작하려 한다.“오, 나의 교주님. 제가 보내드릴게..</t>
         </is>
       </c>
-      <c r="Y26" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z26" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA26" t="n">
+      <c r="Y25" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA25" t="n">
         <v>105</v>
       </c>
-      <c r="AB26" t="inlineStr">
+      <c r="AB25" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
+      <c r="AC25" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD26" t="inlineStr">
+      <c r="AD25" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF26" t="inlineStr"/>
-      <c r="AG26" t="inlineStr"/>
-      <c r="AH26" t="inlineStr">
+      <c r="AE25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI26" t="inlineStr">
+      <c r="AI25" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>2026-07-27 13:10:46</t>
+      <c r="AJ25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:36:11</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C27" t="n">
+      <c r="C26" t="n">
         <v>8</v>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>두 얼굴</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=845646&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>845646</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>2026-07-27 12:19:58</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="b">
-        <v>1</v>
-      </c>
-      <c r="J27" t="inlineStr">
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-08-03 11:56:04</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="b">
+        <v>1</v>
+      </c>
+      <c r="J26" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="N27" t="n">
-        <v>1</v>
-      </c>
-      <c r="O27" t="inlineStr">
+      <c r="N26" t="n">
+        <v>1</v>
+      </c>
+      <c r="O26" t="inlineStr">
         <is>
           <t>두 얼굴의 대표님</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>두 얼굴의 대표님 (총 126화/완결)</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>총 126화/완결</t>
         </is>
       </c>
-      <c r="R27" t="n">
+      <c r="R26" t="n">
         <v>126</v>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>완결</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>평점 6.2 | 1M, KuaiKan, YY 1M, KuaiKan, YY | 2022.10.02. | 총126화/완결 | 3화 무료</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>평점 6.2 | 1M, KuaiKan, YY 1M, KuaiKan, YY | 2022.10.02. | 총126화/완결 | 3화 무료</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=6489984</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>6489984</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>두 얼굴의 대표님 (총 126화/완결)
 평점
@@ -4629,161 +4471,161 @@
 재벌가의 사생아로 태어난 소원은 일찍 엄마를 잃고, 가족들의 멸시 속에서 살아왔다.그러다 언니에게 약혼자까지 뺏기게 되자, 실의에 빠진 소원은 유학을 떠나게 되고, 그곳에서 평범한 남편을 만나 결혼을 하게 된다.1년 후 ..</t>
         </is>
       </c>
-      <c r="Y27" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA27" t="n">
+      <c r="Y26" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA26" t="n">
         <v>105</v>
       </c>
-      <c r="AB27" t="inlineStr">
+      <c r="AB26" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
+      <c r="AC26" t="inlineStr">
         <is>
           <t>matched</t>
         </is>
       </c>
-      <c r="AD27" t="inlineStr">
+      <c r="AD26" t="inlineStr">
         <is>
           <t>first_non_compilation_numeric_download</t>
         </is>
       </c>
-      <c r="AE27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF27" t="inlineStr">
+      <c r="AE26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF26" t="inlineStr">
         <is>
           <t>157.5만</t>
         </is>
       </c>
-      <c r="AG27" t="n">
+      <c r="AG26" t="n">
         <v>1575000</v>
       </c>
-      <c r="AH27" t="inlineStr">
+      <c r="AH26" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="AI27" t="inlineStr">
+      <c r="AI26" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>2026-07-27 13:10:46</t>
+      <c r="AJ26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:36:11</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C28" t="n">
+      <c r="C27" t="n">
         <v>10</v>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>네가 사는 그 집</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=842465&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>842465</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>2026-07-27 12:19:58</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="b">
-        <v>1</v>
-      </c>
-      <c r="J28" t="inlineStr">
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-08-03 11:56:04</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="b">
+        <v>1</v>
+      </c>
+      <c r="J27" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="N28" t="n">
-        <v>1</v>
-      </c>
-      <c r="O28" t="inlineStr">
+      <c r="N27" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" t="inlineStr">
         <is>
           <t>네가 사는 그 집</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>네가 사는 그 집 (총 47화/미완결)</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>총 47화/미완결</t>
         </is>
       </c>
-      <c r="R28" t="n">
+      <c r="R27" t="n">
         <v>47</v>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>평점 9.7 | 석우 해바다 | 2026.06.18. | 총47화/미완결 | 41화 무료</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>평점 9.7 | 석우 해바다 | 2026.06.18. | 총47화/미완결 | 41화 무료</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13090391</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>13090391</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>네가 사는 그 집 (총 47화/미완결)
 평점
@@ -4791,155 +4633,155 @@
 찢어지게 가난한 집에서 두 아이를 키우며 힘겹게 살아가던 30대 화린.어느날, 자기 첫사랑이었던 부유한 선배와 결혼해 행복하게 사는 친구와 몸이 바뀐다.하지만 부러워하던 삶을 얻은 기쁨도 잠시,그 집의 추악한 비밀이 드..</t>
         </is>
       </c>
-      <c r="Y28" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z28" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA28" t="n">
+      <c r="Y27" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA27" t="n">
         <v>105</v>
       </c>
-      <c r="AB28" t="inlineStr">
+      <c r="AB27" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
+      <c r="AC27" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD28" t="inlineStr">
+      <c r="AD27" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF28" t="inlineStr"/>
-      <c r="AG28" t="inlineStr"/>
-      <c r="AH28" t="inlineStr">
+      <c r="AE27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI28" t="inlineStr">
+      <c r="AI27" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>2026-07-27 13:10:46</t>
+      <c r="AJ27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:36:11</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C29" t="n">
+      <c r="C28" t="n">
         <v>11</v>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>그리디</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=845919&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>845919</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>2026-07-27 12:19:58</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="b">
-        <v>1</v>
-      </c>
-      <c r="J29" t="inlineStr">
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-08-03 11:56:04</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="b">
+        <v>1</v>
+      </c>
+      <c r="J28" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr">
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="N29" t="n">
-        <v>1</v>
-      </c>
-      <c r="O29" t="inlineStr">
+      <c r="N28" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" t="inlineStr">
         <is>
           <t>그리디</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>그리디 (총 31화/미완결)</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>총 31화/미완결</t>
         </is>
       </c>
-      <c r="R29" t="n">
+      <c r="R28" t="n">
         <v>31</v>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>평점 9.9 | 영하 랑라리 | 2026.06.18. | 총31화/미완결 | 25화 무료</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>평점 9.9 | 영하 랑라리 | 2026.06.18. | 총31화/미완결 | 25화 무료</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13530624</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>13530624</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>그리디 (총 31화/미완결)
 평점
@@ -4947,155 +4789,155 @@
 파혼했다. 십년지기 친구와 내가 파혼한 남자가 찍힌 청첩장 한 장.한유주는 그걸 끝으로 서른하나에 사랑도 우정도 다 버렸다. 남은 건 칼럼 한 줄에도 이름을 걸 수 없는 5년짜리 패션지 주니어 에디터 신세뿐.일도 사랑도, 마..</t>
         </is>
       </c>
-      <c r="Y29" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA29" t="n">
+      <c r="Y28" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA28" t="n">
         <v>105</v>
       </c>
-      <c r="AB29" t="inlineStr">
+      <c r="AB28" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
+      <c r="AC28" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD29" t="inlineStr">
+      <c r="AD28" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF29" t="inlineStr"/>
-      <c r="AG29" t="inlineStr"/>
-      <c r="AH29" t="inlineStr">
+      <c r="AE28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI29" t="inlineStr">
+      <c r="AI28" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>2026-07-27 13:10:46</t>
+      <c r="AJ28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:36:11</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C30" t="n">
+      <c r="C29" t="n">
         <v>34</v>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>로맨스 저주</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=834035&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>834035</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>2026-07-27 12:19:59</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="b">
-        <v>1</v>
-      </c>
-      <c r="J30" t="inlineStr">
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-08-03 11:56:04</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="b">
+        <v>1</v>
+      </c>
+      <c r="J29" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr">
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="N30" t="n">
-        <v>1</v>
-      </c>
-      <c r="O30" t="inlineStr">
+      <c r="N29" t="n">
+        <v>1</v>
+      </c>
+      <c r="O29" t="inlineStr">
         <is>
           <t>로맨스 저주</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>로맨스 저주 (총 92화/미완결)</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>총 92화/미완결</t>
         </is>
       </c>
-      <c r="R30" t="n">
+      <c r="R29" t="n">
         <v>92</v>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>평점 9.9 | 다원 다원 | 2026.06.18. | 총92화/미완결 | 85화 무료</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>평점 9.9 | 다원 다원 | 2026.06.18. | 총92화/미완결 | 85화 무료</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=11824393</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>11824393</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>로맨스 저주 (총 92화/미완결)
 평점
@@ -5103,155 +4945,155 @@
 희수는 타인을 저주하는 글을 쓰면 현실이 되는 신비한 노트를 택배로 받는다.심지어 저주를 할 때마다 현금이 나온다!희수는 짝사랑하던 남자 현우를 저주해 자신과의 로맨스를 강요한다.하지만 뜻대로 되지 않고, 일이 꼬여..</t>
         </is>
       </c>
-      <c r="Y30" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA30" t="n">
+      <c r="Y29" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA29" t="n">
         <v>105</v>
       </c>
-      <c r="AB30" t="inlineStr">
+      <c r="AB29" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
+      <c r="AC29" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD30" t="inlineStr">
+      <c r="AD29" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE30" t="n">
+      <c r="AE29" t="n">
         <v>2</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
-      <c r="AG30" t="inlineStr"/>
-      <c r="AH30" t="inlineStr">
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI30" t="inlineStr">
+      <c r="AI29" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>2026-07-27 13:10:46</t>
+      <c r="AJ29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:36:11</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C31" t="n">
-        <v>43</v>
-      </c>
-      <c r="D31" t="inlineStr">
+      <c r="C30" t="n">
+        <v>41</v>
+      </c>
+      <c r="D30" t="inlineStr">
         <is>
           <t>사자의 서</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=823737&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>823737</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>2026-07-27 12:19:59</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="b">
-        <v>1</v>
-      </c>
-      <c r="J31" t="inlineStr">
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026-08-03 11:56:05</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="b">
+        <v>1</v>
+      </c>
+      <c r="J30" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr">
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="N31" t="n">
+      <c r="N30" t="n">
         <v>2</v>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>사자의서 [도시정벌 레거시]</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>사자의서 [도시정벌 레거시] (총 219화/완결)</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>총 219화/완결</t>
         </is>
       </c>
-      <c r="R31" t="n">
+      <c r="R30" t="n">
         <v>219</v>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>완결</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>평점 9.2 | 신형빈 신형빈 | 2019.11.06. | 총219화/완결 | 5화 무료</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>평점 9.2 | 신형빈 신형빈 | 2019.11.06. | 총219화/완결 | 5화 무료</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="V30" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=2737090</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>2737090</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>사자의서 [도시정벌 레거시] (총 219화/완결)
 평점
@@ -5259,161 +5101,161 @@
 죽음(死)에서 돌아 온 자. 그가 써내려가는 피의 역사에 도시(都市)가 깨어난다.</t>
         </is>
       </c>
-      <c r="Y31" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z31" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA31" t="n">
+      <c r="Y30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA30" t="n">
         <v>100</v>
       </c>
-      <c r="AB31" t="inlineStr">
+      <c r="AB30" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_2</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
+      <c r="AC30" t="inlineStr">
         <is>
           <t>matched</t>
         </is>
       </c>
-      <c r="AD31" t="inlineStr">
+      <c r="AD30" t="inlineStr">
         <is>
           <t>first_non_compilation_numeric_download</t>
         </is>
       </c>
-      <c r="AE31" t="n">
+      <c r="AE30" t="n">
         <v>2</v>
       </c>
-      <c r="AF31" t="inlineStr">
+      <c r="AF30" t="inlineStr">
         <is>
           <t>121.3만</t>
         </is>
       </c>
-      <c r="AG31" t="n">
+      <c r="AG30" t="n">
         <v>1213000</v>
       </c>
-      <c r="AH31" t="inlineStr">
+      <c r="AH30" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="AI31" t="inlineStr">
+      <c r="AI30" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>2026-07-27 13:10:46</t>
+      <c r="AJ30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:36:11</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C32" t="n">
+      <c r="C31" t="n">
         <v>57</v>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>박제</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=846363&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>846363</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>2026-07-27 12:19:59</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="b">
-        <v>1</v>
-      </c>
-      <c r="J32" t="inlineStr">
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2026-08-03 11:56:05</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="b">
+        <v>1</v>
+      </c>
+      <c r="J31" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr">
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="N32" t="n">
+      <c r="N31" t="n">
         <v>2</v>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>박제하는 시간</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>박제하는 시간 (총 28화/완결)</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>총 28화/완결</t>
         </is>
       </c>
-      <c r="R32" t="n">
+      <c r="R31" t="n">
         <v>28</v>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>완결</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>평점 10.0 | 이언 | 2024.07.19. | 총28화/완결 | 5화 무료</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>평점 10.0 | 이언 | 2024.07.19. | 총28화/완결 | 5화 무료</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
+      <c r="V31" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=10632769</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr">
+      <c r="W31" t="inlineStr">
         <is>
           <t>10632769</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>박제하는 시간 (총 28화/완결)
 평점
@@ -5421,161 +5263,161 @@
 박제사 ‘도연’은 죽은 연인의 시체를 빼돌린다.이 과정을 목격한 작가 ‘이명’은 침묵의 대가로 도연의 삶을 소재로 요구해 온다.일주일간의 취재를 허락한 도연. 죽은 연인과 꼭 닮은 이명의 모습에 혼란을 느낀다.숲속의 ..</t>
         </is>
       </c>
-      <c r="Y32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z32" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA32" t="n">
+      <c r="Y31" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA31" t="n">
         <v>100</v>
       </c>
-      <c r="AB32" t="inlineStr">
+      <c r="AB31" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_2</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
+      <c r="AC31" t="inlineStr">
         <is>
           <t>matched</t>
         </is>
       </c>
-      <c r="AD32" t="inlineStr">
+      <c r="AD31" t="inlineStr">
         <is>
           <t>first_non_compilation_numeric_download</t>
         </is>
       </c>
-      <c r="AE32" t="n">
+      <c r="AE31" t="n">
         <v>2</v>
       </c>
-      <c r="AF32" t="inlineStr">
+      <c r="AF31" t="inlineStr">
         <is>
           <t>7.2만</t>
         </is>
       </c>
-      <c r="AG32" t="n">
+      <c r="AG31" t="n">
         <v>72000</v>
       </c>
-      <c r="AH32" t="inlineStr">
+      <c r="AH31" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="AI32" t="inlineStr">
+      <c r="AI31" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>2026-07-27 13:10:46</t>
+      <c r="AJ31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:36:11</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C33" t="n">
-        <v>70</v>
-      </c>
-      <c r="D33" t="inlineStr">
+      <c r="C32" t="n">
+        <v>67</v>
+      </c>
+      <c r="D32" t="inlineStr">
         <is>
           <t>죽여주는 캐스팅</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=843866&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>843866</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>2026-07-27 12:20:00</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="b">
-        <v>1</v>
-      </c>
-      <c r="J33" t="inlineStr">
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2026-08-03 11:56:05</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="b">
+        <v>1</v>
+      </c>
+      <c r="J32" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr">
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="N33" t="n">
-        <v>1</v>
-      </c>
-      <c r="O33" t="inlineStr">
+      <c r="N32" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" t="inlineStr">
         <is>
           <t>죽여주는 캐스팅 [독점]</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>죽여주는 캐스팅 [독점] (총 42화/미완결)</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>총 42화/미완결</t>
         </is>
       </c>
-      <c r="R33" t="n">
+      <c r="R32" t="n">
         <v>42</v>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>평점 9.6 | 영춘 하보 | 2026.06.18. | 총42화/미완결 | 36화 무료</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>평점 9.6 | 영춘 하보 | 2026.06.18. | 총42화/미완결 | 36화 무료</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13253015</t>
         </is>
       </c>
-      <c r="W33" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>13253015</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>죽여주는 캐스팅 [독점] (총 42화/미완결)
 평점
@@ -5583,155 +5425,155 @@
 영화감상 동호회에서 만난 혜수와 강호.성공한 배우를 꿈꾸는 강호는 오디션과 술자리에 몰두하며 혜수에게 기대어 살아간다.그런 강호를 이해하고자 혜수는 연기 수업을 시작하고 점차 자신의 길을 걷기 시작한다.하지만 강..</t>
         </is>
       </c>
-      <c r="Y33" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z33" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA33" t="n">
+      <c r="Y32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA32" t="n">
         <v>105</v>
       </c>
-      <c r="AB33" t="inlineStr">
+      <c r="AB32" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
+      <c r="AC32" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD33" t="inlineStr">
+      <c r="AD32" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF33" t="inlineStr"/>
-      <c r="AG33" t="inlineStr"/>
-      <c r="AH33" t="inlineStr">
+      <c r="AE32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="inlineStr"/>
+      <c r="AH32" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI33" t="inlineStr">
+      <c r="AI32" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>2026-07-27 13:10:46</t>
+      <c r="AJ32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:36:11</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C34" t="n">
-        <v>72</v>
-      </c>
-      <c r="D34" t="inlineStr">
+      <c r="C33" t="n">
+        <v>71</v>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t>사탄의 순애</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=845378&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>845378</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>2026-07-27 12:20:00</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="b">
-        <v>1</v>
-      </c>
-      <c r="J34" t="inlineStr">
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2026-08-03 11:56:06</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="b">
+        <v>1</v>
+      </c>
+      <c r="J33" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr">
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="N34" t="n">
-        <v>1</v>
-      </c>
-      <c r="O34" t="inlineStr">
+      <c r="N33" t="n">
+        <v>1</v>
+      </c>
+      <c r="O33" t="inlineStr">
         <is>
           <t>사탄의 순애 [독점]</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>사탄의 순애 [독점] (총 35화/미완결)</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>총 35화/미완결</t>
         </is>
       </c>
-      <c r="R34" t="n">
+      <c r="R33" t="n">
         <v>35</v>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>평점 9.8 | 용현 카모모 | 2026.06.18. | 총35화/미완결 | 28화 무료</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>평점 9.8 | 용현 카모모 | 2026.06.18. | 총35화/미완결 | 28화 무료</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
+      <c r="V33" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13451638</t>
         </is>
       </c>
-      <c r="W34" t="inlineStr">
+      <c r="W33" t="inlineStr">
         <is>
           <t>13451638</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>사탄의 순애 [독점] (총 35화/미완결)
 평점
@@ -5739,6 +5581,161 @@
 초식동물계 대표주자 호구남 백은우 VS 육식동물계 대표주자 차도녀 범호연.정반대의 두 사람은 어쩌다 사귀게 됐을까?“백은우. 나한테 취업해라. 내 애인인 척 딱 1년. 그럼 10억이야.”업계에서 악마로 소문난 아티스트 레..</t>
         </is>
       </c>
+      <c r="Y33" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>non_compilation_but_download_not_ok</t>
+        </is>
+      </c>
+      <c r="AE33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:36:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>토</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>4</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>만취남녀</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=846883&amp;tab=sat</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>846883</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2026-08-03 11:56:07</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="b">
+        <v>1</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>1</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>19금 만취남녀</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>19금 만취남녀 (총 26화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>총 26화/미완결</t>
+        </is>
+      </c>
+      <c r="R34" t="n">
+        <v>26</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>평점 9.7 | 금 금 | 2026.06.12. | 총26화/미완결 | 21화 무료</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>평점 9.7 | 금 금 | 2026.06.12. | 총26화/미완결 | 21화 무료</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=13646371</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>13646371</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>19금 만취남녀 (총 26화/미완결)
+평점
+9.7 | 금 금 | 2026.06.12. | 총26화/미완결 | 21화 무료</t>
+        </is>
+      </c>
       <c r="Y34" t="b">
         <v>0</v>
       </c>
@@ -5783,7 +5780,7 @@
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>2026-07-27 13:10:46</t>
+          <t>2026-08-03 12:36:11</t>
         </is>
       </c>
     </row>
@@ -5799,26 +5796,26 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>만취남녀</t>
+          <t>시든 꽃에 눈물을</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=846883&amp;tab=sat</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=827190&amp;tab=sat</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>846883</t>
+          <t>827190</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-07-27 12:20:02</t>
+          <t>2026-08-03 11:56:07</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
@@ -5846,21 +5843,21 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>19금 만취남녀</t>
+          <t>시든 꽃에 눈물을</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>19금 만취남녀 (총 26화/미완결)</t>
+          <t>시든 꽃에 눈물을 (총 106화/미완결)</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>총 26화/미완결</t>
+          <t>총 106화/미완결</t>
         </is>
       </c>
       <c r="R35" t="n">
-        <v>26</v>
+        <v>106</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -5869,180 +5866,25 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>평점 9.7 | 금 금 | 2026.06.12. | 총26화/미완결 | 21화 무료</t>
+          <t>평점 9.8 | 개 개 | 2026.06.12. | 총106화/미완결 | 100화 무료</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>평점 9.7 | 금 금 | 2026.06.12. | 총26화/미완결 | 21화 무료</t>
+          <t>평점 9.8 | 개 개 | 2026.06.12. | 총106화/미완결 | 100화 무료</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=13646371</t>
+          <t>https://series.naver.com/comic/detail.series?productNo=11253061</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>13646371</t>
+          <t>11253061</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
-        <is>
-          <t>19금 만취남녀 (총 26화/미완결)
-평점
-9.7 | 금 금 | 2026.06.12. | 총26화/미완결 | 21화 무료</t>
-        </is>
-      </c>
-      <c r="Y35" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z35" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>105</v>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>review_needed</t>
-        </is>
-      </c>
-      <c r="AD35" t="inlineStr">
-        <is>
-          <t>non_compilation_but_download_not_ok</t>
-        </is>
-      </c>
-      <c r="AE35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF35" t="inlineStr"/>
-      <c r="AG35" t="inlineStr"/>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>2026-07-27 13:10:46</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>토</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>5</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>시든 꽃에 눈물을</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=827190&amp;tab=sat</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>827190</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>2026-07-27 12:20:02</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="b">
-        <v>1</v>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="N36" t="n">
-        <v>1</v>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>시든 꽃에 눈물을</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>시든 꽃에 눈물을 (총 106화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>총 106화/미완결</t>
-        </is>
-      </c>
-      <c r="R36" t="n">
-        <v>106</v>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>평점 9.8 | 개 개 | 2026.06.12. | 총106화/미완결 | 100화 무료</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>평점 9.8 | 개 개 | 2026.06.12. | 총106화/미완결 | 100화 무료</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=11253061</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>11253061</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
         <is>
           <t>시든 꽃에 눈물을 (총 106화/미완결)
 평점
@@ -6050,155 +5892,155 @@
 남편이 불륜을 저질렀다. 엄청난 빚을 떠안기고, 아이를 잃게 한 것으로 모자라, 한참 어린 여자와 제 눈앞에서 몸을 섞었다. 상처 입은 삶은 볼품 없이 시들어 버려질 예정이었다. 그런데-, "어른의 사랑을 가르쳐 주세요."나해..</t>
         </is>
       </c>
-      <c r="Y36" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z36" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA36" t="n">
+      <c r="Y35" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA35" t="n">
         <v>105</v>
       </c>
-      <c r="AB36" t="inlineStr">
+      <c r="AB35" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
+      <c r="AC35" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD36" t="inlineStr">
+      <c r="AD35" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE36" t="n">
+      <c r="AE35" t="n">
         <v>4</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
-      <c r="AG36" t="inlineStr"/>
-      <c r="AH36" t="inlineStr">
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI36" t="inlineStr">
+      <c r="AI35" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>2026-07-27 13:10:46</t>
+      <c r="AJ35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:36:11</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>토</t>
         </is>
       </c>
-      <c r="C37" t="n">
+      <c r="C36" t="n">
         <v>10</v>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>둘째에게</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=845711&amp;tab=sat</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>845711</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>2026-07-27 12:20:02</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="b">
-        <v>1</v>
-      </c>
-      <c r="J37" t="inlineStr">
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2026-08-03 11:56:07</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="b">
+        <v>1</v>
+      </c>
+      <c r="J36" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr">
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="N37" t="n">
-        <v>1</v>
-      </c>
-      <c r="O37" t="inlineStr">
+      <c r="N36" t="n">
+        <v>1</v>
+      </c>
+      <c r="O36" t="inlineStr">
         <is>
           <t>둘째에게</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>둘째에게 (총 32화/미완결)</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>총 32화/미완결</t>
         </is>
       </c>
-      <c r="R37" t="n">
+      <c r="R36" t="n">
         <v>32</v>
       </c>
-      <c r="S37" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>평점 10.0 | 고태호 고태호 | 2026.06.12. | 총32화/미완결 | 27화 무료</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>평점 10.0 | 고태호 고태호 | 2026.06.12. | 총32화/미완결 | 27화 무료</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr">
+      <c r="V36" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13512084</t>
         </is>
       </c>
-      <c r="W37" t="inlineStr">
+      <c r="W36" t="inlineStr">
         <is>
           <t>13512084</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>둘째에게 (총 32화/미완결)
 평점
@@ -6206,155 +6048,155 @@
 슬럼프에 시달리고 있는 작가 '이류진'은 자신의 팬이자 조직폭력배 '둘째'와 우연히 엮이게 되고, 슬럼프를 극복하고 싶은 작가와 글쓰는 법을 배우고 싶어하는 조폭은 필요로 인해 서로 교류를 하게 된다.그렇게 교류를 하며 ..</t>
         </is>
       </c>
-      <c r="Y37" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z37" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA37" t="n">
+      <c r="Y36" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA36" t="n">
         <v>105</v>
       </c>
-      <c r="AB37" t="inlineStr">
+      <c r="AB36" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
+      <c r="AC36" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD37" t="inlineStr">
+      <c r="AD36" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF37" t="inlineStr"/>
-      <c r="AG37" t="inlineStr"/>
-      <c r="AH37" t="inlineStr">
+      <c r="AE36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI37" t="inlineStr">
+      <c r="AI36" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>2026-07-27 13:10:46</t>
+      <c r="AJ36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:36:11</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>토</t>
         </is>
       </c>
-      <c r="C38" t="n">
+      <c r="C37" t="n">
         <v>16</v>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>데이워커</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=828880&amp;tab=sat</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>828880</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>2026-07-27 12:20:02</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="b">
-        <v>1</v>
-      </c>
-      <c r="J38" t="inlineStr">
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2026-08-03 11:56:07</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="b">
+        <v>1</v>
+      </c>
+      <c r="J37" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr">
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="N38" t="n">
-        <v>1</v>
-      </c>
-      <c r="O38" t="inlineStr">
+      <c r="N37" t="n">
+        <v>1</v>
+      </c>
+      <c r="O37" t="inlineStr">
         <is>
           <t>데이워커</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>데이워커 (총 94화/미완결)</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>총 94화/미완결</t>
         </is>
       </c>
-      <c r="R38" t="n">
+      <c r="R37" t="n">
         <v>94</v>
       </c>
-      <c r="S38" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr">
+      <c r="T37" t="inlineStr">
         <is>
           <t>평점 9.6 | MUTE MUTE | 2026.06.12. | 총94화/미완결 | 89화 무료</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>평점 9.6 | MUTE MUTE | 2026.06.12. | 총94화/미완결 | 89화 무료</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr">
+      <c r="V37" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=11433164</t>
         </is>
       </c>
-      <c r="W38" t="inlineStr">
+      <c r="W37" t="inlineStr">
         <is>
           <t>11433164</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>데이워커 (총 94화/미완결)
 평점
@@ -6362,155 +6204,155 @@
 국정원 블랙요원 '수혁'은 한국에 약물을 밀매하는 조직 '나나야구미'의 수장 암살 임무를 받는다.그러나 그 수장은 '안나'란 이름의 싸움과는 연관 없을 법한 매력적인 여자였는데... 이 임무 뭔가 이상하다.자신을 배신한 국정..</t>
         </is>
       </c>
-      <c r="Y38" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z38" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA38" t="n">
+      <c r="Y37" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA37" t="n">
         <v>105</v>
       </c>
-      <c r="AB38" t="inlineStr">
+      <c r="AB37" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
+      <c r="AC37" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD38" t="inlineStr">
+      <c r="AD37" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF38" t="inlineStr"/>
-      <c r="AG38" t="inlineStr"/>
-      <c r="AH38" t="inlineStr">
+      <c r="AE37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="inlineStr"/>
+      <c r="AH37" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI38" t="inlineStr">
+      <c r="AI37" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>2026-07-27 13:10:46</t>
+      <c r="AJ37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:36:11</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>토</t>
         </is>
       </c>
-      <c r="C39" t="n">
-        <v>38</v>
-      </c>
-      <c r="D39" t="inlineStr">
+      <c r="C38" t="n">
+        <v>39</v>
+      </c>
+      <c r="D38" t="inlineStr">
         <is>
           <t>연애 못하면 죽음!</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=846662&amp;tab=sat</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>846662</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>2026-07-27 12:20:03</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="b">
-        <v>1</v>
-      </c>
-      <c r="J39" t="inlineStr">
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2026-08-03 11:56:08</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="b">
+        <v>1</v>
+      </c>
+      <c r="J38" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr">
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="N39" t="n">
-        <v>1</v>
-      </c>
-      <c r="O39" t="inlineStr">
+      <c r="N38" t="n">
+        <v>1</v>
+      </c>
+      <c r="O38" t="inlineStr">
         <is>
           <t>연애 못하면 죽음!</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>연애 못하면 죽음! (총 31화/미완결)</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr">
+      <c r="Q38" t="inlineStr">
         <is>
           <t>총 31화/미완결</t>
         </is>
       </c>
-      <c r="R39" t="n">
+      <c r="R38" t="n">
         <v>31</v>
       </c>
-      <c r="S39" t="inlineStr">
+      <c r="S38" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr">
+      <c r="T38" t="inlineStr">
         <is>
           <t>평점 9.8 | 우연희 pusna | 2026.06.12. | 총31화/미완결 | 23화 무료</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="U38" t="inlineStr">
         <is>
           <t>평점 9.8 | 우연희 pusna | 2026.06.12. | 총31화/미완결 | 23화 무료</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr">
+      <c r="V38" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13633976</t>
         </is>
       </c>
-      <c r="W39" t="inlineStr">
+      <c r="W38" t="inlineStr">
         <is>
           <t>13633976</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>연애 못하면 죽음! (총 31화/미완결)
 평점
@@ -6518,155 +6360,155 @@
 똥차들과의 망한 연애로 인해사랑, 연애에 부정적인 30대가 된 워커홀릭 문주경은어느날 우연히 '금방 사랑에 빠지는' 저주에 걸리게 된다.마음에 드는 상대에게 다짜고짜 고백부터 하게 되는 끔찍한 저주.사랑에 빠지기를 거..</t>
         </is>
       </c>
-      <c r="Y39" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA39" t="n">
+      <c r="Y38" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA38" t="n">
         <v>105</v>
       </c>
-      <c r="AB39" t="inlineStr">
+      <c r="AB38" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
+      <c r="AC38" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD39" t="inlineStr">
+      <c r="AD38" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF39" t="inlineStr"/>
-      <c r="AG39" t="inlineStr"/>
-      <c r="AH39" t="inlineStr">
+      <c r="AE38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="inlineStr"/>
+      <c r="AH38" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI39" t="inlineStr">
+      <c r="AI38" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>2026-07-27 13:10:46</t>
+      <c r="AJ38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:36:11</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>토</t>
         </is>
       </c>
-      <c r="C40" t="n">
-        <v>42</v>
-      </c>
-      <c r="D40" t="inlineStr">
+      <c r="C39" t="n">
+        <v>45</v>
+      </c>
+      <c r="D39" t="inlineStr">
         <is>
           <t>데스루프</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=852086&amp;tab=sat</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>852086</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>2026-07-27 12:20:03</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="b">
-        <v>1</v>
-      </c>
-      <c r="J40" t="inlineStr">
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-08-03 11:56:08</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="b">
+        <v>1</v>
+      </c>
+      <c r="J39" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr">
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="N40" t="n">
-        <v>1</v>
-      </c>
-      <c r="O40" t="inlineStr">
+      <c r="N39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O39" t="inlineStr">
         <is>
           <t>데스루프</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>데스루프 (총 6화/미완결)</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr">
+      <c r="Q39" t="inlineStr">
         <is>
           <t>총 6화/미완결</t>
         </is>
       </c>
-      <c r="R40" t="n">
+      <c r="R39" t="n">
         <v>6</v>
       </c>
-      <c r="S40" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr">
+      <c r="T39" t="inlineStr">
         <is>
           <t>평점 8.3 | 은삼 은삼 | 2026.06.26. | 총6화/미완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="U39" t="inlineStr">
         <is>
           <t>평점 8.3 | 은삼 은삼 | 2026.06.26. | 총6화/미완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr">
+      <c r="V39" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14366954</t>
         </is>
       </c>
-      <c r="W40" t="inlineStr">
+      <c r="W39" t="inlineStr">
         <is>
           <t>14366954</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>데스루프 (총 6화/미완결)
 평점
@@ -6674,155 +6516,155 @@
 정신을 차려 보니 지하 창고에 갇힌 주인공 홍연화.연화는 자신을 가둔 남성에게 여러 번 끔찍한 죽음을 맞이하지만, 계속해서 시간이 반복된다.겨우 그곳을 빠져나오지만 그녀 앞에 마주한 것은 끔찍하게 생긴 괴물.과연 그녀..</t>
         </is>
       </c>
-      <c r="Y40" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z40" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA40" t="n">
+      <c r="Y39" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA39" t="n">
         <v>105</v>
       </c>
-      <c r="AB40" t="inlineStr">
+      <c r="AB39" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
+      <c r="AC39" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD40" t="inlineStr">
+      <c r="AD39" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF40" t="inlineStr"/>
-      <c r="AG40" t="inlineStr"/>
-      <c r="AH40" t="inlineStr">
+      <c r="AE39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="inlineStr"/>
+      <c r="AH39" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI40" t="inlineStr">
+      <c r="AI39" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>2026-07-27 13:10:46</t>
+      <c r="AJ39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:36:11</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C41" t="n">
+      <c r="C40" t="n">
         <v>4</v>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>2회차 환관이 남성을 되찾음</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=832566&amp;tab=sun</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>832566</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>2026-07-27 12:20:06</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="b">
-        <v>1</v>
-      </c>
-      <c r="J41" t="inlineStr">
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2026-08-03 11:56:11</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="b">
+        <v>1</v>
+      </c>
+      <c r="J40" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr">
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="N41" t="n">
-        <v>1</v>
-      </c>
-      <c r="O41" t="inlineStr">
+      <c r="N40" t="n">
+        <v>1</v>
+      </c>
+      <c r="O40" t="inlineStr">
         <is>
           <t>2회차 환관이 남성을 되찾음</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>2회차 환관이 남성을 되찾음 (총 93화/미완결)</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="Q40" t="inlineStr">
         <is>
           <t>총 93화/미완결</t>
         </is>
       </c>
-      <c r="R41" t="n">
+      <c r="R40" t="n">
         <v>93</v>
       </c>
-      <c r="S41" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr">
+      <c r="T40" t="inlineStr">
         <is>
           <t>평점 9.6 | LICO, 노빠꾸맨 포스 스튜디오 | 2026.06.13. | 총93화/미완결 | 89화 무료</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="U40" t="inlineStr">
         <is>
           <t>평점 9.6 | LICO, 노빠꾸맨 포스 스튜디오 | 2026.06.13. | 총93화/미완결 | 89화 무료</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr">
+      <c r="V40" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=11636787</t>
         </is>
       </c>
-      <c r="W41" t="inlineStr">
+      <c r="W40" t="inlineStr">
         <is>
           <t>11636787</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>2회차 환관이 남성을 되찾음 (총 93화/미완결)
 평점
@@ -6830,6 +6672,162 @@
 제국의 국정을 마음대로 주무르는 비선실세 환관, 이철수.절대 권력에 돈 많고, 무공까지 강하지만.. 그게 무슨 의미가 있지? '그걸' 못하는데!!환생대법을 통해, 고자가 되기 전으로 회귀한 철수의 목표는 하나다.알파메일이 되..</t>
         </is>
       </c>
+      <c r="Y40" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>non_compilation_but_download_not_ok</t>
+        </is>
+      </c>
+      <c r="AE40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="inlineStr"/>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:36:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>5</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>럭키비치</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=852498&amp;tab=sun</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>852498</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2026-08-03 11:56:11</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="b">
+        <v>1</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>thu,sun</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>thu,sun</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>1</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>럭키비치</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>럭키비치 (총 8화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>총 8화/미완결</t>
+        </is>
+      </c>
+      <c r="R41" t="n">
+        <v>8</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>평점 10.0 | MAJOR, 약수 약수 | 2026.07.18. | 총8화/미완결 | 3화 무료</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>평점 10.0 | MAJOR, 약수 약수 | 2026.07.18. | 총8화/미완결 | 3화 무료</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=14424733</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>14424733</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>럭키비치 (총 8화/미완결)
+평점
+10.0 | MAJOR, 약수 약수 | 2026.07.18. | 총8화/미완결 | 3화 무료
+“그거 알아? 기는 놈 위에 나는 썅X 있는 거?”불우한 환경과 폐쇄적인 바닷가 촌에서 자라온 소녀 '정임'은,그칠줄 모르는 주변의 부조리와 권태 속에서 결국 폭발,퇴폐업을 하는 고모의 불경한 쌈짓돈을 훔쳐 서울로 상경한..</t>
+        </is>
+      </c>
       <c r="Y41" t="b">
         <v>0</v>
       </c>
@@ -6874,7 +6872,7 @@
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>2026-07-27 13:10:46</t>
+          <t>2026-08-03 12:36:11</t>
         </is>
       </c>
     </row>
@@ -6890,7 +6888,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6909,7 +6907,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-07-27 12:20:06</t>
+          <t>2026-08-03 11:56:11</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
@@ -7030,7 +7028,7 @@
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>2026-07-27 13:10:46</t>
+          <t>2026-08-03 12:36:11</t>
         </is>
       </c>
     </row>
@@ -7046,7 +7044,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -7065,7 +7063,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-07-27 12:20:06</t>
+          <t>2026-08-03 11:56:11</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
@@ -7185,7 +7183,7 @@
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>2026-07-27 13:10:46</t>
+          <t>2026-08-03 12:36:11</t>
         </is>
       </c>
     </row>
@@ -7201,26 +7199,26 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>럭키비치</t>
+          <t>서바이브</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=852498&amp;tab=sun</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=838594&amp;tab=sun</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>852498</t>
+          <t>838594</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-07-27 12:20:06</t>
+          <t>2026-08-03 11:56:12</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
@@ -7235,217 +7233,61 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>thu,sun</t>
+          <t>sun</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>thu,sun</t>
+          <t>sun</t>
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>럭키비치</t>
+          <t>연금술 무인도 서바이브</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>럭키비치 (총 8화/미완결)</t>
+          <t>연금술 무인도 서바이브 (총 42화/완결)</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>총 8화/미완결</t>
+          <t>총 42화/완결</t>
         </is>
       </c>
       <c r="R44" t="n">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>미완결</t>
+          <t>완결</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>평점 10.0 | MAJOR, 약수 약수 | 2026.07.18. | 총8화/미완결 | 3화 무료</t>
+          <t>평점 9.9 | 호시 렌지,이구치 콘 호시 렌지 | 2025.02.24. | 총42화/완결 | 1화 무료</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>평점 10.0 | MAJOR, 약수 약수 | 2026.07.18. | 총8화/미완결 | 3화 무료</t>
+          <t>평점 9.9 | 호시 렌지,이구치 콘 호시 렌지 | 2025.02.24. | 총42화/완결 | 1화 무료</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=14424733</t>
+          <t>https://series.naver.com/comic/detail.series?productNo=10375934</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>14424733</t>
+          <t>10375934</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
-        <is>
-          <t>럭키비치 (총 8화/미완결)
-평점
-10.0 | MAJOR, 약수 약수 | 2026.07.18. | 총8화/미완결 | 3화 무료
-“그거 알아? 기는 놈 위에 나는 썅X 있는 거?”불우한 환경과 폐쇄적인 바닷가 촌에서 자라온 소녀 '정임'은,그칠줄 모르는 주변의 부조리와 권태 속에서 결국 폭발,퇴폐업을 하는 고모의 불경한 쌈짓돈을 훔쳐 서울로 상경한..</t>
-        </is>
-      </c>
-      <c r="Y44" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z44" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>105</v>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>review_needed</t>
-        </is>
-      </c>
-      <c r="AD44" t="inlineStr">
-        <is>
-          <t>non_compilation_but_download_not_ok</t>
-        </is>
-      </c>
-      <c r="AE44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF44" t="inlineStr"/>
-      <c r="AG44" t="inlineStr"/>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>2026-07-27 13:10:46</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>44</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>서바이브</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=838594&amp;tab=sun</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>838594</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>2026-07-27 12:20:07</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="b">
-        <v>1</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="N45" t="n">
-        <v>2</v>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>연금술 무인도 서바이브</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>연금술 무인도 서바이브 (총 42화/완결)</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>총 42화/완결</t>
-        </is>
-      </c>
-      <c r="R45" t="n">
-        <v>42</v>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>완결</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>평점 9.9 | 호시 렌지,이구치 콘 호시 렌지 | 2025.02.24. | 총42화/완결 | 1화 무료</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>평점 9.9 | 호시 렌지,이구치 콘 호시 렌지 | 2025.02.24. | 총42화/완결 | 1화 무료</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=10375934</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>10375934</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr">
         <is>
           <t>연금술 무인도 서바이브 (총 42화/완결)
 평점
@@ -7453,161 +7295,161 @@
 항행 중 사고를 당한 연금술사 니코, 요리사 진, 포로남 셋이 표착한 곳은…… 지도에도 표시돼 있지 않은 무인도였다! 「무인도에서 처음으로 해야 할 일은?」, 「물 확보는 어떻게?」, 「식량 수집의 포인트는?」 살아남기 ..</t>
         </is>
       </c>
-      <c r="Y45" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z45" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA45" t="n">
+      <c r="Y44" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z44" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA44" t="n">
         <v>100</v>
       </c>
-      <c r="AB45" t="inlineStr">
+      <c r="AB44" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_2</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
+      <c r="AC44" t="inlineStr">
         <is>
           <t>matched</t>
         </is>
       </c>
-      <c r="AD45" t="inlineStr">
+      <c r="AD44" t="inlineStr">
         <is>
           <t>first_non_compilation_numeric_download</t>
         </is>
       </c>
-      <c r="AE45" t="n">
+      <c r="AE44" t="n">
         <v>2</v>
       </c>
-      <c r="AF45" t="inlineStr">
+      <c r="AF44" t="inlineStr">
         <is>
           <t>5.6천</t>
         </is>
       </c>
-      <c r="AG45" t="n">
+      <c r="AG44" t="n">
         <v>5600</v>
       </c>
-      <c r="AH45" t="inlineStr">
+      <c r="AH44" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="AI45" t="inlineStr">
+      <c r="AI44" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>2026-07-27 13:10:46</t>
+      <c r="AJ44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:36:11</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C46" t="n">
-        <v>47</v>
-      </c>
-      <c r="D46" t="inlineStr">
+      <c r="C45" t="n">
+        <v>46</v>
+      </c>
+      <c r="D45" t="inlineStr">
         <is>
           <t>화스트 페이스</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=847905&amp;tab=sun</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>847905</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>2026-07-27 12:20:07</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="b">
-        <v>1</v>
-      </c>
-      <c r="J46" t="inlineStr">
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-08-03 11:56:12</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="b">
+        <v>1</v>
+      </c>
+      <c r="J45" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr">
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="N46" t="n">
-        <v>1</v>
-      </c>
-      <c r="O46" t="inlineStr">
+      <c r="N45" t="n">
+        <v>1</v>
+      </c>
+      <c r="O45" t="inlineStr">
         <is>
           <t>화스트 페이스</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>화스트 페이스 (총 24화/미완결)</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="Q45" t="inlineStr">
         <is>
           <t>총 24화/미완결</t>
         </is>
       </c>
-      <c r="R46" t="n">
+      <c r="R45" t="n">
         <v>24</v>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="S45" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr">
+      <c r="T45" t="inlineStr">
         <is>
           <t>평점 9.9 | NO_Teamkill NO_Teamkill | 2026.06.13. | 총24화/미완결 | 20화 무료</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="U45" t="inlineStr">
         <is>
           <t>평점 9.9 | NO_Teamkill NO_Teamkill | 2026.06.13. | 총24화/미완결 | 20화 무료</t>
         </is>
       </c>
-      <c r="V46" t="inlineStr">
+      <c r="V45" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13750354</t>
         </is>
       </c>
-      <c r="W46" t="inlineStr">
+      <c r="W45" t="inlineStr">
         <is>
           <t>13750354</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
+      <c r="X45" t="inlineStr">
         <is>
           <t>화스트 페이스 (총 24화/미완결)
 평점
@@ -7615,155 +7457,155 @@
 화스트 페이스! 상황 발생! 상황 발생!현재 적 대규모 도발로 인해 준전시상태 돌입!전 병력 전투 장비 구비하고 즉각 출동 준비할 수 있도록!제1부 화스트페이스!제2부 20XX년 XX월 XX일 21시44분!제3부 발령권자 군단장!..</t>
         </is>
       </c>
-      <c r="Y46" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z46" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA46" t="n">
+      <c r="Y45" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z45" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA45" t="n">
         <v>105</v>
       </c>
-      <c r="AB46" t="inlineStr">
+      <c r="AB45" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
+      <c r="AC45" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD46" t="inlineStr">
+      <c r="AD45" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF46" t="inlineStr"/>
-      <c r="AG46" t="inlineStr"/>
-      <c r="AH46" t="inlineStr">
+      <c r="AE45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="inlineStr"/>
+      <c r="AH45" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI46" t="inlineStr">
+      <c r="AI45" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>2026-07-27 13:10:46</t>
+      <c r="AJ45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:36:11</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C47" t="n">
-        <v>80</v>
-      </c>
-      <c r="D47" t="inlineStr">
+      <c r="C46" t="n">
+        <v>76</v>
+      </c>
+      <c r="D46" t="inlineStr">
         <is>
           <t>나는 참지 못한다</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=823476&amp;tab=sun</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>823476</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>2026-07-27 12:20:08</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="b">
-        <v>1</v>
-      </c>
-      <c r="J47" t="inlineStr">
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-08-03 11:56:13</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="b">
+        <v>1</v>
+      </c>
+      <c r="J46" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr">
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="N47" t="n">
-        <v>1</v>
-      </c>
-      <c r="O47" t="inlineStr">
+      <c r="N46" t="n">
+        <v>1</v>
+      </c>
+      <c r="O46" t="inlineStr">
         <is>
           <t>나는 참지 못한다</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>나는 참지 못한다 (총 115화/미완결)</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="Q46" t="inlineStr">
         <is>
           <t>총 115화/미완결</t>
         </is>
       </c>
-      <c r="R47" t="n">
+      <c r="R46" t="n">
         <v>115</v>
       </c>
-      <c r="S47" t="inlineStr">
+      <c r="S46" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T47" t="inlineStr">
+      <c r="T46" t="inlineStr">
         <is>
           <t>평점 10.0 | 성현 성현 | 2026.06.13. | 총115화/미완결 | 111화 무료</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="U46" t="inlineStr">
         <is>
           <t>평점 10.0 | 성현 성현 | 2026.06.13. | 총115화/미완결 | 111화 무료</t>
         </is>
       </c>
-      <c r="V47" t="inlineStr">
+      <c r="V46" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=10970308</t>
         </is>
       </c>
-      <c r="W47" t="inlineStr">
+      <c r="W46" t="inlineStr">
         <is>
           <t>10970308</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>나는 참지 못한다 (총 115화/미완결)
 평점
@@ -7771,155 +7613,155 @@
 평범한 회사원 김연지는 교통사고 이후 변화를 겪게 된다.스트레스가 폭발하면 아무것도 참지 못하는 상태가 되고 만다.계속 일어나는 통제불능 사건들, 자신에게 접근하는 의문의 남성 민성훈.사건은 커지고 일상은 꼬여만 가..</t>
         </is>
       </c>
-      <c r="Y47" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z47" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA47" t="n">
+      <c r="Y46" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA46" t="n">
         <v>105</v>
       </c>
-      <c r="AB47" t="inlineStr">
+      <c r="AB46" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
+      <c r="AC46" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD47" t="inlineStr">
+      <c r="AD46" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF47" t="inlineStr"/>
-      <c r="AG47" t="inlineStr"/>
-      <c r="AH47" t="inlineStr">
+      <c r="AE46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="inlineStr"/>
+      <c r="AH46" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI47" t="inlineStr">
+      <c r="AI46" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>2026-07-27 13:10:46</t>
+      <c r="AJ46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:36:11</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C48" t="n">
-        <v>81</v>
-      </c>
-      <c r="D48" t="inlineStr">
+      <c r="C47" t="n">
+        <v>79</v>
+      </c>
+      <c r="D47" t="inlineStr">
         <is>
           <t>사내 계약 연애</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=842148&amp;tab=sun</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>842148</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>2026-07-27 12:20:08</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="b">
-        <v>1</v>
-      </c>
-      <c r="J48" t="inlineStr">
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-08-03 11:56:13</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="b">
+        <v>1</v>
+      </c>
+      <c r="J47" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr">
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="N48" t="n">
-        <v>1</v>
-      </c>
-      <c r="O48" t="inlineStr">
+      <c r="N47" t="n">
+        <v>1</v>
+      </c>
+      <c r="O47" t="inlineStr">
         <is>
           <t>사내 계약 연애</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>사내 계약 연애 (총 48화/미완결)</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
+      <c r="Q47" t="inlineStr">
         <is>
           <t>총 48화/미완결</t>
         </is>
       </c>
-      <c r="R48" t="n">
+      <c r="R47" t="n">
         <v>48</v>
       </c>
-      <c r="S48" t="inlineStr">
+      <c r="S47" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr">
+      <c r="T47" t="inlineStr">
         <is>
           <t>평점 9.9 | 최무탁, 미리엄 울 | 2026.06.13. | 총48화/미완결 | 42화 무료</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="U47" t="inlineStr">
         <is>
           <t>평점 9.9 | 최무탁, 미리엄 울 | 2026.06.13. | 총48화/미완결 | 42화 무료</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr">
+      <c r="V47" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13046250</t>
         </is>
       </c>
-      <c r="W48" t="inlineStr">
+      <c r="W47" t="inlineStr">
         <is>
           <t>13046250</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>사내 계약 연애 (총 48화/미완결)
 평점
@@ -7927,161 +7769,161 @@
 예쁘고 잘생긴 것, '미'를 애정하는 서윤.그리고 그런 그녀가 더 애정하는 것은바로 미의 남녀가 서로를 사랑스럽게 탐하는 19금 만화책!그런데 이 미적 추구미에 도달하는 남자가가장 가까이에 그녀의 직속 상사로 있었으니.....</t>
         </is>
       </c>
-      <c r="Y48" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z48" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA48" t="n">
+      <c r="Y47" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z47" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA47" t="n">
         <v>105</v>
       </c>
-      <c r="AB48" t="inlineStr">
+      <c r="AB47" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
+      <c r="AC47" t="inlineStr">
         <is>
           <t>matched</t>
         </is>
       </c>
-      <c r="AD48" t="inlineStr">
+      <c r="AD47" t="inlineStr">
         <is>
           <t>first_non_compilation_numeric_download</t>
         </is>
       </c>
-      <c r="AE48" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF48" t="inlineStr">
+      <c r="AE47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF47" t="inlineStr">
         <is>
           <t>51.5만</t>
         </is>
       </c>
-      <c r="AG48" t="n">
+      <c r="AG47" t="n">
         <v>515000</v>
       </c>
-      <c r="AH48" t="inlineStr">
+      <c r="AH47" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="AI48" t="inlineStr">
+      <c r="AI47" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>2026-07-27 13:10:46</t>
+      <c r="AJ47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:36:11</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C49" t="n">
+      <c r="C48" t="n">
         <v>86</v>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>죽거나 혹은 사랑에 빠지거나</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=819696&amp;tab=sun</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>819696</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>2026-07-27 12:20:08</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="b">
-        <v>1</v>
-      </c>
-      <c r="J49" t="inlineStr">
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026-08-03 11:56:13</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="b">
+        <v>1</v>
+      </c>
+      <c r="J48" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr">
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="N49" t="n">
-        <v>1</v>
-      </c>
-      <c r="O49" t="inlineStr">
+      <c r="N48" t="n">
+        <v>1</v>
+      </c>
+      <c r="O48" t="inlineStr">
         <is>
           <t>죽거나 혹은 사랑에 빠지거나</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>죽거나 혹은 사랑에 빠지거나 (총 128화/미완결)</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="Q48" t="inlineStr">
         <is>
           <t>총 128화/미완결</t>
         </is>
       </c>
-      <c r="R49" t="n">
+      <c r="R48" t="n">
         <v>128</v>
       </c>
-      <c r="S49" t="inlineStr">
+      <c r="S48" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr">
+      <c r="T48" t="inlineStr">
         <is>
           <t>평점 9.8 | 허니비 허니비 | 2026.06.13. | 총128화/미완결 | 122화 무료</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr">
+      <c r="U48" t="inlineStr">
         <is>
           <t>평점 9.8 | 허니비 허니비 | 2026.06.13. | 총128화/미완결 | 122화 무료</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr">
+      <c r="V48" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=10555314</t>
         </is>
       </c>
-      <c r="W49" t="inlineStr">
+      <c r="W48" t="inlineStr">
         <is>
           <t>10555314</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
+      <c r="X48" t="inlineStr">
         <is>
           <t>죽거나 혹은 사랑에 빠지거나 (총 128화/미완결)
 평점
@@ -8089,51 +7931,51 @@
 아름다운 도시 루베른에서 일어나는 의문의 연쇄살인 사건. 조용하고 눈에 띄지 않는 이자벨라에게 살인마의 초대장이 전달되는데.. 목숨을 건 15일간의 내기. 절대 어떤 쾌락과 환상에도 사랑에 빠져서는 안 된다.</t>
         </is>
       </c>
-      <c r="Y49" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z49" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA49" t="n">
+      <c r="Y48" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z48" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA48" t="n">
         <v>105</v>
       </c>
-      <c r="AB49" t="inlineStr">
+      <c r="AB48" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
+      <c r="AC48" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD49" t="inlineStr">
+      <c r="AD48" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE49" t="n">
+      <c r="AE48" t="n">
         <v>2</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
-      <c r="AG49" t="inlineStr"/>
-      <c r="AH49" t="inlineStr">
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="inlineStr"/>
+      <c r="AH48" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI49" t="inlineStr">
+      <c r="AI48" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>2026-07-27 13:10:46</t>
+      <c r="AJ48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:36:11</t>
         </is>
       </c>
     </row>

--- a/data/adult_login_required_webtoons_v2.xlsx
+++ b/data/adult_login_required_webtoons_v2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK48"/>
+  <dimension ref="A1:AK47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -634,7 +634,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-03 11:55:49</t>
+          <t>2026-08-10 10:53:57</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -754,7 +754,7 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2026-08-03 12:36:11</t>
+          <t>2026-08-10 11:38:13</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-03 11:55:50</t>
+          <t>2026-08-10 10:53:59</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -910,7 +910,7 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2026-08-03 12:36:11</t>
+          <t>2026-08-10 11:38:13</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-03 11:55:50</t>
+          <t>2026-08-10 10:53:59</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2026-08-03 12:36:11</t>
+          <t>2026-08-10 11:38:13</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-03 11:55:51</t>
+          <t>2026-08-10 10:53:59</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2026-08-03 12:36:11</t>
+          <t>2026-08-10 11:38:13</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-03 11:55:51</t>
+          <t>2026-08-10 10:54:00</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -1384,42 +1384,42 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2026-08-03 12:36:11</t>
+          <t>2026-08-10 11:38:13</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mon</t>
+          <t>tue</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>월</t>
+          <t>화</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>78</v>
+        <v>3</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>누가 죄인인가</t>
+          <t>오! 나의 교주님</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=846782&amp;tab=mon</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=841624&amp;tab=tue</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>846782</t>
+          <t>841624</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-03 11:55:52</t>
+          <t>2026-08-10 10:54:00</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -1434,12 +1434,12 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>mon</t>
+          <t>tue,fri</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>mon</t>
+          <t>tue,fri</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -1447,21 +1447,21 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>누가 죄인인가</t>
+          <t>오! 나의 교주님</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>누가 죄인인가 (총 31화/미완결)</t>
+          <t>오! 나의 교주님 (총 94화/미완결)</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>총 31화/미완결</t>
+          <t>총 94화/미완결</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>31</v>
+        <v>94</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1470,181 +1470,25 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>평점 10.0 | 이승우 이승우 | 2026.07.26. | 총31화/미완결 | 24화 무료</t>
+          <t>평점 9.4 | 김꿀빨, 김완두 김꿀빨, 김완두 | 2026.06.18. | 총94화/미완결 | 89화 무료</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>평점 10.0 | 이승우 이승우 | 2026.07.26. | 총31화/미완결 | 24화 무료</t>
+          <t>평점 9.4 | 김꿀빨, 김완두 김꿀빨, 김완두 | 2026.06.18. | 총94화/미완결 | 89화 무료</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=13634954</t>
+          <t>https://series.naver.com/comic/detail.series?productNo=12998643</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>13634954</t>
+          <t>12998643</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
-        <is>
-          <t>누가 죄인인가 (총 31화/미완결)
-평점
-10.0 | 이승우 이승우 | 2026.07.26. | 총31화/미완결 | 24화 무료
-"나의 아버지는 악마로 만들어졌다."연쇄살인마 '허욱열'의 딸로서 30년간 지옥 같은 삶을 살아온 일류 청부업자 '허예주' 오늘날 허욱열의 무고가 밝혀지게 되지만 이들은 여전히 지옥 속에 살고 있고 예주는자신과 같이 지옥 ..</t>
-        </is>
-      </c>
-      <c r="Y7" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>105</v>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>review_needed</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>non_compilation_but_download_not_ok</t>
-        </is>
-      </c>
-      <c r="AE7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>2026-08-03 12:36:11</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>tue</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>화</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>3</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>오! 나의 교주님</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=841624&amp;tab=tue</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>841624</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2026-08-03 11:55:53</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="b">
-        <v>1</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>tue,fri</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>tue,fri</t>
-        </is>
-      </c>
-      <c r="N8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>오! 나의 교주님</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>오! 나의 교주님 (총 94화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>총 94화/미완결</t>
-        </is>
-      </c>
-      <c r="R8" t="n">
-        <v>94</v>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>평점 9.4 | 김꿀빨, 김완두 김꿀빨, 김완두 | 2026.06.18. | 총94화/미완결 | 89화 무료</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>평점 9.4 | 김꿀빨, 김완두 김꿀빨, 김완두 | 2026.06.18. | 총94화/미완결 | 89화 무료</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=12998643</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>12998643</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
         <is>
           <t>오! 나의 교주님 (총 94화/미완결)
 평점
@@ -1652,6 +1496,161 @@
 사이비 종교 ‘진천교’에서 태어나 평생을 그곳에서 살아온 한성민. 그는 결국 모든 것을 잃고 홀로 탈출한다.수년 후, 성인이 된 그는 다시 진천교에 잠입해 처절한 복수를 시작하려 한다.“오, 나의 교주님. 제가 보내드릴게..</t>
         </is>
       </c>
+      <c r="Y7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>non_compilation_but_download_not_ok</t>
+        </is>
+      </c>
+      <c r="AE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:38:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>tue</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>화</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>예쁨 컬렉션</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=844519&amp;tab=tue</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>844519</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:54:01</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>tue</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>tue</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>19금 예쁨 컬렉션</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>19금 예쁨 컬렉션 (총 35화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>총 35화/미완결</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>35</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>평점 9.9 | 김이연 김이연 | 2026.06.15. | 총35화/미완결 | 30화 무료</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>평점 9.9 | 김이연 김이연 | 2026.06.15. | 총35화/미완결 | 30화 무료</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=13365963</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>13365963</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>19금 예쁨 컬렉션 (총 35화/미완결)
+평점
+9.9 | 김이연 김이연 | 2026.06.15. | 총35화/미완결 | 30화 무료</t>
+        </is>
+      </c>
       <c r="Y8" t="b">
         <v>0</v>
       </c>
@@ -1696,7 +1695,7 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2026-08-03 12:36:11</t>
+          <t>2026-08-10 11:38:13</t>
         </is>
       </c>
     </row>
@@ -1712,26 +1711,26 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>예쁨 컬렉션</t>
+          <t>포그랜드</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=844519&amp;tab=tue</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=843116&amp;tab=tue</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>844519</t>
+          <t>843116</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-08-03 11:55:53</t>
+          <t>2026-08-10 10:54:01</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -1759,21 +1758,21 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>19금 예쁨 컬렉션</t>
+          <t>포그랜드</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>19금 예쁨 컬렉션 (총 35화/미완결)</t>
+          <t>포그랜드 (총 44화/미완결)</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>총 35화/미완결</t>
+          <t>총 44화/미완결</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1782,180 +1781,25 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>평점 9.9 | 김이연 김이연 | 2026.06.15. | 총35화/미완결 | 30화 무료</t>
+          <t>평점 10.0 | POGO POGO | 2026.06.15. | 총44화/미완결 | 38화 무료</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>평점 9.9 | 김이연 김이연 | 2026.06.15. | 총35화/미완결 | 30화 무료</t>
+          <t>평점 10.0 | POGO POGO | 2026.06.15. | 총44화/미완결 | 38화 무료</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=13365963</t>
+          <t>https://series.naver.com/comic/detail.series?productNo=13177080</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>13365963</t>
+          <t>13177080</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
-        <is>
-          <t>19금 예쁨 컬렉션 (총 35화/미완결)
-평점
-9.9 | 김이연 김이연 | 2026.06.15. | 총35화/미완결 | 30화 무료</t>
-        </is>
-      </c>
-      <c r="Y9" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>105</v>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>review_needed</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>non_compilation_but_download_not_ok</t>
-        </is>
-      </c>
-      <c r="AE9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>2026-08-03 12:36:11</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>tue</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>화</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>8</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>포그랜드</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=843116&amp;tab=tue</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>843116</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>2026-08-03 11:55:53</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="b">
-        <v>1</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>tue</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>tue</t>
-        </is>
-      </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>포그랜드</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>포그랜드 (총 44화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>총 44화/미완결</t>
-        </is>
-      </c>
-      <c r="R10" t="n">
-        <v>44</v>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>평점 10.0 | POGO POGO | 2026.06.15. | 총44화/미완결 | 38화 무료</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>평점 10.0 | POGO POGO | 2026.06.15. | 총44화/미완결 | 38화 무료</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=13177080</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>13177080</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
         <is>
           <t>포그랜드 (총 44화/미완결)
 평점
@@ -1963,155 +1807,155 @@
 존재만으로도 미스터리한 국제 교도소 포그랜드.죄수 교화 목적으로 파견된 과학교사 단테 강은 한순간의 폭동 속에 포그랜드에 갇히게 된다.탈출하는 방법은 영도자가 되는 길 뿐.무너진 이성과 신성을 목도하라!단테의 아홉 ..</t>
         </is>
       </c>
-      <c r="Y10" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA10" t="n">
+      <c r="Y9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA9" t="n">
         <v>105</v>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="inlineStr"/>
-      <c r="AH10" t="inlineStr">
+      <c r="AE9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
+      <c r="AI9" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>2026-08-03 12:36:11</t>
+      <c r="AJ9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:38:13</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C10" t="n">
         <v>22</v>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>분신</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=845407&amp;tab=tue</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>845407</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>2026-08-03 11:55:53</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="b">
-        <v>1</v>
-      </c>
-      <c r="J11" t="inlineStr">
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:54:01</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="N11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" t="inlineStr">
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>분신으로 자동사냥 [독점]</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>분신으로 자동사냥 [독점] (총 176화/완결)</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>총 176화/완결</t>
         </is>
       </c>
-      <c r="R11" t="n">
+      <c r="R10" t="n">
         <v>176</v>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>완결</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>평점 9.7 | 차씨 오팔 | 2025.12.27. | 총176화/완결 | 7화 무료</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>평점 9.7 | 차씨 오팔 | 2025.12.27. | 총176화/완결 | 7화 무료</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=8833786</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>8833786</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>분신으로 자동사냥 [독점] (총 176화/완결)
 평점
@@ -2119,161 +1963,161 @@
 일해야 하고, 공부도 해야 하고, 밥도 먹어야 하고.‘왜 사람은 한 번에 한 가지 일밖에 못 하는 걸까.’상우는 항상 자신의 몸이 두 개였으면 좋겠다고 생각했다...그랬더니 몸이 두 개가 되었다.</t>
         </is>
       </c>
-      <c r="Y11" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA11" t="n">
+      <c r="Y10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA10" t="n">
         <v>105</v>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>matched</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>first_non_compilation_numeric_download</t>
         </is>
       </c>
-      <c r="AE11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF11" t="inlineStr">
+      <c r="AE10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF10" t="inlineStr">
         <is>
           <t>1,022만</t>
         </is>
       </c>
-      <c r="AG11" t="n">
+      <c r="AG10" t="n">
         <v>10220000</v>
       </c>
-      <c r="AH11" t="inlineStr">
+      <c r="AH10" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
+      <c r="AI10" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>2026-08-03 12:36:11</t>
+      <c r="AJ10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:38:13</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>30</v>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C11" t="n">
+        <v>29</v>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>나쁜남자가 돼라!</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=847491&amp;tab=tue</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>847491</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>2026-08-03 11:55:54</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="b">
-        <v>1</v>
-      </c>
-      <c r="J12" t="inlineStr">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:54:01</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J11" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="N12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" t="inlineStr">
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="inlineStr">
         <is>
           <t>나쁜남자가 돼라!</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>나쁜남자가 돼라! (총 28화/미완결)</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>총 28화/미완결</t>
         </is>
       </c>
-      <c r="R12" t="n">
+      <c r="R11" t="n">
         <v>28</v>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>평점 9.9 | 이연 자개 | 2026.06.15. | 총28화/미완결 | 20화 무료</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>평점 9.9 | 이연 자개 | 2026.06.15. | 총28화/미완결 | 20화 무료</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13704125</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>13704125</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>나쁜남자가 돼라! (총 28화/미완결)
 평점
@@ -2281,155 +2125,155 @@
 구남친에 대한 트라우마로 나쁜남자 취향을 가지게 된 수연은 현재의 남자친구에게 약간의 불만을 느끼지만 잘 지내고 있다.그러던 어느 날, 남자친구의 몸에 수연의 취향 그 자체인 '나쁜 남자'가 빙의하는데…이 저주. 풀어줘..</t>
         </is>
       </c>
-      <c r="Y12" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA12" t="n">
+      <c r="Y11" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA11" t="n">
         <v>105</v>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="inlineStr"/>
-      <c r="AH12" t="inlineStr">
+      <c r="AE11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
+      <c r="AI11" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>2026-08-03 12:36:11</t>
+      <c r="AJ11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:38:13</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>45</v>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C12" t="n">
+        <v>48</v>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>화분</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=851671&amp;tab=tue</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>851671</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>2026-08-03 11:55:54</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="b">
-        <v>1</v>
-      </c>
-      <c r="J13" t="inlineStr">
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:54:02</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J12" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="N13" t="n">
-        <v>1</v>
-      </c>
-      <c r="O13" t="inlineStr">
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="inlineStr">
         <is>
           <t>화분</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>화분 (총 5화/미완결)</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>총 5화/미완결</t>
         </is>
       </c>
-      <c r="R13" t="n">
+      <c r="R12" t="n">
         <v>5</v>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>평점 10.0 | 쿼시 쿼시 | 2026.06.15. | 총5화/미완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>평점 10.0 | 쿼시 쿼시 | 2026.06.15. | 총5화/미완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14284647</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>14284647</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>화분 (총 5화/미완결)
 평점
@@ -2437,155 +2281,155 @@
 버림받는 것이 무서운 여자와 그런 그녀가 무섭게 느껴지는 남자. 오래된 인연으로 시작된 사랑은 다정함의 얼굴을 한 집착이 되어, 두 사람의 일상과 마음을 서서히 갉아먹어 간다.우리 사랑은, 어디서부터 잘못된거지..?</t>
         </is>
       </c>
-      <c r="Y13" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA13" t="n">
+      <c r="Y12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA12" t="n">
         <v>105</v>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD13" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="inlineStr"/>
-      <c r="AH13" t="inlineStr">
+      <c r="AE12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI13" t="inlineStr">
+      <c r="AI12" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>2026-08-03 12:36:11</t>
+      <c r="AJ12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:38:13</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>50</v>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="C13" t="n">
+        <v>51</v>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>원수의 아기를 가졌다</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=846110&amp;tab=tue</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>846110</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>2026-08-03 11:55:54</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="b">
-        <v>1</v>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:54:02</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="N14" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" t="inlineStr">
+      <c r="N13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" t="inlineStr">
         <is>
           <t>원수의 아기를 가졌다</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>원수의 아기를 가졌다 (총 30화/미완결)</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>총 30화/미완결</t>
         </is>
       </c>
-      <c r="R14" t="n">
+      <c r="R13" t="n">
         <v>30</v>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>평점 9.7 | 미니바라기, 안지 이삼 | 2026.06.15. | 총30화/미완결 | 25화 무료</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>평점 9.7 | 미니바라기, 안지 이삼 | 2026.06.15. | 총30화/미완결 | 25화 무료</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13567690</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>13567690</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>원수의 아기를 가졌다 (총 30화/미완결)
 평점
@@ -2593,155 +2437,155 @@
 서로를 끔찍하게 혐오하는 두 가문 버몬테와 템네스.클로델은 강제 화해를 위한 희생양이 되어 템네스 공작 카이안의 신부가 된다.“템네스의 환영을 받지 못하는 신부로군. 주제를 알고 제 발로 걸어들어오라지.”오랜 반목을 ..</t>
         </is>
       </c>
-      <c r="Y14" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA14" t="n">
+      <c r="Y13" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA13" t="n">
         <v>105</v>
       </c>
-      <c r="AB14" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD14" t="inlineStr">
+      <c r="AD13" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="inlineStr"/>
-      <c r="AH14" t="inlineStr">
+      <c r="AE13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI14" t="inlineStr">
+      <c r="AI13" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>2026-08-03 12:36:11</t>
+      <c r="AJ13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:38:13</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>76</v>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="C14" t="n">
+        <v>83</v>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>포 더 퀸덤</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=812414&amp;tab=tue</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>812414</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>2026-08-03 11:55:55</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="b">
-        <v>1</v>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:54:03</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="b">
+        <v>1</v>
+      </c>
+      <c r="J14" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="N15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O15" t="inlineStr">
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>포 더 퀸덤</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>포 더 퀸덤 (총 128화/미완결)</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>총 128화/미완결</t>
         </is>
       </c>
-      <c r="R15" t="n">
+      <c r="R14" t="n">
         <v>128</v>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>평점 9.0 | 로즈옹 로즈옹 | 2026.06.15. | 총128화/미완결 | 123화 무료</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>평점 9.0 | 로즈옹 로즈옹 | 2026.06.15. | 총128화/미완결 | 123화 무료</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=9895056</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>9895056</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>포 더 퀸덤 (총 128화/미완결)
 평점
@@ -2749,155 +2593,155 @@
 악마 아벨은 인간 여자 연리에게 사랑하는 형, 카인을 잃고 만다.분노에 가득 차 연리를 찾아간 아벨은 사랑에 빠지는 금총알을 맞게 되면서, 연리에게 끓어오르는 사랑을 느끼게 되는데…그는 과연 형제의 복수를 택할 것인가..</t>
         </is>
       </c>
-      <c r="Y15" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA15" t="n">
+      <c r="Y14" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA14" t="n">
         <v>105</v>
       </c>
-      <c r="AB15" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
+      <c r="AC14" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD15" t="inlineStr">
+      <c r="AD14" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE15" t="n">
+      <c r="AE14" t="n">
         <v>2</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
-      <c r="AG15" t="inlineStr"/>
-      <c r="AH15" t="inlineStr">
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI15" t="inlineStr">
+      <c r="AI14" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>2026-08-03 12:36:11</t>
+      <c r="AJ14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:38:13</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="C16" t="n">
-        <v>7</v>
-      </c>
-      <c r="D16" t="inlineStr">
+      <c r="C15" t="n">
+        <v>6</v>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>싸이코패스 in 무림</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=846109&amp;tab=wed</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>846109</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>2026-08-03 11:55:57</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="b">
-        <v>1</v>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:54:05</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="b">
+        <v>1</v>
+      </c>
+      <c r="J15" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="N16" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" t="inlineStr">
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t>싸이코패스 in 무림[독점]</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>싸이코패스 in 무림[독점] (총 32화/미완결)</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>총 32화/미완결</t>
         </is>
       </c>
-      <c r="R16" t="n">
+      <c r="R15" t="n">
         <v>32</v>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>평점 9.8 | 김언, 곤붕 송범규 | 2026.06.16. | 총32화/미완결 | 26화 무료</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>평점 9.8 | 김언, 곤붕 송범규 | 2026.06.16. | 총32화/미완결 | 26화 무료</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13566546</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>13566546</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>싸이코패스 in 무림[독점] (총 32화/미완결)
 평점
@@ -2905,155 +2749,155 @@
 [진정한 강자들의 세상, 무림 온라인에 오신 걸 환영합니다.]무림에 떨어진 희대의 싸이코패스.음모와 악의가 가득한 무림에 동봉수, 그의 무정한 이빨이 드리운다.</t>
         </is>
       </c>
-      <c r="Y16" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA16" t="n">
+      <c r="Y15" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA15" t="n">
         <v>105</v>
       </c>
-      <c r="AB16" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
+      <c r="AC15" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD16" t="inlineStr">
+      <c r="AD15" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF16" t="inlineStr"/>
-      <c r="AG16" t="inlineStr"/>
-      <c r="AH16" t="inlineStr">
+      <c r="AE15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI16" t="inlineStr">
+      <c r="AI15" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>2026-08-03 12:36:11</t>
+      <c r="AJ15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:38:13</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="C17" t="n">
-        <v>10</v>
-      </c>
-      <c r="D17" t="inlineStr">
+      <c r="C16" t="n">
+        <v>9</v>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>썰:관계주의</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=834033&amp;tab=wed</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>834033</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>2026-08-03 11:55:57</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="b">
-        <v>1</v>
-      </c>
-      <c r="J17" t="inlineStr">
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:54:05</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="b">
+        <v>1</v>
+      </c>
+      <c r="J16" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="inlineStr">
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>썰:관계주의</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>썰:관계주의 (총 87화/미완결)</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>총 87화/미완결</t>
         </is>
       </c>
-      <c r="R17" t="n">
+      <c r="R16" t="n">
         <v>87</v>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>평점 10.0 | 이삼 장버들 | 2026.06.16. | 총87화/미완결 | 83화 무료</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>평점 10.0 | 이삼 장버들 | 2026.06.16. | 총87화/미완결 | 83화 무료</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=11802777</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>11802777</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>썰:관계주의 (총 87화/미완결)
 평점
@@ -3061,155 +2905,155 @@
 여러 상가가 들어서 있는 강남의 유명타워. 이야기는 유명타워의 한 피부과 안내 데스크 직원 강지영으로부터 시작된다. 동료이자 유부남 의사와 만남을 이어가던 지영은 그에게 또 다른 불륜 상대가 있음을 눈치 채는데 그 상..</t>
         </is>
       </c>
-      <c r="Y17" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA17" t="n">
+      <c r="Y16" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA16" t="n">
         <v>105</v>
       </c>
-      <c r="AB17" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
+      <c r="AC16" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD17" t="inlineStr">
+      <c r="AD16" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF17" t="inlineStr"/>
-      <c r="AG17" t="inlineStr"/>
-      <c r="AH17" t="inlineStr">
+      <c r="AE16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI17" t="inlineStr">
+      <c r="AI16" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>2026-08-03 12:36:11</t>
+      <c r="AJ16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:38:13</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="C17" t="n">
         <v>30</v>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>끝장</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=844588&amp;tab=wed</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>844588</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>2026-08-03 11:55:57</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="b">
-        <v>1</v>
-      </c>
-      <c r="J18" t="inlineStr">
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:54:06</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="b">
+        <v>1</v>
+      </c>
+      <c r="J17" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="N18" t="n">
+      <c r="N17" t="n">
         <v>2</v>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>떨어지면 끝장</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>떨어지면 끝장 (총 70화/완결)</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>총 70화/완결</t>
         </is>
       </c>
-      <c r="R18" t="n">
+      <c r="R17" t="n">
         <v>70</v>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>완결</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>평점 9.7 | Keiko Suenobu Keiko Suenobu | 2024.04.12. | 총70화/완결 | 3화 무료</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>평점 9.7 | Keiko Suenobu Keiko Suenobu | 2024.04.12. | 총70화/완결 | 3화 무료</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=6039213</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>6039213</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>떨어지면 끝장 (총 70화/완결)
 평점
@@ -3217,161 +3061,161 @@
 “떨어지면 끝장이야.”그토록 바라던 신축 초고층 아파트에 입주하게 된 주부 아스미.같은 아파트에 거주하며 아이들 유치원도 같은 세 명의 맘 친구가 생긴다.행복 가득한 새로운 생활이 펼쳐지리라 기대했지만, 어떤 인물과..</t>
         </is>
       </c>
-      <c r="Y18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA18" t="n">
+      <c r="Y17" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA17" t="n">
         <v>100</v>
       </c>
-      <c r="AB18" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_2</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
+      <c r="AC17" t="inlineStr">
         <is>
           <t>matched</t>
         </is>
       </c>
-      <c r="AD18" t="inlineStr">
+      <c r="AD17" t="inlineStr">
         <is>
           <t>first_non_compilation_numeric_download</t>
         </is>
       </c>
-      <c r="AE18" t="n">
+      <c r="AE17" t="n">
         <v>2</v>
       </c>
-      <c r="AF18" t="inlineStr">
+      <c r="AF17" t="inlineStr">
         <is>
           <t>3.9만</t>
         </is>
       </c>
-      <c r="AG18" t="n">
+      <c r="AG17" t="n">
         <v>39000</v>
       </c>
-      <c r="AH18" t="inlineStr">
+      <c r="AH17" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="AI18" t="inlineStr">
+      <c r="AI17" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>2026-08-03 12:36:11</t>
+      <c r="AJ17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:38:13</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v>32</v>
-      </c>
-      <c r="D19" t="inlineStr">
+      <c r="C18" t="n">
+        <v>31</v>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>표절의혹</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=846106&amp;tab=wed</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>846106</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>2026-08-03 11:55:57</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="b">
-        <v>1</v>
-      </c>
-      <c r="J19" t="inlineStr">
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:54:06</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="N19" t="n">
-        <v>1</v>
-      </c>
-      <c r="O19" t="inlineStr">
+      <c r="N18" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" t="inlineStr">
         <is>
           <t>표절의혹</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>표절의혹 (총 29화/미완결)</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>총 29화/미완결</t>
         </is>
       </c>
-      <c r="R19" t="n">
+      <c r="R18" t="n">
         <v>29</v>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>평점 9.4 | 김칸비 황영찬 | 2026.06.16. | 총29화/미완결 | 24화 무료</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>평점 9.4 | 김칸비 황영찬 | 2026.06.16. | 총29화/미완결 | 24화 무료</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13575121</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>13575121</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>표절의혹 (총 29화/미완결)
 평점
@@ -3379,155 +3223,155 @@
 살인사건 피해자들의 시신을 예술품처럼 사고파는 인간성을 잃은 자들, 그리고 그런 예술 살인을 저지르는 ‘자학’이라는 연쇄살인마가 세간의 화제가 되고 있다. 한 예술가는 이 상황에 분노해 자학을 추적하기 시작하는데.....</t>
         </is>
       </c>
-      <c r="Y19" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA19" t="n">
+      <c r="Y18" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA18" t="n">
         <v>105</v>
       </c>
-      <c r="AB19" t="inlineStr">
+      <c r="AB18" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
+      <c r="AC18" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD19" t="inlineStr">
+      <c r="AD18" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF19" t="inlineStr"/>
-      <c r="AG19" t="inlineStr"/>
-      <c r="AH19" t="inlineStr">
+      <c r="AE18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI19" t="inlineStr">
+      <c r="AI18" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>2026-08-03 12:36:11</t>
+      <c r="AJ18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:38:13</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="C20" t="n">
-        <v>83</v>
-      </c>
-      <c r="D20" t="inlineStr">
+      <c r="C19" t="n">
+        <v>85</v>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>일곱 번째 의뢰인</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=850210&amp;tab=wed</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>850210</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>2026-08-03 11:55:59</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="b">
-        <v>1</v>
-      </c>
-      <c r="J20" t="inlineStr">
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:54:08</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="b">
+        <v>1</v>
+      </c>
+      <c r="J19" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="N20" t="n">
-        <v>1</v>
-      </c>
-      <c r="O20" t="inlineStr">
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" t="inlineStr">
         <is>
           <t>일곱 번째 의뢰인</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>일곱 번째 의뢰인 (총 14화/미완결)</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>총 14화/미완결</t>
         </is>
       </c>
-      <c r="R20" t="n">
+      <c r="R19" t="n">
         <v>14</v>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>평점 10.0 | 함영서 함영서 | 2026.06.16. | 총14화/미완결 | 9화 무료</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>평점 10.0 | 함영서 함영서 | 2026.06.16. | 총14화/미완결 | 9화 무료</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14102285</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>14102285</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>일곱 번째 의뢰인 (총 14화/미완결)
 평점
@@ -3535,155 +3379,155 @@
 어린 탐정 맥스는 아무도 주목하지 않는 도박 업자의 죽음을 조사하라는 의뢰를 받는다. 의뢰인이 용의자로 지목한 도박 업자의 아내 제인. 맥스는 그녀를 향한 의심과 이끌림 사이에서 갈등하는데. 제인은 결백한가, 살인자인..</t>
         </is>
       </c>
-      <c r="Y20" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA20" t="n">
+      <c r="Y19" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA19" t="n">
         <v>105</v>
       </c>
-      <c r="AB20" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
+      <c r="AC19" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD20" t="inlineStr">
+      <c r="AD19" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF20" t="inlineStr"/>
-      <c r="AG20" t="inlineStr"/>
-      <c r="AH20" t="inlineStr">
+      <c r="AE19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI20" t="inlineStr">
+      <c r="AI19" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>2026-08-03 12:36:11</t>
+      <c r="AJ19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:38:13</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="C20" t="n">
         <v>5</v>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>소꿉친구 컴플렉스</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=822640&amp;tab=thu</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>822640</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>2026-08-03 11:56:00</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="b">
-        <v>1</v>
-      </c>
-      <c r="J21" t="inlineStr">
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:54:09</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="b">
+        <v>1</v>
+      </c>
+      <c r="J20" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="N21" t="n">
-        <v>1</v>
-      </c>
-      <c r="O21" t="inlineStr">
+      <c r="N20" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" t="inlineStr">
         <is>
           <t>소꿉친구 컴플렉스</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>소꿉친구 컴플렉스 (총 80화/미완결)</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>총 80화/미완결</t>
         </is>
       </c>
-      <c r="R21" t="n">
+      <c r="R20" t="n">
         <v>80</v>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>평점 9.8 | 은하이 은하이 | 2026.06.17. | 총80화/미완결 | 76화 무료</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>평점 9.8 | 은하이 은하이 | 2026.06.17. | 총80화/미완결 | 76화 무료</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=10851069</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>10851069</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>소꿉친구 컴플렉스 (총 80화/미완결)
 평점
@@ -3691,155 +3535,155 @@
 20살에 20년지기, 평생을 함께한 소꿉친구 하늘과 민철.그런 소꿉친구의 알고 싶지 않은 은밀한 사정을 알아버렸다?!서로를 이성으로 생각한 적이 결코 없는 두사람이지만,오해가 오해를 낳고 착각이 착각을 낳는 상황들 속에..</t>
         </is>
       </c>
-      <c r="Y21" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA21" t="n">
+      <c r="Y20" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA20" t="n">
         <v>105</v>
       </c>
-      <c r="AB21" t="inlineStr">
+      <c r="AB20" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
+      <c r="AC20" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD21" t="inlineStr">
+      <c r="AD20" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE21" t="n">
+      <c r="AE20" t="n">
         <v>3</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
-      <c r="AG21" t="inlineStr"/>
-      <c r="AH21" t="inlineStr">
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI21" t="inlineStr">
+      <c r="AI20" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>2026-08-03 12:36:11</t>
+      <c r="AJ20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:38:13</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="C22" t="n">
-        <v>11</v>
-      </c>
-      <c r="D22" t="inlineStr">
+      <c r="C21" t="n">
+        <v>9</v>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>럭키비치</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=852498&amp;tab=thu</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>852498</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>2026-08-03 11:56:00</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="b">
-        <v>1</v>
-      </c>
-      <c r="J22" t="inlineStr">
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:54:09</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J21" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
         <is>
           <t>thu,sun</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>thu,sun</t>
         </is>
       </c>
-      <c r="N22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O22" t="inlineStr">
+      <c r="N21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" t="inlineStr">
         <is>
           <t>럭키비치</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>럭키비치 (총 8화/미완결)</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>총 8화/미완결</t>
         </is>
       </c>
-      <c r="R22" t="n">
+      <c r="R21" t="n">
         <v>8</v>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>평점 10.0 | MAJOR, 약수 약수 | 2026.07.18. | 총8화/미완결 | 3화 무료</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>평점 10.0 | MAJOR, 약수 약수 | 2026.07.18. | 총8화/미완결 | 3화 무료</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14424733</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>14424733</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>럭키비치 (총 8화/미완결)
 평점
@@ -3847,155 +3691,155 @@
 “그거 알아? 기는 놈 위에 나는 썅X 있는 거?”불우한 환경과 폐쇄적인 바닷가 촌에서 자라온 소녀 '정임'은,그칠줄 모르는 주변의 부조리와 권태 속에서 결국 폭발,퇴폐업을 하는 고모의 불경한 쌈짓돈을 훔쳐 서울로 상경한..</t>
         </is>
       </c>
-      <c r="Y22" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z22" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA22" t="n">
+      <c r="Y21" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA21" t="n">
         <v>105</v>
       </c>
-      <c r="AB22" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
+      <c r="AC21" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD22" t="inlineStr">
+      <c r="AD21" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF22" t="inlineStr"/>
-      <c r="AG22" t="inlineStr"/>
-      <c r="AH22" t="inlineStr">
+      <c r="AE21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI22" t="inlineStr">
+      <c r="AI21" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>2026-08-03 12:36:11</t>
+      <c r="AJ21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:38:13</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="C22" t="n">
         <v>57</v>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>당신에게 얽힌 채</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=849879&amp;tab=thu</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>849879</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>2026-08-03 11:56:02</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="b">
-        <v>1</v>
-      </c>
-      <c r="J23" t="inlineStr">
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:54:10</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="b">
+        <v>1</v>
+      </c>
+      <c r="J22" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="N23" t="n">
-        <v>1</v>
-      </c>
-      <c r="O23" t="inlineStr">
+      <c r="N22" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" t="inlineStr">
         <is>
           <t>당신에게 얽힌 채</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>당신에게 얽힌 채 (총 10화/미완결)</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>총 10화/미완결</t>
         </is>
       </c>
-      <c r="R23" t="n">
+      <c r="R22" t="n">
         <v>10</v>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>평점 10.0 | Nicole Knight, 유다 danah789 | 2026.06.17. | 총10화/미완결 | 5화 무료</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>평점 10.0 | Nicole Knight, 유다 danah789 | 2026.06.17. | 총10화/미완결 | 5화 무료</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14041685</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>14041685</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>당신에게 얽힌 채 (총 10화/미완결)
 평점
@@ -4003,155 +3847,155 @@
 상속자가 아닌 복종하는 존재로 길러진 에이바 모레티. 뉴욕에서 가장 강력한 마피아 가문의 막내딸인 그녀는 ‘집안의 사고뭉치’라는 오명을 벗고 자신의 자리를 찾기 위해 분투한다.그러던 어느 날 밤, 낯선 남자와 보낸 뜨..</t>
         </is>
       </c>
-      <c r="Y23" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z23" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA23" t="n">
+      <c r="Y22" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA22" t="n">
         <v>105</v>
       </c>
-      <c r="AB23" t="inlineStr">
+      <c r="AB22" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
+      <c r="AC22" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD23" t="inlineStr">
+      <c r="AD22" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF23" t="inlineStr"/>
-      <c r="AG23" t="inlineStr"/>
-      <c r="AH23" t="inlineStr">
+      <c r="AE22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI23" t="inlineStr">
+      <c r="AI22" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>2026-08-03 12:36:11</t>
+      <c r="AJ22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:38:13</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>87</v>
-      </c>
-      <c r="D24" t="inlineStr">
+      <c r="C23" t="n">
+        <v>88</v>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>휴먼 웨어러블</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=845460&amp;tab=thu</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>845460</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>2026-08-03 11:56:03</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="b">
-        <v>1</v>
-      </c>
-      <c r="J24" t="inlineStr">
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:54:11</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="b">
+        <v>1</v>
+      </c>
+      <c r="J23" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="N24" t="n">
-        <v>1</v>
-      </c>
-      <c r="O24" t="inlineStr">
+      <c r="N23" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" t="inlineStr">
         <is>
           <t>휴먼 웨어러블</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>휴먼 웨어러블 (총 30화/미완결)</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>총 30화/미완결</t>
         </is>
       </c>
-      <c r="R24" t="n">
+      <c r="R23" t="n">
         <v>30</v>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>평점 9.9 | 쥬타인 쥬타인 | 2026.06.03. | 총30화/미완결 | 27화 무료</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>평점 9.9 | 쥬타인 쥬타인 | 2026.06.03. | 총30화/미완결 | 27화 무료</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13481722</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>13481722</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>휴먼 웨어러블 (총 30화/미완결)
 평점
@@ -4159,155 +4003,155 @@
 꿈의 무대, 패션 서바이벌 &lt;휴먼 웨어러블&gt;.고아 출신이지만 명문 ‘순백패션예술학교’를 거쳐 올라온 학생들.이 무대에서 인생 역전의 주인공이 탄생한다—…그런데 무언가, 이상하게 흘러가기 시작했다.</t>
         </is>
       </c>
-      <c r="Y24" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z24" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA24" t="n">
+      <c r="Y23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA23" t="n">
         <v>105</v>
       </c>
-      <c r="AB24" t="inlineStr">
+      <c r="AB23" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
+      <c r="AC23" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD24" t="inlineStr">
+      <c r="AD23" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF24" t="inlineStr"/>
-      <c r="AG24" t="inlineStr"/>
-      <c r="AH24" t="inlineStr">
+      <c r="AE23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI24" t="inlineStr">
+      <c r="AI23" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>2026-08-03 12:36:11</t>
+      <c r="AJ23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:38:13</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C25" t="n">
+      <c r="C24" t="n">
         <v>2</v>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>오! 나의 교주님</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=841624&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>841624</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>2026-08-03 11:56:03</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="b">
-        <v>1</v>
-      </c>
-      <c r="J25" t="inlineStr">
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:54:12</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="b">
+        <v>1</v>
+      </c>
+      <c r="J24" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
         <is>
           <t>tue,fri</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>tue,fri</t>
         </is>
       </c>
-      <c r="N25" t="n">
-        <v>1</v>
-      </c>
-      <c r="O25" t="inlineStr">
+      <c r="N24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" t="inlineStr">
         <is>
           <t>오! 나의 교주님</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>오! 나의 교주님 (총 94화/미완결)</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>총 94화/미완결</t>
         </is>
       </c>
-      <c r="R25" t="n">
+      <c r="R24" t="n">
         <v>94</v>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>평점 9.4 | 김꿀빨, 김완두 김꿀빨, 김완두 | 2026.06.18. | 총94화/미완결 | 89화 무료</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>평점 9.4 | 김꿀빨, 김완두 김꿀빨, 김완두 | 2026.06.18. | 총94화/미완결 | 89화 무료</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=12998643</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>12998643</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>오! 나의 교주님 (총 94화/미완결)
 평점
@@ -4315,155 +4159,155 @@
 사이비 종교 ‘진천교’에서 태어나 평생을 그곳에서 살아온 한성민. 그는 결국 모든 것을 잃고 홀로 탈출한다.수년 후, 성인이 된 그는 다시 진천교에 잠입해 처절한 복수를 시작하려 한다.“오, 나의 교주님. 제가 보내드릴게..</t>
         </is>
       </c>
-      <c r="Y25" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA25" t="n">
+      <c r="Y24" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA24" t="n">
         <v>105</v>
       </c>
-      <c r="AB25" t="inlineStr">
+      <c r="AB24" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
+      <c r="AC24" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD25" t="inlineStr">
+      <c r="AD24" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF25" t="inlineStr"/>
-      <c r="AG25" t="inlineStr"/>
-      <c r="AH25" t="inlineStr">
+      <c r="AE24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI25" t="inlineStr">
+      <c r="AI24" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>2026-08-03 12:36:11</t>
+      <c r="AJ24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:38:13</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C26" t="n">
-        <v>8</v>
-      </c>
-      <c r="D26" t="inlineStr">
+      <c r="C25" t="n">
+        <v>9</v>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>두 얼굴</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=845646&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>845646</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>2026-08-03 11:56:04</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="b">
-        <v>1</v>
-      </c>
-      <c r="J26" t="inlineStr">
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:54:12</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="b">
+        <v>1</v>
+      </c>
+      <c r="J25" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="N26" t="n">
-        <v>1</v>
-      </c>
-      <c r="O26" t="inlineStr">
+      <c r="N25" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" t="inlineStr">
         <is>
           <t>두 얼굴의 대표님</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>두 얼굴의 대표님 (총 126화/완결)</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>총 126화/완결</t>
         </is>
       </c>
-      <c r="R26" t="n">
+      <c r="R25" t="n">
         <v>126</v>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>완결</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>평점 6.2 | 1M, KuaiKan, YY 1M, KuaiKan, YY | 2022.10.02. | 총126화/완결 | 3화 무료</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>평점 6.2 | 1M, KuaiKan, YY 1M, KuaiKan, YY | 2022.10.02. | 총126화/완결 | 3화 무료</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=6489984</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>6489984</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>두 얼굴의 대표님 (총 126화/완결)
 평점
@@ -4471,161 +4315,161 @@
 재벌가의 사생아로 태어난 소원은 일찍 엄마를 잃고, 가족들의 멸시 속에서 살아왔다.그러다 언니에게 약혼자까지 뺏기게 되자, 실의에 빠진 소원은 유학을 떠나게 되고, 그곳에서 평범한 남편을 만나 결혼을 하게 된다.1년 후 ..</t>
         </is>
       </c>
-      <c r="Y26" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z26" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA26" t="n">
+      <c r="Y25" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA25" t="n">
         <v>105</v>
       </c>
-      <c r="AB26" t="inlineStr">
+      <c r="AB25" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
+      <c r="AC25" t="inlineStr">
         <is>
           <t>matched</t>
         </is>
       </c>
-      <c r="AD26" t="inlineStr">
+      <c r="AD25" t="inlineStr">
         <is>
           <t>first_non_compilation_numeric_download</t>
         </is>
       </c>
-      <c r="AE26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF26" t="inlineStr">
+      <c r="AE25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF25" t="inlineStr">
         <is>
           <t>157.5만</t>
         </is>
       </c>
-      <c r="AG26" t="n">
+      <c r="AG25" t="n">
         <v>1575000</v>
       </c>
-      <c r="AH26" t="inlineStr">
+      <c r="AH25" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="AI26" t="inlineStr">
+      <c r="AI25" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>2026-08-03 12:36:11</t>
+      <c r="AJ25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:38:13</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C27" t="n">
+      <c r="C26" t="n">
         <v>10</v>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>네가 사는 그 집</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=842465&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>842465</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>2026-08-03 11:56:04</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="b">
-        <v>1</v>
-      </c>
-      <c r="J27" t="inlineStr">
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:54:12</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="b">
+        <v>1</v>
+      </c>
+      <c r="J26" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="N27" t="n">
-        <v>1</v>
-      </c>
-      <c r="O27" t="inlineStr">
+      <c r="N26" t="n">
+        <v>1</v>
+      </c>
+      <c r="O26" t="inlineStr">
         <is>
           <t>네가 사는 그 집</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>네가 사는 그 집 (총 47화/미완결)</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>총 47화/미완결</t>
         </is>
       </c>
-      <c r="R27" t="n">
+      <c r="R26" t="n">
         <v>47</v>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>평점 9.7 | 석우 해바다 | 2026.06.18. | 총47화/미완결 | 41화 무료</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>평점 9.7 | 석우 해바다 | 2026.06.18. | 총47화/미완결 | 41화 무료</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13090391</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>13090391</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>네가 사는 그 집 (총 47화/미완결)
 평점
@@ -4633,155 +4477,155 @@
 찢어지게 가난한 집에서 두 아이를 키우며 힘겹게 살아가던 30대 화린.어느날, 자기 첫사랑이었던 부유한 선배와 결혼해 행복하게 사는 친구와 몸이 바뀐다.하지만 부러워하던 삶을 얻은 기쁨도 잠시,그 집의 추악한 비밀이 드..</t>
         </is>
       </c>
-      <c r="Y27" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA27" t="n">
+      <c r="Y26" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA26" t="n">
         <v>105</v>
       </c>
-      <c r="AB27" t="inlineStr">
+      <c r="AB26" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
+      <c r="AC26" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD27" t="inlineStr">
+      <c r="AD26" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF27" t="inlineStr"/>
-      <c r="AG27" t="inlineStr"/>
-      <c r="AH27" t="inlineStr">
+      <c r="AE26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI27" t="inlineStr">
+      <c r="AI26" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>2026-08-03 12:36:11</t>
+      <c r="AJ26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:38:13</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C28" t="n">
+      <c r="C27" t="n">
         <v>11</v>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>그리디</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=845919&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>845919</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>2026-08-03 11:56:04</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="b">
-        <v>1</v>
-      </c>
-      <c r="J28" t="inlineStr">
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:54:12</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="b">
+        <v>1</v>
+      </c>
+      <c r="J27" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="N28" t="n">
-        <v>1</v>
-      </c>
-      <c r="O28" t="inlineStr">
+      <c r="N27" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" t="inlineStr">
         <is>
           <t>그리디</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>그리디 (총 31화/미완결)</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>총 31화/미완결</t>
         </is>
       </c>
-      <c r="R28" t="n">
+      <c r="R27" t="n">
         <v>31</v>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>평점 9.9 | 영하 랑라리 | 2026.06.18. | 총31화/미완결 | 25화 무료</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>평점 9.9 | 영하 랑라리 | 2026.06.18. | 총31화/미완결 | 25화 무료</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13530624</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>13530624</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>그리디 (총 31화/미완결)
 평점
@@ -4789,155 +4633,155 @@
 파혼했다. 십년지기 친구와 내가 파혼한 남자가 찍힌 청첩장 한 장.한유주는 그걸 끝으로 서른하나에 사랑도 우정도 다 버렸다. 남은 건 칼럼 한 줄에도 이름을 걸 수 없는 5년짜리 패션지 주니어 에디터 신세뿐.일도 사랑도, 마..</t>
         </is>
       </c>
-      <c r="Y28" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z28" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA28" t="n">
+      <c r="Y27" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA27" t="n">
         <v>105</v>
       </c>
-      <c r="AB28" t="inlineStr">
+      <c r="AB27" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
+      <c r="AC27" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD28" t="inlineStr">
+      <c r="AD27" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF28" t="inlineStr"/>
-      <c r="AG28" t="inlineStr"/>
-      <c r="AH28" t="inlineStr">
+      <c r="AE27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI28" t="inlineStr">
+      <c r="AI27" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>2026-08-03 12:36:11</t>
+      <c r="AJ27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:38:13</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C29" t="n">
-        <v>34</v>
-      </c>
-      <c r="D29" t="inlineStr">
+      <c r="C28" t="n">
+        <v>36</v>
+      </c>
+      <c r="D28" t="inlineStr">
         <is>
           <t>로맨스 저주</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=834035&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>834035</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>2026-08-03 11:56:04</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="b">
-        <v>1</v>
-      </c>
-      <c r="J29" t="inlineStr">
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:54:13</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="b">
+        <v>1</v>
+      </c>
+      <c r="J28" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr">
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="N29" t="n">
-        <v>1</v>
-      </c>
-      <c r="O29" t="inlineStr">
+      <c r="N28" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" t="inlineStr">
         <is>
           <t>로맨스 저주</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>로맨스 저주 (총 92화/미완결)</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>총 92화/미완결</t>
         </is>
       </c>
-      <c r="R29" t="n">
+      <c r="R28" t="n">
         <v>92</v>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>평점 9.9 | 다원 다원 | 2026.06.18. | 총92화/미완결 | 85화 무료</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>평점 9.9 | 다원 다원 | 2026.06.18. | 총92화/미완결 | 85화 무료</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=11824393</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>11824393</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>로맨스 저주 (총 92화/미완결)
 평점
@@ -4945,155 +4789,155 @@
 희수는 타인을 저주하는 글을 쓰면 현실이 되는 신비한 노트를 택배로 받는다.심지어 저주를 할 때마다 현금이 나온다!희수는 짝사랑하던 남자 현우를 저주해 자신과의 로맨스를 강요한다.하지만 뜻대로 되지 않고, 일이 꼬여..</t>
         </is>
       </c>
-      <c r="Y29" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA29" t="n">
+      <c r="Y28" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA28" t="n">
         <v>105</v>
       </c>
-      <c r="AB29" t="inlineStr">
+      <c r="AB28" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
+      <c r="AC28" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD29" t="inlineStr">
+      <c r="AD28" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE29" t="n">
+      <c r="AE28" t="n">
         <v>2</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
-      <c r="AG29" t="inlineStr"/>
-      <c r="AH29" t="inlineStr">
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI29" t="inlineStr">
+      <c r="AI28" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>2026-08-03 12:36:11</t>
+      <c r="AJ28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:38:13</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C30" t="n">
+      <c r="C29" t="n">
         <v>41</v>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>사자의 서</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=823737&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>823737</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>2026-08-03 11:56:05</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="b">
-        <v>1</v>
-      </c>
-      <c r="J30" t="inlineStr">
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:54:13</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="b">
+        <v>1</v>
+      </c>
+      <c r="J29" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr">
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="N30" t="n">
+      <c r="N29" t="n">
         <v>2</v>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>사자의서 [도시정벌 레거시]</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>사자의서 [도시정벌 레거시] (총 219화/완결)</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>총 219화/완결</t>
         </is>
       </c>
-      <c r="R30" t="n">
+      <c r="R29" t="n">
         <v>219</v>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>완결</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>평점 9.2 | 신형빈 신형빈 | 2019.11.06. | 총219화/완결 | 5화 무료</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>평점 9.2 | 신형빈 신형빈 | 2019.11.06. | 총219화/완결 | 5화 무료</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=2737090</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>2737090</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>사자의서 [도시정벌 레거시] (총 219화/완결)
 평점
@@ -5101,161 +4945,161 @@
 죽음(死)에서 돌아 온 자. 그가 써내려가는 피의 역사에 도시(都市)가 깨어난다.</t>
         </is>
       </c>
-      <c r="Y30" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA30" t="n">
+      <c r="Y29" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA29" t="n">
         <v>100</v>
       </c>
-      <c r="AB30" t="inlineStr">
+      <c r="AB29" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_2</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
+      <c r="AC29" t="inlineStr">
         <is>
           <t>matched</t>
         </is>
       </c>
-      <c r="AD30" t="inlineStr">
+      <c r="AD29" t="inlineStr">
         <is>
           <t>first_non_compilation_numeric_download</t>
         </is>
       </c>
-      <c r="AE30" t="n">
+      <c r="AE29" t="n">
         <v>2</v>
       </c>
-      <c r="AF30" t="inlineStr">
+      <c r="AF29" t="inlineStr">
         <is>
           <t>121.3만</t>
         </is>
       </c>
-      <c r="AG30" t="n">
+      <c r="AG29" t="n">
         <v>1213000</v>
       </c>
-      <c r="AH30" t="inlineStr">
+      <c r="AH29" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="AI30" t="inlineStr">
+      <c r="AI29" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>2026-08-03 12:36:11</t>
+      <c r="AJ29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:38:13</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C31" t="n">
-        <v>57</v>
-      </c>
-      <c r="D31" t="inlineStr">
+      <c r="C30" t="n">
+        <v>60</v>
+      </c>
+      <c r="D30" t="inlineStr">
         <is>
           <t>박제</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=846363&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>846363</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>2026-08-03 11:56:05</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="b">
-        <v>1</v>
-      </c>
-      <c r="J31" t="inlineStr">
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:54:14</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="b">
+        <v>1</v>
+      </c>
+      <c r="J30" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr">
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="N31" t="n">
+      <c r="N30" t="n">
         <v>2</v>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>박제하는 시간</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>박제하는 시간 (총 28화/완결)</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>총 28화/완결</t>
         </is>
       </c>
-      <c r="R31" t="n">
+      <c r="R30" t="n">
         <v>28</v>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>완결</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>평점 10.0 | 이언 | 2024.07.19. | 총28화/완결 | 5화 무료</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>평점 10.0 | 이언 | 2024.07.19. | 총28화/완결 | 5화 무료</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="V30" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=10632769</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>10632769</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>박제하는 시간 (총 28화/완결)
 평점
@@ -5263,161 +5107,161 @@
 박제사 ‘도연’은 죽은 연인의 시체를 빼돌린다.이 과정을 목격한 작가 ‘이명’은 침묵의 대가로 도연의 삶을 소재로 요구해 온다.일주일간의 취재를 허락한 도연. 죽은 연인과 꼭 닮은 이명의 모습에 혼란을 느낀다.숲속의 ..</t>
         </is>
       </c>
-      <c r="Y31" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z31" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA31" t="n">
+      <c r="Y30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA30" t="n">
         <v>100</v>
       </c>
-      <c r="AB31" t="inlineStr">
+      <c r="AB30" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_2</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
+      <c r="AC30" t="inlineStr">
         <is>
           <t>matched</t>
         </is>
       </c>
-      <c r="AD31" t="inlineStr">
+      <c r="AD30" t="inlineStr">
         <is>
           <t>first_non_compilation_numeric_download</t>
         </is>
       </c>
-      <c r="AE31" t="n">
+      <c r="AE30" t="n">
         <v>2</v>
       </c>
-      <c r="AF31" t="inlineStr">
+      <c r="AF30" t="inlineStr">
         <is>
           <t>7.2만</t>
         </is>
       </c>
-      <c r="AG31" t="n">
+      <c r="AG30" t="n">
         <v>72000</v>
       </c>
-      <c r="AH31" t="inlineStr">
+      <c r="AH30" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="AI31" t="inlineStr">
+      <c r="AI30" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>2026-08-03 12:36:11</t>
+      <c r="AJ30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:38:13</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C32" t="n">
+      <c r="C31" t="n">
         <v>67</v>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>죽여주는 캐스팅</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=843866&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>843866</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>2026-08-03 11:56:05</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="b">
-        <v>1</v>
-      </c>
-      <c r="J32" t="inlineStr">
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:54:14</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="b">
+        <v>1</v>
+      </c>
+      <c r="J31" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr">
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="N32" t="n">
-        <v>1</v>
-      </c>
-      <c r="O32" t="inlineStr">
+      <c r="N31" t="n">
+        <v>1</v>
+      </c>
+      <c r="O31" t="inlineStr">
         <is>
           <t>죽여주는 캐스팅 [독점]</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>죽여주는 캐스팅 [독점] (총 42화/미완결)</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>총 42화/미완결</t>
         </is>
       </c>
-      <c r="R32" t="n">
+      <c r="R31" t="n">
         <v>42</v>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>평점 9.6 | 영춘 하보 | 2026.06.18. | 총42화/미완결 | 36화 무료</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>평점 9.6 | 영춘 하보 | 2026.06.18. | 총42화/미완결 | 36화 무료</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
+      <c r="V31" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13253015</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr">
+      <c r="W31" t="inlineStr">
         <is>
           <t>13253015</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>죽여주는 캐스팅 [독점] (총 42화/미완결)
 평점
@@ -5425,155 +5269,155 @@
 영화감상 동호회에서 만난 혜수와 강호.성공한 배우를 꿈꾸는 강호는 오디션과 술자리에 몰두하며 혜수에게 기대어 살아간다.그런 강호를 이해하고자 혜수는 연기 수업을 시작하고 점차 자신의 길을 걷기 시작한다.하지만 강..</t>
         </is>
       </c>
-      <c r="Y32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z32" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA32" t="n">
+      <c r="Y31" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA31" t="n">
         <v>105</v>
       </c>
-      <c r="AB32" t="inlineStr">
+      <c r="AB31" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
+      <c r="AC31" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD32" t="inlineStr">
+      <c r="AD31" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF32" t="inlineStr"/>
-      <c r="AG32" t="inlineStr"/>
-      <c r="AH32" t="inlineStr">
+      <c r="AE31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
+      <c r="AH31" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI32" t="inlineStr">
+      <c r="AI31" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>2026-08-03 12:36:11</t>
+      <c r="AJ31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:38:13</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C33" t="n">
-        <v>71</v>
-      </c>
-      <c r="D33" t="inlineStr">
+      <c r="C32" t="n">
+        <v>69</v>
+      </c>
+      <c r="D32" t="inlineStr">
         <is>
           <t>사탄의 순애</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=845378&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>845378</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>2026-08-03 11:56:06</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="b">
-        <v>1</v>
-      </c>
-      <c r="J33" t="inlineStr">
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:54:14</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="b">
+        <v>1</v>
+      </c>
+      <c r="J32" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr">
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="N33" t="n">
-        <v>1</v>
-      </c>
-      <c r="O33" t="inlineStr">
+      <c r="N32" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" t="inlineStr">
         <is>
           <t>사탄의 순애 [독점]</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>사탄의 순애 [독점] (총 35화/미완결)</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>총 35화/미완결</t>
         </is>
       </c>
-      <c r="R33" t="n">
+      <c r="R32" t="n">
         <v>35</v>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>평점 9.8 | 용현 카모모 | 2026.06.18. | 총35화/미완결 | 28화 무료</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>평점 9.8 | 용현 카모모 | 2026.06.18. | 총35화/미완결 | 28화 무료</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13451638</t>
         </is>
       </c>
-      <c r="W33" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>13451638</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>사탄의 순애 [독점] (총 35화/미완결)
 평점
@@ -5581,6 +5425,161 @@
 초식동물계 대표주자 호구남 백은우 VS 육식동물계 대표주자 차도녀 범호연.정반대의 두 사람은 어쩌다 사귀게 됐을까?“백은우. 나한테 취업해라. 내 애인인 척 딱 1년. 그럼 10억이야.”업계에서 악마로 소문난 아티스트 레..</t>
         </is>
       </c>
+      <c r="Y32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>non_compilation_but_download_not_ok</t>
+        </is>
+      </c>
+      <c r="AE32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="inlineStr"/>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:38:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>토</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>3</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>만취남녀</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=846883&amp;tab=sat</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>846883</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:54:16</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="b">
+        <v>1</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>1</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>19금 만취남녀</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>19금 만취남녀 (총 26화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>총 26화/미완결</t>
+        </is>
+      </c>
+      <c r="R33" t="n">
+        <v>26</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>평점 9.7 | 금 금 | 2026.06.12. | 총26화/미완결 | 21화 무료</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>평점 9.7 | 금 금 | 2026.06.12. | 총26화/미완결 | 21화 무료</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=13646371</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>13646371</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>19금 만취남녀 (총 26화/미완결)
+평점
+9.7 | 금 금 | 2026.06.12. | 총26화/미완결 | 21화 무료</t>
+        </is>
+      </c>
       <c r="Y33" t="b">
         <v>0</v>
       </c>
@@ -5625,7 +5624,7 @@
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>2026-08-03 12:36:11</t>
+          <t>2026-08-10 11:38:13</t>
         </is>
       </c>
     </row>
@@ -5641,26 +5640,26 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>만취남녀</t>
+          <t>시든 꽃에 눈물을</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=846883&amp;tab=sat</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=827190&amp;tab=sat</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>846883</t>
+          <t>827190</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-08-03 11:56:07</t>
+          <t>2026-08-10 10:54:16</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
@@ -5688,21 +5687,21 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>19금 만취남녀</t>
+          <t>시든 꽃에 눈물을</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>19금 만취남녀 (총 26화/미완결)</t>
+          <t>시든 꽃에 눈물을 (총 106화/미완결)</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>총 26화/미완결</t>
+          <t>총 106화/미완결</t>
         </is>
       </c>
       <c r="R34" t="n">
-        <v>26</v>
+        <v>106</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -5711,180 +5710,25 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>평점 9.7 | 금 금 | 2026.06.12. | 총26화/미완결 | 21화 무료</t>
+          <t>평점 9.8 | 개 개 | 2026.06.12. | 총106화/미완결 | 100화 무료</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>평점 9.7 | 금 금 | 2026.06.12. | 총26화/미완결 | 21화 무료</t>
+          <t>평점 9.8 | 개 개 | 2026.06.12. | 총106화/미완결 | 100화 무료</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=13646371</t>
+          <t>https://series.naver.com/comic/detail.series?productNo=11253061</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>13646371</t>
+          <t>11253061</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
-        <is>
-          <t>19금 만취남녀 (총 26화/미완결)
-평점
-9.7 | 금 금 | 2026.06.12. | 총26화/미완결 | 21화 무료</t>
-        </is>
-      </c>
-      <c r="Y34" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z34" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>105</v>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>review_needed</t>
-        </is>
-      </c>
-      <c r="AD34" t="inlineStr">
-        <is>
-          <t>non_compilation_but_download_not_ok</t>
-        </is>
-      </c>
-      <c r="AE34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF34" t="inlineStr"/>
-      <c r="AG34" t="inlineStr"/>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>2026-08-03 12:36:11</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>토</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>5</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>시든 꽃에 눈물을</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=827190&amp;tab=sat</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>827190</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>2026-08-03 11:56:07</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="b">
-        <v>1</v>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="N35" t="n">
-        <v>1</v>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>시든 꽃에 눈물을</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>시든 꽃에 눈물을 (총 106화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>총 106화/미완결</t>
-        </is>
-      </c>
-      <c r="R35" t="n">
-        <v>106</v>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>평점 9.8 | 개 개 | 2026.06.12. | 총106화/미완결 | 100화 무료</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>평점 9.8 | 개 개 | 2026.06.12. | 총106화/미완결 | 100화 무료</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=11253061</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>11253061</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
         <is>
           <t>시든 꽃에 눈물을 (총 106화/미완결)
 평점
@@ -5892,155 +5736,155 @@
 남편이 불륜을 저질렀다. 엄청난 빚을 떠안기고, 아이를 잃게 한 것으로 모자라, 한참 어린 여자와 제 눈앞에서 몸을 섞었다. 상처 입은 삶은 볼품 없이 시들어 버려질 예정이었다. 그런데-, "어른의 사랑을 가르쳐 주세요."나해..</t>
         </is>
       </c>
-      <c r="Y35" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z35" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA35" t="n">
+      <c r="Y34" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA34" t="n">
         <v>105</v>
       </c>
-      <c r="AB35" t="inlineStr">
+      <c r="AB34" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
+      <c r="AC34" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD35" t="inlineStr">
+      <c r="AD34" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE35" t="n">
+      <c r="AE34" t="n">
         <v>4</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
-      <c r="AG35" t="inlineStr"/>
-      <c r="AH35" t="inlineStr">
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI35" t="inlineStr">
+      <c r="AI34" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>2026-08-03 12:36:11</t>
+      <c r="AJ34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:38:13</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>토</t>
         </is>
       </c>
-      <c r="C36" t="n">
-        <v>10</v>
-      </c>
-      <c r="D36" t="inlineStr">
+      <c r="C35" t="n">
+        <v>9</v>
+      </c>
+      <c r="D35" t="inlineStr">
         <is>
           <t>둘째에게</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=845711&amp;tab=sat</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>845711</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>2026-08-03 11:56:07</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="b">
-        <v>1</v>
-      </c>
-      <c r="J36" t="inlineStr">
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:54:16</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="b">
+        <v>1</v>
+      </c>
+      <c r="J35" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr">
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="N36" t="n">
-        <v>1</v>
-      </c>
-      <c r="O36" t="inlineStr">
+      <c r="N35" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" t="inlineStr">
         <is>
           <t>둘째에게</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>둘째에게 (총 32화/미완결)</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>총 32화/미완결</t>
         </is>
       </c>
-      <c r="R36" t="n">
+      <c r="R35" t="n">
         <v>32</v>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>평점 10.0 | 고태호 고태호 | 2026.06.12. | 총32화/미완결 | 27화 무료</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>평점 10.0 | 고태호 고태호 | 2026.06.12. | 총32화/미완결 | 27화 무료</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr">
+      <c r="V35" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13512084</t>
         </is>
       </c>
-      <c r="W36" t="inlineStr">
+      <c r="W35" t="inlineStr">
         <is>
           <t>13512084</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>둘째에게 (총 32화/미완결)
 평점
@@ -6048,155 +5892,155 @@
 슬럼프에 시달리고 있는 작가 '이류진'은 자신의 팬이자 조직폭력배 '둘째'와 우연히 엮이게 되고, 슬럼프를 극복하고 싶은 작가와 글쓰는 법을 배우고 싶어하는 조폭은 필요로 인해 서로 교류를 하게 된다.그렇게 교류를 하며 ..</t>
         </is>
       </c>
-      <c r="Y36" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z36" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA36" t="n">
+      <c r="Y35" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA35" t="n">
         <v>105</v>
       </c>
-      <c r="AB36" t="inlineStr">
+      <c r="AB35" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
+      <c r="AC35" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD36" t="inlineStr">
+      <c r="AD35" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF36" t="inlineStr"/>
-      <c r="AG36" t="inlineStr"/>
-      <c r="AH36" t="inlineStr">
+      <c r="AE35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI36" t="inlineStr">
+      <c r="AI35" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>2026-08-03 12:36:11</t>
+      <c r="AJ35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:38:13</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>토</t>
         </is>
       </c>
-      <c r="C37" t="n">
-        <v>16</v>
-      </c>
-      <c r="D37" t="inlineStr">
+      <c r="C36" t="n">
+        <v>18</v>
+      </c>
+      <c r="D36" t="inlineStr">
         <is>
           <t>데이워커</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=828880&amp;tab=sat</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>828880</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>2026-08-03 11:56:07</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="b">
-        <v>1</v>
-      </c>
-      <c r="J37" t="inlineStr">
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:54:16</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="b">
+        <v>1</v>
+      </c>
+      <c r="J36" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr">
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="N37" t="n">
-        <v>1</v>
-      </c>
-      <c r="O37" t="inlineStr">
+      <c r="N36" t="n">
+        <v>1</v>
+      </c>
+      <c r="O36" t="inlineStr">
         <is>
           <t>데이워커</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>데이워커 (총 94화/미완결)</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>총 94화/미완결</t>
         </is>
       </c>
-      <c r="R37" t="n">
+      <c r="R36" t="n">
         <v>94</v>
       </c>
-      <c r="S37" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>평점 9.6 | MUTE MUTE | 2026.06.12. | 총94화/미완결 | 89화 무료</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>평점 9.6 | MUTE MUTE | 2026.06.12. | 총94화/미완결 | 89화 무료</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr">
+      <c r="V36" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=11433164</t>
         </is>
       </c>
-      <c r="W37" t="inlineStr">
+      <c r="W36" t="inlineStr">
         <is>
           <t>11433164</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>데이워커 (총 94화/미완결)
 평점
@@ -6204,155 +6048,155 @@
 국정원 블랙요원 '수혁'은 한국에 약물을 밀매하는 조직 '나나야구미'의 수장 암살 임무를 받는다.그러나 그 수장은 '안나'란 이름의 싸움과는 연관 없을 법한 매력적인 여자였는데... 이 임무 뭔가 이상하다.자신을 배신한 국정..</t>
         </is>
       </c>
-      <c r="Y37" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z37" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA37" t="n">
+      <c r="Y36" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA36" t="n">
         <v>105</v>
       </c>
-      <c r="AB37" t="inlineStr">
+      <c r="AB36" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
+      <c r="AC36" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD37" t="inlineStr">
+      <c r="AD36" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF37" t="inlineStr"/>
-      <c r="AG37" t="inlineStr"/>
-      <c r="AH37" t="inlineStr">
+      <c r="AE36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI37" t="inlineStr">
+      <c r="AI36" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>2026-08-03 12:36:11</t>
+      <c r="AJ36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:38:13</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>토</t>
         </is>
       </c>
-      <c r="C38" t="n">
+      <c r="C37" t="n">
         <v>39</v>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>연애 못하면 죽음!</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=846662&amp;tab=sat</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>846662</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>2026-08-03 11:56:08</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="b">
-        <v>1</v>
-      </c>
-      <c r="J38" t="inlineStr">
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:54:17</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="b">
+        <v>1</v>
+      </c>
+      <c r="J37" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr">
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="N38" t="n">
-        <v>1</v>
-      </c>
-      <c r="O38" t="inlineStr">
+      <c r="N37" t="n">
+        <v>1</v>
+      </c>
+      <c r="O37" t="inlineStr">
         <is>
           <t>연애 못하면 죽음!</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>연애 못하면 죽음! (총 31화/미완결)</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>총 31화/미완결</t>
         </is>
       </c>
-      <c r="R38" t="n">
+      <c r="R37" t="n">
         <v>31</v>
       </c>
-      <c r="S38" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr">
+      <c r="T37" t="inlineStr">
         <is>
           <t>평점 9.8 | 우연희 pusna | 2026.06.12. | 총31화/미완결 | 23화 무료</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>평점 9.8 | 우연희 pusna | 2026.06.12. | 총31화/미완결 | 23화 무료</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr">
+      <c r="V37" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13633976</t>
         </is>
       </c>
-      <c r="W38" t="inlineStr">
+      <c r="W37" t="inlineStr">
         <is>
           <t>13633976</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>연애 못하면 죽음! (총 31화/미완결)
 평점
@@ -6360,155 +6204,155 @@
 똥차들과의 망한 연애로 인해사랑, 연애에 부정적인 30대가 된 워커홀릭 문주경은어느날 우연히 '금방 사랑에 빠지는' 저주에 걸리게 된다.마음에 드는 상대에게 다짜고짜 고백부터 하게 되는 끔찍한 저주.사랑에 빠지기를 거..</t>
         </is>
       </c>
-      <c r="Y38" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z38" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA38" t="n">
+      <c r="Y37" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA37" t="n">
         <v>105</v>
       </c>
-      <c r="AB38" t="inlineStr">
+      <c r="AB37" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
+      <c r="AC37" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD38" t="inlineStr">
+      <c r="AD37" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF38" t="inlineStr"/>
-      <c r="AG38" t="inlineStr"/>
-      <c r="AH38" t="inlineStr">
+      <c r="AE37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="inlineStr"/>
+      <c r="AH37" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI38" t="inlineStr">
+      <c r="AI37" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>2026-08-03 12:36:11</t>
+      <c r="AJ37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:38:13</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>토</t>
         </is>
       </c>
-      <c r="C39" t="n">
-        <v>45</v>
-      </c>
-      <c r="D39" t="inlineStr">
+      <c r="C38" t="n">
+        <v>46</v>
+      </c>
+      <c r="D38" t="inlineStr">
         <is>
           <t>데스루프</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=852086&amp;tab=sat</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>852086</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>2026-08-03 11:56:08</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="b">
-        <v>1</v>
-      </c>
-      <c r="J39" t="inlineStr">
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:54:17</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="b">
+        <v>1</v>
+      </c>
+      <c r="J38" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr">
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="N39" t="n">
-        <v>1</v>
-      </c>
-      <c r="O39" t="inlineStr">
+      <c r="N38" t="n">
+        <v>1</v>
+      </c>
+      <c r="O38" t="inlineStr">
         <is>
           <t>데스루프</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>데스루프 (총 6화/미완결)</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr">
+      <c r="Q38" t="inlineStr">
         <is>
           <t>총 6화/미완결</t>
         </is>
       </c>
-      <c r="R39" t="n">
+      <c r="R38" t="n">
         <v>6</v>
       </c>
-      <c r="S39" t="inlineStr">
+      <c r="S38" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr">
+      <c r="T38" t="inlineStr">
         <is>
           <t>평점 8.3 | 은삼 은삼 | 2026.06.26. | 총6화/미완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="U38" t="inlineStr">
         <is>
           <t>평점 8.3 | 은삼 은삼 | 2026.06.26. | 총6화/미완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr">
+      <c r="V38" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14366954</t>
         </is>
       </c>
-      <c r="W39" t="inlineStr">
+      <c r="W38" t="inlineStr">
         <is>
           <t>14366954</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>데스루프 (총 6화/미완결)
 평점
@@ -6516,6 +6360,162 @@
 정신을 차려 보니 지하 창고에 갇힌 주인공 홍연화.연화는 자신을 가둔 남성에게 여러 번 끔찍한 죽음을 맞이하지만, 계속해서 시간이 반복된다.겨우 그곳을 빠져나오지만 그녀 앞에 마주한 것은 끔찍하게 생긴 괴물.과연 그녀..</t>
         </is>
       </c>
+      <c r="Y38" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>non_compilation_but_download_not_ok</t>
+        </is>
+      </c>
+      <c r="AE38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="inlineStr"/>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:38:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>4</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>럭키비치</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=852498&amp;tab=sun</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>852498</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:54:20</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="b">
+        <v>1</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>thu,sun</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>thu,sun</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>럭키비치</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>럭키비치 (총 8화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>총 8화/미완결</t>
+        </is>
+      </c>
+      <c r="R39" t="n">
+        <v>8</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>평점 10.0 | MAJOR, 약수 약수 | 2026.07.18. | 총8화/미완결 | 3화 무료</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>평점 10.0 | MAJOR, 약수 약수 | 2026.07.18. | 총8화/미완결 | 3화 무료</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=14424733</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>14424733</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>럭키비치 (총 8화/미완결)
+평점
+10.0 | MAJOR, 약수 약수 | 2026.07.18. | 총8화/미완결 | 3화 무료
+“그거 알아? 기는 놈 위에 나는 썅X 있는 거?”불우한 환경과 폐쇄적인 바닷가 촌에서 자라온 소녀 '정임'은,그칠줄 모르는 주변의 부조리와 권태 속에서 결국 폭발,퇴폐업을 하는 고모의 불경한 쌈짓돈을 훔쳐 서울로 상경한..</t>
+        </is>
+      </c>
       <c r="Y39" t="b">
         <v>0</v>
       </c>
@@ -6560,7 +6560,7 @@
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>2026-08-03 12:36:11</t>
+          <t>2026-08-10 11:38:13</t>
         </is>
       </c>
     </row>
@@ -6576,7 +6576,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-08-03 11:56:11</t>
+          <t>2026-08-10 10:54:20</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>2026-08-03 12:36:11</t>
+          <t>2026-08-10 11:38:13</t>
         </is>
       </c>
     </row>
@@ -6732,26 +6732,26 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>럭키비치</t>
+          <t>어린 아내와 나쁜 짓</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=852498&amp;tab=sun</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=851385&amp;tab=sun</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>852498</t>
+          <t>851385</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-08-03 11:56:11</t>
+          <t>2026-08-10 10:54:20</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -6766,12 +6766,12 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>thu,sun</t>
+          <t>sun</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>thu,sun</t>
+          <t>sun</t>
         </is>
       </c>
       <c r="N41" t="n">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>럭키비치</t>
+          <t>어린 아내와 나쁜 짓</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>럭키비치 (총 8화/미완결)</t>
+          <t>어린 아내와 나쁜 짓 (총 8화/미완결)</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -6802,181 +6802,25 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>평점 10.0 | MAJOR, 약수 약수 | 2026.07.18. | 총8화/미완결 | 3화 무료</t>
+          <t>평점 9.9 | 이리와, 무멘 83 | 2026.06.13. | 총8화/미완결 | 2화 무료</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>평점 10.0 | MAJOR, 약수 약수 | 2026.07.18. | 총8화/미완결 | 3화 무료</t>
+          <t>평점 9.9 | 이리와, 무멘 83 | 2026.06.13. | 총8화/미완결 | 2화 무료</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=14424733</t>
+          <t>https://series.naver.com/comic/detail.series?productNo=14245757</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>14424733</t>
+          <t>14245757</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
-        <is>
-          <t>럭키비치 (총 8화/미완결)
-평점
-10.0 | MAJOR, 약수 약수 | 2026.07.18. | 총8화/미완결 | 3화 무료
-“그거 알아? 기는 놈 위에 나는 썅X 있는 거?”불우한 환경과 폐쇄적인 바닷가 촌에서 자라온 소녀 '정임'은,그칠줄 모르는 주변의 부조리와 권태 속에서 결국 폭발,퇴폐업을 하는 고모의 불경한 쌈짓돈을 훔쳐 서울로 상경한..</t>
-        </is>
-      </c>
-      <c r="Y41" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z41" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>105</v>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>review_needed</t>
-        </is>
-      </c>
-      <c r="AD41" t="inlineStr">
-        <is>
-          <t>non_compilation_but_download_not_ok</t>
-        </is>
-      </c>
-      <c r="AE41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF41" t="inlineStr"/>
-      <c r="AG41" t="inlineStr"/>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>2026-08-03 12:36:11</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>7</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>어린 아내와 나쁜 짓</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=851385&amp;tab=sun</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>851385</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>2026-08-03 11:56:11</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="b">
-        <v>1</v>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="N42" t="n">
-        <v>1</v>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>어린 아내와 나쁜 짓</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>어린 아내와 나쁜 짓 (총 8화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>총 8화/미완결</t>
-        </is>
-      </c>
-      <c r="R42" t="n">
-        <v>8</v>
-      </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>평점 9.9 | 이리와, 무멘 83 | 2026.06.13. | 총8화/미완결 | 2화 무료</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>평점 9.9 | 이리와, 무멘 83 | 2026.06.13. | 총8화/미완결 | 2화 무료</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=14245757</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>14245757</t>
-        </is>
-      </c>
-      <c r="X42" t="inlineStr">
         <is>
           <t>어린 아내와 나쁜 짓 (총 8화/미완결)
 평점
@@ -6984,6 +6828,161 @@
 절망의 끝에서 나를 구원해준 남자, 범도건.작고 지켜야할 애기님이라며 내 고백을 짓밞았던 그때와는 다르게...이 남자, 남편 역할을 해도 너무 잘한다.낮에는 세상 든든한 보호자이던 그가 밤만 되면 맹수처럼 집착하며 나를 ..</t>
         </is>
       </c>
+      <c r="Y41" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z41" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>non_compilation_but_download_not_ok</t>
+        </is>
+      </c>
+      <c r="AE41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="inlineStr"/>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:38:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>9</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>시루/24/1km</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=850068&amp;tab=sun</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>850068</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:54:20</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="b">
+        <v>1</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>1</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>19금 시루/24/1km</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>19금 시루/24/1km (총 12화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>총 12화/미완결</t>
+        </is>
+      </c>
+      <c r="R42" t="n">
+        <v>12</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>평점 10.0 | 6M 941 | 2026.06.13. | 총12화/미완결 | 7화 무료</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>평점 10.0 | 6M 941 | 2026.06.13. | 총12화/미완결 | 7화 무료</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=14081030</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>14081030</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>19금 시루/24/1km (총 12화/미완결)
+평점
+10.0 | 6M 941 | 2026.06.13. | 총12화/미완결 | 7화 무료</t>
+        </is>
+      </c>
       <c r="Y42" t="b">
         <v>0</v>
       </c>
@@ -7028,7 +7027,7 @@
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>2026-08-03 12:36:11</t>
+          <t>2026-08-10 11:38:13</t>
         </is>
       </c>
     </row>
@@ -7044,26 +7043,26 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>시루/24/1km</t>
+          <t>서바이브</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=850068&amp;tab=sun</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=838594&amp;tab=sun</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>850068</t>
+          <t>838594</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-08-03 11:56:11</t>
+          <t>2026-08-10 10:54:21</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
@@ -7087,207 +7086,52 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>19금 시루/24/1km</t>
+          <t>연금술 무인도 서바이브</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>19금 시루/24/1km (총 12화/미완결)</t>
+          <t>연금술 무인도 서바이브 (총 42화/완결)</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>총 12화/미완결</t>
+          <t>총 42화/완결</t>
         </is>
       </c>
       <c r="R43" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>미완결</t>
+          <t>완결</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>평점 10.0 | 6M 941 | 2026.06.13. | 총12화/미완결 | 7화 무료</t>
+          <t>평점 9.9 | 호시 렌지,이구치 콘 호시 렌지 | 2025.02.24. | 총42화/완결 | 1화 무료</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>평점 10.0 | 6M 941 | 2026.06.13. | 총12화/미완결 | 7화 무료</t>
+          <t>평점 9.9 | 호시 렌지,이구치 콘 호시 렌지 | 2025.02.24. | 총42화/완결 | 1화 무료</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=14081030</t>
+          <t>https://series.naver.com/comic/detail.series?productNo=10375934</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>14081030</t>
+          <t>10375934</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
-        <is>
-          <t>19금 시루/24/1km (총 12화/미완결)
-평점
-10.0 | 6M 941 | 2026.06.13. | 총12화/미완결 | 7화 무료</t>
-        </is>
-      </c>
-      <c r="Y43" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z43" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>105</v>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>review_needed</t>
-        </is>
-      </c>
-      <c r="AD43" t="inlineStr">
-        <is>
-          <t>non_compilation_but_download_not_ok</t>
-        </is>
-      </c>
-      <c r="AE43" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF43" t="inlineStr"/>
-      <c r="AG43" t="inlineStr"/>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>2026-08-03 12:36:11</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>42</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>서바이브</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=838594&amp;tab=sun</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>838594</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>2026-08-03 11:56:12</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="b">
-        <v>1</v>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="N44" t="n">
-        <v>2</v>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>연금술 무인도 서바이브</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>연금술 무인도 서바이브 (총 42화/완결)</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>총 42화/완결</t>
-        </is>
-      </c>
-      <c r="R44" t="n">
-        <v>42</v>
-      </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>완결</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>평점 9.9 | 호시 렌지,이구치 콘 호시 렌지 | 2025.02.24. | 총42화/완결 | 1화 무료</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>평점 9.9 | 호시 렌지,이구치 콘 호시 렌지 | 2025.02.24. | 총42화/완결 | 1화 무료</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=10375934</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>10375934</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
         <is>
           <t>연금술 무인도 서바이브 (총 42화/완결)
 평점
@@ -7295,161 +7139,161 @@
 항행 중 사고를 당한 연금술사 니코, 요리사 진, 포로남 셋이 표착한 곳은…… 지도에도 표시돼 있지 않은 무인도였다! 「무인도에서 처음으로 해야 할 일은?」, 「물 확보는 어떻게?」, 「식량 수집의 포인트는?」 살아남기 ..</t>
         </is>
       </c>
-      <c r="Y44" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z44" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA44" t="n">
+      <c r="Y43" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z43" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA43" t="n">
         <v>100</v>
       </c>
-      <c r="AB44" t="inlineStr">
+      <c r="AB43" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_2</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
+      <c r="AC43" t="inlineStr">
         <is>
           <t>matched</t>
         </is>
       </c>
-      <c r="AD44" t="inlineStr">
+      <c r="AD43" t="inlineStr">
         <is>
           <t>first_non_compilation_numeric_download</t>
         </is>
       </c>
-      <c r="AE44" t="n">
+      <c r="AE43" t="n">
         <v>2</v>
       </c>
-      <c r="AF44" t="inlineStr">
+      <c r="AF43" t="inlineStr">
         <is>
           <t>5.6천</t>
         </is>
       </c>
-      <c r="AG44" t="n">
+      <c r="AG43" t="n">
         <v>5600</v>
       </c>
-      <c r="AH44" t="inlineStr">
+      <c r="AH43" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="AI44" t="inlineStr">
+      <c r="AI43" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>2026-08-03 12:36:11</t>
+      <c r="AJ43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:38:13</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C45" t="n">
-        <v>46</v>
-      </c>
-      <c r="D45" t="inlineStr">
+      <c r="C44" t="n">
+        <v>45</v>
+      </c>
+      <c r="D44" t="inlineStr">
         <is>
           <t>화스트 페이스</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=847905&amp;tab=sun</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>847905</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>2026-08-03 11:56:12</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="b">
-        <v>1</v>
-      </c>
-      <c r="J45" t="inlineStr">
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:54:21</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="b">
+        <v>1</v>
+      </c>
+      <c r="J44" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr">
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="N45" t="n">
-        <v>1</v>
-      </c>
-      <c r="O45" t="inlineStr">
+      <c r="N44" t="n">
+        <v>1</v>
+      </c>
+      <c r="O44" t="inlineStr">
         <is>
           <t>화스트 페이스</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>화스트 페이스 (총 24화/미완결)</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>총 24화/미완결</t>
         </is>
       </c>
-      <c r="R45" t="n">
+      <c r="R44" t="n">
         <v>24</v>
       </c>
-      <c r="S45" t="inlineStr">
+      <c r="S44" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr">
+      <c r="T44" t="inlineStr">
         <is>
           <t>평점 9.9 | NO_Teamkill NO_Teamkill | 2026.06.13. | 총24화/미완결 | 20화 무료</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="U44" t="inlineStr">
         <is>
           <t>평점 9.9 | NO_Teamkill NO_Teamkill | 2026.06.13. | 총24화/미완결 | 20화 무료</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr">
+      <c r="V44" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13750354</t>
         </is>
       </c>
-      <c r="W45" t="inlineStr">
+      <c r="W44" t="inlineStr">
         <is>
           <t>13750354</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>화스트 페이스 (총 24화/미완결)
 평점
@@ -7457,155 +7301,155 @@
 화스트 페이스! 상황 발생! 상황 발생!현재 적 대규모 도발로 인해 준전시상태 돌입!전 병력 전투 장비 구비하고 즉각 출동 준비할 수 있도록!제1부 화스트페이스!제2부 20XX년 XX월 XX일 21시44분!제3부 발령권자 군단장!..</t>
         </is>
       </c>
-      <c r="Y45" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z45" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA45" t="n">
+      <c r="Y44" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z44" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA44" t="n">
         <v>105</v>
       </c>
-      <c r="AB45" t="inlineStr">
+      <c r="AB44" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
+      <c r="AC44" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD45" t="inlineStr">
+      <c r="AD44" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF45" t="inlineStr"/>
-      <c r="AG45" t="inlineStr"/>
-      <c r="AH45" t="inlineStr">
+      <c r="AE44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="inlineStr"/>
+      <c r="AH44" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI45" t="inlineStr">
+      <c r="AI44" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>2026-08-03 12:36:11</t>
+      <c r="AJ44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:38:13</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C46" t="n">
-        <v>76</v>
-      </c>
-      <c r="D46" t="inlineStr">
+      <c r="C45" t="n">
+        <v>75</v>
+      </c>
+      <c r="D45" t="inlineStr">
         <is>
           <t>나는 참지 못한다</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=823476&amp;tab=sun</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>823476</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>2026-08-03 11:56:13</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="b">
-        <v>1</v>
-      </c>
-      <c r="J46" t="inlineStr">
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:54:22</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="b">
+        <v>1</v>
+      </c>
+      <c r="J45" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr">
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="N46" t="n">
-        <v>1</v>
-      </c>
-      <c r="O46" t="inlineStr">
+      <c r="N45" t="n">
+        <v>1</v>
+      </c>
+      <c r="O45" t="inlineStr">
         <is>
           <t>나는 참지 못한다</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>나는 참지 못한다 (총 115화/미완결)</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="Q45" t="inlineStr">
         <is>
           <t>총 115화/미완결</t>
         </is>
       </c>
-      <c r="R46" t="n">
+      <c r="R45" t="n">
         <v>115</v>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="S45" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr">
+      <c r="T45" t="inlineStr">
         <is>
           <t>평점 10.0 | 성현 성현 | 2026.06.13. | 총115화/미완결 | 111화 무료</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="U45" t="inlineStr">
         <is>
           <t>평점 10.0 | 성현 성현 | 2026.06.13. | 총115화/미완결 | 111화 무료</t>
         </is>
       </c>
-      <c r="V46" t="inlineStr">
+      <c r="V45" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=10970308</t>
         </is>
       </c>
-      <c r="W46" t="inlineStr">
+      <c r="W45" t="inlineStr">
         <is>
           <t>10970308</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
+      <c r="X45" t="inlineStr">
         <is>
           <t>나는 참지 못한다 (총 115화/미완결)
 평점
@@ -7613,155 +7457,155 @@
 평범한 회사원 김연지는 교통사고 이후 변화를 겪게 된다.스트레스가 폭발하면 아무것도 참지 못하는 상태가 되고 만다.계속 일어나는 통제불능 사건들, 자신에게 접근하는 의문의 남성 민성훈.사건은 커지고 일상은 꼬여만 가..</t>
         </is>
       </c>
-      <c r="Y46" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z46" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA46" t="n">
+      <c r="Y45" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z45" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA45" t="n">
         <v>105</v>
       </c>
-      <c r="AB46" t="inlineStr">
+      <c r="AB45" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
+      <c r="AC45" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD46" t="inlineStr">
+      <c r="AD45" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF46" t="inlineStr"/>
-      <c r="AG46" t="inlineStr"/>
-      <c r="AH46" t="inlineStr">
+      <c r="AE45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="inlineStr"/>
+      <c r="AH45" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI46" t="inlineStr">
+      <c r="AI45" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>2026-08-03 12:36:11</t>
+      <c r="AJ45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:38:13</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C47" t="n">
-        <v>79</v>
-      </c>
-      <c r="D47" t="inlineStr">
+      <c r="C46" t="n">
+        <v>80</v>
+      </c>
+      <c r="D46" t="inlineStr">
         <is>
           <t>사내 계약 연애</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=842148&amp;tab=sun</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>842148</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>2026-08-03 11:56:13</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="b">
-        <v>1</v>
-      </c>
-      <c r="J47" t="inlineStr">
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:54:22</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="b">
+        <v>1</v>
+      </c>
+      <c r="J46" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr">
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="N47" t="n">
-        <v>1</v>
-      </c>
-      <c r="O47" t="inlineStr">
+      <c r="N46" t="n">
+        <v>1</v>
+      </c>
+      <c r="O46" t="inlineStr">
         <is>
           <t>사내 계약 연애</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>사내 계약 연애 (총 48화/미완결)</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="Q46" t="inlineStr">
         <is>
           <t>총 48화/미완결</t>
         </is>
       </c>
-      <c r="R47" t="n">
+      <c r="R46" t="n">
         <v>48</v>
       </c>
-      <c r="S47" t="inlineStr">
+      <c r="S46" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T47" t="inlineStr">
+      <c r="T46" t="inlineStr">
         <is>
           <t>평점 9.9 | 최무탁, 미리엄 울 | 2026.06.13. | 총48화/미완결 | 42화 무료</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="U46" t="inlineStr">
         <is>
           <t>평점 9.9 | 최무탁, 미리엄 울 | 2026.06.13. | 총48화/미완결 | 42화 무료</t>
         </is>
       </c>
-      <c r="V47" t="inlineStr">
+      <c r="V46" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13046250</t>
         </is>
       </c>
-      <c r="W47" t="inlineStr">
+      <c r="W46" t="inlineStr">
         <is>
           <t>13046250</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>사내 계약 연애 (총 48화/미완결)
 평점
@@ -7769,161 +7613,161 @@
 예쁘고 잘생긴 것, '미'를 애정하는 서윤.그리고 그런 그녀가 더 애정하는 것은바로 미의 남녀가 서로를 사랑스럽게 탐하는 19금 만화책!그런데 이 미적 추구미에 도달하는 남자가가장 가까이에 그녀의 직속 상사로 있었으니.....</t>
         </is>
       </c>
-      <c r="Y47" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z47" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA47" t="n">
+      <c r="Y46" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA46" t="n">
         <v>105</v>
       </c>
-      <c r="AB47" t="inlineStr">
+      <c r="AB46" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
+      <c r="AC46" t="inlineStr">
         <is>
           <t>matched</t>
         </is>
       </c>
-      <c r="AD47" t="inlineStr">
+      <c r="AD46" t="inlineStr">
         <is>
           <t>first_non_compilation_numeric_download</t>
         </is>
       </c>
-      <c r="AE47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF47" t="inlineStr">
+      <c r="AE46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF46" t="inlineStr">
         <is>
           <t>51.5만</t>
         </is>
       </c>
-      <c r="AG47" t="n">
+      <c r="AG46" t="n">
         <v>515000</v>
       </c>
-      <c r="AH47" t="inlineStr">
+      <c r="AH46" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="AI47" t="inlineStr">
+      <c r="AI46" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>2026-08-03 12:36:11</t>
+      <c r="AJ46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:38:13</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C48" t="n">
-        <v>86</v>
-      </c>
-      <c r="D48" t="inlineStr">
+      <c r="C47" t="n">
+        <v>85</v>
+      </c>
+      <c r="D47" t="inlineStr">
         <is>
           <t>죽거나 혹은 사랑에 빠지거나</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=819696&amp;tab=sun</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>819696</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>2026-08-03 11:56:13</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="b">
-        <v>1</v>
-      </c>
-      <c r="J48" t="inlineStr">
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:54:22</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="b">
+        <v>1</v>
+      </c>
+      <c r="J47" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr">
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="N48" t="n">
-        <v>1</v>
-      </c>
-      <c r="O48" t="inlineStr">
+      <c r="N47" t="n">
+        <v>1</v>
+      </c>
+      <c r="O47" t="inlineStr">
         <is>
           <t>죽거나 혹은 사랑에 빠지거나</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>죽거나 혹은 사랑에 빠지거나 (총 128화/미완결)</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
+      <c r="Q47" t="inlineStr">
         <is>
           <t>총 128화/미완결</t>
         </is>
       </c>
-      <c r="R48" t="n">
+      <c r="R47" t="n">
         <v>128</v>
       </c>
-      <c r="S48" t="inlineStr">
+      <c r="S47" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr">
+      <c r="T47" t="inlineStr">
         <is>
           <t>평점 9.8 | 허니비 허니비 | 2026.06.13. | 총128화/미완결 | 122화 무료</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="U47" t="inlineStr">
         <is>
           <t>평점 9.8 | 허니비 허니비 | 2026.06.13. | 총128화/미완결 | 122화 무료</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr">
+      <c r="V47" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=10555314</t>
         </is>
       </c>
-      <c r="W48" t="inlineStr">
+      <c r="W47" t="inlineStr">
         <is>
           <t>10555314</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>죽거나 혹은 사랑에 빠지거나 (총 128화/미완결)
 평점
@@ -7931,51 +7775,51 @@
 아름다운 도시 루베른에서 일어나는 의문의 연쇄살인 사건. 조용하고 눈에 띄지 않는 이자벨라에게 살인마의 초대장이 전달되는데.. 목숨을 건 15일간의 내기. 절대 어떤 쾌락과 환상에도 사랑에 빠져서는 안 된다.</t>
         </is>
       </c>
-      <c r="Y48" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z48" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA48" t="n">
+      <c r="Y47" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z47" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA47" t="n">
         <v>105</v>
       </c>
-      <c r="AB48" t="inlineStr">
+      <c r="AB47" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
+      <c r="AC47" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD48" t="inlineStr">
+      <c r="AD47" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE48" t="n">
+      <c r="AE47" t="n">
         <v>2</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
-      <c r="AG48" t="inlineStr"/>
-      <c r="AH48" t="inlineStr">
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="inlineStr"/>
+      <c r="AH47" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI48" t="inlineStr">
+      <c r="AI47" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>2026-08-03 12:36:11</t>
+      <c r="AJ47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:38:13</t>
         </is>
       </c>
     </row>

--- a/data/adult_login_required_webtoons_v2.xlsx
+++ b/data/adult_login_required_webtoons_v2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK47"/>
+  <dimension ref="A1:AK48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -634,7 +634,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-10 10:53:57</t>
+          <t>2026-08-17 10:20:07</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -754,7 +754,7 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:38:13</t>
+          <t>2026-08-17 11:07:23</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-10 10:53:59</t>
+          <t>2026-08-17 10:20:08</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -910,7 +910,7 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2026-08-10 11:38:13</t>
+          <t>2026-08-17 11:07:23</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-10 10:53:59</t>
+          <t>2026-08-17 10:20:09</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2026-08-10 11:38:13</t>
+          <t>2026-08-17 11:07:23</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-10 10:53:59</t>
+          <t>2026-08-17 10:20:09</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2026-08-10 11:38:13</t>
+          <t>2026-08-17 11:07:23</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-10 10:54:00</t>
+          <t>2026-08-17 10:20:09</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -1384,42 +1384,42 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2026-08-10 11:38:13</t>
+          <t>2026-08-17 11:07:23</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>화</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>81</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>오! 나의 교주님</t>
+          <t>누가 죄인인가</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=841624&amp;tab=tue</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=846782&amp;tab=mon</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>841624</t>
+          <t>846782</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-10 10:54:00</t>
+          <t>2026-08-17 10:20:10</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -1434,61 +1434,217 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>누가 죄인인가</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>누가 죄인인가 (총 34화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>총 34화/미완결</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>34</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>평점 10.0 | 이승우 이승우 | 2026.08.16. | 총34화/미완결 | 27화 무료</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>평점 10.0 | 이승우 이승우 | 2026.08.16. | 총34화/미완결 | 27화 무료</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=13634954</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>13634954</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>누가 죄인인가 (총 34화/미완결)
+평점
+10.0 | 이승우 이승우 | 2026.08.16. | 총34화/미완결 | 27화 무료
+"나의 아버지는 악마로 만들어졌다."연쇄살인마 '허욱열'의 딸로서 30년간 지옥 같은 삶을 살아온 일류 청부업자 '허예주' 오늘날 허욱열의 무고가 밝혀지게 되지만 이들은 여전히 지옥 속에 살고 있고 예주는자신과 같이 지옥 ..</t>
+        </is>
+      </c>
+      <c r="Y7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>non_compilation_but_download_not_ok</t>
+        </is>
+      </c>
+      <c r="AE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>searched_series</t>
+        </is>
+      </c>
+      <c r="AJ7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>2026-08-17 11:07:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>tue</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>화</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>오! 나의 교주님</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=841624&amp;tab=tue</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>841624</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:11</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
           <t>tue,fri</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>tue,fri</t>
         </is>
       </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>오! 나의 교주님</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>오! 나의 교주님 (총 94화/미완결)</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>총 94화/미완결</t>
         </is>
       </c>
-      <c r="R7" t="n">
+      <c r="R8" t="n">
         <v>94</v>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>평점 9.4 | 김꿀빨, 김완두 김꿀빨, 김완두 | 2026.06.18. | 총94화/미완결 | 89화 무료</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>평점 9.4 | 김꿀빨, 김완두 김꿀빨, 김완두 | 2026.06.18. | 총94화/미완결 | 89화 무료</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=12998643</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>12998643</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>오! 나의 교주님 (총 94화/미완결)
 평점
@@ -1496,310 +1652,310 @@
 사이비 종교 ‘진천교’에서 태어나 평생을 그곳에서 살아온 한성민. 그는 결국 모든 것을 잃고 홀로 탈출한다.수년 후, 성인이 된 그는 다시 진천교에 잠입해 처절한 복수를 시작하려 한다.“오, 나의 교주님. 제가 보내드릴게..</t>
         </is>
       </c>
-      <c r="Y7" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA7" t="n">
+      <c r="Y8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA8" t="n">
         <v>105</v>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr">
+      <c r="AE8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>2026-08-10 11:38:13</t>
+      <c r="AJ8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>2026-08-17 11:07:23</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>6</v>
-      </c>
-      <c r="D8" t="inlineStr">
+      <c r="C9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>예쁨 컬렉션</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=844519&amp;tab=tue</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>844519</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2026-08-10 10:54:01</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="b">
-        <v>1</v>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:11</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="N8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>19금 예쁨 컬렉션</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>19금 예쁨 컬렉션 (총 35화/미완결)</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>총 35화/미완결</t>
         </is>
       </c>
-      <c r="R8" t="n">
+      <c r="R9" t="n">
         <v>35</v>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>평점 9.9 | 김이연 김이연 | 2026.06.15. | 총35화/미완결 | 30화 무료</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>평점 9.9 | 김이연 김이연 | 2026.06.15. | 총35화/미완결 | 30화 무료</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13365963</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>13365963</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>19금 예쁨 컬렉션 (총 35화/미완결)
 평점
 9.9 | 김이연 김이연 | 2026.06.15. | 총35화/미완결 | 30화 무료</t>
         </is>
       </c>
-      <c r="Y8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA8" t="n">
+      <c r="Y9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA9" t="n">
         <v>105</v>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="inlineStr">
+      <c r="AE9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AI9" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>2026-08-10 11:38:13</t>
+      <c r="AJ9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>2026-08-17 11:07:23</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C10" t="n">
         <v>8</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>포그랜드</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=843116&amp;tab=tue</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>843116</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>2026-08-10 10:54:01</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="b">
-        <v>1</v>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:12</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>포그랜드</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>포그랜드 (총 44화/미완결)</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>총 44화/미완결</t>
         </is>
       </c>
-      <c r="R9" t="n">
+      <c r="R10" t="n">
         <v>44</v>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>평점 10.0 | POGO POGO | 2026.06.15. | 총44화/미완결 | 38화 무료</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>평점 10.0 | POGO POGO | 2026.06.15. | 총44화/미완결 | 38화 무료</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13177080</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>13177080</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>포그랜드 (총 44화/미완결)
 평점
@@ -1807,155 +1963,155 @@
 존재만으로도 미스터리한 국제 교도소 포그랜드.죄수 교화 목적으로 파견된 과학교사 단테 강은 한순간의 폭동 속에 포그랜드에 갇히게 된다.탈출하는 방법은 영도자가 되는 길 뿐.무너진 이성과 신성을 목도하라!단테의 아홉 ..</t>
         </is>
       </c>
-      <c r="Y9" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA9" t="n">
+      <c r="Y10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA10" t="n">
         <v>105</v>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="inlineStr">
+      <c r="AE10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
+      <c r="AI10" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>2026-08-10 11:38:13</t>
+      <c r="AJ10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>2026-08-17 11:07:23</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>22</v>
-      </c>
-      <c r="D10" t="inlineStr">
+      <c r="C11" t="n">
+        <v>19</v>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>분신</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=845407&amp;tab=tue</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>845407</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>2026-08-10 10:54:01</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="b">
-        <v>1</v>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:12</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J11" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="inlineStr">
         <is>
           <t>분신으로 자동사냥 [독점]</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>분신으로 자동사냥 [독점] (총 176화/완결)</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>총 176화/완결</t>
         </is>
       </c>
-      <c r="R10" t="n">
+      <c r="R11" t="n">
         <v>176</v>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>완결</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>평점 9.7 | 차씨 오팔 | 2025.12.27. | 총176화/완결 | 7화 무료</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>평점 9.7 | 차씨 오팔 | 2025.12.27. | 총176화/완결 | 7화 무료</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=8833786</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>8833786</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>분신으로 자동사냥 [독점] (총 176화/완결)
 평점
@@ -1963,161 +2119,161 @@
 일해야 하고, 공부도 해야 하고, 밥도 먹어야 하고.‘왜 사람은 한 번에 한 가지 일밖에 못 하는 걸까.’상우는 항상 자신의 몸이 두 개였으면 좋겠다고 생각했다...그랬더니 몸이 두 개가 되었다.</t>
         </is>
       </c>
-      <c r="Y10" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA10" t="n">
+      <c r="Y11" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA11" t="n">
         <v>105</v>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>matched</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>first_non_compilation_numeric_download</t>
         </is>
       </c>
-      <c r="AE10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF10" t="inlineStr">
+      <c r="AE11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF11" t="inlineStr">
         <is>
           <t>1,022만</t>
         </is>
       </c>
-      <c r="AG10" t="n">
+      <c r="AG11" t="n">
         <v>10220000</v>
       </c>
-      <c r="AH10" t="inlineStr">
+      <c r="AH11" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
+      <c r="AI11" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>2026-08-10 11:38:13</t>
+      <c r="AJ11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>2026-08-17 11:07:23</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C12" t="n">
         <v>29</v>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>나쁜남자가 돼라!</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=847491&amp;tab=tue</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>847491</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>2026-08-10 10:54:01</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="b">
-        <v>1</v>
-      </c>
-      <c r="J11" t="inlineStr">
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:13</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J12" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="N11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" t="inlineStr">
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="inlineStr">
         <is>
           <t>나쁜남자가 돼라!</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>나쁜남자가 돼라! (총 28화/미완결)</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>총 28화/미완결</t>
         </is>
       </c>
-      <c r="R11" t="n">
+      <c r="R12" t="n">
         <v>28</v>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>평점 9.9 | 이연 자개 | 2026.06.15. | 총28화/미완결 | 20화 무료</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>평점 9.9 | 이연 자개 | 2026.06.15. | 총28화/미완결 | 20화 무료</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13704125</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>13704125</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>나쁜남자가 돼라! (총 28화/미완결)
 평점
@@ -2125,155 +2281,155 @@
 구남친에 대한 트라우마로 나쁜남자 취향을 가지게 된 수연은 현재의 남자친구에게 약간의 불만을 느끼지만 잘 지내고 있다.그러던 어느 날, 남자친구의 몸에 수연의 취향 그 자체인 '나쁜 남자'가 빙의하는데…이 저주. 풀어줘..</t>
         </is>
       </c>
-      <c r="Y11" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA11" t="n">
+      <c r="Y12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA12" t="n">
         <v>105</v>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF11" t="inlineStr"/>
-      <c r="AG11" t="inlineStr"/>
-      <c r="AH11" t="inlineStr">
+      <c r="AE12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
+      <c r="AI12" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>2026-08-10 11:38:13</t>
+      <c r="AJ12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>2026-08-17 11:07:23</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>48</v>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="n">
+        <v>49</v>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>화분</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=851671&amp;tab=tue</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>851671</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>2026-08-10 10:54:02</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="b">
-        <v>1</v>
-      </c>
-      <c r="J12" t="inlineStr">
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:13</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="N12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" t="inlineStr">
+      <c r="N13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" t="inlineStr">
         <is>
           <t>화분</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>화분 (총 5화/미완결)</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>총 5화/미완결</t>
         </is>
       </c>
-      <c r="R12" t="n">
+      <c r="R13" t="n">
         <v>5</v>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>평점 10.0 | 쿼시 쿼시 | 2026.06.15. | 총5화/미완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>평점 10.0 | 쿼시 쿼시 | 2026.06.15. | 총5화/미완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14284647</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>14284647</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>화분 (총 5화/미완결)
 평점
@@ -2281,155 +2437,155 @@
 버림받는 것이 무서운 여자와 그런 그녀가 무섭게 느껴지는 남자. 오래된 인연으로 시작된 사랑은 다정함의 얼굴을 한 집착이 되어, 두 사람의 일상과 마음을 서서히 갉아먹어 간다.우리 사랑은, 어디서부터 잘못된거지..?</t>
         </is>
       </c>
-      <c r="Y12" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA12" t="n">
+      <c r="Y13" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA13" t="n">
         <v>105</v>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AD13" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="inlineStr"/>
-      <c r="AH12" t="inlineStr">
+      <c r="AE13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
+      <c r="AI13" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>2026-08-10 11:38:13</t>
+      <c r="AJ13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>2026-08-17 11:07:23</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>51</v>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C14" t="n">
+        <v>50</v>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>원수의 아기를 가졌다</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=846110&amp;tab=tue</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>846110</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>2026-08-10 10:54:02</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="b">
-        <v>1</v>
-      </c>
-      <c r="J13" t="inlineStr">
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:13</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="b">
+        <v>1</v>
+      </c>
+      <c r="J14" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="N13" t="n">
-        <v>1</v>
-      </c>
-      <c r="O13" t="inlineStr">
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>원수의 아기를 가졌다</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>원수의 아기를 가졌다 (총 30화/미완결)</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>총 30화/미완결</t>
         </is>
       </c>
-      <c r="R13" t="n">
+      <c r="R14" t="n">
         <v>30</v>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>평점 9.7 | 미니바라기, 안지 이삼 | 2026.06.15. | 총30화/미완결 | 25화 무료</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>평점 9.7 | 미니바라기, 안지 이삼 | 2026.06.15. | 총30화/미완결 | 25화 무료</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13567690</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>13567690</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>원수의 아기를 가졌다 (총 30화/미완결)
 평점
@@ -2437,155 +2593,155 @@
 서로를 끔찍하게 혐오하는 두 가문 버몬테와 템네스.클로델은 강제 화해를 위한 희생양이 되어 템네스 공작 카이안의 신부가 된다.“템네스의 환영을 받지 못하는 신부로군. 주제를 알고 제 발로 걸어들어오라지.”오랜 반목을 ..</t>
         </is>
       </c>
-      <c r="Y13" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA13" t="n">
+      <c r="Y14" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA14" t="n">
         <v>105</v>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
+      <c r="AC14" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD13" t="inlineStr">
+      <c r="AD14" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="inlineStr"/>
-      <c r="AH13" t="inlineStr">
+      <c r="AE14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI13" t="inlineStr">
+      <c r="AI14" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>2026-08-10 11:38:13</t>
+      <c r="AJ14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>2026-08-17 11:07:23</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>83</v>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="C15" t="n">
+        <v>81</v>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>포 더 퀸덤</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=812414&amp;tab=tue</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>812414</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>2026-08-10 10:54:03</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="b">
-        <v>1</v>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:14</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="b">
+        <v>1</v>
+      </c>
+      <c r="J15" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="N14" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" t="inlineStr">
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t>포 더 퀸덤</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>포 더 퀸덤 (총 128화/미완결)</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>총 128화/미완결</t>
         </is>
       </c>
-      <c r="R14" t="n">
+      <c r="R15" t="n">
         <v>128</v>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>평점 9.0 | 로즈옹 로즈옹 | 2026.06.15. | 총128화/미완결 | 123화 무료</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>평점 9.0 | 로즈옹 로즈옹 | 2026.06.15. | 총128화/미완결 | 123화 무료</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=9895056</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>9895056</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>포 더 퀸덤 (총 128화/미완결)
 평점
@@ -2593,155 +2749,155 @@
 악마 아벨은 인간 여자 연리에게 사랑하는 형, 카인을 잃고 만다.분노에 가득 차 연리를 찾아간 아벨은 사랑에 빠지는 금총알을 맞게 되면서, 연리에게 끓어오르는 사랑을 느끼게 되는데…그는 과연 형제의 복수를 택할 것인가..</t>
         </is>
       </c>
-      <c r="Y14" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA14" t="n">
+      <c r="Y15" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA15" t="n">
         <v>105</v>
       </c>
-      <c r="AB14" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
+      <c r="AC15" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD14" t="inlineStr">
+      <c r="AD15" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE14" t="n">
+      <c r="AE15" t="n">
         <v>2</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="inlineStr"/>
-      <c r="AH14" t="inlineStr">
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI14" t="inlineStr">
+      <c r="AI15" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>2026-08-10 11:38:13</t>
+      <c r="AJ15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>2026-08-17 11:07:23</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="C16" t="n">
         <v>6</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>싸이코패스 in 무림</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=846109&amp;tab=wed</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>846109</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>2026-08-10 10:54:05</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="b">
-        <v>1</v>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:15</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="b">
+        <v>1</v>
+      </c>
+      <c r="J16" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="N15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O15" t="inlineStr">
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>싸이코패스 in 무림[독점]</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>싸이코패스 in 무림[독점] (총 32화/미완결)</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>총 32화/미완결</t>
         </is>
       </c>
-      <c r="R15" t="n">
+      <c r="R16" t="n">
         <v>32</v>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>평점 9.8 | 김언, 곤붕 송범규 | 2026.06.16. | 총32화/미완결 | 26화 무료</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>평점 9.8 | 김언, 곤붕 송범규 | 2026.06.16. | 총32화/미완결 | 26화 무료</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13566546</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>13566546</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>싸이코패스 in 무림[독점] (총 32화/미완결)
 평점
@@ -2749,155 +2905,155 @@
 [진정한 강자들의 세상, 무림 온라인에 오신 걸 환영합니다.]무림에 떨어진 희대의 싸이코패스.음모와 악의가 가득한 무림에 동봉수, 그의 무정한 이빨이 드리운다.</t>
         </is>
       </c>
-      <c r="Y15" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA15" t="n">
+      <c r="Y16" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA16" t="n">
         <v>105</v>
       </c>
-      <c r="AB15" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
+      <c r="AC16" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD15" t="inlineStr">
+      <c r="AD16" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF15" t="inlineStr"/>
-      <c r="AG15" t="inlineStr"/>
-      <c r="AH15" t="inlineStr">
+      <c r="AE16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI15" t="inlineStr">
+      <c r="AI16" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>2026-08-10 11:38:13</t>
+      <c r="AJ16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>2026-08-17 11:07:23</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C17" t="n">
         <v>9</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>썰:관계주의</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=834033&amp;tab=wed</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>834033</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>2026-08-10 10:54:05</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="b">
-        <v>1</v>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:15</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="b">
+        <v>1</v>
+      </c>
+      <c r="J17" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="N16" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" t="inlineStr">
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="inlineStr">
         <is>
           <t>썰:관계주의</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>썰:관계주의 (총 87화/미완결)</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>총 87화/미완결</t>
         </is>
       </c>
-      <c r="R16" t="n">
+      <c r="R17" t="n">
         <v>87</v>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>평점 10.0 | 이삼 장버들 | 2026.06.16. | 총87화/미완결 | 83화 무료</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>평점 10.0 | 이삼 장버들 | 2026.06.16. | 총87화/미완결 | 83화 무료</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=11802777</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>11802777</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>썰:관계주의 (총 87화/미완결)
 평점
@@ -2905,155 +3061,155 @@
 여러 상가가 들어서 있는 강남의 유명타워. 이야기는 유명타워의 한 피부과 안내 데스크 직원 강지영으로부터 시작된다. 동료이자 유부남 의사와 만남을 이어가던 지영은 그에게 또 다른 불륜 상대가 있음을 눈치 채는데 그 상..</t>
         </is>
       </c>
-      <c r="Y16" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA16" t="n">
+      <c r="Y17" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA17" t="n">
         <v>105</v>
       </c>
-      <c r="AB16" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
+      <c r="AC17" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD16" t="inlineStr">
+      <c r="AD17" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF16" t="inlineStr"/>
-      <c r="AG16" t="inlineStr"/>
-      <c r="AH16" t="inlineStr">
+      <c r="AE17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI16" t="inlineStr">
+      <c r="AI17" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>2026-08-10 11:38:13</t>
+      <c r="AJ17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>2026-08-17 11:07:23</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="C17" t="n">
-        <v>30</v>
-      </c>
-      <c r="D17" t="inlineStr">
+      <c r="C18" t="n">
+        <v>32</v>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>끝장</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=844588&amp;tab=wed</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>844588</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>2026-08-10 10:54:06</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="b">
-        <v>1</v>
-      </c>
-      <c r="J17" t="inlineStr">
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:16</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="N17" t="n">
+      <c r="N18" t="n">
         <v>2</v>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>떨어지면 끝장</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>떨어지면 끝장 (총 70화/완결)</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>총 70화/완결</t>
         </is>
       </c>
-      <c r="R17" t="n">
+      <c r="R18" t="n">
         <v>70</v>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>완결</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>평점 9.7 | Keiko Suenobu Keiko Suenobu | 2024.04.12. | 총70화/완결 | 3화 무료</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>평점 9.7 | Keiko Suenobu Keiko Suenobu | 2024.04.12. | 총70화/완결 | 3화 무료</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=6039213</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>6039213</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>떨어지면 끝장 (총 70화/완결)
 평점
@@ -3061,161 +3217,161 @@
 “떨어지면 끝장이야.”그토록 바라던 신축 초고층 아파트에 입주하게 된 주부 아스미.같은 아파트에 거주하며 아이들 유치원도 같은 세 명의 맘 친구가 생긴다.행복 가득한 새로운 생활이 펼쳐지리라 기대했지만, 어떤 인물과..</t>
         </is>
       </c>
-      <c r="Y17" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA17" t="n">
+      <c r="Y18" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA18" t="n">
         <v>100</v>
       </c>
-      <c r="AB17" t="inlineStr">
+      <c r="AB18" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_2</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
+      <c r="AC18" t="inlineStr">
         <is>
           <t>matched</t>
         </is>
       </c>
-      <c r="AD17" t="inlineStr">
+      <c r="AD18" t="inlineStr">
         <is>
           <t>first_non_compilation_numeric_download</t>
         </is>
       </c>
-      <c r="AE17" t="n">
+      <c r="AE18" t="n">
         <v>2</v>
       </c>
-      <c r="AF17" t="inlineStr">
+      <c r="AF18" t="inlineStr">
         <is>
           <t>3.9만</t>
         </is>
       </c>
-      <c r="AG17" t="n">
+      <c r="AG18" t="n">
         <v>39000</v>
       </c>
-      <c r="AH17" t="inlineStr">
+      <c r="AH18" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="AI17" t="inlineStr">
+      <c r="AI18" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>2026-08-10 11:38:13</t>
+      <c r="AJ18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>2026-08-17 11:07:23</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>31</v>
-      </c>
-      <c r="D18" t="inlineStr">
+      <c r="C19" t="n">
+        <v>33</v>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>표절의혹</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=846106&amp;tab=wed</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>846106</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>2026-08-10 10:54:06</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="b">
-        <v>1</v>
-      </c>
-      <c r="J18" t="inlineStr">
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:16</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="b">
+        <v>1</v>
+      </c>
+      <c r="J19" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="N18" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" t="inlineStr">
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" t="inlineStr">
         <is>
           <t>표절의혹</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>표절의혹 (총 29화/미완결)</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>총 29화/미완결</t>
         </is>
       </c>
-      <c r="R18" t="n">
+      <c r="R19" t="n">
         <v>29</v>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>평점 9.4 | 김칸비 황영찬 | 2026.06.16. | 총29화/미완결 | 24화 무료</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>평점 9.4 | 김칸비 황영찬 | 2026.06.16. | 총29화/미완결 | 24화 무료</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13575121</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>13575121</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>표절의혹 (총 29화/미완결)
 평점
@@ -3223,155 +3379,155 @@
 살인사건 피해자들의 시신을 예술품처럼 사고파는 인간성을 잃은 자들, 그리고 그런 예술 살인을 저지르는 ‘자학’이라는 연쇄살인마가 세간의 화제가 되고 있다. 한 예술가는 이 상황에 분노해 자학을 추적하기 시작하는데.....</t>
         </is>
       </c>
-      <c r="Y18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA18" t="n">
+      <c r="Y19" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA19" t="n">
         <v>105</v>
       </c>
-      <c r="AB18" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
+      <c r="AC19" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD18" t="inlineStr">
+      <c r="AD19" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF18" t="inlineStr"/>
-      <c r="AG18" t="inlineStr"/>
-      <c r="AH18" t="inlineStr">
+      <c r="AE19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI18" t="inlineStr">
+      <c r="AI19" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>2026-08-10 11:38:13</t>
+      <c r="AJ19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>2026-08-17 11:07:23</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="C20" t="n">
         <v>85</v>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>일곱 번째 의뢰인</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=850210&amp;tab=wed</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>850210</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>2026-08-10 10:54:08</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="b">
-        <v>1</v>
-      </c>
-      <c r="J19" t="inlineStr">
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:18</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="b">
+        <v>1</v>
+      </c>
+      <c r="J20" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="N19" t="n">
-        <v>1</v>
-      </c>
-      <c r="O19" t="inlineStr">
+      <c r="N20" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" t="inlineStr">
         <is>
           <t>일곱 번째 의뢰인</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>일곱 번째 의뢰인 (총 14화/미완결)</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>총 14화/미완결</t>
         </is>
       </c>
-      <c r="R19" t="n">
+      <c r="R20" t="n">
         <v>14</v>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>평점 10.0 | 함영서 함영서 | 2026.06.16. | 총14화/미완결 | 9화 무료</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>평점 10.0 | 함영서 함영서 | 2026.06.16. | 총14화/미완결 | 9화 무료</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14102285</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>14102285</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>일곱 번째 의뢰인 (총 14화/미완결)
 평점
@@ -3379,155 +3535,155 @@
 어린 탐정 맥스는 아무도 주목하지 않는 도박 업자의 죽음을 조사하라는 의뢰를 받는다. 의뢰인이 용의자로 지목한 도박 업자의 아내 제인. 맥스는 그녀를 향한 의심과 이끌림 사이에서 갈등하는데. 제인은 결백한가, 살인자인..</t>
         </is>
       </c>
-      <c r="Y19" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA19" t="n">
+      <c r="Y20" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA20" t="n">
         <v>105</v>
       </c>
-      <c r="AB19" t="inlineStr">
+      <c r="AB20" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
+      <c r="AC20" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD19" t="inlineStr">
+      <c r="AD20" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF19" t="inlineStr"/>
-      <c r="AG19" t="inlineStr"/>
-      <c r="AH19" t="inlineStr">
+      <c r="AE20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI19" t="inlineStr">
+      <c r="AI20" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>2026-08-10 11:38:13</t>
+      <c r="AJ20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>2026-08-17 11:07:23</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="C21" t="n">
         <v>5</v>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>소꿉친구 컴플렉스</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=822640&amp;tab=thu</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>822640</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>2026-08-10 10:54:09</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="b">
-        <v>1</v>
-      </c>
-      <c r="J20" t="inlineStr">
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:19</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J21" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="N20" t="n">
-        <v>1</v>
-      </c>
-      <c r="O20" t="inlineStr">
+      <c r="N21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" t="inlineStr">
         <is>
           <t>소꿉친구 컴플렉스</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>소꿉친구 컴플렉스 (총 80화/미완결)</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>총 80화/미완결</t>
         </is>
       </c>
-      <c r="R20" t="n">
+      <c r="R21" t="n">
         <v>80</v>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>평점 9.8 | 은하이 은하이 | 2026.06.17. | 총80화/미완결 | 76화 무료</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>평점 9.8 | 은하이 은하이 | 2026.06.17. | 총80화/미완결 | 76화 무료</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=10851069</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>10851069</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>소꿉친구 컴플렉스 (총 80화/미완결)
 평점
@@ -3535,155 +3691,155 @@
 20살에 20년지기, 평생을 함께한 소꿉친구 하늘과 민철.그런 소꿉친구의 알고 싶지 않은 은밀한 사정을 알아버렸다?!서로를 이성으로 생각한 적이 결코 없는 두사람이지만,오해가 오해를 낳고 착각이 착각을 낳는 상황들 속에..</t>
         </is>
       </c>
-      <c r="Y20" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA20" t="n">
+      <c r="Y21" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA21" t="n">
         <v>105</v>
       </c>
-      <c r="AB20" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
+      <c r="AC21" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD20" t="inlineStr">
+      <c r="AD21" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE20" t="n">
+      <c r="AE21" t="n">
         <v>3</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
-      <c r="AG20" t="inlineStr"/>
-      <c r="AH20" t="inlineStr">
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI20" t="inlineStr">
+      <c r="AI21" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>2026-08-10 11:38:13</t>
+      <c r="AJ21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>2026-08-17 11:07:23</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="C21" t="n">
-        <v>9</v>
-      </c>
-      <c r="D21" t="inlineStr">
+      <c r="C22" t="n">
+        <v>6</v>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>럭키비치</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=852498&amp;tab=thu</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>852498</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>2026-08-10 10:54:09</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="b">
-        <v>1</v>
-      </c>
-      <c r="J21" t="inlineStr">
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:19</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="b">
+        <v>1</v>
+      </c>
+      <c r="J22" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
         <is>
           <t>thu,sun</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>thu,sun</t>
         </is>
       </c>
-      <c r="N21" t="n">
-        <v>1</v>
-      </c>
-      <c r="O21" t="inlineStr">
+      <c r="N22" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" t="inlineStr">
         <is>
           <t>럭키비치</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>럭키비치 (총 8화/미완결)</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>총 8화/미완결</t>
         </is>
       </c>
-      <c r="R21" t="n">
+      <c r="R22" t="n">
         <v>8</v>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>평점 10.0 | MAJOR, 약수 약수 | 2026.07.18. | 총8화/미완결 | 3화 무료</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>평점 10.0 | MAJOR, 약수 약수 | 2026.07.18. | 총8화/미완결 | 3화 무료</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14424733</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>14424733</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>럭키비치 (총 8화/미완결)
 평점
@@ -3691,155 +3847,311 @@
 “그거 알아? 기는 놈 위에 나는 썅X 있는 거?”불우한 환경과 폐쇄적인 바닷가 촌에서 자라온 소녀 '정임'은,그칠줄 모르는 주변의 부조리와 권태 속에서 결국 폭발,퇴폐업을 하는 고모의 불경한 쌈짓돈을 훔쳐 서울로 상경한..</t>
         </is>
       </c>
-      <c r="Y21" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA21" t="n">
+      <c r="Y22" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA22" t="n">
         <v>105</v>
       </c>
-      <c r="AB21" t="inlineStr">
+      <c r="AB22" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
+      <c r="AC22" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD21" t="inlineStr">
+      <c r="AD22" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF21" t="inlineStr"/>
-      <c r="AG21" t="inlineStr"/>
-      <c r="AH21" t="inlineStr">
+      <c r="AE22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI21" t="inlineStr">
+      <c r="AI22" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>2026-08-10 11:38:13</t>
+      <c r="AJ22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>2026-08-17 11:07:23</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="C22" t="n">
-        <v>57</v>
-      </c>
-      <c r="D22" t="inlineStr">
+      <c r="C23" t="n">
+        <v>34</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>나의 경험</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=853278&amp;tab=thu</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>853278</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:20</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="b">
+        <v>1</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>thu</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>thu</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>나의 경험</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>나의 경험 (총 6화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>총 6화/미완결</t>
+        </is>
+      </c>
+      <c r="R23" t="n">
+        <v>6</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>평점 7.0 | 윤박 윤박 | 2026.08.12. | 총6화/미완결 | 1화 무료</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>평점 7.0 | 윤박 윤박 | 2026.08.12. | 총6화/미완결 | 1화 무료</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=14532341</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>14532341</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>나의 경험 (총 6화/미완결)
+평점
+7.0 | 윤박 윤박 | 2026.08.12. | 총6화/미완결 | 1화 무료
+살다 보면 한 번쯤 인연이 물밀듯 밀려 들어오는 순간들이 있다.별다를 것 없던 평범한 스무 살 재우의 일상에도예상치 못한 만남이 하나둘 찾아오기 시작한다.서툴지만 사랑만큼은 누구보다 진심인 재우는 믿는다.이번만큼은 ..</t>
+        </is>
+      </c>
+      <c r="Y23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>non_compilation_but_download_not_ok</t>
+        </is>
+      </c>
+      <c r="AE23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>searched_series</t>
+        </is>
+      </c>
+      <c r="AJ23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>2026-08-17 11:07:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>thu</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>58</v>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>당신에게 얽힌 채</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=849879&amp;tab=thu</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>849879</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>2026-08-10 10:54:10</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="b">
-        <v>1</v>
-      </c>
-      <c r="J22" t="inlineStr">
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:20</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="b">
+        <v>1</v>
+      </c>
+      <c r="J24" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="N22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O22" t="inlineStr">
+      <c r="N24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" t="inlineStr">
         <is>
           <t>당신에게 얽힌 채</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>당신에게 얽힌 채 (총 10화/미완결)</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>총 10화/미완결</t>
         </is>
       </c>
-      <c r="R22" t="n">
+      <c r="R24" t="n">
         <v>10</v>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>평점 10.0 | Nicole Knight, 유다 danah789 | 2026.06.17. | 총10화/미완결 | 5화 무료</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>평점 10.0 | Nicole Knight, 유다 danah789 | 2026.06.17. | 총10화/미완결 | 5화 무료</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14041685</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>14041685</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>당신에게 얽힌 채 (총 10화/미완결)
 평점
@@ -3847,311 +4159,155 @@
 상속자가 아닌 복종하는 존재로 길러진 에이바 모레티. 뉴욕에서 가장 강력한 마피아 가문의 막내딸인 그녀는 ‘집안의 사고뭉치’라는 오명을 벗고 자신의 자리를 찾기 위해 분투한다.그러던 어느 날 밤, 낯선 남자와 보낸 뜨..</t>
         </is>
       </c>
-      <c r="Y22" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z22" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA22" t="n">
+      <c r="Y24" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA24" t="n">
         <v>105</v>
       </c>
-      <c r="AB22" t="inlineStr">
+      <c r="AB24" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
+      <c r="AC24" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD22" t="inlineStr">
+      <c r="AD24" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF22" t="inlineStr"/>
-      <c r="AG22" t="inlineStr"/>
-      <c r="AH22" t="inlineStr">
+      <c r="AE24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI22" t="inlineStr">
+      <c r="AI24" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>2026-08-10 11:38:13</t>
+      <c r="AJ24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>2026-08-17 11:07:23</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>thu</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>목</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>88</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>휴먼 웨어러블</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=845460&amp;tab=thu</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>845460</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>2026-08-10 10:54:11</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="b">
-        <v>1</v>
-      </c>
-      <c r="J23" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>오! 나의 교주님</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=841624&amp;tab=fri</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>841624</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:22</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="b">
+        <v>1</v>
+      </c>
+      <c r="J25" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>thu</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>thu</t>
-        </is>
-      </c>
-      <c r="N23" t="n">
-        <v>1</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>휴먼 웨어러블</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>휴먼 웨어러블 (총 30화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>총 30화/미완결</t>
-        </is>
-      </c>
-      <c r="R23" t="n">
-        <v>30</v>
-      </c>
-      <c r="S23" t="inlineStr">
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>tue,fri</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>tue,fri</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>오! 나의 교주님</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>오! 나의 교주님 (총 94화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>총 94화/미완결</t>
+        </is>
+      </c>
+      <c r="R25" t="n">
+        <v>94</v>
+      </c>
+      <c r="S25" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>평점 9.9 | 쥬타인 쥬타인 | 2026.06.03. | 총30화/미완결 | 27화 무료</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>평점 9.9 | 쥬타인 쥬타인 | 2026.06.03. | 총30화/미완결 | 27화 무료</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=13481722</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>13481722</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>휴먼 웨어러블 (총 30화/미완결)
-평점
-9.9 | 쥬타인 쥬타인 | 2026.06.03. | 총30화/미완결 | 27화 무료
-꿈의 무대, 패션 서바이벌 &lt;휴먼 웨어러블&gt;.고아 출신이지만 명문 ‘순백패션예술학교’를 거쳐 올라온 학생들.이 무대에서 인생 역전의 주인공이 탄생한다—…그런데 무언가, 이상하게 흘러가기 시작했다.</t>
-        </is>
-      </c>
-      <c r="Y23" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z23" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>105</v>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>review_needed</t>
-        </is>
-      </c>
-      <c r="AD23" t="inlineStr">
-        <is>
-          <t>non_compilation_but_download_not_ok</t>
-        </is>
-      </c>
-      <c r="AE23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF23" t="inlineStr"/>
-      <c r="AG23" t="inlineStr"/>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>2026-08-10 11:38:13</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>fri</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>금</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>2</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>오! 나의 교주님</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=841624&amp;tab=fri</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>841624</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>2026-08-10 10:54:12</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="b">
-        <v>1</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>tue,fri</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>tue,fri</t>
-        </is>
-      </c>
-      <c r="N24" t="n">
-        <v>1</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>오! 나의 교주님</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>오! 나의 교주님 (총 94화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>총 94화/미완결</t>
-        </is>
-      </c>
-      <c r="R24" t="n">
-        <v>94</v>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>평점 9.4 | 김꿀빨, 김완두 김꿀빨, 김완두 | 2026.06.18. | 총94화/미완결 | 89화 무료</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>평점 9.4 | 김꿀빨, 김완두 김꿀빨, 김완두 | 2026.06.18. | 총94화/미완결 | 89화 무료</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=12998643</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>12998643</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>오! 나의 교주님 (총 94화/미완결)
 평점
@@ -4159,155 +4315,155 @@
 사이비 종교 ‘진천교’에서 태어나 평생을 그곳에서 살아온 한성민. 그는 결국 모든 것을 잃고 홀로 탈출한다.수년 후, 성인이 된 그는 다시 진천교에 잠입해 처절한 복수를 시작하려 한다.“오, 나의 교주님. 제가 보내드릴게..</t>
         </is>
       </c>
-      <c r="Y24" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z24" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA24" t="n">
+      <c r="Y25" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA25" t="n">
         <v>105</v>
       </c>
-      <c r="AB24" t="inlineStr">
+      <c r="AB25" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
+      <c r="AC25" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD24" t="inlineStr">
+      <c r="AD25" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF24" t="inlineStr"/>
-      <c r="AG24" t="inlineStr"/>
-      <c r="AH24" t="inlineStr">
+      <c r="AE25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI24" t="inlineStr">
+      <c r="AI25" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>2026-08-10 11:38:13</t>
+      <c r="AJ25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>2026-08-17 11:07:23</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C25" t="n">
+      <c r="C26" t="n">
         <v>9</v>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>두 얼굴</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=845646&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>845646</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>2026-08-10 10:54:12</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="b">
-        <v>1</v>
-      </c>
-      <c r="J25" t="inlineStr">
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:22</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="b">
+        <v>1</v>
+      </c>
+      <c r="J26" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="N25" t="n">
-        <v>1</v>
-      </c>
-      <c r="O25" t="inlineStr">
+      <c r="N26" t="n">
+        <v>1</v>
+      </c>
+      <c r="O26" t="inlineStr">
         <is>
           <t>두 얼굴의 대표님</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>두 얼굴의 대표님 (총 126화/완결)</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>총 126화/완결</t>
         </is>
       </c>
-      <c r="R25" t="n">
+      <c r="R26" t="n">
         <v>126</v>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>완결</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>평점 6.2 | 1M, KuaiKan, YY 1M, KuaiKan, YY | 2022.10.02. | 총126화/완결 | 3화 무료</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>평점 6.2 | 1M, KuaiKan, YY 1M, KuaiKan, YY | 2022.10.02. | 총126화/완결 | 3화 무료</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=6489984</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>6489984</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>두 얼굴의 대표님 (총 126화/완결)
 평점
@@ -4315,161 +4471,161 @@
 재벌가의 사생아로 태어난 소원은 일찍 엄마를 잃고, 가족들의 멸시 속에서 살아왔다.그러다 언니에게 약혼자까지 뺏기게 되자, 실의에 빠진 소원은 유학을 떠나게 되고, 그곳에서 평범한 남편을 만나 결혼을 하게 된다.1년 후 ..</t>
         </is>
       </c>
-      <c r="Y25" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA25" t="n">
+      <c r="Y26" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA26" t="n">
         <v>105</v>
       </c>
-      <c r="AB25" t="inlineStr">
+      <c r="AB26" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
+      <c r="AC26" t="inlineStr">
         <is>
           <t>matched</t>
         </is>
       </c>
-      <c r="AD25" t="inlineStr">
+      <c r="AD26" t="inlineStr">
         <is>
           <t>first_non_compilation_numeric_download</t>
         </is>
       </c>
-      <c r="AE25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF25" t="inlineStr">
+      <c r="AE26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF26" t="inlineStr">
         <is>
           <t>157.5만</t>
         </is>
       </c>
-      <c r="AG25" t="n">
+      <c r="AG26" t="n">
         <v>1575000</v>
       </c>
-      <c r="AH25" t="inlineStr">
+      <c r="AH26" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="AI25" t="inlineStr">
+      <c r="AI26" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>2026-08-10 11:38:13</t>
+      <c r="AJ26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>2026-08-17 11:07:23</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C26" t="n">
+      <c r="C27" t="n">
         <v>10</v>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>네가 사는 그 집</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=842465&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>842465</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>2026-08-10 10:54:12</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="b">
-        <v>1</v>
-      </c>
-      <c r="J26" t="inlineStr">
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:22</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="b">
+        <v>1</v>
+      </c>
+      <c r="J27" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="N26" t="n">
-        <v>1</v>
-      </c>
-      <c r="O26" t="inlineStr">
+      <c r="N27" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" t="inlineStr">
         <is>
           <t>네가 사는 그 집</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>네가 사는 그 집 (총 47화/미완결)</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>총 47화/미완결</t>
         </is>
       </c>
-      <c r="R26" t="n">
+      <c r="R27" t="n">
         <v>47</v>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>평점 9.7 | 석우 해바다 | 2026.06.18. | 총47화/미완결 | 41화 무료</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>평점 9.7 | 석우 해바다 | 2026.06.18. | 총47화/미완결 | 41화 무료</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13090391</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>13090391</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>네가 사는 그 집 (총 47화/미완결)
 평점
@@ -4477,155 +4633,155 @@
 찢어지게 가난한 집에서 두 아이를 키우며 힘겹게 살아가던 30대 화린.어느날, 자기 첫사랑이었던 부유한 선배와 결혼해 행복하게 사는 친구와 몸이 바뀐다.하지만 부러워하던 삶을 얻은 기쁨도 잠시,그 집의 추악한 비밀이 드..</t>
         </is>
       </c>
-      <c r="Y26" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z26" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA26" t="n">
+      <c r="Y27" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA27" t="n">
         <v>105</v>
       </c>
-      <c r="AB26" t="inlineStr">
+      <c r="AB27" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
+      <c r="AC27" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD26" t="inlineStr">
+      <c r="AD27" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF26" t="inlineStr"/>
-      <c r="AG26" t="inlineStr"/>
-      <c r="AH26" t="inlineStr">
+      <c r="AE27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI26" t="inlineStr">
+      <c r="AI27" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>2026-08-10 11:38:13</t>
+      <c r="AJ27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>2026-08-17 11:07:23</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C27" t="n">
+      <c r="C28" t="n">
         <v>11</v>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>그리디</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=845919&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>845919</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>2026-08-10 10:54:12</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="b">
-        <v>1</v>
-      </c>
-      <c r="J27" t="inlineStr">
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:22</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="b">
+        <v>1</v>
+      </c>
+      <c r="J28" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="N27" t="n">
-        <v>1</v>
-      </c>
-      <c r="O27" t="inlineStr">
+      <c r="N28" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" t="inlineStr">
         <is>
           <t>그리디</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>그리디 (총 31화/미완결)</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>총 31화/미완결</t>
         </is>
       </c>
-      <c r="R27" t="n">
+      <c r="R28" t="n">
         <v>31</v>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>평점 9.9 | 영하 랑라리 | 2026.06.18. | 총31화/미완결 | 25화 무료</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>평점 9.9 | 영하 랑라리 | 2026.06.18. | 총31화/미완결 | 25화 무료</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13530624</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>13530624</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>그리디 (총 31화/미완결)
 평점
@@ -4633,155 +4789,155 @@
 파혼했다. 십년지기 친구와 내가 파혼한 남자가 찍힌 청첩장 한 장.한유주는 그걸 끝으로 서른하나에 사랑도 우정도 다 버렸다. 남은 건 칼럼 한 줄에도 이름을 걸 수 없는 5년짜리 패션지 주니어 에디터 신세뿐.일도 사랑도, 마..</t>
         </is>
       </c>
-      <c r="Y27" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA27" t="n">
+      <c r="Y28" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA28" t="n">
         <v>105</v>
       </c>
-      <c r="AB27" t="inlineStr">
+      <c r="AB28" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
+      <c r="AC28" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD27" t="inlineStr">
+      <c r="AD28" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF27" t="inlineStr"/>
-      <c r="AG27" t="inlineStr"/>
-      <c r="AH27" t="inlineStr">
+      <c r="AE28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI27" t="inlineStr">
+      <c r="AI28" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>2026-08-10 11:38:13</t>
+      <c r="AJ28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>2026-08-17 11:07:23</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C28" t="n">
+      <c r="C29" t="n">
         <v>36</v>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>로맨스 저주</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=834035&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>834035</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>2026-08-10 10:54:13</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="b">
-        <v>1</v>
-      </c>
-      <c r="J28" t="inlineStr">
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:23</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="b">
+        <v>1</v>
+      </c>
+      <c r="J29" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="N28" t="n">
-        <v>1</v>
-      </c>
-      <c r="O28" t="inlineStr">
+      <c r="N29" t="n">
+        <v>1</v>
+      </c>
+      <c r="O29" t="inlineStr">
         <is>
           <t>로맨스 저주</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>로맨스 저주 (총 92화/미완결)</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>총 92화/미완결</t>
         </is>
       </c>
-      <c r="R28" t="n">
+      <c r="R29" t="n">
         <v>92</v>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>평점 9.9 | 다원 다원 | 2026.06.18. | 총92화/미완결 | 85화 무료</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>평점 9.9 | 다원 다원 | 2026.06.18. | 총92화/미완결 | 85화 무료</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=11824393</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>11824393</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>로맨스 저주 (총 92화/미완결)
 평점
@@ -4789,155 +4945,155 @@
 희수는 타인을 저주하는 글을 쓰면 현실이 되는 신비한 노트를 택배로 받는다.심지어 저주를 할 때마다 현금이 나온다!희수는 짝사랑하던 남자 현우를 저주해 자신과의 로맨스를 강요한다.하지만 뜻대로 되지 않고, 일이 꼬여..</t>
         </is>
       </c>
-      <c r="Y28" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z28" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA28" t="n">
+      <c r="Y29" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA29" t="n">
         <v>105</v>
       </c>
-      <c r="AB28" t="inlineStr">
+      <c r="AB29" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
+      <c r="AC29" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD28" t="inlineStr">
+      <c r="AD29" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE28" t="n">
+      <c r="AE29" t="n">
         <v>2</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
-      <c r="AG28" t="inlineStr"/>
-      <c r="AH28" t="inlineStr">
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI28" t="inlineStr">
+      <c r="AI29" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>2026-08-10 11:38:13</t>
+      <c r="AJ29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>2026-08-17 11:07:23</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C29" t="n">
-        <v>41</v>
-      </c>
-      <c r="D29" t="inlineStr">
+      <c r="C30" t="n">
+        <v>42</v>
+      </c>
+      <c r="D30" t="inlineStr">
         <is>
           <t>사자의 서</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=823737&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>823737</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>2026-08-10 10:54:13</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="b">
-        <v>1</v>
-      </c>
-      <c r="J29" t="inlineStr">
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:23</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="b">
+        <v>1</v>
+      </c>
+      <c r="J30" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr">
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="N29" t="n">
+      <c r="N30" t="n">
         <v>2</v>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>사자의서 [도시정벌 레거시]</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>사자의서 [도시정벌 레거시] (총 219화/완결)</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>총 219화/완결</t>
         </is>
       </c>
-      <c r="R29" t="n">
+      <c r="R30" t="n">
         <v>219</v>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>완결</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>평점 9.2 | 신형빈 신형빈 | 2019.11.06. | 총219화/완결 | 5화 무료</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>평점 9.2 | 신형빈 신형빈 | 2019.11.06. | 총219화/완결 | 5화 무료</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="V30" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=2737090</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>2737090</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>사자의서 [도시정벌 레거시] (총 219화/완결)
 평점
@@ -4945,161 +5101,161 @@
 죽음(死)에서 돌아 온 자. 그가 써내려가는 피의 역사에 도시(都市)가 깨어난다.</t>
         </is>
       </c>
-      <c r="Y29" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA29" t="n">
+      <c r="Y30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA30" t="n">
         <v>100</v>
       </c>
-      <c r="AB29" t="inlineStr">
+      <c r="AB30" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_2</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
+      <c r="AC30" t="inlineStr">
         <is>
           <t>matched</t>
         </is>
       </c>
-      <c r="AD29" t="inlineStr">
+      <c r="AD30" t="inlineStr">
         <is>
           <t>first_non_compilation_numeric_download</t>
         </is>
       </c>
-      <c r="AE29" t="n">
+      <c r="AE30" t="n">
         <v>2</v>
       </c>
-      <c r="AF29" t="inlineStr">
+      <c r="AF30" t="inlineStr">
         <is>
           <t>121.3만</t>
         </is>
       </c>
-      <c r="AG29" t="n">
+      <c r="AG30" t="n">
         <v>1213000</v>
       </c>
-      <c r="AH29" t="inlineStr">
+      <c r="AH30" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="AI29" t="inlineStr">
+      <c r="AI30" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>2026-08-10 11:38:13</t>
+      <c r="AJ30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>2026-08-17 11:07:23</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C30" t="n">
-        <v>60</v>
-      </c>
-      <c r="D30" t="inlineStr">
+      <c r="C31" t="n">
+        <v>61</v>
+      </c>
+      <c r="D31" t="inlineStr">
         <is>
           <t>박제</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=846363&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>846363</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>2026-08-10 10:54:14</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="b">
-        <v>1</v>
-      </c>
-      <c r="J30" t="inlineStr">
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:24</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="b">
+        <v>1</v>
+      </c>
+      <c r="J31" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr">
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="N30" t="n">
+      <c r="N31" t="n">
         <v>2</v>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>박제하는 시간</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>박제하는 시간 (총 28화/완결)</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>총 28화/완결</t>
         </is>
       </c>
-      <c r="R30" t="n">
+      <c r="R31" t="n">
         <v>28</v>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>완결</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>평점 10.0 | 이언 | 2024.07.19. | 총28화/완결 | 5화 무료</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>평점 10.0 | 이언 | 2024.07.19. | 총28화/완결 | 5화 무료</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="V31" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=10632769</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
+      <c r="W31" t="inlineStr">
         <is>
           <t>10632769</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>박제하는 시간 (총 28화/완결)
 평점
@@ -5107,161 +5263,161 @@
 박제사 ‘도연’은 죽은 연인의 시체를 빼돌린다.이 과정을 목격한 작가 ‘이명’은 침묵의 대가로 도연의 삶을 소재로 요구해 온다.일주일간의 취재를 허락한 도연. 죽은 연인과 꼭 닮은 이명의 모습에 혼란을 느낀다.숲속의 ..</t>
         </is>
       </c>
-      <c r="Y30" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA30" t="n">
+      <c r="Y31" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA31" t="n">
         <v>100</v>
       </c>
-      <c r="AB30" t="inlineStr">
+      <c r="AB31" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_2</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
+      <c r="AC31" t="inlineStr">
         <is>
           <t>matched</t>
         </is>
       </c>
-      <c r="AD30" t="inlineStr">
+      <c r="AD31" t="inlineStr">
         <is>
           <t>first_non_compilation_numeric_download</t>
         </is>
       </c>
-      <c r="AE30" t="n">
+      <c r="AE31" t="n">
         <v>2</v>
       </c>
-      <c r="AF30" t="inlineStr">
+      <c r="AF31" t="inlineStr">
         <is>
           <t>7.2만</t>
         </is>
       </c>
-      <c r="AG30" t="n">
+      <c r="AG31" t="n">
         <v>72000</v>
       </c>
-      <c r="AH30" t="inlineStr">
+      <c r="AH31" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="AI30" t="inlineStr">
+      <c r="AI31" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>2026-08-10 11:38:13</t>
+      <c r="AJ31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>2026-08-17 11:07:23</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C31" t="n">
-        <v>67</v>
-      </c>
-      <c r="D31" t="inlineStr">
+      <c r="C32" t="n">
+        <v>68</v>
+      </c>
+      <c r="D32" t="inlineStr">
         <is>
           <t>죽여주는 캐스팅</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=843866&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>843866</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>2026-08-10 10:54:14</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="b">
-        <v>1</v>
-      </c>
-      <c r="J31" t="inlineStr">
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:24</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="b">
+        <v>1</v>
+      </c>
+      <c r="J32" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr">
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="N31" t="n">
-        <v>1</v>
-      </c>
-      <c r="O31" t="inlineStr">
+      <c r="N32" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" t="inlineStr">
         <is>
           <t>죽여주는 캐스팅 [독점]</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>죽여주는 캐스팅 [독점] (총 42화/미완결)</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>총 42화/미완결</t>
         </is>
       </c>
-      <c r="R31" t="n">
+      <c r="R32" t="n">
         <v>42</v>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>평점 9.6 | 영춘 하보 | 2026.06.18. | 총42화/미완결 | 36화 무료</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>평점 9.6 | 영춘 하보 | 2026.06.18. | 총42화/미완결 | 36화 무료</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13253015</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>13253015</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>죽여주는 캐스팅 [독점] (총 42화/미완결)
 평점
@@ -5269,155 +5425,155 @@
 영화감상 동호회에서 만난 혜수와 강호.성공한 배우를 꿈꾸는 강호는 오디션과 술자리에 몰두하며 혜수에게 기대어 살아간다.그런 강호를 이해하고자 혜수는 연기 수업을 시작하고 점차 자신의 길을 걷기 시작한다.하지만 강..</t>
         </is>
       </c>
-      <c r="Y31" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z31" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA31" t="n">
+      <c r="Y32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA32" t="n">
         <v>105</v>
       </c>
-      <c r="AB31" t="inlineStr">
+      <c r="AB32" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
+      <c r="AC32" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD31" t="inlineStr">
+      <c r="AD32" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF31" t="inlineStr"/>
-      <c r="AG31" t="inlineStr"/>
-      <c r="AH31" t="inlineStr">
+      <c r="AE32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="inlineStr"/>
+      <c r="AH32" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI31" t="inlineStr">
+      <c r="AI32" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>2026-08-10 11:38:13</t>
+      <c r="AJ32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>2026-08-17 11:07:23</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C32" t="n">
-        <v>69</v>
-      </c>
-      <c r="D32" t="inlineStr">
+      <c r="C33" t="n">
+        <v>70</v>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t>사탄의 순애</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=845378&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>845378</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>2026-08-10 10:54:14</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="b">
-        <v>1</v>
-      </c>
-      <c r="J32" t="inlineStr">
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:24</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="b">
+        <v>1</v>
+      </c>
+      <c r="J33" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr">
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="N32" t="n">
-        <v>1</v>
-      </c>
-      <c r="O32" t="inlineStr">
+      <c r="N33" t="n">
+        <v>1</v>
+      </c>
+      <c r="O33" t="inlineStr">
         <is>
           <t>사탄의 순애 [독점]</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>사탄의 순애 [독점] (총 35화/미완결)</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>총 35화/미완결</t>
         </is>
       </c>
-      <c r="R32" t="n">
+      <c r="R33" t="n">
         <v>35</v>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>평점 9.8 | 용현 카모모 | 2026.06.18. | 총35화/미완결 | 28화 무료</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>평점 9.8 | 용현 카모모 | 2026.06.18. | 총35화/미완결 | 28화 무료</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
+      <c r="V33" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13451638</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr">
+      <c r="W33" t="inlineStr">
         <is>
           <t>13451638</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>사탄의 순애 [독점] (총 35화/미완결)
 평점
@@ -5425,310 +5581,310 @@
 초식동물계 대표주자 호구남 백은우 VS 육식동물계 대표주자 차도녀 범호연.정반대의 두 사람은 어쩌다 사귀게 됐을까?“백은우. 나한테 취업해라. 내 애인인 척 딱 1년. 그럼 10억이야.”업계에서 악마로 소문난 아티스트 레..</t>
         </is>
       </c>
-      <c r="Y32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z32" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA32" t="n">
+      <c r="Y33" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA33" t="n">
         <v>105</v>
       </c>
-      <c r="AB32" t="inlineStr">
+      <c r="AB33" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
+      <c r="AC33" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD32" t="inlineStr">
+      <c r="AD33" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF32" t="inlineStr"/>
-      <c r="AG32" t="inlineStr"/>
-      <c r="AH32" t="inlineStr">
+      <c r="AE33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI32" t="inlineStr">
+      <c r="AI33" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>2026-08-10 11:38:13</t>
+      <c r="AJ33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>2026-08-17 11:07:23</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>토</t>
         </is>
       </c>
-      <c r="C33" t="n">
+      <c r="C34" t="n">
         <v>3</v>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>만취남녀</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=846883&amp;tab=sat</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>846883</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>2026-08-10 10:54:16</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="b">
-        <v>1</v>
-      </c>
-      <c r="J33" t="inlineStr">
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:26</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="b">
+        <v>1</v>
+      </c>
+      <c r="J34" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr">
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="N33" t="n">
-        <v>1</v>
-      </c>
-      <c r="O33" t="inlineStr">
+      <c r="N34" t="n">
+        <v>1</v>
+      </c>
+      <c r="O34" t="inlineStr">
         <is>
           <t>19금 만취남녀</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>19금 만취남녀 (총 26화/미완결)</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>총 26화/미완결</t>
         </is>
       </c>
-      <c r="R33" t="n">
+      <c r="R34" t="n">
         <v>26</v>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>평점 9.7 | 금 금 | 2026.06.12. | 총26화/미완결 | 21화 무료</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>평점 9.7 | 금 금 | 2026.06.12. | 총26화/미완결 | 21화 무료</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr">
+      <c r="V34" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13646371</t>
         </is>
       </c>
-      <c r="W33" t="inlineStr">
+      <c r="W34" t="inlineStr">
         <is>
           <t>13646371</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>19금 만취남녀 (총 26화/미완결)
 평점
 9.7 | 금 금 | 2026.06.12. | 총26화/미완결 | 21화 무료</t>
         </is>
       </c>
-      <c r="Y33" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z33" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA33" t="n">
+      <c r="Y34" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA34" t="n">
         <v>105</v>
       </c>
-      <c r="AB33" t="inlineStr">
+      <c r="AB34" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
+      <c r="AC34" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD33" t="inlineStr">
+      <c r="AD34" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF33" t="inlineStr"/>
-      <c r="AG33" t="inlineStr"/>
-      <c r="AH33" t="inlineStr">
+      <c r="AE34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI33" t="inlineStr">
+      <c r="AI34" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>2026-08-10 11:38:13</t>
+      <c r="AJ34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>2026-08-17 11:07:23</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>토</t>
         </is>
       </c>
-      <c r="C34" t="n">
-        <v>6</v>
-      </c>
-      <c r="D34" t="inlineStr">
+      <c r="C35" t="n">
+        <v>4</v>
+      </c>
+      <c r="D35" t="inlineStr">
         <is>
           <t>시든 꽃에 눈물을</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=827190&amp;tab=sat</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>827190</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>2026-08-10 10:54:16</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="b">
-        <v>1</v>
-      </c>
-      <c r="J34" t="inlineStr">
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:26</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="b">
+        <v>1</v>
+      </c>
+      <c r="J35" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr">
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="N34" t="n">
-        <v>1</v>
-      </c>
-      <c r="O34" t="inlineStr">
+      <c r="N35" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" t="inlineStr">
         <is>
           <t>시든 꽃에 눈물을</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>시든 꽃에 눈물을 (총 106화/미완결)</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>총 106화/미완결</t>
         </is>
       </c>
-      <c r="R34" t="n">
+      <c r="R35" t="n">
         <v>106</v>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>평점 9.8 | 개 개 | 2026.06.12. | 총106화/미완결 | 100화 무료</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>평점 9.8 | 개 개 | 2026.06.12. | 총106화/미완결 | 100화 무료</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
+      <c r="V35" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=11253061</t>
         </is>
       </c>
-      <c r="W34" t="inlineStr">
+      <c r="W35" t="inlineStr">
         <is>
           <t>11253061</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>시든 꽃에 눈물을 (총 106화/미완결)
 평점
@@ -5736,155 +5892,155 @@
 남편이 불륜을 저질렀다. 엄청난 빚을 떠안기고, 아이를 잃게 한 것으로 모자라, 한참 어린 여자와 제 눈앞에서 몸을 섞었다. 상처 입은 삶은 볼품 없이 시들어 버려질 예정이었다. 그런데-, "어른의 사랑을 가르쳐 주세요."나해..</t>
         </is>
       </c>
-      <c r="Y34" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z34" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA34" t="n">
+      <c r="Y35" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA35" t="n">
         <v>105</v>
       </c>
-      <c r="AB34" t="inlineStr">
+      <c r="AB35" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
+      <c r="AC35" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD34" t="inlineStr">
+      <c r="AD35" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE34" t="n">
+      <c r="AE35" t="n">
         <v>4</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
-      <c r="AG34" t="inlineStr"/>
-      <c r="AH34" t="inlineStr">
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI34" t="inlineStr">
+      <c r="AI35" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>2026-08-10 11:38:13</t>
+      <c r="AJ35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>2026-08-17 11:07:23</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>토</t>
         </is>
       </c>
-      <c r="C35" t="n">
+      <c r="C36" t="n">
         <v>9</v>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>둘째에게</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=845711&amp;tab=sat</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>845711</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>2026-08-10 10:54:16</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="b">
-        <v>1</v>
-      </c>
-      <c r="J35" t="inlineStr">
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:26</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="b">
+        <v>1</v>
+      </c>
+      <c r="J36" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr">
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="N35" t="n">
-        <v>1</v>
-      </c>
-      <c r="O35" t="inlineStr">
+      <c r="N36" t="n">
+        <v>1</v>
+      </c>
+      <c r="O36" t="inlineStr">
         <is>
           <t>둘째에게</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>둘째에게 (총 32화/미완결)</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>총 32화/미완결</t>
         </is>
       </c>
-      <c r="R35" t="n">
+      <c r="R36" t="n">
         <v>32</v>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>평점 10.0 | 고태호 고태호 | 2026.06.12. | 총32화/미완결 | 27화 무료</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>평점 10.0 | 고태호 고태호 | 2026.06.12. | 총32화/미완결 | 27화 무료</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr">
+      <c r="V36" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13512084</t>
         </is>
       </c>
-      <c r="W35" t="inlineStr">
+      <c r="W36" t="inlineStr">
         <is>
           <t>13512084</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>둘째에게 (총 32화/미완결)
 평점
@@ -5892,155 +6048,155 @@
 슬럼프에 시달리고 있는 작가 '이류진'은 자신의 팬이자 조직폭력배 '둘째'와 우연히 엮이게 되고, 슬럼프를 극복하고 싶은 작가와 글쓰는 법을 배우고 싶어하는 조폭은 필요로 인해 서로 교류를 하게 된다.그렇게 교류를 하며 ..</t>
         </is>
       </c>
-      <c r="Y35" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z35" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA35" t="n">
+      <c r="Y36" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA36" t="n">
         <v>105</v>
       </c>
-      <c r="AB35" t="inlineStr">
+      <c r="AB36" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
+      <c r="AC36" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD35" t="inlineStr">
+      <c r="AD36" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF35" t="inlineStr"/>
-      <c r="AG35" t="inlineStr"/>
-      <c r="AH35" t="inlineStr">
+      <c r="AE36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI35" t="inlineStr">
+      <c r="AI36" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>2026-08-10 11:38:13</t>
+      <c r="AJ36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>2026-08-17 11:07:23</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>토</t>
         </is>
       </c>
-      <c r="C36" t="n">
-        <v>18</v>
-      </c>
-      <c r="D36" t="inlineStr">
+      <c r="C37" t="n">
+        <v>19</v>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>데이워커</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=828880&amp;tab=sat</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>828880</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>2026-08-10 10:54:16</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="b">
-        <v>1</v>
-      </c>
-      <c r="J36" t="inlineStr">
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:26</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="b">
+        <v>1</v>
+      </c>
+      <c r="J37" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr">
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="N36" t="n">
-        <v>1</v>
-      </c>
-      <c r="O36" t="inlineStr">
+      <c r="N37" t="n">
+        <v>1</v>
+      </c>
+      <c r="O37" t="inlineStr">
         <is>
           <t>데이워커</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>데이워커 (총 94화/미완결)</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>총 94화/미완결</t>
         </is>
       </c>
-      <c r="R36" t="n">
+      <c r="R37" t="n">
         <v>94</v>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="T37" t="inlineStr">
         <is>
           <t>평점 9.6 | MUTE MUTE | 2026.06.12. | 총94화/미완결 | 89화 무료</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>평점 9.6 | MUTE MUTE | 2026.06.12. | 총94화/미완결 | 89화 무료</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr">
+      <c r="V37" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=11433164</t>
         </is>
       </c>
-      <c r="W36" t="inlineStr">
+      <c r="W37" t="inlineStr">
         <is>
           <t>11433164</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>데이워커 (총 94화/미완결)
 평점
@@ -6048,155 +6204,155 @@
 국정원 블랙요원 '수혁'은 한국에 약물을 밀매하는 조직 '나나야구미'의 수장 암살 임무를 받는다.그러나 그 수장은 '안나'란 이름의 싸움과는 연관 없을 법한 매력적인 여자였는데... 이 임무 뭔가 이상하다.자신을 배신한 국정..</t>
         </is>
       </c>
-      <c r="Y36" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z36" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA36" t="n">
+      <c r="Y37" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA37" t="n">
         <v>105</v>
       </c>
-      <c r="AB36" t="inlineStr">
+      <c r="AB37" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
+      <c r="AC37" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD36" t="inlineStr">
+      <c r="AD37" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF36" t="inlineStr"/>
-      <c r="AG36" t="inlineStr"/>
-      <c r="AH36" t="inlineStr">
+      <c r="AE37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="inlineStr"/>
+      <c r="AH37" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI36" t="inlineStr">
+      <c r="AI37" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>2026-08-10 11:38:13</t>
+      <c r="AJ37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>2026-08-17 11:07:23</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>토</t>
         </is>
       </c>
-      <c r="C37" t="n">
+      <c r="C38" t="n">
         <v>39</v>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>연애 못하면 죽음!</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=846662&amp;tab=sat</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>846662</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>2026-08-10 10:54:17</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="b">
-        <v>1</v>
-      </c>
-      <c r="J37" t="inlineStr">
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:27</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="b">
+        <v>1</v>
+      </c>
+      <c r="J38" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr">
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="N37" t="n">
-        <v>1</v>
-      </c>
-      <c r="O37" t="inlineStr">
+      <c r="N38" t="n">
+        <v>1</v>
+      </c>
+      <c r="O38" t="inlineStr">
         <is>
           <t>연애 못하면 죽음!</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>연애 못하면 죽음! (총 31화/미완결)</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
+      <c r="Q38" t="inlineStr">
         <is>
           <t>총 31화/미완결</t>
         </is>
       </c>
-      <c r="R37" t="n">
+      <c r="R38" t="n">
         <v>31</v>
       </c>
-      <c r="S37" t="inlineStr">
+      <c r="S38" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr">
+      <c r="T38" t="inlineStr">
         <is>
           <t>평점 9.8 | 우연희 pusna | 2026.06.12. | 총31화/미완결 | 23화 무료</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="U38" t="inlineStr">
         <is>
           <t>평점 9.8 | 우연희 pusna | 2026.06.12. | 총31화/미완결 | 23화 무료</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr">
+      <c r="V38" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13633976</t>
         </is>
       </c>
-      <c r="W37" t="inlineStr">
+      <c r="W38" t="inlineStr">
         <is>
           <t>13633976</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>연애 못하면 죽음! (총 31화/미완결)
 평점
@@ -6204,155 +6360,155 @@
 똥차들과의 망한 연애로 인해사랑, 연애에 부정적인 30대가 된 워커홀릭 문주경은어느날 우연히 '금방 사랑에 빠지는' 저주에 걸리게 된다.마음에 드는 상대에게 다짜고짜 고백부터 하게 되는 끔찍한 저주.사랑에 빠지기를 거..</t>
         </is>
       </c>
-      <c r="Y37" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z37" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA37" t="n">
+      <c r="Y38" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA38" t="n">
         <v>105</v>
       </c>
-      <c r="AB37" t="inlineStr">
+      <c r="AB38" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
+      <c r="AC38" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD37" t="inlineStr">
+      <c r="AD38" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF37" t="inlineStr"/>
-      <c r="AG37" t="inlineStr"/>
-      <c r="AH37" t="inlineStr">
+      <c r="AE38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="inlineStr"/>
+      <c r="AH38" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI37" t="inlineStr">
+      <c r="AI38" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>2026-08-10 11:38:13</t>
+      <c r="AJ38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>2026-08-17 11:07:23</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>토</t>
         </is>
       </c>
-      <c r="C38" t="n">
-        <v>46</v>
-      </c>
-      <c r="D38" t="inlineStr">
+      <c r="C39" t="n">
+        <v>49</v>
+      </c>
+      <c r="D39" t="inlineStr">
         <is>
           <t>데스루프</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=852086&amp;tab=sat</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>852086</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>2026-08-10 10:54:17</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="b">
-        <v>1</v>
-      </c>
-      <c r="J38" t="inlineStr">
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:27</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="b">
+        <v>1</v>
+      </c>
+      <c r="J39" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr">
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="N38" t="n">
-        <v>1</v>
-      </c>
-      <c r="O38" t="inlineStr">
+      <c r="N39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O39" t="inlineStr">
         <is>
           <t>데스루프</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>데스루프 (총 6화/미완결)</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr">
+      <c r="Q39" t="inlineStr">
         <is>
           <t>총 6화/미완결</t>
         </is>
       </c>
-      <c r="R38" t="n">
+      <c r="R39" t="n">
         <v>6</v>
       </c>
-      <c r="S38" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr">
+      <c r="T39" t="inlineStr">
         <is>
           <t>평점 8.3 | 은삼 은삼 | 2026.06.26. | 총6화/미완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="U39" t="inlineStr">
         <is>
           <t>평점 8.3 | 은삼 은삼 | 2026.06.26. | 총6화/미완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr">
+      <c r="V39" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14366954</t>
         </is>
       </c>
-      <c r="W38" t="inlineStr">
+      <c r="W39" t="inlineStr">
         <is>
           <t>14366954</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>데스루프 (총 6화/미완결)
 평점
@@ -6360,155 +6516,155 @@
 정신을 차려 보니 지하 창고에 갇힌 주인공 홍연화.연화는 자신을 가둔 남성에게 여러 번 끔찍한 죽음을 맞이하지만, 계속해서 시간이 반복된다.겨우 그곳을 빠져나오지만 그녀 앞에 마주한 것은 끔찍하게 생긴 괴물.과연 그녀..</t>
         </is>
       </c>
-      <c r="Y38" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z38" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA38" t="n">
+      <c r="Y39" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA39" t="n">
         <v>105</v>
       </c>
-      <c r="AB38" t="inlineStr">
+      <c r="AB39" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
+      <c r="AC39" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD38" t="inlineStr">
+      <c r="AD39" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF38" t="inlineStr"/>
-      <c r="AG38" t="inlineStr"/>
-      <c r="AH38" t="inlineStr">
+      <c r="AE39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="inlineStr"/>
+      <c r="AH39" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI38" t="inlineStr">
+      <c r="AI39" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>2026-08-10 11:38:13</t>
+      <c r="AJ39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>2026-08-17 11:07:23</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C39" t="n">
-        <v>4</v>
-      </c>
-      <c r="D39" t="inlineStr">
+      <c r="C40" t="n">
+        <v>3</v>
+      </c>
+      <c r="D40" t="inlineStr">
         <is>
           <t>럭키비치</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=852498&amp;tab=sun</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>852498</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>2026-08-10 10:54:20</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="b">
-        <v>1</v>
-      </c>
-      <c r="J39" t="inlineStr">
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:30</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="b">
+        <v>1</v>
+      </c>
+      <c r="J40" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr">
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
         <is>
           <t>thu,sun</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>thu,sun</t>
         </is>
       </c>
-      <c r="N39" t="n">
-        <v>1</v>
-      </c>
-      <c r="O39" t="inlineStr">
+      <c r="N40" t="n">
+        <v>1</v>
+      </c>
+      <c r="O40" t="inlineStr">
         <is>
           <t>럭키비치</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>럭키비치 (총 8화/미완결)</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr">
+      <c r="Q40" t="inlineStr">
         <is>
           <t>총 8화/미완결</t>
         </is>
       </c>
-      <c r="R39" t="n">
+      <c r="R40" t="n">
         <v>8</v>
       </c>
-      <c r="S39" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr">
+      <c r="T40" t="inlineStr">
         <is>
           <t>평점 10.0 | MAJOR, 약수 약수 | 2026.07.18. | 총8화/미완결 | 3화 무료</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="U40" t="inlineStr">
         <is>
           <t>평점 10.0 | MAJOR, 약수 약수 | 2026.07.18. | 총8화/미완결 | 3화 무료</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr">
+      <c r="V40" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14424733</t>
         </is>
       </c>
-      <c r="W39" t="inlineStr">
+      <c r="W40" t="inlineStr">
         <is>
           <t>14424733</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>럭키비치 (총 8화/미완결)
 평점
@@ -6516,155 +6672,155 @@
 “그거 알아? 기는 놈 위에 나는 썅X 있는 거?”불우한 환경과 폐쇄적인 바닷가 촌에서 자라온 소녀 '정임'은,그칠줄 모르는 주변의 부조리와 권태 속에서 결국 폭발,퇴폐업을 하는 고모의 불경한 쌈짓돈을 훔쳐 서울로 상경한..</t>
         </is>
       </c>
-      <c r="Y39" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA39" t="n">
+      <c r="Y40" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA40" t="n">
         <v>105</v>
       </c>
-      <c r="AB39" t="inlineStr">
+      <c r="AB40" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
+      <c r="AC40" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD39" t="inlineStr">
+      <c r="AD40" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF39" t="inlineStr"/>
-      <c r="AG39" t="inlineStr"/>
-      <c r="AH39" t="inlineStr">
+      <c r="AE40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="inlineStr"/>
+      <c r="AH40" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI39" t="inlineStr">
+      <c r="AI40" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>2026-08-10 11:38:13</t>
+      <c r="AJ40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>2026-08-17 11:07:23</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C40" t="n">
+      <c r="C41" t="n">
         <v>5</v>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>2회차 환관이 남성을 되찾음</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=832566&amp;tab=sun</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>832566</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>2026-08-10 10:54:20</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="b">
-        <v>1</v>
-      </c>
-      <c r="J40" t="inlineStr">
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:30</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="b">
+        <v>1</v>
+      </c>
+      <c r="J41" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr">
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="N40" t="n">
-        <v>1</v>
-      </c>
-      <c r="O40" t="inlineStr">
+      <c r="N41" t="n">
+        <v>1</v>
+      </c>
+      <c r="O41" t="inlineStr">
         <is>
           <t>2회차 환관이 남성을 되찾음</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>2회차 환관이 남성을 되찾음 (총 93화/미완결)</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr">
+      <c r="Q41" t="inlineStr">
         <is>
           <t>총 93화/미완결</t>
         </is>
       </c>
-      <c r="R40" t="n">
+      <c r="R41" t="n">
         <v>93</v>
       </c>
-      <c r="S40" t="inlineStr">
+      <c r="S41" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr">
+      <c r="T41" t="inlineStr">
         <is>
           <t>평점 9.6 | LICO, 노빠꾸맨 포스 스튜디오 | 2026.06.13. | 총93화/미완결 | 89화 무료</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="U41" t="inlineStr">
         <is>
           <t>평점 9.6 | LICO, 노빠꾸맨 포스 스튜디오 | 2026.06.13. | 총93화/미완결 | 89화 무료</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr">
+      <c r="V41" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=11636787</t>
         </is>
       </c>
-      <c r="W40" t="inlineStr">
+      <c r="W41" t="inlineStr">
         <is>
           <t>11636787</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>2회차 환관이 남성을 되찾음 (총 93화/미완결)
 평점
@@ -6672,155 +6828,155 @@
 제국의 국정을 마음대로 주무르는 비선실세 환관, 이철수.절대 권력에 돈 많고, 무공까지 강하지만.. 그게 무슨 의미가 있지? '그걸' 못하는데!!환생대법을 통해, 고자가 되기 전으로 회귀한 철수의 목표는 하나다.알파메일이 되..</t>
         </is>
       </c>
-      <c r="Y40" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z40" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA40" t="n">
+      <c r="Y41" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z41" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA41" t="n">
         <v>105</v>
       </c>
-      <c r="AB40" t="inlineStr">
+      <c r="AB41" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
+      <c r="AC41" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD40" t="inlineStr">
+      <c r="AD41" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF40" t="inlineStr"/>
-      <c r="AG40" t="inlineStr"/>
-      <c r="AH40" t="inlineStr">
+      <c r="AE41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="inlineStr"/>
+      <c r="AH41" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI40" t="inlineStr">
+      <c r="AI41" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>2026-08-10 11:38:13</t>
+      <c r="AJ41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>2026-08-17 11:07:23</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C41" t="n">
-        <v>7</v>
-      </c>
-      <c r="D41" t="inlineStr">
+      <c r="C42" t="n">
+        <v>8</v>
+      </c>
+      <c r="D42" t="inlineStr">
         <is>
           <t>어린 아내와 나쁜 짓</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=851385&amp;tab=sun</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>851385</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>2026-08-10 10:54:20</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="b">
-        <v>1</v>
-      </c>
-      <c r="J41" t="inlineStr">
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:30</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="b">
+        <v>1</v>
+      </c>
+      <c r="J42" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr">
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="N41" t="n">
-        <v>1</v>
-      </c>
-      <c r="O41" t="inlineStr">
+      <c r="N42" t="n">
+        <v>1</v>
+      </c>
+      <c r="O42" t="inlineStr">
         <is>
           <t>어린 아내와 나쁜 짓</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>어린 아내와 나쁜 짓 (총 8화/미완결)</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="Q42" t="inlineStr">
         <is>
           <t>총 8화/미완결</t>
         </is>
       </c>
-      <c r="R41" t="n">
+      <c r="R42" t="n">
         <v>8</v>
       </c>
-      <c r="S41" t="inlineStr">
+      <c r="S42" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr">
+      <c r="T42" t="inlineStr">
         <is>
           <t>평점 9.9 | 이리와, 무멘 83 | 2026.06.13. | 총8화/미완결 | 2화 무료</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="U42" t="inlineStr">
         <is>
           <t>평점 9.9 | 이리와, 무멘 83 | 2026.06.13. | 총8화/미완결 | 2화 무료</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr">
+      <c r="V42" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14245757</t>
         </is>
       </c>
-      <c r="W41" t="inlineStr">
+      <c r="W42" t="inlineStr">
         <is>
           <t>14245757</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
+      <c r="X42" t="inlineStr">
         <is>
           <t>어린 아내와 나쁜 짓 (총 8화/미완결)
 평점
@@ -6828,310 +6984,310 @@
 절망의 끝에서 나를 구원해준 남자, 범도건.작고 지켜야할 애기님이라며 내 고백을 짓밞았던 그때와는 다르게...이 남자, 남편 역할을 해도 너무 잘한다.낮에는 세상 든든한 보호자이던 그가 밤만 되면 맹수처럼 집착하며 나를 ..</t>
         </is>
       </c>
-      <c r="Y41" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z41" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA41" t="n">
+      <c r="Y42" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA42" t="n">
         <v>105</v>
       </c>
-      <c r="AB41" t="inlineStr">
+      <c r="AB42" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
+      <c r="AC42" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD41" t="inlineStr">
+      <c r="AD42" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF41" t="inlineStr"/>
-      <c r="AG41" t="inlineStr"/>
-      <c r="AH41" t="inlineStr">
+      <c r="AE42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="inlineStr"/>
+      <c r="AH42" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI41" t="inlineStr">
+      <c r="AI42" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>2026-08-10 11:38:13</t>
+      <c r="AJ42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>2026-08-17 11:07:23</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C42" t="n">
-        <v>9</v>
-      </c>
-      <c r="D42" t="inlineStr">
+      <c r="C43" t="n">
+        <v>11</v>
+      </c>
+      <c r="D43" t="inlineStr">
         <is>
           <t>시루/24/1km</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=850068&amp;tab=sun</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>850068</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>2026-08-10 10:54:20</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="b">
-        <v>1</v>
-      </c>
-      <c r="J42" t="inlineStr">
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:30</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="b">
+        <v>1</v>
+      </c>
+      <c r="J43" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr">
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="N42" t="n">
-        <v>1</v>
-      </c>
-      <c r="O42" t="inlineStr">
+      <c r="N43" t="n">
+        <v>1</v>
+      </c>
+      <c r="O43" t="inlineStr">
         <is>
           <t>19금 시루/24/1km</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>19금 시루/24/1km (총 12화/미완결)</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="Q43" t="inlineStr">
         <is>
           <t>총 12화/미완결</t>
         </is>
       </c>
-      <c r="R42" t="n">
+      <c r="R43" t="n">
         <v>12</v>
       </c>
-      <c r="S42" t="inlineStr">
+      <c r="S43" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr">
+      <c r="T43" t="inlineStr">
         <is>
           <t>평점 10.0 | 6M 941 | 2026.06.13. | 총12화/미완결 | 7화 무료</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="U43" t="inlineStr">
         <is>
           <t>평점 10.0 | 6M 941 | 2026.06.13. | 총12화/미완결 | 7화 무료</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr">
+      <c r="V43" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14081030</t>
         </is>
       </c>
-      <c r="W42" t="inlineStr">
+      <c r="W43" t="inlineStr">
         <is>
           <t>14081030</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
+      <c r="X43" t="inlineStr">
         <is>
           <t>19금 시루/24/1km (총 12화/미완결)
 평점
 10.0 | 6M 941 | 2026.06.13. | 총12화/미완결 | 7화 무료</t>
         </is>
       </c>
-      <c r="Y42" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z42" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA42" t="n">
+      <c r="Y43" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z43" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA43" t="n">
         <v>105</v>
       </c>
-      <c r="AB42" t="inlineStr">
+      <c r="AB43" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
+      <c r="AC43" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD42" t="inlineStr">
+      <c r="AD43" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF42" t="inlineStr"/>
-      <c r="AG42" t="inlineStr"/>
-      <c r="AH42" t="inlineStr">
+      <c r="AE43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="inlineStr"/>
+      <c r="AH43" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI42" t="inlineStr">
+      <c r="AI43" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>2026-08-10 11:38:13</t>
+      <c r="AJ43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>2026-08-17 11:07:23</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C43" t="n">
-        <v>40</v>
-      </c>
-      <c r="D43" t="inlineStr">
+      <c r="C44" t="n">
+        <v>39</v>
+      </c>
+      <c r="D44" t="inlineStr">
         <is>
           <t>서바이브</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=838594&amp;tab=sun</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>838594</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>2026-08-10 10:54:21</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="b">
-        <v>1</v>
-      </c>
-      <c r="J43" t="inlineStr">
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:31</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="b">
+        <v>1</v>
+      </c>
+      <c r="J44" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr">
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="N43" t="n">
+      <c r="N44" t="n">
         <v>2</v>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>연금술 무인도 서바이브</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>연금술 무인도 서바이브 (총 42화/완결)</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>총 42화/완결</t>
         </is>
       </c>
-      <c r="R43" t="n">
+      <c r="R44" t="n">
         <v>42</v>
       </c>
-      <c r="S43" t="inlineStr">
+      <c r="S44" t="inlineStr">
         <is>
           <t>완결</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr">
+      <c r="T44" t="inlineStr">
         <is>
           <t>평점 9.9 | 호시 렌지,이구치 콘 호시 렌지 | 2025.02.24. | 총42화/완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="U44" t="inlineStr">
         <is>
           <t>평점 9.9 | 호시 렌지,이구치 콘 호시 렌지 | 2025.02.24. | 총42화/완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr">
+      <c r="V44" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=10375934</t>
         </is>
       </c>
-      <c r="W43" t="inlineStr">
+      <c r="W44" t="inlineStr">
         <is>
           <t>10375934</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>연금술 무인도 서바이브 (총 42화/완결)
 평점
@@ -7139,161 +7295,161 @@
 항행 중 사고를 당한 연금술사 니코, 요리사 진, 포로남 셋이 표착한 곳은…… 지도에도 표시돼 있지 않은 무인도였다! 「무인도에서 처음으로 해야 할 일은?」, 「물 확보는 어떻게?」, 「식량 수집의 포인트는?」 살아남기 ..</t>
         </is>
       </c>
-      <c r="Y43" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z43" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA43" t="n">
+      <c r="Y44" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z44" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA44" t="n">
         <v>100</v>
       </c>
-      <c r="AB43" t="inlineStr">
+      <c r="AB44" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_2</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
+      <c r="AC44" t="inlineStr">
         <is>
           <t>matched</t>
         </is>
       </c>
-      <c r="AD43" t="inlineStr">
+      <c r="AD44" t="inlineStr">
         <is>
           <t>first_non_compilation_numeric_download</t>
         </is>
       </c>
-      <c r="AE43" t="n">
+      <c r="AE44" t="n">
         <v>2</v>
       </c>
-      <c r="AF43" t="inlineStr">
+      <c r="AF44" t="inlineStr">
         <is>
           <t>5.6천</t>
         </is>
       </c>
-      <c r="AG43" t="n">
+      <c r="AG44" t="n">
         <v>5600</v>
       </c>
-      <c r="AH43" t="inlineStr">
+      <c r="AH44" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="AI43" t="inlineStr">
+      <c r="AI44" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>2026-08-10 11:38:13</t>
+      <c r="AJ44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>2026-08-17 11:07:23</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C44" t="n">
-        <v>45</v>
-      </c>
-      <c r="D44" t="inlineStr">
+      <c r="C45" t="n">
+        <v>44</v>
+      </c>
+      <c r="D45" t="inlineStr">
         <is>
           <t>화스트 페이스</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=847905&amp;tab=sun</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>847905</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>2026-08-10 10:54:21</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="b">
-        <v>1</v>
-      </c>
-      <c r="J44" t="inlineStr">
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:31</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="b">
+        <v>1</v>
+      </c>
+      <c r="J45" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr">
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="N44" t="n">
-        <v>1</v>
-      </c>
-      <c r="O44" t="inlineStr">
+      <c r="N45" t="n">
+        <v>1</v>
+      </c>
+      <c r="O45" t="inlineStr">
         <is>
           <t>화스트 페이스</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>화스트 페이스 (총 24화/미완결)</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
+      <c r="Q45" t="inlineStr">
         <is>
           <t>총 24화/미완결</t>
         </is>
       </c>
-      <c r="R44" t="n">
+      <c r="R45" t="n">
         <v>24</v>
       </c>
-      <c r="S44" t="inlineStr">
+      <c r="S45" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr">
+      <c r="T45" t="inlineStr">
         <is>
           <t>평점 9.9 | NO_Teamkill NO_Teamkill | 2026.06.13. | 총24화/미완결 | 20화 무료</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="U45" t="inlineStr">
         <is>
           <t>평점 9.9 | NO_Teamkill NO_Teamkill | 2026.06.13. | 총24화/미완결 | 20화 무료</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr">
+      <c r="V45" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13750354</t>
         </is>
       </c>
-      <c r="W44" t="inlineStr">
+      <c r="W45" t="inlineStr">
         <is>
           <t>13750354</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
+      <c r="X45" t="inlineStr">
         <is>
           <t>화스트 페이스 (총 24화/미완결)
 평점
@@ -7301,155 +7457,155 @@
 화스트 페이스! 상황 발생! 상황 발생!현재 적 대규모 도발로 인해 준전시상태 돌입!전 병력 전투 장비 구비하고 즉각 출동 준비할 수 있도록!제1부 화스트페이스!제2부 20XX년 XX월 XX일 21시44분!제3부 발령권자 군단장!..</t>
         </is>
       </c>
-      <c r="Y44" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z44" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA44" t="n">
+      <c r="Y45" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z45" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA45" t="n">
         <v>105</v>
       </c>
-      <c r="AB44" t="inlineStr">
+      <c r="AB45" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
+      <c r="AC45" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD44" t="inlineStr">
+      <c r="AD45" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF44" t="inlineStr"/>
-      <c r="AG44" t="inlineStr"/>
-      <c r="AH44" t="inlineStr">
+      <c r="AE45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="inlineStr"/>
+      <c r="AH45" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI44" t="inlineStr">
+      <c r="AI45" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>2026-08-10 11:38:13</t>
+      <c r="AJ45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>2026-08-17 11:07:23</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C45" t="n">
-        <v>75</v>
-      </c>
-      <c r="D45" t="inlineStr">
+      <c r="C46" t="n">
+        <v>76</v>
+      </c>
+      <c r="D46" t="inlineStr">
         <is>
           <t>나는 참지 못한다</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=823476&amp;tab=sun</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>823476</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>2026-08-10 10:54:22</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="b">
-        <v>1</v>
-      </c>
-      <c r="J45" t="inlineStr">
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:33</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="b">
+        <v>1</v>
+      </c>
+      <c r="J46" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr">
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="N45" t="n">
-        <v>1</v>
-      </c>
-      <c r="O45" t="inlineStr">
+      <c r="N46" t="n">
+        <v>1</v>
+      </c>
+      <c r="O46" t="inlineStr">
         <is>
           <t>나는 참지 못한다</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>나는 참지 못한다 (총 115화/미완결)</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="Q46" t="inlineStr">
         <is>
           <t>총 115화/미완결</t>
         </is>
       </c>
-      <c r="R45" t="n">
+      <c r="R46" t="n">
         <v>115</v>
       </c>
-      <c r="S45" t="inlineStr">
+      <c r="S46" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr">
+      <c r="T46" t="inlineStr">
         <is>
           <t>평점 10.0 | 성현 성현 | 2026.06.13. | 총115화/미완결 | 111화 무료</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="U46" t="inlineStr">
         <is>
           <t>평점 10.0 | 성현 성현 | 2026.06.13. | 총115화/미완결 | 111화 무료</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr">
+      <c r="V46" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=10970308</t>
         </is>
       </c>
-      <c r="W45" t="inlineStr">
+      <c r="W46" t="inlineStr">
         <is>
           <t>10970308</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>나는 참지 못한다 (총 115화/미완결)
 평점
@@ -7457,155 +7613,155 @@
 평범한 회사원 김연지는 교통사고 이후 변화를 겪게 된다.스트레스가 폭발하면 아무것도 참지 못하는 상태가 되고 만다.계속 일어나는 통제불능 사건들, 자신에게 접근하는 의문의 남성 민성훈.사건은 커지고 일상은 꼬여만 가..</t>
         </is>
       </c>
-      <c r="Y45" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z45" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA45" t="n">
+      <c r="Y46" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA46" t="n">
         <v>105</v>
       </c>
-      <c r="AB45" t="inlineStr">
+      <c r="AB46" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
+      <c r="AC46" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD45" t="inlineStr">
+      <c r="AD46" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF45" t="inlineStr"/>
-      <c r="AG45" t="inlineStr"/>
-      <c r="AH45" t="inlineStr">
+      <c r="AE46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="inlineStr"/>
+      <c r="AH46" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI45" t="inlineStr">
+      <c r="AI46" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>2026-08-10 11:38:13</t>
+      <c r="AJ46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>2026-08-17 11:07:23</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C46" t="n">
-        <v>80</v>
-      </c>
-      <c r="D46" t="inlineStr">
+      <c r="C47" t="n">
+        <v>79</v>
+      </c>
+      <c r="D47" t="inlineStr">
         <is>
           <t>사내 계약 연애</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=842148&amp;tab=sun</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>842148</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>2026-08-10 10:54:22</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="b">
-        <v>1</v>
-      </c>
-      <c r="J46" t="inlineStr">
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:33</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="b">
+        <v>1</v>
+      </c>
+      <c r="J47" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr">
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="N46" t="n">
-        <v>1</v>
-      </c>
-      <c r="O46" t="inlineStr">
+      <c r="N47" t="n">
+        <v>1</v>
+      </c>
+      <c r="O47" t="inlineStr">
         <is>
           <t>사내 계약 연애</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>사내 계약 연애 (총 48화/미완결)</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="Q47" t="inlineStr">
         <is>
           <t>총 48화/미완결</t>
         </is>
       </c>
-      <c r="R46" t="n">
+      <c r="R47" t="n">
         <v>48</v>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="S47" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr">
+      <c r="T47" t="inlineStr">
         <is>
           <t>평점 9.9 | 최무탁, 미리엄 울 | 2026.06.13. | 총48화/미완결 | 42화 무료</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="U47" t="inlineStr">
         <is>
           <t>평점 9.9 | 최무탁, 미리엄 울 | 2026.06.13. | 총48화/미완결 | 42화 무료</t>
         </is>
       </c>
-      <c r="V46" t="inlineStr">
+      <c r="V47" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13046250</t>
         </is>
       </c>
-      <c r="W46" t="inlineStr">
+      <c r="W47" t="inlineStr">
         <is>
           <t>13046250</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>사내 계약 연애 (총 48화/미완결)
 평점
@@ -7613,161 +7769,161 @@
 예쁘고 잘생긴 것, '미'를 애정하는 서윤.그리고 그런 그녀가 더 애정하는 것은바로 미의 남녀가 서로를 사랑스럽게 탐하는 19금 만화책!그런데 이 미적 추구미에 도달하는 남자가가장 가까이에 그녀의 직속 상사로 있었으니.....</t>
         </is>
       </c>
-      <c r="Y46" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z46" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA46" t="n">
+      <c r="Y47" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z47" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA47" t="n">
         <v>105</v>
       </c>
-      <c r="AB46" t="inlineStr">
+      <c r="AB47" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
+      <c r="AC47" t="inlineStr">
         <is>
           <t>matched</t>
         </is>
       </c>
-      <c r="AD46" t="inlineStr">
+      <c r="AD47" t="inlineStr">
         <is>
           <t>first_non_compilation_numeric_download</t>
         </is>
       </c>
-      <c r="AE46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF46" t="inlineStr">
+      <c r="AE47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF47" t="inlineStr">
         <is>
           <t>51.5만</t>
         </is>
       </c>
-      <c r="AG46" t="n">
+      <c r="AG47" t="n">
         <v>515000</v>
       </c>
-      <c r="AH46" t="inlineStr">
+      <c r="AH47" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="AI46" t="inlineStr">
+      <c r="AI47" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>2026-08-10 11:38:13</t>
+      <c r="AJ47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>2026-08-17 11:07:23</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C47" t="n">
+      <c r="C48" t="n">
         <v>85</v>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>죽거나 혹은 사랑에 빠지거나</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=819696&amp;tab=sun</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>819696</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>2026-08-10 10:54:22</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="b">
-        <v>1</v>
-      </c>
-      <c r="J47" t="inlineStr">
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:33</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="b">
+        <v>1</v>
+      </c>
+      <c r="J48" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr">
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="N47" t="n">
-        <v>1</v>
-      </c>
-      <c r="O47" t="inlineStr">
+      <c r="N48" t="n">
+        <v>1</v>
+      </c>
+      <c r="O48" t="inlineStr">
         <is>
           <t>죽거나 혹은 사랑에 빠지거나</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>죽거나 혹은 사랑에 빠지거나 (총 128화/미완결)</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="Q48" t="inlineStr">
         <is>
           <t>총 128화/미완결</t>
         </is>
       </c>
-      <c r="R47" t="n">
+      <c r="R48" t="n">
         <v>128</v>
       </c>
-      <c r="S47" t="inlineStr">
+      <c r="S48" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T47" t="inlineStr">
+      <c r="T48" t="inlineStr">
         <is>
           <t>평점 9.8 | 허니비 허니비 | 2026.06.13. | 총128화/미완결 | 122화 무료</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="U48" t="inlineStr">
         <is>
           <t>평점 9.8 | 허니비 허니비 | 2026.06.13. | 총128화/미완결 | 122화 무료</t>
         </is>
       </c>
-      <c r="V47" t="inlineStr">
+      <c r="V48" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=10555314</t>
         </is>
       </c>
-      <c r="W47" t="inlineStr">
+      <c r="W48" t="inlineStr">
         <is>
           <t>10555314</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
+      <c r="X48" t="inlineStr">
         <is>
           <t>죽거나 혹은 사랑에 빠지거나 (총 128화/미완결)
 평점
@@ -7775,51 +7931,51 @@
 아름다운 도시 루베른에서 일어나는 의문의 연쇄살인 사건. 조용하고 눈에 띄지 않는 이자벨라에게 살인마의 초대장이 전달되는데.. 목숨을 건 15일간의 내기. 절대 어떤 쾌락과 환상에도 사랑에 빠져서는 안 된다.</t>
         </is>
       </c>
-      <c r="Y47" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z47" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA47" t="n">
+      <c r="Y48" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z48" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA48" t="n">
         <v>105</v>
       </c>
-      <c r="AB47" t="inlineStr">
+      <c r="AB48" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
+      <c r="AC48" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD47" t="inlineStr">
+      <c r="AD48" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE47" t="n">
+      <c r="AE48" t="n">
         <v>2</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
-      <c r="AG47" t="inlineStr"/>
-      <c r="AH47" t="inlineStr">
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="inlineStr"/>
+      <c r="AH48" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI47" t="inlineStr">
+      <c r="AI48" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>2026-08-10 11:38:13</t>
+      <c r="AJ48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>2026-08-17 11:07:23</t>
         </is>
       </c>
     </row>

--- a/data/adult_login_required_webtoons_v2.xlsx
+++ b/data/adult_login_required_webtoons_v2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK48"/>
+  <dimension ref="A1:AK49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -634,7 +634,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:07</t>
+          <t>2026-08-24 10:21:49</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -754,7 +754,7 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:08</t>
+          <t>2026-08-24 10:21:50</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -910,7 +910,7 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:09</t>
+          <t>2026-08-24 10:21:50</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:09</t>
+          <t>2026-08-24 10:21:51</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:09</t>
+          <t>2026-08-24 10:21:51</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:10</t>
+          <t>2026-08-24 10:21:52</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>searched_series</t>
+          <t>reused_existing_product_no</t>
         </is>
       </c>
       <c r="AJ7" t="b">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:11</t>
+          <t>2026-08-24 10:21:53</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:11</t>
+          <t>2026-08-24 10:21:53</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:12</t>
+          <t>2026-08-24 10:21:53</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:12</t>
+          <t>2026-08-24 10:21:53</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:13</t>
+          <t>2026-08-24 10:21:53</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -2345,22 +2345,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>화분</t>
+          <t>원수의 아기를 가졌다</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=851671&amp;tab=tue</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=846110&amp;tab=tue</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>851671</t>
+          <t>846110</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:13</t>
+          <t>2026-08-24 10:21:54</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -2388,48 +2388,204 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
+          <t>원수의 아기를 가졌다</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>원수의 아기를 가졌다 (총 30화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>총 30화/미완결</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>30</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>평점 9.7 | 미니바라기, 안지 이삼 | 2026.06.15. | 총30화/미완결 | 25화 무료</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>평점 9.7 | 미니바라기, 안지 이삼 | 2026.06.15. | 총30화/미완결 | 25화 무료</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=13567690</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>13567690</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>원수의 아기를 가졌다 (총 30화/미완결)
+평점
+9.7 | 미니바라기, 안지 이삼 | 2026.06.15. | 총30화/미완결 | 25화 무료
+서로를 끔찍하게 혐오하는 두 가문 버몬테와 템네스.클로델은 강제 화해를 위한 희생양이 되어 템네스 공작 카이안의 신부가 된다.“템네스의 환영을 받지 못하는 신부로군. 주제를 알고 제 발로 걸어들어오라지.”오랜 반목을 ..</t>
+        </is>
+      </c>
+      <c r="Y13" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>non_compilation_but_download_not_ok</t>
+        </is>
+      </c>
+      <c r="AE13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>2026-08-24 11:08:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>tue</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>화</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>51</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>화분</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=851671&amp;tab=tue</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>851671</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:21:54</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="b">
+        <v>1</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>tue</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>tue</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>화분</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
         <is>
           <t>화분 (총 5화/미완결)</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>총 5화/미완결</t>
         </is>
       </c>
-      <c r="R13" t="n">
+      <c r="R14" t="n">
         <v>5</v>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>평점 10.0 | 쿼시 쿼시 | 2026.06.15. | 총5화/미완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>평점 10.0 | 쿼시 쿼시 | 2026.06.15. | 총5화/미완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14284647</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>14284647</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>화분 (총 5화/미완결)
 평점
@@ -2437,162 +2593,6 @@
 버림받는 것이 무서운 여자와 그런 그녀가 무섭게 느껴지는 남자. 오래된 인연으로 시작된 사랑은 다정함의 얼굴을 한 집착이 되어, 두 사람의 일상과 마음을 서서히 갉아먹어 간다.우리 사랑은, 어디서부터 잘못된거지..?</t>
         </is>
       </c>
-      <c r="Y13" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>105</v>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>review_needed</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>non_compilation_but_download_not_ok</t>
-        </is>
-      </c>
-      <c r="AE13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="inlineStr"/>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>2026-08-17 11:07:23</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>tue</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>화</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>50</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>원수의 아기를 가졌다</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=846110&amp;tab=tue</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>846110</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>2026-08-17 10:20:13</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="b">
-        <v>1</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>tue</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>tue</t>
-        </is>
-      </c>
-      <c r="N14" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>원수의 아기를 가졌다</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>원수의 아기를 가졌다 (총 30화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>총 30화/미완결</t>
-        </is>
-      </c>
-      <c r="R14" t="n">
-        <v>30</v>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>평점 9.7 | 미니바라기, 안지 이삼 | 2026.06.15. | 총30화/미완결 | 25화 무료</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>평점 9.7 | 미니바라기, 안지 이삼 | 2026.06.15. | 총30화/미완결 | 25화 무료</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=13567690</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>13567690</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>원수의 아기를 가졌다 (총 30화/미완결)
-평점
-9.7 | 미니바라기, 안지 이삼 | 2026.06.15. | 총30화/미완결 | 25화 무료
-서로를 끔찍하게 혐오하는 두 가문 버몬테와 템네스.클로델은 강제 화해를 위한 희생양이 되어 템네스 공작 카이안의 신부가 된다.“템네스의 환영을 받지 못하는 신부로군. 주제를 알고 제 발로 걸어들어오라지.”오랜 반목을 ..</t>
-        </is>
-      </c>
       <c r="Y14" t="b">
         <v>0</v>
       </c>
@@ -2637,7 +2637,7 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:14</t>
+          <t>2026-08-24 10:21:55</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -2809,7 +2809,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:15</t>
+          <t>2026-08-24 10:21:56</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:15</t>
+          <t>2026-08-24 10:21:56</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -3105,7 +3105,7 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3121,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:16</t>
+          <t>2026-08-24 10:21:57</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:16</t>
+          <t>2026-08-24 10:21:57</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -3439,26 +3439,26 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>일곱 번째 의뢰인</t>
+          <t>숙녀가 대머리이면 어떻단말인가</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=850210&amp;tab=wed</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=853619&amp;tab=wed</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>850210</t>
+          <t>853619</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:18</t>
+          <t>2026-08-24 10:21:57</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -3486,48 +3486,204 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
+          <t>숙녀가 대머리이면 어떻단 말인가</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>숙녀가 대머리이면 어떻단 말인가 (총 6화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>총 6화/미완결</t>
+        </is>
+      </c>
+      <c r="R20" t="n">
+        <v>6</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>평점 9.6 | 아가사마기 | 2026.08.18. | 총6화/미완결 | 1화 무료</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>평점 9.6 | 아가사마기 | 2026.08.18. | 총6화/미완결 | 1화 무료</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=14563924</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>14563924</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>숙녀가 대머리이면 어떻단 말인가 (총 6화/미완결)
+평점
+9.6 | 아가사마기 | 2026.08.18. | 총6화/미완결 | 1화 무료
+타인의 시선속에서만 살아왔던 정숙녀(23세, 공시생)는 지쳤다. 좋아하는 것도 없고 해야 될 일들만 가득한 인생... 더는 이렇게 살기 싫어!! 기분전환이라도 할까 들어간 미용실에서. 어랏? 뿅! 대머리가 되어버렸다. 오늘부터 대머..</t>
+        </is>
+      </c>
+      <c r="Y20" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>non_compilation_but_download_not_ok</t>
+        </is>
+      </c>
+      <c r="AE20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>searched_series</t>
+        </is>
+      </c>
+      <c r="AJ20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>2026-08-24 11:08:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>wed</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>86</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t>일곱 번째 의뢰인</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=850210&amp;tab=wed</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>850210</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:21:58</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>wed</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>wed</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>일곱 번째 의뢰인</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
         <is>
           <t>일곱 번째 의뢰인 (총 14화/미완결)</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>총 14화/미완결</t>
         </is>
       </c>
-      <c r="R20" t="n">
+      <c r="R21" t="n">
         <v>14</v>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>평점 10.0 | 함영서 함영서 | 2026.06.16. | 총14화/미완결 | 9화 무료</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>평점 10.0 | 함영서 함영서 | 2026.06.16. | 총14화/미완결 | 9화 무료</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14102285</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>14102285</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>일곱 번째 의뢰인 (총 14화/미완결)
 평점
@@ -3535,155 +3691,155 @@
 어린 탐정 맥스는 아무도 주목하지 않는 도박 업자의 죽음을 조사하라는 의뢰를 받는다. 의뢰인이 용의자로 지목한 도박 업자의 아내 제인. 맥스는 그녀를 향한 의심과 이끌림 사이에서 갈등하는데. 제인은 결백한가, 살인자인..</t>
         </is>
       </c>
-      <c r="Y20" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA20" t="n">
+      <c r="Y21" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA21" t="n">
         <v>105</v>
       </c>
-      <c r="AB20" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
+      <c r="AC21" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD20" t="inlineStr">
+      <c r="AD21" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF20" t="inlineStr"/>
-      <c r="AG20" t="inlineStr"/>
-      <c r="AH20" t="inlineStr">
+      <c r="AE21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI20" t="inlineStr">
+      <c r="AI21" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>2026-08-17 11:07:23</t>
+      <c r="AJ21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="C22" t="n">
         <v>5</v>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>소꿉친구 컴플렉스</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=822640&amp;tab=thu</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>822640</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>2026-08-17 10:20:19</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="b">
-        <v>1</v>
-      </c>
-      <c r="J21" t="inlineStr">
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:21:59</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="b">
+        <v>1</v>
+      </c>
+      <c r="J22" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="N21" t="n">
-        <v>1</v>
-      </c>
-      <c r="O21" t="inlineStr">
+      <c r="N22" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" t="inlineStr">
         <is>
           <t>소꿉친구 컴플렉스</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>소꿉친구 컴플렉스 (총 80화/미완결)</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>총 80화/미완결</t>
         </is>
       </c>
-      <c r="R21" t="n">
+      <c r="R22" t="n">
         <v>80</v>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>평점 9.8 | 은하이 은하이 | 2026.06.17. | 총80화/미완결 | 76화 무료</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>평점 9.8 | 은하이 은하이 | 2026.06.17. | 총80화/미완결 | 76화 무료</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=10851069</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>10851069</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>소꿉친구 컴플렉스 (총 80화/미완결)
 평점
@@ -3691,155 +3847,155 @@
 20살에 20년지기, 평생을 함께한 소꿉친구 하늘과 민철.그런 소꿉친구의 알고 싶지 않은 은밀한 사정을 알아버렸다?!서로를 이성으로 생각한 적이 결코 없는 두사람이지만,오해가 오해를 낳고 착각이 착각을 낳는 상황들 속에..</t>
         </is>
       </c>
-      <c r="Y21" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA21" t="n">
+      <c r="Y22" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA22" t="n">
         <v>105</v>
       </c>
-      <c r="AB21" t="inlineStr">
+      <c r="AB22" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
+      <c r="AC22" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD21" t="inlineStr">
+      <c r="AD22" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE21" t="n">
+      <c r="AE22" t="n">
         <v>3</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
-      <c r="AG21" t="inlineStr"/>
-      <c r="AH21" t="inlineStr">
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI21" t="inlineStr">
+      <c r="AI22" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>2026-08-17 11:07:23</t>
+      <c r="AJ22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="C22" t="n">
+      <c r="C23" t="n">
         <v>6</v>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>럭키비치</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=852498&amp;tab=thu</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>852498</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>2026-08-17 10:20:19</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="b">
-        <v>1</v>
-      </c>
-      <c r="J22" t="inlineStr">
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:21:59</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="b">
+        <v>1</v>
+      </c>
+      <c r="J23" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
         <is>
           <t>thu,sun</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>thu,sun</t>
         </is>
       </c>
-      <c r="N22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O22" t="inlineStr">
+      <c r="N23" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" t="inlineStr">
         <is>
           <t>럭키비치</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>럭키비치 (총 8화/미완결)</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>총 8화/미완결</t>
         </is>
       </c>
-      <c r="R22" t="n">
+      <c r="R23" t="n">
         <v>8</v>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>평점 10.0 | MAJOR, 약수 약수 | 2026.07.18. | 총8화/미완결 | 3화 무료</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>평점 10.0 | MAJOR, 약수 약수 | 2026.07.18. | 총8화/미완결 | 3화 무료</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14424733</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>14424733</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>럭키비치 (총 8화/미완결)
 평점
@@ -3847,155 +4003,155 @@
 “그거 알아? 기는 놈 위에 나는 썅X 있는 거?”불우한 환경과 폐쇄적인 바닷가 촌에서 자라온 소녀 '정임'은,그칠줄 모르는 주변의 부조리와 권태 속에서 결국 폭발,퇴폐업을 하는 고모의 불경한 쌈짓돈을 훔쳐 서울로 상경한..</t>
         </is>
       </c>
-      <c r="Y22" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z22" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA22" t="n">
+      <c r="Y23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA23" t="n">
         <v>105</v>
       </c>
-      <c r="AB22" t="inlineStr">
+      <c r="AB23" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
+      <c r="AC23" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD22" t="inlineStr">
+      <c r="AD23" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF22" t="inlineStr"/>
-      <c r="AG22" t="inlineStr"/>
-      <c r="AH22" t="inlineStr">
+      <c r="AE23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI22" t="inlineStr">
+      <c r="AI23" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>2026-08-17 11:07:23</t>
+      <c r="AJ23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="C23" t="n">
-        <v>34</v>
-      </c>
-      <c r="D23" t="inlineStr">
+      <c r="C24" t="n">
+        <v>22</v>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>나의 경험</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=853278&amp;tab=thu</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>853278</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>2026-08-17 10:20:20</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="b">
-        <v>1</v>
-      </c>
-      <c r="J23" t="inlineStr">
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:21:59</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="b">
+        <v>1</v>
+      </c>
+      <c r="J24" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="N23" t="n">
-        <v>1</v>
-      </c>
-      <c r="O23" t="inlineStr">
+      <c r="N24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" t="inlineStr">
         <is>
           <t>나의 경험</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>나의 경험 (총 6화/미완결)</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>총 6화/미완결</t>
         </is>
       </c>
-      <c r="R23" t="n">
+      <c r="R24" t="n">
         <v>6</v>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>평점 7.0 | 윤박 윤박 | 2026.08.12. | 총6화/미완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>평점 7.0 | 윤박 윤박 | 2026.08.12. | 총6화/미완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14532341</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>14532341</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>나의 경험 (총 6화/미완결)
 평점
@@ -4003,155 +4159,155 @@
 살다 보면 한 번쯤 인연이 물밀듯 밀려 들어오는 순간들이 있다.별다를 것 없던 평범한 스무 살 재우의 일상에도예상치 못한 만남이 하나둘 찾아오기 시작한다.서툴지만 사랑만큼은 누구보다 진심인 재우는 믿는다.이번만큼은 ..</t>
         </is>
       </c>
-      <c r="Y23" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z23" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA23" t="n">
+      <c r="Y24" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA24" t="n">
         <v>105</v>
       </c>
-      <c r="AB23" t="inlineStr">
+      <c r="AB24" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
+      <c r="AC24" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD23" t="inlineStr">
+      <c r="AD24" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF23" t="inlineStr"/>
-      <c r="AG23" t="inlineStr"/>
-      <c r="AH23" t="inlineStr">
+      <c r="AE24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>searched_series</t>
-        </is>
-      </c>
-      <c r="AJ23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>2026-08-17 11:07:23</t>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>58</v>
-      </c>
-      <c r="D24" t="inlineStr">
+      <c r="C25" t="n">
+        <v>62</v>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>당신에게 얽힌 채</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=849879&amp;tab=thu</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>849879</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>2026-08-17 10:20:20</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="b">
-        <v>1</v>
-      </c>
-      <c r="J24" t="inlineStr">
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:22:00</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="b">
+        <v>1</v>
+      </c>
+      <c r="J25" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="N24" t="n">
-        <v>1</v>
-      </c>
-      <c r="O24" t="inlineStr">
+      <c r="N25" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" t="inlineStr">
         <is>
           <t>당신에게 얽힌 채</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>당신에게 얽힌 채 (총 10화/미완결)</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>총 10화/미완결</t>
         </is>
       </c>
-      <c r="R24" t="n">
+      <c r="R25" t="n">
         <v>10</v>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>평점 10.0 | Nicole Knight, 유다 danah789 | 2026.06.17. | 총10화/미완결 | 5화 무료</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>평점 10.0 | Nicole Knight, 유다 danah789 | 2026.06.17. | 총10화/미완결 | 5화 무료</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14041685</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>14041685</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>당신에게 얽힌 채 (총 10화/미완결)
 평점
@@ -4159,155 +4315,155 @@
 상속자가 아닌 복종하는 존재로 길러진 에이바 모레티. 뉴욕에서 가장 강력한 마피아 가문의 막내딸인 그녀는 ‘집안의 사고뭉치’라는 오명을 벗고 자신의 자리를 찾기 위해 분투한다.그러던 어느 날 밤, 낯선 남자와 보낸 뜨..</t>
         </is>
       </c>
-      <c r="Y24" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z24" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA24" t="n">
+      <c r="Y25" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA25" t="n">
         <v>105</v>
       </c>
-      <c r="AB24" t="inlineStr">
+      <c r="AB25" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
+      <c r="AC25" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD24" t="inlineStr">
+      <c r="AD25" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF24" t="inlineStr"/>
-      <c r="AG24" t="inlineStr"/>
-      <c r="AH24" t="inlineStr">
+      <c r="AE25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI24" t="inlineStr">
+      <c r="AI25" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>2026-08-17 11:07:23</t>
+      <c r="AJ25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C25" t="n">
+      <c r="C26" t="n">
         <v>2</v>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>오! 나의 교주님</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=841624&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>841624</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>2026-08-17 10:20:22</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="b">
-        <v>1</v>
-      </c>
-      <c r="J25" t="inlineStr">
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:22:02</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="b">
+        <v>1</v>
+      </c>
+      <c r="J26" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
         <is>
           <t>tue,fri</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>tue,fri</t>
         </is>
       </c>
-      <c r="N25" t="n">
-        <v>1</v>
-      </c>
-      <c r="O25" t="inlineStr">
+      <c r="N26" t="n">
+        <v>1</v>
+      </c>
+      <c r="O26" t="inlineStr">
         <is>
           <t>오! 나의 교주님</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>오! 나의 교주님 (총 94화/미완결)</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>총 94화/미완결</t>
         </is>
       </c>
-      <c r="R25" t="n">
+      <c r="R26" t="n">
         <v>94</v>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>평점 9.4 | 김꿀빨, 김완두 김꿀빨, 김완두 | 2026.06.18. | 총94화/미완결 | 89화 무료</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>평점 9.4 | 김꿀빨, 김완두 김꿀빨, 김완두 | 2026.06.18. | 총94화/미완결 | 89화 무료</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=12998643</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>12998643</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>오! 나의 교주님 (총 94화/미완결)
 평점
@@ -4315,155 +4471,155 @@
 사이비 종교 ‘진천교’에서 태어나 평생을 그곳에서 살아온 한성민. 그는 결국 모든 것을 잃고 홀로 탈출한다.수년 후, 성인이 된 그는 다시 진천교에 잠입해 처절한 복수를 시작하려 한다.“오, 나의 교주님. 제가 보내드릴게..</t>
         </is>
       </c>
-      <c r="Y25" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA25" t="n">
+      <c r="Y26" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA26" t="n">
         <v>105</v>
       </c>
-      <c r="AB25" t="inlineStr">
+      <c r="AB26" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
+      <c r="AC26" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD25" t="inlineStr">
+      <c r="AD26" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF25" t="inlineStr"/>
-      <c r="AG25" t="inlineStr"/>
-      <c r="AH25" t="inlineStr">
+      <c r="AE26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI25" t="inlineStr">
+      <c r="AI26" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>2026-08-17 11:07:23</t>
+      <c r="AJ26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C26" t="n">
+      <c r="C27" t="n">
         <v>9</v>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>두 얼굴</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=845646&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>845646</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>2026-08-17 10:20:22</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="b">
-        <v>1</v>
-      </c>
-      <c r="J26" t="inlineStr">
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:22:02</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="b">
+        <v>1</v>
+      </c>
+      <c r="J27" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="N26" t="n">
-        <v>1</v>
-      </c>
-      <c r="O26" t="inlineStr">
+      <c r="N27" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" t="inlineStr">
         <is>
           <t>두 얼굴의 대표님</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>두 얼굴의 대표님 (총 126화/완결)</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>총 126화/완결</t>
         </is>
       </c>
-      <c r="R26" t="n">
+      <c r="R27" t="n">
         <v>126</v>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>완결</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>평점 6.2 | 1M, KuaiKan, YY 1M, KuaiKan, YY | 2022.10.02. | 총126화/완결 | 3화 무료</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>평점 6.2 | 1M, KuaiKan, YY 1M, KuaiKan, YY | 2022.10.02. | 총126화/완결 | 3화 무료</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=6489984</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>6489984</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>두 얼굴의 대표님 (총 126화/완결)
 평점
@@ -4471,161 +4627,161 @@
 재벌가의 사생아로 태어난 소원은 일찍 엄마를 잃고, 가족들의 멸시 속에서 살아왔다.그러다 언니에게 약혼자까지 뺏기게 되자, 실의에 빠진 소원은 유학을 떠나게 되고, 그곳에서 평범한 남편을 만나 결혼을 하게 된다.1년 후 ..</t>
         </is>
       </c>
-      <c r="Y26" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z26" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA26" t="n">
+      <c r="Y27" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA27" t="n">
         <v>105</v>
       </c>
-      <c r="AB26" t="inlineStr">
+      <c r="AB27" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
+      <c r="AC27" t="inlineStr">
         <is>
           <t>matched</t>
         </is>
       </c>
-      <c r="AD26" t="inlineStr">
+      <c r="AD27" t="inlineStr">
         <is>
           <t>first_non_compilation_numeric_download</t>
         </is>
       </c>
-      <c r="AE26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF26" t="inlineStr">
+      <c r="AE27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF27" t="inlineStr">
         <is>
           <t>157.5만</t>
         </is>
       </c>
-      <c r="AG26" t="n">
+      <c r="AG27" t="n">
         <v>1575000</v>
       </c>
-      <c r="AH26" t="inlineStr">
+      <c r="AH27" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="AI26" t="inlineStr">
+      <c r="AI27" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>2026-08-17 11:07:23</t>
+      <c r="AJ27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C27" t="n">
+      <c r="C28" t="n">
         <v>10</v>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>네가 사는 그 집</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=842465&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>842465</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>2026-08-17 10:20:22</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="b">
-        <v>1</v>
-      </c>
-      <c r="J27" t="inlineStr">
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:22:02</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="b">
+        <v>1</v>
+      </c>
+      <c r="J28" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="N27" t="n">
-        <v>1</v>
-      </c>
-      <c r="O27" t="inlineStr">
+      <c r="N28" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" t="inlineStr">
         <is>
           <t>네가 사는 그 집</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>네가 사는 그 집 (총 47화/미완결)</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>총 47화/미완결</t>
         </is>
       </c>
-      <c r="R27" t="n">
+      <c r="R28" t="n">
         <v>47</v>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>평점 9.7 | 석우 해바다 | 2026.06.18. | 총47화/미완결 | 41화 무료</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>평점 9.7 | 석우 해바다 | 2026.06.18. | 총47화/미완결 | 41화 무료</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13090391</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>13090391</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>네가 사는 그 집 (총 47화/미완결)
 평점
@@ -4633,155 +4789,155 @@
 찢어지게 가난한 집에서 두 아이를 키우며 힘겹게 살아가던 30대 화린.어느날, 자기 첫사랑이었던 부유한 선배와 결혼해 행복하게 사는 친구와 몸이 바뀐다.하지만 부러워하던 삶을 얻은 기쁨도 잠시,그 집의 추악한 비밀이 드..</t>
         </is>
       </c>
-      <c r="Y27" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA27" t="n">
+      <c r="Y28" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA28" t="n">
         <v>105</v>
       </c>
-      <c r="AB27" t="inlineStr">
+      <c r="AB28" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
+      <c r="AC28" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD27" t="inlineStr">
+      <c r="AD28" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF27" t="inlineStr"/>
-      <c r="AG27" t="inlineStr"/>
-      <c r="AH27" t="inlineStr">
+      <c r="AE28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI27" t="inlineStr">
+      <c r="AI28" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>2026-08-17 11:07:23</t>
+      <c r="AJ28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C28" t="n">
+      <c r="C29" t="n">
         <v>11</v>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>그리디</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=845919&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>845919</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>2026-08-17 10:20:22</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="b">
-        <v>1</v>
-      </c>
-      <c r="J28" t="inlineStr">
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:22:02</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="b">
+        <v>1</v>
+      </c>
+      <c r="J29" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="N28" t="n">
-        <v>1</v>
-      </c>
-      <c r="O28" t="inlineStr">
+      <c r="N29" t="n">
+        <v>1</v>
+      </c>
+      <c r="O29" t="inlineStr">
         <is>
           <t>그리디</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>그리디 (총 31화/미완결)</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>총 31화/미완결</t>
         </is>
       </c>
-      <c r="R28" t="n">
+      <c r="R29" t="n">
         <v>31</v>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>평점 9.9 | 영하 랑라리 | 2026.06.18. | 총31화/미완결 | 25화 무료</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>평점 9.9 | 영하 랑라리 | 2026.06.18. | 총31화/미완결 | 25화 무료</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13530624</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>13530624</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>그리디 (총 31화/미완결)
 평점
@@ -4789,162 +4945,6 @@
 파혼했다. 십년지기 친구와 내가 파혼한 남자가 찍힌 청첩장 한 장.한유주는 그걸 끝으로 서른하나에 사랑도 우정도 다 버렸다. 남은 건 칼럼 한 줄에도 이름을 걸 수 없는 5년짜리 패션지 주니어 에디터 신세뿐.일도 사랑도, 마..</t>
         </is>
       </c>
-      <c r="Y28" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z28" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>105</v>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>review_needed</t>
-        </is>
-      </c>
-      <c r="AD28" t="inlineStr">
-        <is>
-          <t>non_compilation_but_download_not_ok</t>
-        </is>
-      </c>
-      <c r="AE28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF28" t="inlineStr"/>
-      <c r="AG28" t="inlineStr"/>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>2026-08-17 11:07:23</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>fri</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>금</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>36</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>로맨스 저주</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=834035&amp;tab=fri</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>834035</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>2026-08-17 10:20:23</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="b">
-        <v>1</v>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>fri</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>fri</t>
-        </is>
-      </c>
-      <c r="N29" t="n">
-        <v>1</v>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>로맨스 저주</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>로맨스 저주 (총 92화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>총 92화/미완결</t>
-        </is>
-      </c>
-      <c r="R29" t="n">
-        <v>92</v>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>평점 9.9 | 다원 다원 | 2026.06.18. | 총92화/미완결 | 85화 무료</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>평점 9.9 | 다원 다원 | 2026.06.18. | 총92화/미완결 | 85화 무료</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=11824393</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>11824393</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>로맨스 저주 (총 92화/미완결)
-평점
-9.9 | 다원 다원 | 2026.06.18. | 총92화/미완결 | 85화 무료
-희수는 타인을 저주하는 글을 쓰면 현실이 되는 신비한 노트를 택배로 받는다.심지어 저주를 할 때마다 현금이 나온다!희수는 짝사랑하던 남자 현우를 저주해 자신과의 로맨스를 강요한다.하지만 뜻대로 되지 않고, 일이 꼬여..</t>
-        </is>
-      </c>
       <c r="Y29" t="b">
         <v>0</v>
       </c>
@@ -4970,7 +4970,7 @@
         </is>
       </c>
       <c r="AE29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="inlineStr"/>
@@ -4989,7 +4989,7 @@
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:23</t>
+          <t>2026-08-24 10:22:03</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:24</t>
+          <t>2026-08-24 10:22:04</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -5333,22 +5333,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>죽여주는 캐스팅</t>
+          <t>사탄의 순애</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=843866&amp;tab=fri</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=845378&amp;tab=fri</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>843866</t>
+          <t>845378</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:24</t>
+          <t>2026-08-24 10:22:04</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
@@ -5376,48 +5376,204 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
+          <t>사탄의 순애 [독점]</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>사탄의 순애 [독점] (총 35화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>총 35화/미완결</t>
+        </is>
+      </c>
+      <c r="R32" t="n">
+        <v>35</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>평점 9.8 | 용현 카모모 | 2026.06.18. | 총35화/미완결 | 28화 무료</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>평점 9.8 | 용현 카모모 | 2026.06.18. | 총35화/미완결 | 28화 무료</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=13451638</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>13451638</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>사탄의 순애 [독점] (총 35화/미완결)
+평점
+9.8 | 용현 카모모 | 2026.06.18. | 총35화/미완결 | 28화 무료
+초식동물계 대표주자 호구남 백은우 VS 육식동물계 대표주자 차도녀 범호연.정반대의 두 사람은 어쩌다 사귀게 됐을까?“백은우. 나한테 취업해라. 내 애인인 척 딱 1년. 그럼 10억이야.”업계에서 악마로 소문난 아티스트 레..</t>
+        </is>
+      </c>
+      <c r="Y32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>non_compilation_but_download_not_ok</t>
+        </is>
+      </c>
+      <c r="AE32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="inlineStr"/>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>2026-08-24 11:08:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>70</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>죽여주는 캐스팅</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=843866&amp;tab=fri</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>843866</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:22:04</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="b">
+        <v>1</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>1</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
           <t>죽여주는 캐스팅 [독점]</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>죽여주는 캐스팅 [독점] (총 42화/미완결)</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>총 42화/미완결</t>
         </is>
       </c>
-      <c r="R32" t="n">
+      <c r="R33" t="n">
         <v>42</v>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>평점 9.6 | 영춘 하보 | 2026.06.18. | 총42화/미완결 | 36화 무료</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>평점 9.6 | 영춘 하보 | 2026.06.18. | 총42화/미완결 | 36화 무료</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
+      <c r="V33" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13253015</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr">
+      <c r="W33" t="inlineStr">
         <is>
           <t>13253015</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>죽여주는 캐스팅 [독점] (총 42화/미완결)
 평점
@@ -5425,162 +5581,6 @@
 영화감상 동호회에서 만난 혜수와 강호.성공한 배우를 꿈꾸는 강호는 오디션과 술자리에 몰두하며 혜수에게 기대어 살아간다.그런 강호를 이해하고자 혜수는 연기 수업을 시작하고 점차 자신의 길을 걷기 시작한다.하지만 강..</t>
         </is>
       </c>
-      <c r="Y32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z32" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>105</v>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>review_needed</t>
-        </is>
-      </c>
-      <c r="AD32" t="inlineStr">
-        <is>
-          <t>non_compilation_but_download_not_ok</t>
-        </is>
-      </c>
-      <c r="AE32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF32" t="inlineStr"/>
-      <c r="AG32" t="inlineStr"/>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>2026-08-17 11:07:23</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>fri</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>금</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>70</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>사탄의 순애</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=845378&amp;tab=fri</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>845378</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>2026-08-17 10:20:24</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="b">
-        <v>1</v>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>fri</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>fri</t>
-        </is>
-      </c>
-      <c r="N33" t="n">
-        <v>1</v>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>사탄의 순애 [독점]</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>사탄의 순애 [독점] (총 35화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>총 35화/미완결</t>
-        </is>
-      </c>
-      <c r="R33" t="n">
-        <v>35</v>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>평점 9.8 | 용현 카모모 | 2026.06.18. | 총35화/미완결 | 28화 무료</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>평점 9.8 | 용현 카모모 | 2026.06.18. | 총35화/미완결 | 28화 무료</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=13451638</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>13451638</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>사탄의 순애 [독점] (총 35화/미완결)
-평점
-9.8 | 용현 카모모 | 2026.06.18. | 총35화/미완결 | 28화 무료
-초식동물계 대표주자 호구남 백은우 VS 육식동물계 대표주자 차도녀 범호연.정반대의 두 사람은 어쩌다 사귀게 됐을까?“백은우. 나한테 취업해라. 내 애인인 척 딱 1년. 그럼 10억이야.”업계에서 악마로 소문난 아티스트 레..</t>
-        </is>
-      </c>
       <c r="Y33" t="b">
         <v>0</v>
       </c>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:26</t>
+          <t>2026-08-24 10:22:05</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -5815,7 +5815,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:26</t>
+          <t>2026-08-24 10:22:05</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
@@ -5936,7 +5936,7 @@
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -5971,7 +5971,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:26</t>
+          <t>2026-08-24 10:22:06</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -6108,7 +6108,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:26</t>
+          <t>2026-08-24 10:22:06</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -6264,7 +6264,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:27</t>
+          <t>2026-08-24 10:22:06</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -6404,7 +6404,7 @@
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -6439,7 +6439,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:27</t>
+          <t>2026-08-24 10:22:07</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
@@ -6560,7 +6560,7 @@
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -6595,7 +6595,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:30</t>
+          <t>2026-08-24 10:22:09</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -6732,7 +6732,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6751,7 +6751,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:30</t>
+          <t>2026-08-24 10:22:09</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -6872,7 +6872,7 @@
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -6888,7 +6888,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:30</t>
+          <t>2026-08-24 10:22:09</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
@@ -7028,7 +7028,7 @@
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -7044,7 +7044,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:30</t>
+          <t>2026-08-24 10:22:09</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
@@ -7183,7 +7183,7 @@
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -7218,7 +7218,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:31</t>
+          <t>2026-08-24 10:22:10</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
@@ -7345,7 +7345,7 @@
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -7361,7 +7361,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -7380,7 +7380,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:31</t>
+          <t>2026-08-24 10:22:10</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
@@ -7501,7 +7501,7 @@
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -7517,26 +7517,26 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>나는 참지 못한다</t>
+          <t>지옥심판</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=823476&amp;tab=sun</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=854096&amp;tab=sun</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>823476</t>
+          <t>854096</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:33</t>
+          <t>2026-08-24 10:22:10</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
@@ -7564,48 +7564,204 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
+          <t>지옥심판</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>지옥심판 (총 7화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>총 7화/미완결</t>
+        </is>
+      </c>
+      <c r="R46" t="n">
+        <v>7</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>평점 9.6 | 가강 주혁 | 2026.08.22. | 총7화/미완결 | 2화 무료</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>평점 9.6 | 가강 주혁 | 2026.08.22. | 총7화/미완결 | 2화 무료</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=14622042</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>14622042</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>지옥심판 (총 7화/미완결)
+평점
+9.6 | 가강 주혁 | 2026.08.22. | 총7화/미완결 | 2화 무료
+죄를 지은 인간은 언젠가 벌을 받게 되어있다. 이승이 아닌 저승에서라도.죄인을 심판하고 지옥으로 인도하는 저승사자 이현의 이야기.</t>
+        </is>
+      </c>
+      <c r="Y46" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>non_compilation_but_download_not_ok</t>
+        </is>
+      </c>
+      <c r="AE46" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="inlineStr"/>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>searched_series</t>
+        </is>
+      </c>
+      <c r="AJ46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>2026-08-24 11:08:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>76</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
           <t>나는 참지 못한다</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=823476&amp;tab=sun</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>823476</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:22:10</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="b">
+        <v>1</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>1</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>나는 참지 못한다</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
         <is>
           <t>나는 참지 못한다 (총 115화/미완결)</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="Q47" t="inlineStr">
         <is>
           <t>총 115화/미완결</t>
         </is>
       </c>
-      <c r="R46" t="n">
+      <c r="R47" t="n">
         <v>115</v>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="S47" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr">
+      <c r="T47" t="inlineStr">
         <is>
           <t>평점 10.0 | 성현 성현 | 2026.06.13. | 총115화/미완결 | 111화 무료</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="U47" t="inlineStr">
         <is>
           <t>평점 10.0 | 성현 성현 | 2026.06.13. | 총115화/미완결 | 111화 무료</t>
         </is>
       </c>
-      <c r="V46" t="inlineStr">
+      <c r="V47" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=10970308</t>
         </is>
       </c>
-      <c r="W46" t="inlineStr">
+      <c r="W47" t="inlineStr">
         <is>
           <t>10970308</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>나는 참지 못한다 (총 115화/미완결)
 평점
@@ -7613,162 +7769,6 @@
 평범한 회사원 김연지는 교통사고 이후 변화를 겪게 된다.스트레스가 폭발하면 아무것도 참지 못하는 상태가 되고 만다.계속 일어나는 통제불능 사건들, 자신에게 접근하는 의문의 남성 민성훈.사건은 커지고 일상은 꼬여만 가..</t>
         </is>
       </c>
-      <c r="Y46" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z46" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>105</v>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>review_needed</t>
-        </is>
-      </c>
-      <c r="AD46" t="inlineStr">
-        <is>
-          <t>non_compilation_but_download_not_ok</t>
-        </is>
-      </c>
-      <c r="AE46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF46" t="inlineStr"/>
-      <c r="AG46" t="inlineStr"/>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>2026-08-17 11:07:23</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>79</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>사내 계약 연애</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=842148&amp;tab=sun</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>842148</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>2026-08-17 10:20:33</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="b">
-        <v>1</v>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="N47" t="n">
-        <v>1</v>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>사내 계약 연애</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>사내 계약 연애 (총 48화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>총 48화/미완결</t>
-        </is>
-      </c>
-      <c r="R47" t="n">
-        <v>48</v>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>평점 9.9 | 최무탁, 미리엄 울 | 2026.06.13. | 총48화/미완결 | 42화 무료</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>평점 9.9 | 최무탁, 미리엄 울 | 2026.06.13. | 총48화/미완결 | 42화 무료</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=13046250</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>13046250</t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>사내 계약 연애 (총 48화/미완결)
-평점
-9.9 | 최무탁, 미리엄 울 | 2026.06.13. | 총48화/미완결 | 42화 무료
-예쁘고 잘생긴 것, '미'를 애정하는 서윤.그리고 그런 그녀가 더 애정하는 것은바로 미의 남녀가 서로를 사랑스럽게 탐하는 19금 만화책!그런데 이 미적 추구미에 도달하는 남자가가장 가까이에 그녀의 직속 상사로 있었으니.....</t>
-        </is>
-      </c>
       <c r="Y47" t="b">
         <v>0</v>
       </c>
@@ -7785,28 +7785,22 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>matched</t>
+          <t>review_needed</t>
         </is>
       </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>first_non_compilation_numeric_download</t>
+          <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
       <c r="AE47" t="n">
         <v>1</v>
       </c>
-      <c r="AF47" t="inlineStr">
-        <is>
-          <t>51.5만</t>
-        </is>
-      </c>
-      <c r="AG47" t="n">
-        <v>515000</v>
-      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="inlineStr"/>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>not_found</t>
         </is>
       </c>
       <c r="AI47" t="inlineStr">
@@ -7819,7 +7813,7 @@
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>2026-08-17 11:07:23</t>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>
@@ -7839,22 +7833,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>죽거나 혹은 사랑에 빠지거나</t>
+          <t>꿈에서 본 그놈이 대단해!</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=819696&amp;tab=sun</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=854132&amp;tab=sun</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>819696</t>
+          <t>854132</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:33</t>
+          <t>2026-08-24 10:22:11</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
@@ -7882,48 +7876,204 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
+          <t>꿈에서 본 그놈이 대단해! [독점]</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>꿈에서 본 그놈이 대단해! [독점] (총 6화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>총 6화/미완결</t>
+        </is>
+      </c>
+      <c r="R48" t="n">
+        <v>6</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>평점 8.5 | LICO 미지 | 2026.08.22. | 총6화/미완결 | 1화 무료</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>평점 8.5 | LICO 미지 | 2026.08.22. | 총6화/미완결 | 1화 무료</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=14626941</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>14626941</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>꿈에서 본 그놈이 대단해! [독점] (총 6화/미완결)
+평점
+8.5 | LICO 미지 | 2026.08.22. | 총6화/미완결 | 1화 무료
+MBTI TTTT인 28세 여성 공무정. 어느날부터 누군가와 살이 닿으면 그 사람의 섹X를 꿈으로 보는 일명 '색몽'을 꾸게 된다. 그런 무정에게 친구 남순과 인턴 강이 들이대기 시작하고. 무정은 원치 않게 남순과 강의 색몽을 보..</t>
+        </is>
+      </c>
+      <c r="Y48" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z48" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t>non_compilation_but_download_not_ok</t>
+        </is>
+      </c>
+      <c r="AE48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="inlineStr"/>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>searched_series</t>
+        </is>
+      </c>
+      <c r="AJ48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>2026-08-24 11:08:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>88</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
           <t>죽거나 혹은 사랑에 빠지거나</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=819696&amp;tab=sun</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>819696</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:22:11</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="b">
+        <v>1</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>1</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>죽거나 혹은 사랑에 빠지거나</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
         <is>
           <t>죽거나 혹은 사랑에 빠지거나 (총 128화/미완결)</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
+      <c r="Q49" t="inlineStr">
         <is>
           <t>총 128화/미완결</t>
         </is>
       </c>
-      <c r="R48" t="n">
+      <c r="R49" t="n">
         <v>128</v>
       </c>
-      <c r="S48" t="inlineStr">
+      <c r="S49" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr">
+      <c r="T49" t="inlineStr">
         <is>
           <t>평점 9.8 | 허니비 허니비 | 2026.06.13. | 총128화/미완결 | 122화 무료</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="U49" t="inlineStr">
         <is>
           <t>평점 9.8 | 허니비 허니비 | 2026.06.13. | 총128화/미완결 | 122화 무료</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr">
+      <c r="V49" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=10555314</t>
         </is>
       </c>
-      <c r="W48" t="inlineStr">
+      <c r="W49" t="inlineStr">
         <is>
           <t>10555314</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
+      <c r="X49" t="inlineStr">
         <is>
           <t>죽거나 혹은 사랑에 빠지거나 (총 128화/미완결)
 평점
@@ -7931,51 +8081,51 @@
 아름다운 도시 루베른에서 일어나는 의문의 연쇄살인 사건. 조용하고 눈에 띄지 않는 이자벨라에게 살인마의 초대장이 전달되는데.. 목숨을 건 15일간의 내기. 절대 어떤 쾌락과 환상에도 사랑에 빠져서는 안 된다.</t>
         </is>
       </c>
-      <c r="Y48" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z48" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA48" t="n">
+      <c r="Y49" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z49" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA49" t="n">
         <v>105</v>
       </c>
-      <c r="AB48" t="inlineStr">
+      <c r="AB49" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
+      <c r="AC49" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD48" t="inlineStr">
+      <c r="AD49" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE48" t="n">
+      <c r="AE49" t="n">
         <v>2</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
-      <c r="AG48" t="inlineStr"/>
-      <c r="AH48" t="inlineStr">
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="inlineStr"/>
+      <c r="AH49" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI48" t="inlineStr">
+      <c r="AI49" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>2026-08-17 11:07:23</t>
+      <c r="AJ49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>2026-08-24 11:08:04</t>
         </is>
       </c>
     </row>

--- a/data/adult_login_required_webtoons_v2.xlsx
+++ b/data/adult_login_required_webtoons_v2.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-24 10:21:49</t>
+          <t>2026-08-31 13:16:31</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -754,7 +754,7 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2026-08-24 11:08:04</t>
+          <t>2026-08-31 13:56:12</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-24 10:21:50</t>
+          <t>2026-08-31 13:16:32</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -910,7 +910,7 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2026-08-24 11:08:04</t>
+          <t>2026-08-31 13:56:12</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-24 10:21:50</t>
+          <t>2026-08-31 13:16:33</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2026-08-24 11:08:04</t>
+          <t>2026-08-31 13:56:12</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-24 10:21:51</t>
+          <t>2026-08-31 13:16:33</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2026-08-24 11:08:04</t>
+          <t>2026-08-31 13:56:12</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-24 10:21:51</t>
+          <t>2026-08-31 13:16:33</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -1384,42 +1384,42 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2026-08-24 11:08:04</t>
+          <t>2026-08-31 13:56:12</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mon</t>
+          <t>tue</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>월</t>
+          <t>화</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>80</v>
+        <v>4</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>누가 죄인인가</t>
+          <t>오! 나의 교주님</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=846782&amp;tab=mon</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=841624&amp;tab=tue</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>846782</t>
+          <t>841624</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-24 10:21:52</t>
+          <t>2026-08-31 13:16:34</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -1434,12 +1434,12 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>mon</t>
+          <t>tue,fri</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>mon</t>
+          <t>tue,fri</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -1447,21 +1447,21 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>누가 죄인인가</t>
+          <t>오! 나의 교주님</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>누가 죄인인가 (총 34화/미완결)</t>
+          <t>오! 나의 교주님 (총 94화/미완결)</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>총 34화/미완결</t>
+          <t>총 94화/미완결</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>34</v>
+        <v>94</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1470,181 +1470,25 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>평점 10.0 | 이승우 이승우 | 2026.08.16. | 총34화/미완결 | 27화 무료</t>
+          <t>평점 9.4 | 김꿀빨, 김완두 김꿀빨, 김완두 | 2026.06.18. | 총94화/미완결 | 89화 무료</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>평점 10.0 | 이승우 이승우 | 2026.08.16. | 총34화/미완결 | 27화 무료</t>
+          <t>평점 9.4 | 김꿀빨, 김완두 김꿀빨, 김완두 | 2026.06.18. | 총94화/미완결 | 89화 무료</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=13634954</t>
+          <t>https://series.naver.com/comic/detail.series?productNo=12998643</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>13634954</t>
+          <t>12998643</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
-        <is>
-          <t>누가 죄인인가 (총 34화/미완결)
-평점
-10.0 | 이승우 이승우 | 2026.08.16. | 총34화/미완결 | 27화 무료
-"나의 아버지는 악마로 만들어졌다."연쇄살인마 '허욱열'의 딸로서 30년간 지옥 같은 삶을 살아온 일류 청부업자 '허예주' 오늘날 허욱열의 무고가 밝혀지게 되지만 이들은 여전히 지옥 속에 살고 있고 예주는자신과 같이 지옥 ..</t>
-        </is>
-      </c>
-      <c r="Y7" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>105</v>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>review_needed</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>non_compilation_but_download_not_ok</t>
-        </is>
-      </c>
-      <c r="AE7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>2026-08-24 11:08:04</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>tue</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>화</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>3</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>오! 나의 교주님</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=841624&amp;tab=tue</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>841624</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2026-08-24 10:21:53</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="b">
-        <v>1</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>tue,fri</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>tue,fri</t>
-        </is>
-      </c>
-      <c r="N8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>오! 나의 교주님</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>오! 나의 교주님 (총 94화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>총 94화/미완결</t>
-        </is>
-      </c>
-      <c r="R8" t="n">
-        <v>94</v>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>평점 9.4 | 김꿀빨, 김완두 김꿀빨, 김완두 | 2026.06.18. | 총94화/미완결 | 89화 무료</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>평점 9.4 | 김꿀빨, 김완두 김꿀빨, 김완두 | 2026.06.18. | 총94화/미완결 | 89화 무료</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=12998643</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>12998643</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
         <is>
           <t>오! 나의 교주님 (총 94화/미완결)
 평점
@@ -1652,6 +1496,161 @@
 사이비 종교 ‘진천교’에서 태어나 평생을 그곳에서 살아온 한성민. 그는 결국 모든 것을 잃고 홀로 탈출한다.수년 후, 성인이 된 그는 다시 진천교에 잠입해 처절한 복수를 시작하려 한다.“오, 나의 교주님. 제가 보내드릴게..</t>
         </is>
       </c>
+      <c r="Y7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>non_compilation_but_download_not_ok</t>
+        </is>
+      </c>
+      <c r="AE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:56:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>tue</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>화</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>예쁨 컬렉션</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=844519&amp;tab=tue</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>844519</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:16:34</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>tue</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>tue</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>19금 예쁨 컬렉션</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>19금 예쁨 컬렉션 (총 35화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>총 35화/미완결</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>35</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>평점 9.9 | 김이연 김이연 | 2026.06.15. | 총35화/미완결 | 30화 무료</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>평점 9.9 | 김이연 김이연 | 2026.06.15. | 총35화/미완결 | 30화 무료</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=13365963</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>13365963</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>19금 예쁨 컬렉션 (총 35화/미완결)
+평점
+9.9 | 김이연 김이연 | 2026.06.15. | 총35화/미완결 | 30화 무료</t>
+        </is>
+      </c>
       <c r="Y8" t="b">
         <v>0</v>
       </c>
@@ -1696,7 +1695,7 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2026-08-24 11:08:04</t>
+          <t>2026-08-31 13:56:12</t>
         </is>
       </c>
     </row>
@@ -1712,26 +1711,26 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>예쁨 컬렉션</t>
+          <t>포그랜드</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=844519&amp;tab=tue</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=843116&amp;tab=tue</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>844519</t>
+          <t>843116</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-08-24 10:21:53</t>
+          <t>2026-08-31 13:16:34</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -1759,21 +1758,21 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>19금 예쁨 컬렉션</t>
+          <t>포그랜드</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>19금 예쁨 컬렉션 (총 35화/미완결)</t>
+          <t>포그랜드 (총 44화/미완결)</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>총 35화/미완결</t>
+          <t>총 44화/미완결</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1782,180 +1781,25 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>평점 9.9 | 김이연 김이연 | 2026.06.15. | 총35화/미완결 | 30화 무료</t>
+          <t>평점 10.0 | POGO POGO | 2026.06.15. | 총44화/미완결 | 38화 무료</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>평점 9.9 | 김이연 김이연 | 2026.06.15. | 총35화/미완결 | 30화 무료</t>
+          <t>평점 10.0 | POGO POGO | 2026.06.15. | 총44화/미완결 | 38화 무료</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=13365963</t>
+          <t>https://series.naver.com/comic/detail.series?productNo=13177080</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>13365963</t>
+          <t>13177080</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
-        <is>
-          <t>19금 예쁨 컬렉션 (총 35화/미완결)
-평점
-9.9 | 김이연 김이연 | 2026.06.15. | 총35화/미완결 | 30화 무료</t>
-        </is>
-      </c>
-      <c r="Y9" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>105</v>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>review_needed</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>non_compilation_but_download_not_ok</t>
-        </is>
-      </c>
-      <c r="AE9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>2026-08-24 11:08:04</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>tue</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>화</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>8</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>포그랜드</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=843116&amp;tab=tue</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>843116</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>2026-08-24 10:21:53</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="b">
-        <v>1</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>tue</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>tue</t>
-        </is>
-      </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>포그랜드</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>포그랜드 (총 44화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>총 44화/미완결</t>
-        </is>
-      </c>
-      <c r="R10" t="n">
-        <v>44</v>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>평점 10.0 | POGO POGO | 2026.06.15. | 총44화/미완결 | 38화 무료</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>평점 10.0 | POGO POGO | 2026.06.15. | 총44화/미완결 | 38화 무료</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=13177080</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>13177080</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
         <is>
           <t>포그랜드 (총 44화/미완결)
 평점
@@ -1963,155 +1807,155 @@
 존재만으로도 미스터리한 국제 교도소 포그랜드.죄수 교화 목적으로 파견된 과학교사 단테 강은 한순간의 폭동 속에 포그랜드에 갇히게 된다.탈출하는 방법은 영도자가 되는 길 뿐.무너진 이성과 신성을 목도하라!단테의 아홉 ..</t>
         </is>
       </c>
-      <c r="Y10" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA10" t="n">
+      <c r="Y9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA9" t="n">
         <v>105</v>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="inlineStr"/>
-      <c r="AH10" t="inlineStr">
+      <c r="AE9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
+      <c r="AI9" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>2026-08-24 11:08:04</t>
+      <c r="AJ9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:56:12</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>19</v>
-      </c>
-      <c r="D11" t="inlineStr">
+      <c r="C10" t="n">
+        <v>20</v>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>분신</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=845407&amp;tab=tue</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>845407</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>2026-08-24 10:21:53</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="b">
-        <v>1</v>
-      </c>
-      <c r="J11" t="inlineStr">
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:16:34</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="N11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" t="inlineStr">
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>분신으로 자동사냥 [독점]</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>분신으로 자동사냥 [독점] (총 176화/완결)</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>총 176화/완결</t>
         </is>
       </c>
-      <c r="R11" t="n">
+      <c r="R10" t="n">
         <v>176</v>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>완결</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>평점 9.7 | 차씨 오팔 | 2025.12.27. | 총176화/완결 | 7화 무료</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>평점 9.7 | 차씨 오팔 | 2025.12.27. | 총176화/완결 | 7화 무료</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=8833786</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>8833786</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>분신으로 자동사냥 [독점] (총 176화/완결)
 평점
@@ -2119,161 +1963,161 @@
 일해야 하고, 공부도 해야 하고, 밥도 먹어야 하고.‘왜 사람은 한 번에 한 가지 일밖에 못 하는 걸까.’상우는 항상 자신의 몸이 두 개였으면 좋겠다고 생각했다...그랬더니 몸이 두 개가 되었다.</t>
         </is>
       </c>
-      <c r="Y11" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA11" t="n">
+      <c r="Y10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA10" t="n">
         <v>105</v>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>matched</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>first_non_compilation_numeric_download</t>
         </is>
       </c>
-      <c r="AE11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF11" t="inlineStr">
+      <c r="AE10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF10" t="inlineStr">
         <is>
           <t>1,022만</t>
         </is>
       </c>
-      <c r="AG11" t="n">
+      <c r="AG10" t="n">
         <v>10220000</v>
       </c>
-      <c r="AH11" t="inlineStr">
+      <c r="AH10" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
+      <c r="AI10" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>2026-08-24 11:08:04</t>
+      <c r="AJ10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:56:12</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>27</v>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C11" t="n">
+        <v>26</v>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>나쁜남자가 돼라!</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=847491&amp;tab=tue</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>847491</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>2026-08-24 10:21:53</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="b">
-        <v>1</v>
-      </c>
-      <c r="J12" t="inlineStr">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:16:35</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J11" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="N12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" t="inlineStr">
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="inlineStr">
         <is>
           <t>나쁜남자가 돼라!</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>나쁜남자가 돼라! (총 28화/미완결)</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>총 28화/미완결</t>
         </is>
       </c>
-      <c r="R12" t="n">
+      <c r="R11" t="n">
         <v>28</v>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>평점 9.9 | 이연 자개 | 2026.06.15. | 총28화/미완결 | 20화 무료</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>평점 9.9 | 이연 자개 | 2026.06.15. | 총28화/미완결 | 20화 무료</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13704125</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>13704125</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>나쁜남자가 돼라! (총 28화/미완결)
 평점
@@ -2281,155 +2125,155 @@
 구남친에 대한 트라우마로 나쁜남자 취향을 가지게 된 수연은 현재의 남자친구에게 약간의 불만을 느끼지만 잘 지내고 있다.그러던 어느 날, 남자친구의 몸에 수연의 취향 그 자체인 '나쁜 남자'가 빙의하는데…이 저주. 풀어줘..</t>
         </is>
       </c>
-      <c r="Y12" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA12" t="n">
+      <c r="Y11" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA11" t="n">
         <v>105</v>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="inlineStr"/>
-      <c r="AH12" t="inlineStr">
+      <c r="AE11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
+      <c r="AI11" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>2026-08-24 11:08:04</t>
+      <c r="AJ11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:56:12</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>49</v>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C12" t="n">
+        <v>50</v>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>원수의 아기를 가졌다</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=846110&amp;tab=tue</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>846110</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>2026-08-24 10:21:54</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="b">
-        <v>1</v>
-      </c>
-      <c r="J13" t="inlineStr">
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:16:35</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J12" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="N13" t="n">
-        <v>1</v>
-      </c>
-      <c r="O13" t="inlineStr">
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="inlineStr">
         <is>
           <t>원수의 아기를 가졌다</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>원수의 아기를 가졌다 (총 30화/미완결)</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>총 30화/미완결</t>
         </is>
       </c>
-      <c r="R13" t="n">
+      <c r="R12" t="n">
         <v>30</v>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>평점 9.7 | 미니바라기, 안지 이삼 | 2026.06.15. | 총30화/미완결 | 25화 무료</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>평점 9.7 | 미니바라기, 안지 이삼 | 2026.06.15. | 총30화/미완결 | 25화 무료</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13567690</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>13567690</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>원수의 아기를 가졌다 (총 30화/미완결)
 평점
@@ -2437,155 +2281,155 @@
 서로를 끔찍하게 혐오하는 두 가문 버몬테와 템네스.클로델은 강제 화해를 위한 희생양이 되어 템네스 공작 카이안의 신부가 된다.“템네스의 환영을 받지 못하는 신부로군. 주제를 알고 제 발로 걸어들어오라지.”오랜 반목을 ..</t>
         </is>
       </c>
-      <c r="Y13" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA13" t="n">
+      <c r="Y12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA12" t="n">
         <v>105</v>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD13" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="inlineStr"/>
-      <c r="AH13" t="inlineStr">
+      <c r="AE12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI13" t="inlineStr">
+      <c r="AI12" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>2026-08-24 11:08:04</t>
+      <c r="AJ12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:56:12</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>51</v>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="C13" t="n">
+        <v>53</v>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>화분</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=851671&amp;tab=tue</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>851671</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>2026-08-24 10:21:54</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="b">
-        <v>1</v>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:16:35</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="N14" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" t="inlineStr">
+      <c r="N13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" t="inlineStr">
         <is>
           <t>화분</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>화분 (총 5화/미완결)</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>총 5화/미완결</t>
         </is>
       </c>
-      <c r="R14" t="n">
+      <c r="R13" t="n">
         <v>5</v>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>평점 10.0 | 쿼시 쿼시 | 2026.06.15. | 총5화/미완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>평점 10.0 | 쿼시 쿼시 | 2026.06.15. | 총5화/미완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14284647</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>14284647</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>화분 (총 5화/미완결)
 평점
@@ -2593,155 +2437,155 @@
 버림받는 것이 무서운 여자와 그런 그녀가 무섭게 느껴지는 남자. 오래된 인연으로 시작된 사랑은 다정함의 얼굴을 한 집착이 되어, 두 사람의 일상과 마음을 서서히 갉아먹어 간다.우리 사랑은, 어디서부터 잘못된거지..?</t>
         </is>
       </c>
-      <c r="Y14" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA14" t="n">
+      <c r="Y13" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA13" t="n">
         <v>105</v>
       </c>
-      <c r="AB14" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD14" t="inlineStr">
+      <c r="AD13" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="inlineStr"/>
-      <c r="AH14" t="inlineStr">
+      <c r="AE13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI14" t="inlineStr">
+      <c r="AI13" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>2026-08-24 11:08:04</t>
+      <c r="AJ13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:56:12</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>81</v>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="C14" t="n">
+        <v>80</v>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>포 더 퀸덤</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=812414&amp;tab=tue</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>812414</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>2026-08-24 10:21:55</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="b">
-        <v>1</v>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:16:36</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="b">
+        <v>1</v>
+      </c>
+      <c r="J14" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="N15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O15" t="inlineStr">
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>포 더 퀸덤</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>포 더 퀸덤 (총 128화/미완결)</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>총 128화/미완결</t>
         </is>
       </c>
-      <c r="R15" t="n">
+      <c r="R14" t="n">
         <v>128</v>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>평점 9.0 | 로즈옹 로즈옹 | 2026.06.15. | 총128화/미완결 | 123화 무료</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>평점 9.0 | 로즈옹 로즈옹 | 2026.06.15. | 총128화/미완결 | 123화 무료</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=9895056</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>9895056</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>포 더 퀸덤 (총 128화/미완결)
 평점
@@ -2749,155 +2593,155 @@
 악마 아벨은 인간 여자 연리에게 사랑하는 형, 카인을 잃고 만다.분노에 가득 차 연리를 찾아간 아벨은 사랑에 빠지는 금총알을 맞게 되면서, 연리에게 끓어오르는 사랑을 느끼게 되는데…그는 과연 형제의 복수를 택할 것인가..</t>
         </is>
       </c>
-      <c r="Y15" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA15" t="n">
+      <c r="Y14" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA14" t="n">
         <v>105</v>
       </c>
-      <c r="AB15" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
+      <c r="AC14" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD15" t="inlineStr">
+      <c r="AD14" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE15" t="n">
+      <c r="AE14" t="n">
         <v>2</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
-      <c r="AG15" t="inlineStr"/>
-      <c r="AH15" t="inlineStr">
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI15" t="inlineStr">
+      <c r="AI14" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>2026-08-24 11:08:04</t>
+      <c r="AJ14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:56:12</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C15" t="n">
         <v>5</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>싸이코패스 in 무림</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=846109&amp;tab=wed</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>846109</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>2026-08-24 10:21:56</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="b">
-        <v>1</v>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:16:37</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="b">
+        <v>1</v>
+      </c>
+      <c r="J15" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="N16" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" t="inlineStr">
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t>싸이코패스 in 무림[독점]</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>싸이코패스 in 무림[독점] (총 32화/미완결)</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>총 32화/미완결</t>
         </is>
       </c>
-      <c r="R16" t="n">
+      <c r="R15" t="n">
         <v>32</v>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>평점 9.8 | 김언, 곤붕 송범규 | 2026.06.16. | 총32화/미완결 | 26화 무료</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>평점 9.8 | 김언, 곤붕 송범규 | 2026.06.16. | 총32화/미완결 | 26화 무료</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13566546</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>13566546</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>싸이코패스 in 무림[독점] (총 32화/미완결)
 평점
@@ -2905,155 +2749,155 @@
 [진정한 강자들의 세상, 무림 온라인에 오신 걸 환영합니다.]무림에 떨어진 희대의 싸이코패스.음모와 악의가 가득한 무림에 동봉수, 그의 무정한 이빨이 드리운다.</t>
         </is>
       </c>
-      <c r="Y16" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA16" t="n">
+      <c r="Y15" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA15" t="n">
         <v>105</v>
       </c>
-      <c r="AB16" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
+      <c r="AC15" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD16" t="inlineStr">
+      <c r="AD15" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF16" t="inlineStr"/>
-      <c r="AG16" t="inlineStr"/>
-      <c r="AH16" t="inlineStr">
+      <c r="AE15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI16" t="inlineStr">
+      <c r="AI15" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>2026-08-24 11:08:04</t>
+      <c r="AJ15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:56:12</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="C17" t="n">
-        <v>9</v>
-      </c>
-      <c r="D17" t="inlineStr">
+      <c r="C16" t="n">
+        <v>8</v>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>썰:관계주의</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=834033&amp;tab=wed</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>834033</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>2026-08-24 10:21:56</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="b">
-        <v>1</v>
-      </c>
-      <c r="J17" t="inlineStr">
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:16:37</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="b">
+        <v>1</v>
+      </c>
+      <c r="J16" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="inlineStr">
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>썰:관계주의</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>썰:관계주의 (총 87화/미완결)</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>총 87화/미완결</t>
         </is>
       </c>
-      <c r="R17" t="n">
+      <c r="R16" t="n">
         <v>87</v>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>평점 10.0 | 이삼 장버들 | 2026.06.16. | 총87화/미완결 | 83화 무료</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>평점 10.0 | 이삼 장버들 | 2026.06.16. | 총87화/미완결 | 83화 무료</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=11802777</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>11802777</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>썰:관계주의 (총 87화/미완결)
 평점
@@ -3061,155 +2905,155 @@
 여러 상가가 들어서 있는 강남의 유명타워. 이야기는 유명타워의 한 피부과 안내 데스크 직원 강지영으로부터 시작된다. 동료이자 유부남 의사와 만남을 이어가던 지영은 그에게 또 다른 불륜 상대가 있음을 눈치 채는데 그 상..</t>
         </is>
       </c>
-      <c r="Y17" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA17" t="n">
+      <c r="Y16" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA16" t="n">
         <v>105</v>
       </c>
-      <c r="AB17" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
+      <c r="AC16" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD17" t="inlineStr">
+      <c r="AD16" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF17" t="inlineStr"/>
-      <c r="AG17" t="inlineStr"/>
-      <c r="AH17" t="inlineStr">
+      <c r="AE16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI17" t="inlineStr">
+      <c r="AI16" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>2026-08-24 11:08:04</t>
+      <c r="AJ16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:56:12</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>30</v>
-      </c>
-      <c r="D18" t="inlineStr">
+      <c r="C17" t="n">
+        <v>29</v>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>끝장</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=844588&amp;tab=wed</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>844588</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>2026-08-24 10:21:57</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="b">
-        <v>1</v>
-      </c>
-      <c r="J18" t="inlineStr">
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:16:38</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="b">
+        <v>1</v>
+      </c>
+      <c r="J17" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="N18" t="n">
+      <c r="N17" t="n">
         <v>2</v>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>떨어지면 끝장</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>떨어지면 끝장 (총 70화/완결)</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>총 70화/완결</t>
         </is>
       </c>
-      <c r="R18" t="n">
+      <c r="R17" t="n">
         <v>70</v>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>완결</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>평점 9.7 | Keiko Suenobu Keiko Suenobu | 2024.04.12. | 총70화/완결 | 3화 무료</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>평점 9.7 | Keiko Suenobu Keiko Suenobu | 2024.04.12. | 총70화/완결 | 3화 무료</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=6039213</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>6039213</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>떨어지면 끝장 (총 70화/완결)
 평점
@@ -3217,161 +3061,161 @@
 “떨어지면 끝장이야.”그토록 바라던 신축 초고층 아파트에 입주하게 된 주부 아스미.같은 아파트에 거주하며 아이들 유치원도 같은 세 명의 맘 친구가 생긴다.행복 가득한 새로운 생활이 펼쳐지리라 기대했지만, 어떤 인물과..</t>
         </is>
       </c>
-      <c r="Y18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA18" t="n">
+      <c r="Y17" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA17" t="n">
         <v>100</v>
       </c>
-      <c r="AB18" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_2</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
+      <c r="AC17" t="inlineStr">
         <is>
           <t>matched</t>
         </is>
       </c>
-      <c r="AD18" t="inlineStr">
+      <c r="AD17" t="inlineStr">
         <is>
           <t>first_non_compilation_numeric_download</t>
         </is>
       </c>
-      <c r="AE18" t="n">
+      <c r="AE17" t="n">
         <v>2</v>
       </c>
-      <c r="AF18" t="inlineStr">
+      <c r="AF17" t="inlineStr">
         <is>
           <t>3.9만</t>
         </is>
       </c>
-      <c r="AG18" t="n">
+      <c r="AG17" t="n">
         <v>39000</v>
       </c>
-      <c r="AH18" t="inlineStr">
+      <c r="AH17" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="AI18" t="inlineStr">
+      <c r="AI17" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>2026-08-24 11:08:04</t>
+      <c r="AJ17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:56:12</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="C18" t="n">
         <v>31</v>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>표절의혹</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=846106&amp;tab=wed</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>846106</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>2026-08-24 10:21:57</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="b">
-        <v>1</v>
-      </c>
-      <c r="J19" t="inlineStr">
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:16:38</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="N19" t="n">
-        <v>1</v>
-      </c>
-      <c r="O19" t="inlineStr">
+      <c r="N18" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" t="inlineStr">
         <is>
           <t>표절의혹</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>표절의혹 (총 29화/미완결)</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>총 29화/미완결</t>
         </is>
       </c>
-      <c r="R19" t="n">
+      <c r="R18" t="n">
         <v>29</v>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>평점 9.4 | 김칸비 황영찬 | 2026.06.16. | 총29화/미완결 | 24화 무료</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>평점 9.4 | 김칸비 황영찬 | 2026.06.16. | 총29화/미완결 | 24화 무료</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13575121</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>13575121</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>표절의혹 (총 29화/미완결)
 평점
@@ -3379,155 +3223,155 @@
 살인사건 피해자들의 시신을 예술품처럼 사고파는 인간성을 잃은 자들, 그리고 그런 예술 살인을 저지르는 ‘자학’이라는 연쇄살인마가 세간의 화제가 되고 있다. 한 예술가는 이 상황에 분노해 자학을 추적하기 시작하는데.....</t>
         </is>
       </c>
-      <c r="Y19" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA19" t="n">
+      <c r="Y18" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA18" t="n">
         <v>105</v>
       </c>
-      <c r="AB19" t="inlineStr">
+      <c r="AB18" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
+      <c r="AC18" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD19" t="inlineStr">
+      <c r="AD18" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF19" t="inlineStr"/>
-      <c r="AG19" t="inlineStr"/>
-      <c r="AH19" t="inlineStr">
+      <c r="AE18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI19" t="inlineStr">
+      <c r="AI18" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>2026-08-24 11:08:04</t>
+      <c r="AJ18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:56:12</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="C20" t="n">
-        <v>54</v>
-      </c>
-      <c r="D20" t="inlineStr">
+      <c r="C19" t="n">
+        <v>43</v>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>숙녀가 대머리이면 어떻단말인가</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=853619&amp;tab=wed</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>853619</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>2026-08-24 10:21:57</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="b">
-        <v>1</v>
-      </c>
-      <c r="J20" t="inlineStr">
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:16:39</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="b">
+        <v>1</v>
+      </c>
+      <c r="J19" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="N20" t="n">
-        <v>1</v>
-      </c>
-      <c r="O20" t="inlineStr">
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" t="inlineStr">
         <is>
           <t>숙녀가 대머리이면 어떻단 말인가</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>숙녀가 대머리이면 어떻단 말인가 (총 6화/미완결)</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>총 6화/미완결</t>
         </is>
       </c>
-      <c r="R20" t="n">
+      <c r="R19" t="n">
         <v>6</v>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>평점 9.6 | 아가사마기 | 2026.08.18. | 총6화/미완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>평점 9.6 | 아가사마기 | 2026.08.18. | 총6화/미완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14563924</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>14563924</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>숙녀가 대머리이면 어떻단 말인가 (총 6화/미완결)
 평점
@@ -3535,155 +3379,155 @@
 타인의 시선속에서만 살아왔던 정숙녀(23세, 공시생)는 지쳤다. 좋아하는 것도 없고 해야 될 일들만 가득한 인생... 더는 이렇게 살기 싫어!! 기분전환이라도 할까 들어간 미용실에서. 어랏? 뿅! 대머리가 되어버렸다. 오늘부터 대머..</t>
         </is>
       </c>
-      <c r="Y20" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA20" t="n">
+      <c r="Y19" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA19" t="n">
         <v>105</v>
       </c>
-      <c r="AB20" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
+      <c r="AC19" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD20" t="inlineStr">
+      <c r="AD19" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF20" t="inlineStr"/>
-      <c r="AG20" t="inlineStr"/>
-      <c r="AH20" t="inlineStr">
+      <c r="AE19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>searched_series</t>
-        </is>
-      </c>
-      <c r="AJ20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>2026-08-24 11:08:04</t>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:56:12</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="C21" t="n">
-        <v>86</v>
-      </c>
-      <c r="D21" t="inlineStr">
+      <c r="C20" t="n">
+        <v>87</v>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>일곱 번째 의뢰인</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=850210&amp;tab=wed</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>850210</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>2026-08-24 10:21:58</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="b">
-        <v>1</v>
-      </c>
-      <c r="J21" t="inlineStr">
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:16:40</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="b">
+        <v>1</v>
+      </c>
+      <c r="J20" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="N21" t="n">
-        <v>1</v>
-      </c>
-      <c r="O21" t="inlineStr">
+      <c r="N20" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" t="inlineStr">
         <is>
           <t>일곱 번째 의뢰인</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>일곱 번째 의뢰인 (총 14화/미완결)</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>총 14화/미완결</t>
         </is>
       </c>
-      <c r="R21" t="n">
+      <c r="R20" t="n">
         <v>14</v>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>평점 10.0 | 함영서 함영서 | 2026.06.16. | 총14화/미완결 | 9화 무료</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>평점 10.0 | 함영서 함영서 | 2026.06.16. | 총14화/미완결 | 9화 무료</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14102285</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>14102285</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>일곱 번째 의뢰인 (총 14화/미완결)
 평점
@@ -3691,155 +3535,155 @@
 어린 탐정 맥스는 아무도 주목하지 않는 도박 업자의 죽음을 조사하라는 의뢰를 받는다. 의뢰인이 용의자로 지목한 도박 업자의 아내 제인. 맥스는 그녀를 향한 의심과 이끌림 사이에서 갈등하는데. 제인은 결백한가, 살인자인..</t>
         </is>
       </c>
-      <c r="Y21" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA21" t="n">
+      <c r="Y20" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA20" t="n">
         <v>105</v>
       </c>
-      <c r="AB21" t="inlineStr">
+      <c r="AB20" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
+      <c r="AC20" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD21" t="inlineStr">
+      <c r="AD20" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF21" t="inlineStr"/>
-      <c r="AG21" t="inlineStr"/>
-      <c r="AH21" t="inlineStr">
+      <c r="AE20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI21" t="inlineStr">
+      <c r="AI20" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>2026-08-24 11:08:04</t>
+      <c r="AJ20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:56:12</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="C22" t="n">
+      <c r="C21" t="n">
         <v>5</v>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>소꿉친구 컴플렉스</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=822640&amp;tab=thu</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>822640</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>2026-08-24 10:21:59</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="b">
-        <v>1</v>
-      </c>
-      <c r="J22" t="inlineStr">
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:16:41</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J21" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="N22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O22" t="inlineStr">
+      <c r="N21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" t="inlineStr">
         <is>
           <t>소꿉친구 컴플렉스</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>소꿉친구 컴플렉스 (총 80화/미완결)</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>총 80화/미완결</t>
         </is>
       </c>
-      <c r="R22" t="n">
+      <c r="R21" t="n">
         <v>80</v>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>평점 9.8 | 은하이 은하이 | 2026.06.17. | 총80화/미완결 | 76화 무료</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>평점 9.8 | 은하이 은하이 | 2026.06.17. | 총80화/미완결 | 76화 무료</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=10851069</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>10851069</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>소꿉친구 컴플렉스 (총 80화/미완결)
 평점
@@ -3847,155 +3691,155 @@
 20살에 20년지기, 평생을 함께한 소꿉친구 하늘과 민철.그런 소꿉친구의 알고 싶지 않은 은밀한 사정을 알아버렸다?!서로를 이성으로 생각한 적이 결코 없는 두사람이지만,오해가 오해를 낳고 착각이 착각을 낳는 상황들 속에..</t>
         </is>
       </c>
-      <c r="Y22" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z22" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA22" t="n">
+      <c r="Y21" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA21" t="n">
         <v>105</v>
       </c>
-      <c r="AB22" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
+      <c r="AC21" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD22" t="inlineStr">
+      <c r="AD21" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE22" t="n">
+      <c r="AE21" t="n">
         <v>3</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
-      <c r="AG22" t="inlineStr"/>
-      <c r="AH22" t="inlineStr">
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI22" t="inlineStr">
+      <c r="AI21" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>2026-08-24 11:08:04</t>
+      <c r="AJ21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:56:12</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="C22" t="n">
         <v>6</v>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>럭키비치</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=852498&amp;tab=thu</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>852498</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>2026-08-24 10:21:59</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="b">
-        <v>1</v>
-      </c>
-      <c r="J23" t="inlineStr">
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:16:41</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="b">
+        <v>1</v>
+      </c>
+      <c r="J22" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
         <is>
           <t>thu,sun</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>thu,sun</t>
         </is>
       </c>
-      <c r="N23" t="n">
-        <v>1</v>
-      </c>
-      <c r="O23" t="inlineStr">
+      <c r="N22" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" t="inlineStr">
         <is>
           <t>럭키비치</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>럭키비치 (총 8화/미완결)</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>총 8화/미완결</t>
         </is>
       </c>
-      <c r="R23" t="n">
+      <c r="R22" t="n">
         <v>8</v>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>평점 10.0 | MAJOR, 약수 약수 | 2026.07.18. | 총8화/미완결 | 3화 무료</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>평점 10.0 | MAJOR, 약수 약수 | 2026.07.18. | 총8화/미완결 | 3화 무료</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14424733</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>14424733</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>럭키비치 (총 8화/미완결)
 평점
@@ -4003,155 +3847,155 @@
 “그거 알아? 기는 놈 위에 나는 썅X 있는 거?”불우한 환경과 폐쇄적인 바닷가 촌에서 자라온 소녀 '정임'은,그칠줄 모르는 주변의 부조리와 권태 속에서 결국 폭발,퇴폐업을 하는 고모의 불경한 쌈짓돈을 훔쳐 서울로 상경한..</t>
         </is>
       </c>
-      <c r="Y23" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z23" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA23" t="n">
+      <c r="Y22" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA22" t="n">
         <v>105</v>
       </c>
-      <c r="AB23" t="inlineStr">
+      <c r="AB22" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
+      <c r="AC22" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD23" t="inlineStr">
+      <c r="AD22" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF23" t="inlineStr"/>
-      <c r="AG23" t="inlineStr"/>
-      <c r="AH23" t="inlineStr">
+      <c r="AE22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI23" t="inlineStr">
+      <c r="AI22" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>2026-08-24 11:08:04</t>
+      <c r="AJ22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:56:12</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>22</v>
-      </c>
-      <c r="D24" t="inlineStr">
+      <c r="C23" t="n">
+        <v>18</v>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>나의 경험</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=853278&amp;tab=thu</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>853278</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>2026-08-24 10:21:59</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="b">
-        <v>1</v>
-      </c>
-      <c r="J24" t="inlineStr">
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:16:41</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="b">
+        <v>1</v>
+      </c>
+      <c r="J23" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="N24" t="n">
-        <v>1</v>
-      </c>
-      <c r="O24" t="inlineStr">
+      <c r="N23" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" t="inlineStr">
         <is>
           <t>나의 경험</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>나의 경험 (총 6화/미완결)</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>총 6화/미완결</t>
         </is>
       </c>
-      <c r="R24" t="n">
+      <c r="R23" t="n">
         <v>6</v>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>평점 7.0 | 윤박 윤박 | 2026.08.12. | 총6화/미완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>평점 7.0 | 윤박 윤박 | 2026.08.12. | 총6화/미완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14532341</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>14532341</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>나의 경험 (총 6화/미완결)
 평점
@@ -4159,155 +4003,155 @@
 살다 보면 한 번쯤 인연이 물밀듯 밀려 들어오는 순간들이 있다.별다를 것 없던 평범한 스무 살 재우의 일상에도예상치 못한 만남이 하나둘 찾아오기 시작한다.서툴지만 사랑만큼은 누구보다 진심인 재우는 믿는다.이번만큼은 ..</t>
         </is>
       </c>
-      <c r="Y24" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z24" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA24" t="n">
+      <c r="Y23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA23" t="n">
         <v>105</v>
       </c>
-      <c r="AB24" t="inlineStr">
+      <c r="AB23" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
+      <c r="AC23" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD24" t="inlineStr">
+      <c r="AD23" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF24" t="inlineStr"/>
-      <c r="AG24" t="inlineStr"/>
-      <c r="AH24" t="inlineStr">
+      <c r="AE23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI24" t="inlineStr">
+      <c r="AI23" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>2026-08-24 11:08:04</t>
+      <c r="AJ23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:56:12</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="C25" t="n">
-        <v>62</v>
-      </c>
-      <c r="D25" t="inlineStr">
+      <c r="C24" t="n">
+        <v>63</v>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>당신에게 얽힌 채</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=849879&amp;tab=thu</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>849879</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>2026-08-24 10:22:00</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="b">
-        <v>1</v>
-      </c>
-      <c r="J25" t="inlineStr">
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:16:43</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="b">
+        <v>1</v>
+      </c>
+      <c r="J24" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="N25" t="n">
-        <v>1</v>
-      </c>
-      <c r="O25" t="inlineStr">
+      <c r="N24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" t="inlineStr">
         <is>
           <t>당신에게 얽힌 채</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>당신에게 얽힌 채 (총 10화/미완결)</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>총 10화/미완결</t>
         </is>
       </c>
-      <c r="R25" t="n">
+      <c r="R24" t="n">
         <v>10</v>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>평점 10.0 | Nicole Knight, 유다 danah789 | 2026.06.17. | 총10화/미완결 | 5화 무료</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>평점 10.0 | Nicole Knight, 유다 danah789 | 2026.06.17. | 총10화/미완결 | 5화 무료</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14041685</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>14041685</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>당신에게 얽힌 채 (총 10화/미완결)
 평점
@@ -4315,155 +4159,155 @@
 상속자가 아닌 복종하는 존재로 길러진 에이바 모레티. 뉴욕에서 가장 강력한 마피아 가문의 막내딸인 그녀는 ‘집안의 사고뭉치’라는 오명을 벗고 자신의 자리를 찾기 위해 분투한다.그러던 어느 날 밤, 낯선 남자와 보낸 뜨..</t>
         </is>
       </c>
-      <c r="Y25" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA25" t="n">
+      <c r="Y24" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA24" t="n">
         <v>105</v>
       </c>
-      <c r="AB25" t="inlineStr">
+      <c r="AB24" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
+      <c r="AC24" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD25" t="inlineStr">
+      <c r="AD24" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF25" t="inlineStr"/>
-      <c r="AG25" t="inlineStr"/>
-      <c r="AH25" t="inlineStr">
+      <c r="AE24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI25" t="inlineStr">
+      <c r="AI24" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>2026-08-24 11:08:04</t>
+      <c r="AJ24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:56:12</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C26" t="n">
+      <c r="C25" t="n">
         <v>2</v>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>오! 나의 교주님</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=841624&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>841624</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>2026-08-24 10:22:02</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="b">
-        <v>1</v>
-      </c>
-      <c r="J26" t="inlineStr">
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:16:44</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="b">
+        <v>1</v>
+      </c>
+      <c r="J25" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
         <is>
           <t>tue,fri</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>tue,fri</t>
         </is>
       </c>
-      <c r="N26" t="n">
-        <v>1</v>
-      </c>
-      <c r="O26" t="inlineStr">
+      <c r="N25" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" t="inlineStr">
         <is>
           <t>오! 나의 교주님</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>오! 나의 교주님 (총 94화/미완결)</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>총 94화/미완결</t>
         </is>
       </c>
-      <c r="R26" t="n">
+      <c r="R25" t="n">
         <v>94</v>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>평점 9.4 | 김꿀빨, 김완두 김꿀빨, 김완두 | 2026.06.18. | 총94화/미완결 | 89화 무료</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>평점 9.4 | 김꿀빨, 김완두 김꿀빨, 김완두 | 2026.06.18. | 총94화/미완결 | 89화 무료</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=12998643</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>12998643</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>오! 나의 교주님 (총 94화/미완결)
 평점
@@ -4471,155 +4315,155 @@
 사이비 종교 ‘진천교’에서 태어나 평생을 그곳에서 살아온 한성민. 그는 결국 모든 것을 잃고 홀로 탈출한다.수년 후, 성인이 된 그는 다시 진천교에 잠입해 처절한 복수를 시작하려 한다.“오, 나의 교주님. 제가 보내드릴게..</t>
         </is>
       </c>
-      <c r="Y26" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z26" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA26" t="n">
+      <c r="Y25" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA25" t="n">
         <v>105</v>
       </c>
-      <c r="AB26" t="inlineStr">
+      <c r="AB25" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
+      <c r="AC25" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD26" t="inlineStr">
+      <c r="AD25" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF26" t="inlineStr"/>
-      <c r="AG26" t="inlineStr"/>
-      <c r="AH26" t="inlineStr">
+      <c r="AE25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI26" t="inlineStr">
+      <c r="AI25" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>2026-08-24 11:08:04</t>
+      <c r="AJ25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:56:12</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C27" t="n">
+      <c r="C26" t="n">
         <v>9</v>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>두 얼굴</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=845646&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>845646</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>2026-08-24 10:22:02</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="b">
-        <v>1</v>
-      </c>
-      <c r="J27" t="inlineStr">
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:16:45</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="b">
+        <v>1</v>
+      </c>
+      <c r="J26" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="N27" t="n">
-        <v>1</v>
-      </c>
-      <c r="O27" t="inlineStr">
+      <c r="N26" t="n">
+        <v>1</v>
+      </c>
+      <c r="O26" t="inlineStr">
         <is>
           <t>두 얼굴의 대표님</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>두 얼굴의 대표님 (총 126화/완결)</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>총 126화/완결</t>
         </is>
       </c>
-      <c r="R27" t="n">
+      <c r="R26" t="n">
         <v>126</v>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>완결</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>평점 6.2 | 1M, KuaiKan, YY 1M, KuaiKan, YY | 2022.10.02. | 총126화/완결 | 3화 무료</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>평점 6.2 | 1M, KuaiKan, YY 1M, KuaiKan, YY | 2022.10.02. | 총126화/완결 | 3화 무료</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=6489984</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>6489984</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>두 얼굴의 대표님 (총 126화/완결)
 평점
@@ -4627,161 +4471,161 @@
 재벌가의 사생아로 태어난 소원은 일찍 엄마를 잃고, 가족들의 멸시 속에서 살아왔다.그러다 언니에게 약혼자까지 뺏기게 되자, 실의에 빠진 소원은 유학을 떠나게 되고, 그곳에서 평범한 남편을 만나 결혼을 하게 된다.1년 후 ..</t>
         </is>
       </c>
-      <c r="Y27" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA27" t="n">
+      <c r="Y26" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA26" t="n">
         <v>105</v>
       </c>
-      <c r="AB27" t="inlineStr">
+      <c r="AB26" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
+      <c r="AC26" t="inlineStr">
         <is>
           <t>matched</t>
         </is>
       </c>
-      <c r="AD27" t="inlineStr">
+      <c r="AD26" t="inlineStr">
         <is>
           <t>first_non_compilation_numeric_download</t>
         </is>
       </c>
-      <c r="AE27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF27" t="inlineStr">
+      <c r="AE26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF26" t="inlineStr">
         <is>
           <t>157.5만</t>
         </is>
       </c>
-      <c r="AG27" t="n">
+      <c r="AG26" t="n">
         <v>1575000</v>
       </c>
-      <c r="AH27" t="inlineStr">
+      <c r="AH26" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="AI27" t="inlineStr">
+      <c r="AI26" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>2026-08-24 11:08:04</t>
+      <c r="AJ26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:56:12</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C28" t="n">
+      <c r="C27" t="n">
         <v>10</v>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>네가 사는 그 집</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=842465&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>842465</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>2026-08-24 10:22:02</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="b">
-        <v>1</v>
-      </c>
-      <c r="J28" t="inlineStr">
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:16:45</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="b">
+        <v>1</v>
+      </c>
+      <c r="J27" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="N28" t="n">
-        <v>1</v>
-      </c>
-      <c r="O28" t="inlineStr">
+      <c r="N27" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" t="inlineStr">
         <is>
           <t>네가 사는 그 집</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>네가 사는 그 집 (총 47화/미완결)</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>총 47화/미완결</t>
         </is>
       </c>
-      <c r="R28" t="n">
+      <c r="R27" t="n">
         <v>47</v>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>평점 9.7 | 석우 해바다 | 2026.06.18. | 총47화/미완결 | 41화 무료</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>평점 9.7 | 석우 해바다 | 2026.06.18. | 총47화/미완결 | 41화 무료</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13090391</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>13090391</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>네가 사는 그 집 (총 47화/미완결)
 평점
@@ -4789,155 +4633,155 @@
 찢어지게 가난한 집에서 두 아이를 키우며 힘겹게 살아가던 30대 화린.어느날, 자기 첫사랑이었던 부유한 선배와 결혼해 행복하게 사는 친구와 몸이 바뀐다.하지만 부러워하던 삶을 얻은 기쁨도 잠시,그 집의 추악한 비밀이 드..</t>
         </is>
       </c>
-      <c r="Y28" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z28" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA28" t="n">
+      <c r="Y27" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA27" t="n">
         <v>105</v>
       </c>
-      <c r="AB28" t="inlineStr">
+      <c r="AB27" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
+      <c r="AC27" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD28" t="inlineStr">
+      <c r="AD27" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF28" t="inlineStr"/>
-      <c r="AG28" t="inlineStr"/>
-      <c r="AH28" t="inlineStr">
+      <c r="AE27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI28" t="inlineStr">
+      <c r="AI27" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>2026-08-24 11:08:04</t>
+      <c r="AJ27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:56:12</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C29" t="n">
+      <c r="C28" t="n">
         <v>11</v>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>그리디</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=845919&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>845919</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>2026-08-24 10:22:02</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="b">
-        <v>1</v>
-      </c>
-      <c r="J29" t="inlineStr">
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:16:45</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="b">
+        <v>1</v>
+      </c>
+      <c r="J28" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr">
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="N29" t="n">
-        <v>1</v>
-      </c>
-      <c r="O29" t="inlineStr">
+      <c r="N28" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" t="inlineStr">
         <is>
           <t>그리디</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>그리디 (총 31화/미완결)</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>총 31화/미완결</t>
         </is>
       </c>
-      <c r="R29" t="n">
+      <c r="R28" t="n">
         <v>31</v>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>평점 9.9 | 영하 랑라리 | 2026.06.18. | 총31화/미완결 | 25화 무료</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>평점 9.9 | 영하 랑라리 | 2026.06.18. | 총31화/미완결 | 25화 무료</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13530624</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>13530624</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>그리디 (총 31화/미완결)
 평점
@@ -4945,155 +4789,155 @@
 파혼했다. 십년지기 친구와 내가 파혼한 남자가 찍힌 청첩장 한 장.한유주는 그걸 끝으로 서른하나에 사랑도 우정도 다 버렸다. 남은 건 칼럼 한 줄에도 이름을 걸 수 없는 5년짜리 패션지 주니어 에디터 신세뿐.일도 사랑도, 마..</t>
         </is>
       </c>
-      <c r="Y29" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA29" t="n">
+      <c r="Y28" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA28" t="n">
         <v>105</v>
       </c>
-      <c r="AB29" t="inlineStr">
+      <c r="AB28" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
+      <c r="AC28" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD29" t="inlineStr">
+      <c r="AD28" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF29" t="inlineStr"/>
-      <c r="AG29" t="inlineStr"/>
-      <c r="AH29" t="inlineStr">
+      <c r="AE28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI29" t="inlineStr">
+      <c r="AI28" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>2026-08-24 11:08:04</t>
+      <c r="AJ28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:56:12</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C30" t="n">
+      <c r="C29" t="n">
         <v>38</v>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>사자의 서</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=823737&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>823737</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>2026-08-24 10:22:03</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="b">
-        <v>1</v>
-      </c>
-      <c r="J30" t="inlineStr">
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:16:45</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="b">
+        <v>1</v>
+      </c>
+      <c r="J29" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr">
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="N30" t="n">
+      <c r="N29" t="n">
         <v>2</v>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>사자의서 [도시정벌 레거시]</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>사자의서 [도시정벌 레거시] (총 219화/완결)</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>총 219화/완결</t>
         </is>
       </c>
-      <c r="R30" t="n">
+      <c r="R29" t="n">
         <v>219</v>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>완결</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>평점 9.2 | 신형빈 신형빈 | 2019.11.06. | 총219화/완결 | 5화 무료</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>평점 9.2 | 신형빈 신형빈 | 2019.11.06. | 총219화/완결 | 5화 무료</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=2737090</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>2737090</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>사자의서 [도시정벌 레거시] (총 219화/완결)
 평점
@@ -5101,161 +4945,161 @@
 죽음(死)에서 돌아 온 자. 그가 써내려가는 피의 역사에 도시(都市)가 깨어난다.</t>
         </is>
       </c>
-      <c r="Y30" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA30" t="n">
+      <c r="Y29" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA29" t="n">
         <v>100</v>
       </c>
-      <c r="AB30" t="inlineStr">
+      <c r="AB29" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_2</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
+      <c r="AC29" t="inlineStr">
         <is>
           <t>matched</t>
         </is>
       </c>
-      <c r="AD30" t="inlineStr">
+      <c r="AD29" t="inlineStr">
         <is>
           <t>first_non_compilation_numeric_download</t>
         </is>
       </c>
-      <c r="AE30" t="n">
+      <c r="AE29" t="n">
         <v>2</v>
       </c>
-      <c r="AF30" t="inlineStr">
+      <c r="AF29" t="inlineStr">
         <is>
           <t>121.3만</t>
         </is>
       </c>
-      <c r="AG30" t="n">
+      <c r="AG29" t="n">
         <v>1213000</v>
       </c>
-      <c r="AH30" t="inlineStr">
+      <c r="AH29" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="AI30" t="inlineStr">
+      <c r="AI29" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>2026-08-24 11:08:04</t>
+      <c r="AJ29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:56:12</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C31" t="n">
-        <v>59</v>
-      </c>
-      <c r="D31" t="inlineStr">
+      <c r="C30" t="n">
+        <v>58</v>
+      </c>
+      <c r="D30" t="inlineStr">
         <is>
           <t>박제</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=846363&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>846363</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>2026-08-24 10:22:04</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="b">
-        <v>1</v>
-      </c>
-      <c r="J31" t="inlineStr">
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:16:46</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="b">
+        <v>1</v>
+      </c>
+      <c r="J30" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr">
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="N31" t="n">
+      <c r="N30" t="n">
         <v>2</v>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>박제하는 시간</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>박제하는 시간 (총 28화/완결)</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>총 28화/완결</t>
         </is>
       </c>
-      <c r="R31" t="n">
+      <c r="R30" t="n">
         <v>28</v>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>완결</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>평점 10.0 | 이언 | 2024.07.19. | 총28화/완결 | 5화 무료</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>평점 10.0 | 이언 | 2024.07.19. | 총28화/완결 | 5화 무료</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="V30" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=10632769</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>10632769</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>박제하는 시간 (총 28화/완결)
 평점
@@ -5263,161 +5107,161 @@
 박제사 ‘도연’은 죽은 연인의 시체를 빼돌린다.이 과정을 목격한 작가 ‘이명’은 침묵의 대가로 도연의 삶을 소재로 요구해 온다.일주일간의 취재를 허락한 도연. 죽은 연인과 꼭 닮은 이명의 모습에 혼란을 느낀다.숲속의 ..</t>
         </is>
       </c>
-      <c r="Y31" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z31" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA31" t="n">
+      <c r="Y30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA30" t="n">
         <v>100</v>
       </c>
-      <c r="AB31" t="inlineStr">
+      <c r="AB30" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_2</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
+      <c r="AC30" t="inlineStr">
         <is>
           <t>matched</t>
         </is>
       </c>
-      <c r="AD31" t="inlineStr">
+      <c r="AD30" t="inlineStr">
         <is>
           <t>first_non_compilation_numeric_download</t>
         </is>
       </c>
-      <c r="AE31" t="n">
+      <c r="AE30" t="n">
         <v>2</v>
       </c>
-      <c r="AF31" t="inlineStr">
+      <c r="AF30" t="inlineStr">
         <is>
           <t>7.2만</t>
         </is>
       </c>
-      <c r="AG31" t="n">
+      <c r="AG30" t="n">
         <v>72000</v>
       </c>
-      <c r="AH31" t="inlineStr">
+      <c r="AH30" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="AI31" t="inlineStr">
+      <c r="AI30" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>2026-08-24 11:08:04</t>
+      <c r="AJ30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:56:12</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C32" t="n">
-        <v>68</v>
-      </c>
-      <c r="D32" t="inlineStr">
+      <c r="C31" t="n">
+        <v>67</v>
+      </c>
+      <c r="D31" t="inlineStr">
         <is>
           <t>사탄의 순애</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=845378&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>845378</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>2026-08-24 10:22:04</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="b">
-        <v>1</v>
-      </c>
-      <c r="J32" t="inlineStr">
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:16:46</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="b">
+        <v>1</v>
+      </c>
+      <c r="J31" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr">
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="N32" t="n">
-        <v>1</v>
-      </c>
-      <c r="O32" t="inlineStr">
+      <c r="N31" t="n">
+        <v>1</v>
+      </c>
+      <c r="O31" t="inlineStr">
         <is>
           <t>사탄의 순애 [독점]</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>사탄의 순애 [독점] (총 35화/미완결)</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>총 35화/미완결</t>
         </is>
       </c>
-      <c r="R32" t="n">
+      <c r="R31" t="n">
         <v>35</v>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>평점 9.8 | 용현 카모모 | 2026.06.18. | 총35화/미완결 | 28화 무료</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>평점 9.8 | 용현 카모모 | 2026.06.18. | 총35화/미완결 | 28화 무료</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
+      <c r="V31" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13451638</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr">
+      <c r="W31" t="inlineStr">
         <is>
           <t>13451638</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>사탄의 순애 [독점] (총 35화/미완결)
 평점
@@ -5425,155 +5269,155 @@
 초식동물계 대표주자 호구남 백은우 VS 육식동물계 대표주자 차도녀 범호연.정반대의 두 사람은 어쩌다 사귀게 됐을까?“백은우. 나한테 취업해라. 내 애인인 척 딱 1년. 그럼 10억이야.”업계에서 악마로 소문난 아티스트 레..</t>
         </is>
       </c>
-      <c r="Y32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z32" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA32" t="n">
+      <c r="Y31" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA31" t="n">
         <v>105</v>
       </c>
-      <c r="AB32" t="inlineStr">
+      <c r="AB31" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
+      <c r="AC31" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD32" t="inlineStr">
+      <c r="AD31" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF32" t="inlineStr"/>
-      <c r="AG32" t="inlineStr"/>
-      <c r="AH32" t="inlineStr">
+      <c r="AE31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
+      <c r="AH31" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI32" t="inlineStr">
+      <c r="AI31" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>2026-08-24 11:08:04</t>
+      <c r="AJ31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:56:12</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C33" t="n">
-        <v>70</v>
-      </c>
-      <c r="D33" t="inlineStr">
+      <c r="C32" t="n">
+        <v>71</v>
+      </c>
+      <c r="D32" t="inlineStr">
         <is>
           <t>죽여주는 캐스팅</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=843866&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>843866</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>2026-08-24 10:22:04</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="b">
-        <v>1</v>
-      </c>
-      <c r="J33" t="inlineStr">
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:16:47</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="b">
+        <v>1</v>
+      </c>
+      <c r="J32" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr">
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="N33" t="n">
-        <v>1</v>
-      </c>
-      <c r="O33" t="inlineStr">
+      <c r="N32" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" t="inlineStr">
         <is>
           <t>죽여주는 캐스팅 [독점]</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>죽여주는 캐스팅 [독점] (총 42화/미완결)</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>총 42화/미완결</t>
         </is>
       </c>
-      <c r="R33" t="n">
+      <c r="R32" t="n">
         <v>42</v>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>평점 9.6 | 영춘 하보 | 2026.06.18. | 총42화/미완결 | 36화 무료</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>평점 9.6 | 영춘 하보 | 2026.06.18. | 총42화/미완결 | 36화 무료</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13253015</t>
         </is>
       </c>
-      <c r="W33" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>13253015</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>죽여주는 캐스팅 [독점] (총 42화/미완결)
 평점
@@ -5581,6 +5425,161 @@
 영화감상 동호회에서 만난 혜수와 강호.성공한 배우를 꿈꾸는 강호는 오디션과 술자리에 몰두하며 혜수에게 기대어 살아간다.그런 강호를 이해하고자 혜수는 연기 수업을 시작하고 점차 자신의 길을 걷기 시작한다.하지만 강..</t>
         </is>
       </c>
+      <c r="Y32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>non_compilation_but_download_not_ok</t>
+        </is>
+      </c>
+      <c r="AE32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="inlineStr"/>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:56:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>토</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>4</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>만취남녀</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=846883&amp;tab=sat</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>846883</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:16:48</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="b">
+        <v>1</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>1</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>19금 만취남녀</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>19금 만취남녀 (총 26화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>총 26화/미완결</t>
+        </is>
+      </c>
+      <c r="R33" t="n">
+        <v>26</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>평점 9.7 | 금 금 | 2026.06.12. | 총26화/미완결 | 21화 무료</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>평점 9.7 | 금 금 | 2026.06.12. | 총26화/미완결 | 21화 무료</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=13646371</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>13646371</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>19금 만취남녀 (총 26화/미완결)
+평점
+9.7 | 금 금 | 2026.06.12. | 총26화/미완결 | 21화 무료</t>
+        </is>
+      </c>
       <c r="Y33" t="b">
         <v>0</v>
       </c>
@@ -5625,7 +5624,7 @@
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>2026-08-24 11:08:04</t>
+          <t>2026-08-31 13:56:12</t>
         </is>
       </c>
     </row>
@@ -5641,26 +5640,26 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>만취남녀</t>
+          <t>시든 꽃에 눈물을</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=846883&amp;tab=sat</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=827190&amp;tab=sat</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>846883</t>
+          <t>827190</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-08-24 10:22:05</t>
+          <t>2026-08-31 13:16:48</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
@@ -5688,21 +5687,21 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>19금 만취남녀</t>
+          <t>시든 꽃에 눈물을</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>19금 만취남녀 (총 26화/미완결)</t>
+          <t>시든 꽃에 눈물을 (총 106화/미완결)</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>총 26화/미완결</t>
+          <t>총 106화/미완결</t>
         </is>
       </c>
       <c r="R34" t="n">
-        <v>26</v>
+        <v>106</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -5711,180 +5710,25 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>평점 9.7 | 금 금 | 2026.06.12. | 총26화/미완결 | 21화 무료</t>
+          <t>평점 9.8 | 개 개 | 2026.06.12. | 총106화/미완결 | 100화 무료</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>평점 9.7 | 금 금 | 2026.06.12. | 총26화/미완결 | 21화 무료</t>
+          <t>평점 9.8 | 개 개 | 2026.06.12. | 총106화/미완결 | 100화 무료</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=13646371</t>
+          <t>https://series.naver.com/comic/detail.series?productNo=11253061</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>13646371</t>
+          <t>11253061</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
-        <is>
-          <t>19금 만취남녀 (총 26화/미완결)
-평점
-9.7 | 금 금 | 2026.06.12. | 총26화/미완결 | 21화 무료</t>
-        </is>
-      </c>
-      <c r="Y34" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z34" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>105</v>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>review_needed</t>
-        </is>
-      </c>
-      <c r="AD34" t="inlineStr">
-        <is>
-          <t>non_compilation_but_download_not_ok</t>
-        </is>
-      </c>
-      <c r="AE34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF34" t="inlineStr"/>
-      <c r="AG34" t="inlineStr"/>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>2026-08-24 11:08:04</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>토</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>4</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>시든 꽃에 눈물을</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=827190&amp;tab=sat</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>827190</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>2026-08-24 10:22:05</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="b">
-        <v>1</v>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="N35" t="n">
-        <v>1</v>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>시든 꽃에 눈물을</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>시든 꽃에 눈물을 (총 106화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>총 106화/미완결</t>
-        </is>
-      </c>
-      <c r="R35" t="n">
-        <v>106</v>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>평점 9.8 | 개 개 | 2026.06.12. | 총106화/미완결 | 100화 무료</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>평점 9.8 | 개 개 | 2026.06.12. | 총106화/미완결 | 100화 무료</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=11253061</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>11253061</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
         <is>
           <t>시든 꽃에 눈물을 (총 106화/미완결)
 평점
@@ -5892,155 +5736,155 @@
 남편이 불륜을 저질렀다. 엄청난 빚을 떠안기고, 아이를 잃게 한 것으로 모자라, 한참 어린 여자와 제 눈앞에서 몸을 섞었다. 상처 입은 삶은 볼품 없이 시들어 버려질 예정이었다. 그런데-, "어른의 사랑을 가르쳐 주세요."나해..</t>
         </is>
       </c>
-      <c r="Y35" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z35" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA35" t="n">
+      <c r="Y34" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA34" t="n">
         <v>105</v>
       </c>
-      <c r="AB35" t="inlineStr">
+      <c r="AB34" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
+      <c r="AC34" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD35" t="inlineStr">
+      <c r="AD34" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE35" t="n">
+      <c r="AE34" t="n">
         <v>4</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
-      <c r="AG35" t="inlineStr"/>
-      <c r="AH35" t="inlineStr">
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI35" t="inlineStr">
+      <c r="AI34" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>2026-08-24 11:08:04</t>
+      <c r="AJ34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:56:12</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>토</t>
         </is>
       </c>
-      <c r="C36" t="n">
+      <c r="C35" t="n">
         <v>9</v>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>둘째에게</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=845711&amp;tab=sat</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>845711</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>2026-08-24 10:22:06</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="b">
-        <v>1</v>
-      </c>
-      <c r="J36" t="inlineStr">
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:16:49</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="b">
+        <v>1</v>
+      </c>
+      <c r="J35" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr">
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="N36" t="n">
-        <v>1</v>
-      </c>
-      <c r="O36" t="inlineStr">
+      <c r="N35" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" t="inlineStr">
         <is>
           <t>둘째에게</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>둘째에게 (총 32화/미완결)</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>총 32화/미완결</t>
         </is>
       </c>
-      <c r="R36" t="n">
+      <c r="R35" t="n">
         <v>32</v>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>평점 10.0 | 고태호 고태호 | 2026.06.12. | 총32화/미완결 | 27화 무료</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>평점 10.0 | 고태호 고태호 | 2026.06.12. | 총32화/미완결 | 27화 무료</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr">
+      <c r="V35" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13512084</t>
         </is>
       </c>
-      <c r="W36" t="inlineStr">
+      <c r="W35" t="inlineStr">
         <is>
           <t>13512084</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>둘째에게 (총 32화/미완결)
 평점
@@ -6048,155 +5892,155 @@
 슬럼프에 시달리고 있는 작가 '이류진'은 자신의 팬이자 조직폭력배 '둘째'와 우연히 엮이게 되고, 슬럼프를 극복하고 싶은 작가와 글쓰는 법을 배우고 싶어하는 조폭은 필요로 인해 서로 교류를 하게 된다.그렇게 교류를 하며 ..</t>
         </is>
       </c>
-      <c r="Y36" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z36" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA36" t="n">
+      <c r="Y35" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA35" t="n">
         <v>105</v>
       </c>
-      <c r="AB36" t="inlineStr">
+      <c r="AB35" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
+      <c r="AC35" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD36" t="inlineStr">
+      <c r="AD35" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF36" t="inlineStr"/>
-      <c r="AG36" t="inlineStr"/>
-      <c r="AH36" t="inlineStr">
+      <c r="AE35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI36" t="inlineStr">
+      <c r="AI35" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>2026-08-24 11:08:04</t>
+      <c r="AJ35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:56:12</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>토</t>
         </is>
       </c>
-      <c r="C37" t="n">
+      <c r="C36" t="n">
         <v>18</v>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>데이워커</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=828880&amp;tab=sat</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>828880</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>2026-08-24 10:22:06</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="b">
-        <v>1</v>
-      </c>
-      <c r="J37" t="inlineStr">
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:16:49</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="b">
+        <v>1</v>
+      </c>
+      <c r="J36" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr">
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="N37" t="n">
-        <v>1</v>
-      </c>
-      <c r="O37" t="inlineStr">
+      <c r="N36" t="n">
+        <v>1</v>
+      </c>
+      <c r="O36" t="inlineStr">
         <is>
           <t>데이워커</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>데이워커 (총 94화/미완결)</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>총 94화/미완결</t>
         </is>
       </c>
-      <c r="R37" t="n">
+      <c r="R36" t="n">
         <v>94</v>
       </c>
-      <c r="S37" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>평점 9.6 | MUTE MUTE | 2026.06.12. | 총94화/미완결 | 89화 무료</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>평점 9.6 | MUTE MUTE | 2026.06.12. | 총94화/미완결 | 89화 무료</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr">
+      <c r="V36" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=11433164</t>
         </is>
       </c>
-      <c r="W37" t="inlineStr">
+      <c r="W36" t="inlineStr">
         <is>
           <t>11433164</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>데이워커 (총 94화/미완결)
 평점
@@ -6204,155 +6048,155 @@
 국정원 블랙요원 '수혁'은 한국에 약물을 밀매하는 조직 '나나야구미'의 수장 암살 임무를 받는다.그러나 그 수장은 '안나'란 이름의 싸움과는 연관 없을 법한 매력적인 여자였는데... 이 임무 뭔가 이상하다.자신을 배신한 국정..</t>
         </is>
       </c>
-      <c r="Y37" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z37" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA37" t="n">
+      <c r="Y36" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA36" t="n">
         <v>105</v>
       </c>
-      <c r="AB37" t="inlineStr">
+      <c r="AB36" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
+      <c r="AC36" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD37" t="inlineStr">
+      <c r="AD36" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF37" t="inlineStr"/>
-      <c r="AG37" t="inlineStr"/>
-      <c r="AH37" t="inlineStr">
+      <c r="AE36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI37" t="inlineStr">
+      <c r="AI36" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>2026-08-24 11:08:04</t>
+      <c r="AJ36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:56:12</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>토</t>
         </is>
       </c>
-      <c r="C38" t="n">
-        <v>37</v>
-      </c>
-      <c r="D38" t="inlineStr">
+      <c r="C37" t="n">
+        <v>38</v>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>연애 못하면 죽음!</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=846662&amp;tab=sat</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>846662</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>2026-08-24 10:22:06</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="b">
-        <v>1</v>
-      </c>
-      <c r="J38" t="inlineStr">
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:16:50</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="b">
+        <v>1</v>
+      </c>
+      <c r="J37" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr">
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="N38" t="n">
-        <v>1</v>
-      </c>
-      <c r="O38" t="inlineStr">
+      <c r="N37" t="n">
+        <v>1</v>
+      </c>
+      <c r="O37" t="inlineStr">
         <is>
           <t>연애 못하면 죽음!</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>연애 못하면 죽음! (총 31화/미완결)</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>총 31화/미완결</t>
         </is>
       </c>
-      <c r="R38" t="n">
+      <c r="R37" t="n">
         <v>31</v>
       </c>
-      <c r="S38" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr">
+      <c r="T37" t="inlineStr">
         <is>
           <t>평점 9.8 | 우연희 pusna | 2026.06.12. | 총31화/미완결 | 23화 무료</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>평점 9.8 | 우연희 pusna | 2026.06.12. | 총31화/미완결 | 23화 무료</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr">
+      <c r="V37" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13633976</t>
         </is>
       </c>
-      <c r="W38" t="inlineStr">
+      <c r="W37" t="inlineStr">
         <is>
           <t>13633976</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>연애 못하면 죽음! (총 31화/미완결)
 평점
@@ -6360,155 +6204,155 @@
 똥차들과의 망한 연애로 인해사랑, 연애에 부정적인 30대가 된 워커홀릭 문주경은어느날 우연히 '금방 사랑에 빠지는' 저주에 걸리게 된다.마음에 드는 상대에게 다짜고짜 고백부터 하게 되는 끔찍한 저주.사랑에 빠지기를 거..</t>
         </is>
       </c>
-      <c r="Y38" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z38" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA38" t="n">
+      <c r="Y37" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA37" t="n">
         <v>105</v>
       </c>
-      <c r="AB38" t="inlineStr">
+      <c r="AB37" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
+      <c r="AC37" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD38" t="inlineStr">
+      <c r="AD37" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF38" t="inlineStr"/>
-      <c r="AG38" t="inlineStr"/>
-      <c r="AH38" t="inlineStr">
+      <c r="AE37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="inlineStr"/>
+      <c r="AH37" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI38" t="inlineStr">
+      <c r="AI37" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>2026-08-24 11:08:04</t>
+      <c r="AJ37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:56:12</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>토</t>
         </is>
       </c>
-      <c r="C39" t="n">
-        <v>49</v>
-      </c>
-      <c r="D39" t="inlineStr">
+      <c r="C38" t="n">
+        <v>51</v>
+      </c>
+      <c r="D38" t="inlineStr">
         <is>
           <t>데스루프</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=852086&amp;tab=sat</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>852086</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>2026-08-24 10:22:07</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="b">
-        <v>1</v>
-      </c>
-      <c r="J39" t="inlineStr">
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:16:50</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="b">
+        <v>1</v>
+      </c>
+      <c r="J38" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr">
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="N39" t="n">
-        <v>1</v>
-      </c>
-      <c r="O39" t="inlineStr">
+      <c r="N38" t="n">
+        <v>1</v>
+      </c>
+      <c r="O38" t="inlineStr">
         <is>
           <t>데스루프</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>데스루프 (총 6화/미완결)</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr">
+      <c r="Q38" t="inlineStr">
         <is>
           <t>총 6화/미완결</t>
         </is>
       </c>
-      <c r="R39" t="n">
+      <c r="R38" t="n">
         <v>6</v>
       </c>
-      <c r="S39" t="inlineStr">
+      <c r="S38" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr">
+      <c r="T38" t="inlineStr">
         <is>
           <t>평점 8.3 | 은삼 은삼 | 2026.06.26. | 총6화/미완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="U38" t="inlineStr">
         <is>
           <t>평점 8.3 | 은삼 은삼 | 2026.06.26. | 총6화/미완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr">
+      <c r="V38" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14366954</t>
         </is>
       </c>
-      <c r="W39" t="inlineStr">
+      <c r="W38" t="inlineStr">
         <is>
           <t>14366954</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>데스루프 (총 6화/미완결)
 평점
@@ -6516,6 +6360,161 @@
 정신을 차려 보니 지하 창고에 갇힌 주인공 홍연화.연화는 자신을 가둔 남성에게 여러 번 끔찍한 죽음을 맞이하지만, 계속해서 시간이 반복된다.겨우 그곳을 빠져나오지만 그녀 앞에 마주한 것은 끔찍하게 생긴 괴물.과연 그녀..</t>
         </is>
       </c>
+      <c r="Y38" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>non_compilation_but_download_not_ok</t>
+        </is>
+      </c>
+      <c r="AE38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="inlineStr"/>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:56:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>토</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>53</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>초임계지옥</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=854340&amp;tab=sat</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>854340</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:16:50</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="b">
+        <v>1</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>19금 초임계지옥</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>19금 초임계지옥 (총 4화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>총 4화/미완결</t>
+        </is>
+      </c>
+      <c r="R39" t="n">
+        <v>4</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>평점 10.0 | 김성진 김성진 | 2026.08.28. | 총4화/미완결 | 1화 무료</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>평점 10.0 | 김성진 김성진 | 2026.08.28. | 총4화/미완결 | 1화 무료</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=14649867</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>14649867</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>19금 초임계지옥 (총 4화/미완결)
+평점
+10.0 | 김성진 김성진 | 2026.08.28. | 총4화/미완결 | 1화 무료</t>
+        </is>
+      </c>
       <c r="Y39" t="b">
         <v>0</v>
       </c>
@@ -6552,7 +6551,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>reused_existing_product_no</t>
+          <t>searched_series</t>
         </is>
       </c>
       <c r="AJ39" t="b">
@@ -6560,7 +6559,7 @@
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>2026-08-24 11:08:04</t>
+          <t>2026-08-31 13:56:12</t>
         </is>
       </c>
     </row>
@@ -6595,7 +6594,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-08-24 10:22:09</t>
+          <t>2026-08-31 13:16:53</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
@@ -6716,7 +6715,7 @@
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>2026-08-24 11:08:04</t>
+          <t>2026-08-31 13:56:12</t>
         </is>
       </c>
     </row>
@@ -6732,7 +6731,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6751,7 +6750,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-08-24 10:22:09</t>
+          <t>2026-08-31 13:16:53</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -6872,7 +6871,7 @@
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>2026-08-24 11:08:04</t>
+          <t>2026-08-31 13:56:12</t>
         </is>
       </c>
     </row>
@@ -6907,7 +6906,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-08-24 10:22:09</t>
+          <t>2026-08-31 13:16:53</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
@@ -7028,7 +7027,7 @@
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>2026-08-24 11:08:04</t>
+          <t>2026-08-31 13:56:12</t>
         </is>
       </c>
     </row>
@@ -7063,7 +7062,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-08-24 10:22:09</t>
+          <t>2026-08-31 13:16:53</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
@@ -7183,7 +7182,7 @@
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>2026-08-24 11:08:04</t>
+          <t>2026-08-31 13:56:12</t>
         </is>
       </c>
     </row>
@@ -7199,7 +7198,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -7218,7 +7217,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-08-24 10:22:10</t>
+          <t>2026-08-31 13:16:54</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
@@ -7345,7 +7344,7 @@
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>2026-08-24 11:08:04</t>
+          <t>2026-08-31 13:56:12</t>
         </is>
       </c>
     </row>
@@ -7361,26 +7360,26 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>화스트 페이스</t>
+          <t>지옥심판</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=847905&amp;tab=sun</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=854096&amp;tab=sun</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>847905</t>
+          <t>854096</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-08-24 10:22:10</t>
+          <t>2026-08-31 13:16:54</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
@@ -7408,48 +7407,204 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
+          <t>지옥심판</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>지옥심판 (총 7화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>총 7화/미완결</t>
+        </is>
+      </c>
+      <c r="R45" t="n">
+        <v>7</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>평점 9.6 | 가강 주혁 | 2026.08.22. | 총7화/미완결 | 2화 무료</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>평점 9.6 | 가강 주혁 | 2026.08.22. | 총7화/미완결 | 2화 무료</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=14622042</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>14622042</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>지옥심판 (총 7화/미완결)
+평점
+9.6 | 가강 주혁 | 2026.08.22. | 총7화/미완결 | 2화 무료
+죄를 지은 인간은 언젠가 벌을 받게 되어있다. 이승이 아닌 저승에서라도.죄인을 심판하고 지옥으로 인도하는 저승사자 이현의 이야기.</t>
+        </is>
+      </c>
+      <c r="Y45" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z45" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>non_compilation_but_download_not_ok</t>
+        </is>
+      </c>
+      <c r="AE45" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="inlineStr"/>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:56:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>47</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
           <t>화스트 페이스</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=847905&amp;tab=sun</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>847905</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:16:54</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="b">
+        <v>1</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>1</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>화스트 페이스</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
         <is>
           <t>화스트 페이스 (총 24화/미완결)</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="Q46" t="inlineStr">
         <is>
           <t>총 24화/미완결</t>
         </is>
       </c>
-      <c r="R45" t="n">
+      <c r="R46" t="n">
         <v>24</v>
       </c>
-      <c r="S45" t="inlineStr">
+      <c r="S46" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr">
+      <c r="T46" t="inlineStr">
         <is>
           <t>평점 9.9 | NO_Teamkill NO_Teamkill | 2026.06.13. | 총24화/미완결 | 20화 무료</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="U46" t="inlineStr">
         <is>
           <t>평점 9.9 | NO_Teamkill NO_Teamkill | 2026.06.13. | 총24화/미완결 | 20화 무료</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr">
+      <c r="V46" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13750354</t>
         </is>
       </c>
-      <c r="W45" t="inlineStr">
+      <c r="W46" t="inlineStr">
         <is>
           <t>13750354</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>화스트 페이스 (총 24화/미완결)
 평점
@@ -7457,162 +7612,6 @@
 화스트 페이스! 상황 발생! 상황 발생!현재 적 대규모 도발로 인해 준전시상태 돌입!전 병력 전투 장비 구비하고 즉각 출동 준비할 수 있도록!제1부 화스트페이스!제2부 20XX년 XX월 XX일 21시44분!제3부 발령권자 군단장!..</t>
         </is>
       </c>
-      <c r="Y45" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z45" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>105</v>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>review_needed</t>
-        </is>
-      </c>
-      <c r="AD45" t="inlineStr">
-        <is>
-          <t>non_compilation_but_download_not_ok</t>
-        </is>
-      </c>
-      <c r="AE45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF45" t="inlineStr"/>
-      <c r="AG45" t="inlineStr"/>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>2026-08-24 11:08:04</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>64</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>지옥심판</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=854096&amp;tab=sun</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>854096</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>2026-08-24 10:22:10</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="b">
-        <v>1</v>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="N46" t="n">
-        <v>1</v>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>지옥심판</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>지옥심판 (총 7화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>총 7화/미완결</t>
-        </is>
-      </c>
-      <c r="R46" t="n">
-        <v>7</v>
-      </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>평점 9.6 | 가강 주혁 | 2026.08.22. | 총7화/미완결 | 2화 무료</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>평점 9.6 | 가강 주혁 | 2026.08.22. | 총7화/미완결 | 2화 무료</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=14622042</t>
-        </is>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>14622042</t>
-        </is>
-      </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>지옥심판 (총 7화/미완결)
-평점
-9.6 | 가강 주혁 | 2026.08.22. | 총7화/미완결 | 2화 무료
-죄를 지은 인간은 언젠가 벌을 받게 되어있다. 이승이 아닌 저승에서라도.죄인을 심판하고 지옥으로 인도하는 저승사자 이현의 이야기.</t>
-        </is>
-      </c>
       <c r="Y46" t="b">
         <v>0</v>
       </c>
@@ -7638,7 +7637,7 @@
         </is>
       </c>
       <c r="AE46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="inlineStr"/>
@@ -7649,7 +7648,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>searched_series</t>
+          <t>reused_existing_product_no</t>
         </is>
       </c>
       <c r="AJ46" t="b">
@@ -7657,7 +7656,7 @@
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>2026-08-24 11:08:04</t>
+          <t>2026-08-31 13:56:12</t>
         </is>
       </c>
     </row>
@@ -7673,26 +7672,26 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>나는 참지 못한다</t>
+          <t>꿈에서 본 그놈이 대단해!</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=823476&amp;tab=sun</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=854132&amp;tab=sun</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>823476</t>
+          <t>854132</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-08-24 10:22:10</t>
+          <t>2026-08-31 13:16:55</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
@@ -7720,48 +7719,204 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
+          <t>꿈에서 본 그놈이 대단해! [독점]</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>꿈에서 본 그놈이 대단해! [독점] (총 6화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>총 6화/미완결</t>
+        </is>
+      </c>
+      <c r="R47" t="n">
+        <v>6</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>평점 8.5 | LICO 미지 | 2026.08.22. | 총6화/미완결 | 1화 무료</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>평점 8.5 | LICO 미지 | 2026.08.22. | 총6화/미완결 | 1화 무료</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=14626941</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>14626941</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>꿈에서 본 그놈이 대단해! [독점] (총 6화/미완결)
+평점
+8.5 | LICO 미지 | 2026.08.22. | 총6화/미완결 | 1화 무료
+MBTI TTTT인 28세 여성 공무정. 어느날부터 누군가와 살이 닿으면 그 사람의 섹X를 꿈으로 보는 일명 '색몽'을 꾸게 된다. 그런 무정에게 친구 남순과 인턴 강이 들이대기 시작하고. 무정은 원치 않게 남순과 강의 색몽을 보..</t>
+        </is>
+      </c>
+      <c r="Y47" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z47" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>non_compilation_but_download_not_ok</t>
+        </is>
+      </c>
+      <c r="AE47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="inlineStr"/>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:56:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>79</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
           <t>나는 참지 못한다</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=823476&amp;tab=sun</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>823476</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:16:55</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="b">
+        <v>1</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>1</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>나는 참지 못한다</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
         <is>
           <t>나는 참지 못한다 (총 115화/미완결)</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="Q48" t="inlineStr">
         <is>
           <t>총 115화/미완결</t>
         </is>
       </c>
-      <c r="R47" t="n">
+      <c r="R48" t="n">
         <v>115</v>
       </c>
-      <c r="S47" t="inlineStr">
+      <c r="S48" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T47" t="inlineStr">
+      <c r="T48" t="inlineStr">
         <is>
           <t>평점 10.0 | 성현 성현 | 2026.06.13. | 총115화/미완결 | 111화 무료</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="U48" t="inlineStr">
         <is>
           <t>평점 10.0 | 성현 성현 | 2026.06.13. | 총115화/미완결 | 111화 무료</t>
         </is>
       </c>
-      <c r="V47" t="inlineStr">
+      <c r="V48" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=10970308</t>
         </is>
       </c>
-      <c r="W47" t="inlineStr">
+      <c r="W48" t="inlineStr">
         <is>
           <t>10970308</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
+      <c r="X48" t="inlineStr">
         <is>
           <t>나는 참지 못한다 (총 115화/미완결)
 평점
@@ -7769,162 +7924,6 @@
 평범한 회사원 김연지는 교통사고 이후 변화를 겪게 된다.스트레스가 폭발하면 아무것도 참지 못하는 상태가 되고 만다.계속 일어나는 통제불능 사건들, 자신에게 접근하는 의문의 남성 민성훈.사건은 커지고 일상은 꼬여만 가..</t>
         </is>
       </c>
-      <c r="Y47" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z47" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>105</v>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>review_needed</t>
-        </is>
-      </c>
-      <c r="AD47" t="inlineStr">
-        <is>
-          <t>non_compilation_but_download_not_ok</t>
-        </is>
-      </c>
-      <c r="AE47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF47" t="inlineStr"/>
-      <c r="AG47" t="inlineStr"/>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>2026-08-24 11:08:04</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>85</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>꿈에서 본 그놈이 대단해!</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=854132&amp;tab=sun</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>854132</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>2026-08-24 10:22:11</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="b">
-        <v>1</v>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="N48" t="n">
-        <v>1</v>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>꿈에서 본 그놈이 대단해! [독점]</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>꿈에서 본 그놈이 대단해! [독점] (총 6화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>총 6화/미완결</t>
-        </is>
-      </c>
-      <c r="R48" t="n">
-        <v>6</v>
-      </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>평점 8.5 | LICO 미지 | 2026.08.22. | 총6화/미완결 | 1화 무료</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>평점 8.5 | LICO 미지 | 2026.08.22. | 총6화/미완결 | 1화 무료</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=14626941</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>14626941</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>꿈에서 본 그놈이 대단해! [독점] (총 6화/미완결)
-평점
-8.5 | LICO 미지 | 2026.08.22. | 총6화/미완결 | 1화 무료
-MBTI TTTT인 28세 여성 공무정. 어느날부터 누군가와 살이 닿으면 그 사람의 섹X를 꿈으로 보는 일명 '색몽'을 꾸게 된다. 그런 무정에게 친구 남순과 인턴 강이 들이대기 시작하고. 무정은 원치 않게 남순과 강의 색몽을 보..</t>
-        </is>
-      </c>
       <c r="Y48" t="b">
         <v>0</v>
       </c>
@@ -7961,7 +7960,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>searched_series</t>
+          <t>reused_existing_product_no</t>
         </is>
       </c>
       <c r="AJ48" t="b">
@@ -7969,7 +7968,7 @@
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>2026-08-24 11:08:04</t>
+          <t>2026-08-31 13:56:12</t>
         </is>
       </c>
     </row>
@@ -7985,7 +7984,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -8004,7 +8003,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-08-24 10:22:11</t>
+          <t>2026-08-31 13:16:56</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
@@ -8125,7 +8124,7 @@
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>2026-08-24 11:08:04</t>
+          <t>2026-08-31 13:56:12</t>
         </is>
       </c>
     </row>

--- a/data/adult_login_required_webtoons_v2.xlsx
+++ b/data/adult_login_required_webtoons_v2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK49"/>
+  <dimension ref="A1:AK51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -634,7 +634,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-31 13:16:31</t>
+          <t>2026-09-07 12:24:54</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -754,7 +754,7 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2026-08-31 13:56:12</t>
+          <t>2026-09-07 13:14:01</t>
         </is>
       </c>
     </row>
@@ -789,7 +789,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-31 13:16:32</t>
+          <t>2026-09-07 12:24:55</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -910,7 +910,7 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2026-08-31 13:56:12</t>
+          <t>2026-09-07 13:14:01</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-31 13:16:33</t>
+          <t>2026-09-07 12:24:55</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2026-08-31 13:56:12</t>
+          <t>2026-09-07 13:14:01</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-31 13:16:33</t>
+          <t>2026-09-07 12:24:56</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2026-08-31 13:56:12</t>
+          <t>2026-09-07 13:14:01</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-31 13:16:33</t>
+          <t>2026-09-07 12:24:56</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -1384,42 +1384,42 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2026-08-31 13:56:12</t>
+          <t>2026-09-07 13:14:01</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>화</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>82</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>오! 나의 교주님</t>
+          <t>누가 죄인인가</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=841624&amp;tab=tue</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=846782&amp;tab=mon</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>841624</t>
+          <t>846782</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-31 13:16:34</t>
+          <t>2026-09-07 12:24:57</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -1434,61 +1434,217 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>누가 죄인인가</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>누가 죄인인가 (총 37화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>총 37화/미완결</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>37</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>평점 10.0 | 이승우 이승우 | 2026.09.06. | 총37화/미완결 | 30화 무료</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>평점 10.0 | 이승우 이승우 | 2026.09.06. | 총37화/미완결 | 30화 무료</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=13634954</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>13634954</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>누가 죄인인가 (총 37화/미완결)
+평점
+10.0 | 이승우 이승우 | 2026.09.06. | 총37화/미완결 | 30화 무료
+"나의 아버지는 악마로 만들어졌다."연쇄살인마 '허욱열'의 딸로서 30년간 지옥 같은 삶을 살아온 일류 청부업자 '허예주' 오늘날 허욱열의 무고가 밝혀지게 되지만 이들은 여전히 지옥 속에 살고 있고 예주는자신과 같이 지옥 ..</t>
+        </is>
+      </c>
+      <c r="Y7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>non_compilation_but_download_not_ok</t>
+        </is>
+      </c>
+      <c r="AE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>searched_series</t>
+        </is>
+      </c>
+      <c r="AJ7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>2026-09-07 13:14:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>tue</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>화</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>오! 나의 교주님</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=841624&amp;tab=tue</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>841624</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:24:58</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
           <t>tue,fri</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>tue,fri</t>
         </is>
       </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>오! 나의 교주님</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>오! 나의 교주님 (총 94화/미완결)</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>총 94화/미완결</t>
         </is>
       </c>
-      <c r="R7" t="n">
+      <c r="R8" t="n">
         <v>94</v>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>평점 9.4 | 김꿀빨, 김완두 김꿀빨, 김완두 | 2026.06.18. | 총94화/미완결 | 89화 무료</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>평점 9.4 | 김꿀빨, 김완두 김꿀빨, 김완두 | 2026.06.18. | 총94화/미완결 | 89화 무료</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=12998643</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>12998643</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>오! 나의 교주님 (총 94화/미완결)
 평점
@@ -1496,310 +1652,310 @@
 사이비 종교 ‘진천교’에서 태어나 평생을 그곳에서 살아온 한성민. 그는 결국 모든 것을 잃고 홀로 탈출한다.수년 후, 성인이 된 그는 다시 진천교에 잠입해 처절한 복수를 시작하려 한다.“오, 나의 교주님. 제가 보내드릴게..</t>
         </is>
       </c>
-      <c r="Y7" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA7" t="n">
+      <c r="Y8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA8" t="n">
         <v>105</v>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr">
+      <c r="AE8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:56:12</t>
+      <c r="AJ8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>2026-09-07 13:14:01</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C9" t="n">
         <v>6</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>예쁨 컬렉션</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=844519&amp;tab=tue</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>844519</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:16:34</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="b">
-        <v>1</v>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:24:58</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="N8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>19금 예쁨 컬렉션</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>19금 예쁨 컬렉션 (총 35화/미완결)</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>총 35화/미완결</t>
         </is>
       </c>
-      <c r="R8" t="n">
+      <c r="R9" t="n">
         <v>35</v>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>평점 9.9 | 김이연 김이연 | 2026.06.15. | 총35화/미완결 | 30화 무료</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>평점 9.9 | 김이연 김이연 | 2026.06.15. | 총35화/미완결 | 30화 무료</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13365963</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>13365963</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>19금 예쁨 컬렉션 (총 35화/미완결)
 평점
 9.9 | 김이연 김이연 | 2026.06.15. | 총35화/미완결 | 30화 무료</t>
         </is>
       </c>
-      <c r="Y8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA8" t="n">
+      <c r="Y9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA9" t="n">
         <v>105</v>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="inlineStr">
+      <c r="AE9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AI9" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:56:12</t>
+      <c r="AJ9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>2026-09-07 13:14:01</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C10" t="n">
         <v>8</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>포그랜드</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=843116&amp;tab=tue</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>843116</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:16:34</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="b">
-        <v>1</v>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:24:58</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>포그랜드</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>포그랜드 (총 44화/미완결)</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>총 44화/미완결</t>
         </is>
       </c>
-      <c r="R9" t="n">
+      <c r="R10" t="n">
         <v>44</v>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>평점 10.0 | POGO POGO | 2026.06.15. | 총44화/미완결 | 38화 무료</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>평점 10.0 | POGO POGO | 2026.06.15. | 총44화/미완결 | 38화 무료</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13177080</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>13177080</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>포그랜드 (총 44화/미완결)
 평점
@@ -1807,155 +1963,155 @@
 존재만으로도 미스터리한 국제 교도소 포그랜드.죄수 교화 목적으로 파견된 과학교사 단테 강은 한순간의 폭동 속에 포그랜드에 갇히게 된다.탈출하는 방법은 영도자가 되는 길 뿐.무너진 이성과 신성을 목도하라!단테의 아홉 ..</t>
         </is>
       </c>
-      <c r="Y9" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA9" t="n">
+      <c r="Y10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA10" t="n">
         <v>105</v>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="inlineStr">
+      <c r="AE10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
+      <c r="AI10" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:56:12</t>
+      <c r="AJ10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>2026-09-07 13:14:01</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C11" t="n">
         <v>20</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>분신</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=845407&amp;tab=tue</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>845407</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:16:34</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="b">
-        <v>1</v>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:24:58</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J11" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="inlineStr">
         <is>
           <t>분신으로 자동사냥 [독점]</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>분신으로 자동사냥 [독점] (총 176화/완결)</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>총 176화/완결</t>
         </is>
       </c>
-      <c r="R10" t="n">
+      <c r="R11" t="n">
         <v>176</v>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>완결</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>평점 9.7 | 차씨 오팔 | 2025.12.27. | 총176화/완결 | 7화 무료</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>평점 9.7 | 차씨 오팔 | 2025.12.27. | 총176화/완결 | 7화 무료</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=8833786</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>8833786</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>분신으로 자동사냥 [독점] (총 176화/완결)
 평점
@@ -1963,161 +2119,161 @@
 일해야 하고, 공부도 해야 하고, 밥도 먹어야 하고.‘왜 사람은 한 번에 한 가지 일밖에 못 하는 걸까.’상우는 항상 자신의 몸이 두 개였으면 좋겠다고 생각했다...그랬더니 몸이 두 개가 되었다.</t>
         </is>
       </c>
-      <c r="Y10" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA10" t="n">
+      <c r="Y11" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA11" t="n">
         <v>105</v>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>matched</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>first_non_compilation_numeric_download</t>
         </is>
       </c>
-      <c r="AE10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF10" t="inlineStr">
+      <c r="AE11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF11" t="inlineStr">
         <is>
           <t>1,022만</t>
         </is>
       </c>
-      <c r="AG10" t="n">
+      <c r="AG11" t="n">
         <v>10220000</v>
       </c>
-      <c r="AH10" t="inlineStr">
+      <c r="AH11" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
+      <c r="AI11" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:56:12</t>
+      <c r="AJ11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>2026-09-07 13:14:01</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C12" t="n">
         <v>26</v>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>나쁜남자가 돼라!</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=847491&amp;tab=tue</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>847491</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:16:35</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="b">
-        <v>1</v>
-      </c>
-      <c r="J11" t="inlineStr">
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:24:58</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J12" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="N11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" t="inlineStr">
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="inlineStr">
         <is>
           <t>나쁜남자가 돼라!</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>나쁜남자가 돼라! (총 28화/미완결)</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>총 28화/미완결</t>
         </is>
       </c>
-      <c r="R11" t="n">
+      <c r="R12" t="n">
         <v>28</v>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>평점 9.9 | 이연 자개 | 2026.06.15. | 총28화/미완결 | 20화 무료</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>평점 9.9 | 이연 자개 | 2026.06.15. | 총28화/미완결 | 20화 무료</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13704125</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>13704125</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>나쁜남자가 돼라! (총 28화/미완결)
 평점
@@ -2125,155 +2281,155 @@
 구남친에 대한 트라우마로 나쁜남자 취향을 가지게 된 수연은 현재의 남자친구에게 약간의 불만을 느끼지만 잘 지내고 있다.그러던 어느 날, 남자친구의 몸에 수연의 취향 그 자체인 '나쁜 남자'가 빙의하는데…이 저주. 풀어줘..</t>
         </is>
       </c>
-      <c r="Y11" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA11" t="n">
+      <c r="Y12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA12" t="n">
         <v>105</v>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF11" t="inlineStr"/>
-      <c r="AG11" t="inlineStr"/>
-      <c r="AH11" t="inlineStr">
+      <c r="AE12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
+      <c r="AI12" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:56:12</t>
+      <c r="AJ12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>2026-09-07 13:14:01</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>50</v>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="n">
+        <v>51</v>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>원수의 아기를 가졌다</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=846110&amp;tab=tue</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>846110</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:16:35</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="b">
-        <v>1</v>
-      </c>
-      <c r="J12" t="inlineStr">
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:24:59</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="N12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" t="inlineStr">
+      <c r="N13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" t="inlineStr">
         <is>
           <t>원수의 아기를 가졌다</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>원수의 아기를 가졌다 (총 30화/미완결)</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>총 30화/미완결</t>
         </is>
       </c>
-      <c r="R12" t="n">
+      <c r="R13" t="n">
         <v>30</v>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>평점 9.7 | 미니바라기, 안지 이삼 | 2026.06.15. | 총30화/미완결 | 25화 무료</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>평점 9.7 | 미니바라기, 안지 이삼 | 2026.06.15. | 총30화/미완결 | 25화 무료</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13567690</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>13567690</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>원수의 아기를 가졌다 (총 30화/미완결)
 평점
@@ -2281,155 +2437,155 @@
 서로를 끔찍하게 혐오하는 두 가문 버몬테와 템네스.클로델은 강제 화해를 위한 희생양이 되어 템네스 공작 카이안의 신부가 된다.“템네스의 환영을 받지 못하는 신부로군. 주제를 알고 제 발로 걸어들어오라지.”오랜 반목을 ..</t>
         </is>
       </c>
-      <c r="Y12" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA12" t="n">
+      <c r="Y13" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA13" t="n">
         <v>105</v>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AD13" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="inlineStr"/>
-      <c r="AH12" t="inlineStr">
+      <c r="AE13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
+      <c r="AI13" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:56:12</t>
+      <c r="AJ13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>2026-09-07 13:14:01</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>53</v>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C14" t="n">
+        <v>55</v>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>화분</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=851671&amp;tab=tue</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>851671</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:16:35</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="b">
-        <v>1</v>
-      </c>
-      <c r="J13" t="inlineStr">
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:24:59</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="b">
+        <v>1</v>
+      </c>
+      <c r="J14" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="N13" t="n">
-        <v>1</v>
-      </c>
-      <c r="O13" t="inlineStr">
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>화분</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>화분 (총 5화/미완결)</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>총 5화/미완결</t>
         </is>
       </c>
-      <c r="R13" t="n">
+      <c r="R14" t="n">
         <v>5</v>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>평점 10.0 | 쿼시 쿼시 | 2026.06.15. | 총5화/미완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>평점 10.0 | 쿼시 쿼시 | 2026.06.15. | 총5화/미완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14284647</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>14284647</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>화분 (총 5화/미완결)
 평점
@@ -2437,155 +2593,155 @@
 버림받는 것이 무서운 여자와 그런 그녀가 무섭게 느껴지는 남자. 오래된 인연으로 시작된 사랑은 다정함의 얼굴을 한 집착이 되어, 두 사람의 일상과 마음을 서서히 갉아먹어 간다.우리 사랑은, 어디서부터 잘못된거지..?</t>
         </is>
       </c>
-      <c r="Y13" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA13" t="n">
+      <c r="Y14" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA14" t="n">
         <v>105</v>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
+      <c r="AC14" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD13" t="inlineStr">
+      <c r="AD14" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="inlineStr"/>
-      <c r="AH13" t="inlineStr">
+      <c r="AE14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI13" t="inlineStr">
+      <c r="AI14" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:56:12</t>
+      <c r="AJ14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>2026-09-07 13:14:01</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>80</v>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="C15" t="n">
+        <v>82</v>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>포 더 퀸덤</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=812414&amp;tab=tue</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>812414</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:16:36</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="b">
-        <v>1</v>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:25:00</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="b">
+        <v>1</v>
+      </c>
+      <c r="J15" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>tue</t>
         </is>
       </c>
-      <c r="N14" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" t="inlineStr">
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t>포 더 퀸덤</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>포 더 퀸덤 (총 128화/미완결)</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>총 128화/미완결</t>
         </is>
       </c>
-      <c r="R14" t="n">
+      <c r="R15" t="n">
         <v>128</v>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>평점 9.0 | 로즈옹 로즈옹 | 2026.06.15. | 총128화/미완결 | 123화 무료</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>평점 9.0 | 로즈옹 로즈옹 | 2026.06.15. | 총128화/미완결 | 123화 무료</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=9895056</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>9895056</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>포 더 퀸덤 (총 128화/미완결)
 평점
@@ -2593,155 +2749,155 @@
 악마 아벨은 인간 여자 연리에게 사랑하는 형, 카인을 잃고 만다.분노에 가득 차 연리를 찾아간 아벨은 사랑에 빠지는 금총알을 맞게 되면서, 연리에게 끓어오르는 사랑을 느끼게 되는데…그는 과연 형제의 복수를 택할 것인가..</t>
         </is>
       </c>
-      <c r="Y14" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA14" t="n">
+      <c r="Y15" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA15" t="n">
         <v>105</v>
       </c>
-      <c r="AB14" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
+      <c r="AC15" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD14" t="inlineStr">
+      <c r="AD15" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE14" t="n">
+      <c r="AE15" t="n">
         <v>2</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="inlineStr"/>
-      <c r="AH14" t="inlineStr">
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI14" t="inlineStr">
+      <c r="AI15" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:56:12</t>
+      <c r="AJ15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>2026-09-07 13:14:01</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>5</v>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="C16" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>싸이코패스 in 무림</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=846109&amp;tab=wed</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>846109</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:16:37</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="b">
-        <v>1</v>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:25:01</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="b">
+        <v>1</v>
+      </c>
+      <c r="J16" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="N15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O15" t="inlineStr">
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>싸이코패스 in 무림[독점]</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>싸이코패스 in 무림[독점] (총 32화/미완결)</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>총 32화/미완결</t>
         </is>
       </c>
-      <c r="R15" t="n">
+      <c r="R16" t="n">
         <v>32</v>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>평점 9.8 | 김언, 곤붕 송범규 | 2026.06.16. | 총32화/미완결 | 26화 무료</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>평점 9.8 | 김언, 곤붕 송범규 | 2026.06.16. | 총32화/미완결 | 26화 무료</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13566546</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>13566546</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>싸이코패스 in 무림[독점] (총 32화/미완결)
 평점
@@ -2749,155 +2905,155 @@
 [진정한 강자들의 세상, 무림 온라인에 오신 걸 환영합니다.]무림에 떨어진 희대의 싸이코패스.음모와 악의가 가득한 무림에 동봉수, 그의 무정한 이빨이 드리운다.</t>
         </is>
       </c>
-      <c r="Y15" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA15" t="n">
+      <c r="Y16" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA16" t="n">
         <v>105</v>
       </c>
-      <c r="AB15" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
+      <c r="AC16" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD15" t="inlineStr">
+      <c r="AD16" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF15" t="inlineStr"/>
-      <c r="AG15" t="inlineStr"/>
-      <c r="AH15" t="inlineStr">
+      <c r="AE16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI15" t="inlineStr">
+      <c r="AI16" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:56:12</t>
+      <c r="AJ16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>2026-09-07 13:14:01</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C17" t="n">
         <v>8</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>썰:관계주의</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=834033&amp;tab=wed</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>834033</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:16:37</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="b">
-        <v>1</v>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:25:01</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="b">
+        <v>1</v>
+      </c>
+      <c r="J17" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="N16" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" t="inlineStr">
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="inlineStr">
         <is>
           <t>썰:관계주의</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>썰:관계주의 (총 87화/미완결)</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>총 87화/미완결</t>
         </is>
       </c>
-      <c r="R16" t="n">
+      <c r="R17" t="n">
         <v>87</v>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>평점 10.0 | 이삼 장버들 | 2026.06.16. | 총87화/미완결 | 83화 무료</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>평점 10.0 | 이삼 장버들 | 2026.06.16. | 총87화/미완결 | 83화 무료</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=11802777</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>11802777</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>썰:관계주의 (총 87화/미완결)
 평점
@@ -2905,155 +3061,155 @@
 여러 상가가 들어서 있는 강남의 유명타워. 이야기는 유명타워의 한 피부과 안내 데스크 직원 강지영으로부터 시작된다. 동료이자 유부남 의사와 만남을 이어가던 지영은 그에게 또 다른 불륜 상대가 있음을 눈치 채는데 그 상..</t>
         </is>
       </c>
-      <c r="Y16" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA16" t="n">
+      <c r="Y17" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA17" t="n">
         <v>105</v>
       </c>
-      <c r="AB16" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
+      <c r="AC17" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD16" t="inlineStr">
+      <c r="AD17" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF16" t="inlineStr"/>
-      <c r="AG16" t="inlineStr"/>
-      <c r="AH16" t="inlineStr">
+      <c r="AE17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI16" t="inlineStr">
+      <c r="AI17" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:56:12</t>
+      <c r="AJ17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>2026-09-07 13:14:01</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C18" t="n">
         <v>29</v>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>끝장</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=844588&amp;tab=wed</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>844588</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:16:38</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="b">
-        <v>1</v>
-      </c>
-      <c r="J17" t="inlineStr">
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:25:01</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="N17" t="n">
+      <c r="N18" t="n">
         <v>2</v>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>떨어지면 끝장</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>떨어지면 끝장 (총 70화/완결)</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>총 70화/완결</t>
         </is>
       </c>
-      <c r="R17" t="n">
+      <c r="R18" t="n">
         <v>70</v>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>완결</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>평점 9.7 | Keiko Suenobu Keiko Suenobu | 2024.04.12. | 총70화/완결 | 3화 무료</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>평점 9.7 | Keiko Suenobu Keiko Suenobu | 2024.04.12. | 총70화/완결 | 3화 무료</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=6039213</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>6039213</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>떨어지면 끝장 (총 70화/완결)
 평점
@@ -3061,161 +3217,161 @@
 “떨어지면 끝장이야.”그토록 바라던 신축 초고층 아파트에 입주하게 된 주부 아스미.같은 아파트에 거주하며 아이들 유치원도 같은 세 명의 맘 친구가 생긴다.행복 가득한 새로운 생활이 펼쳐지리라 기대했지만, 어떤 인물과..</t>
         </is>
       </c>
-      <c r="Y17" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA17" t="n">
+      <c r="Y18" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA18" t="n">
         <v>100</v>
       </c>
-      <c r="AB17" t="inlineStr">
+      <c r="AB18" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_2</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
+      <c r="AC18" t="inlineStr">
         <is>
           <t>matched</t>
         </is>
       </c>
-      <c r="AD17" t="inlineStr">
+      <c r="AD18" t="inlineStr">
         <is>
           <t>first_non_compilation_numeric_download</t>
         </is>
       </c>
-      <c r="AE17" t="n">
+      <c r="AE18" t="n">
         <v>2</v>
       </c>
-      <c r="AF17" t="inlineStr">
+      <c r="AF18" t="inlineStr">
         <is>
           <t>3.9만</t>
         </is>
       </c>
-      <c r="AG17" t="n">
+      <c r="AG18" t="n">
         <v>39000</v>
       </c>
-      <c r="AH17" t="inlineStr">
+      <c r="AH18" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="AI17" t="inlineStr">
+      <c r="AI18" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:56:12</t>
+      <c r="AJ18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>2026-09-07 13:14:01</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>31</v>
-      </c>
-      <c r="D18" t="inlineStr">
+      <c r="C19" t="n">
+        <v>32</v>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>표절의혹</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=846106&amp;tab=wed</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>846106</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:16:38</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="b">
-        <v>1</v>
-      </c>
-      <c r="J18" t="inlineStr">
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:25:02</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="b">
+        <v>1</v>
+      </c>
+      <c r="J19" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="N18" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" t="inlineStr">
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" t="inlineStr">
         <is>
           <t>표절의혹</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>표절의혹 (총 29화/미완결)</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>총 29화/미완결</t>
         </is>
       </c>
-      <c r="R18" t="n">
+      <c r="R19" t="n">
         <v>29</v>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>평점 9.4 | 김칸비 황영찬 | 2026.06.16. | 총29화/미완결 | 24화 무료</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>평점 9.4 | 김칸비 황영찬 | 2026.06.16. | 총29화/미완결 | 24화 무료</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13575121</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>13575121</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>표절의혹 (총 29화/미완결)
 평점
@@ -3223,155 +3379,155 @@
 살인사건 피해자들의 시신을 예술품처럼 사고파는 인간성을 잃은 자들, 그리고 그런 예술 살인을 저지르는 ‘자학’이라는 연쇄살인마가 세간의 화제가 되고 있다. 한 예술가는 이 상황에 분노해 자학을 추적하기 시작하는데.....</t>
         </is>
       </c>
-      <c r="Y18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA18" t="n">
+      <c r="Y19" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA19" t="n">
         <v>105</v>
       </c>
-      <c r="AB18" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
+      <c r="AC19" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD18" t="inlineStr">
+      <c r="AD19" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF18" t="inlineStr"/>
-      <c r="AG18" t="inlineStr"/>
-      <c r="AH18" t="inlineStr">
+      <c r="AE19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI18" t="inlineStr">
+      <c r="AI19" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:56:12</t>
+      <c r="AJ19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>2026-09-07 13:14:01</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v>43</v>
-      </c>
-      <c r="D19" t="inlineStr">
+      <c r="C20" t="n">
+        <v>40</v>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>숙녀가 대머리이면 어떻단말인가</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=853619&amp;tab=wed</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>853619</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:16:39</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="b">
-        <v>1</v>
-      </c>
-      <c r="J19" t="inlineStr">
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:25:02</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="b">
+        <v>1</v>
+      </c>
+      <c r="J20" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="N19" t="n">
-        <v>1</v>
-      </c>
-      <c r="O19" t="inlineStr">
+      <c r="N20" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" t="inlineStr">
         <is>
           <t>숙녀가 대머리이면 어떻단 말인가</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>숙녀가 대머리이면 어떻단 말인가 (총 6화/미완결)</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>총 6화/미완결</t>
         </is>
       </c>
-      <c r="R19" t="n">
+      <c r="R20" t="n">
         <v>6</v>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>평점 9.6 | 아가사마기 | 2026.08.18. | 총6화/미완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>평점 9.6 | 아가사마기 | 2026.08.18. | 총6화/미완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14563924</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>14563924</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>숙녀가 대머리이면 어떻단 말인가 (총 6화/미완결)
 평점
@@ -3379,155 +3535,155 @@
 타인의 시선속에서만 살아왔던 정숙녀(23세, 공시생)는 지쳤다. 좋아하는 것도 없고 해야 될 일들만 가득한 인생... 더는 이렇게 살기 싫어!! 기분전환이라도 할까 들어간 미용실에서. 어랏? 뿅! 대머리가 되어버렸다. 오늘부터 대머..</t>
         </is>
       </c>
-      <c r="Y19" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA19" t="n">
+      <c r="Y20" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA20" t="n">
         <v>105</v>
       </c>
-      <c r="AB19" t="inlineStr">
+      <c r="AB20" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
+      <c r="AC20" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD19" t="inlineStr">
+      <c r="AD20" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF19" t="inlineStr"/>
-      <c r="AG19" t="inlineStr"/>
-      <c r="AH19" t="inlineStr">
+      <c r="AE20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI19" t="inlineStr">
+      <c r="AI20" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:56:12</t>
+      <c r="AJ20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>2026-09-07 13:14:01</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="C20" t="n">
-        <v>87</v>
-      </c>
-      <c r="D20" t="inlineStr">
+      <c r="C21" t="n">
+        <v>88</v>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>일곱 번째 의뢰인</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=850210&amp;tab=wed</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>850210</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:16:40</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="b">
-        <v>1</v>
-      </c>
-      <c r="J20" t="inlineStr">
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:25:03</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J21" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>wed</t>
         </is>
       </c>
-      <c r="N20" t="n">
-        <v>1</v>
-      </c>
-      <c r="O20" t="inlineStr">
+      <c r="N21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" t="inlineStr">
         <is>
           <t>일곱 번째 의뢰인</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>일곱 번째 의뢰인 (총 14화/미완결)</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>총 14화/미완결</t>
         </is>
       </c>
-      <c r="R20" t="n">
+      <c r="R21" t="n">
         <v>14</v>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>평점 10.0 | 함영서 함영서 | 2026.06.16. | 총14화/미완결 | 9화 무료</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>평점 10.0 | 함영서 함영서 | 2026.06.16. | 총14화/미완결 | 9화 무료</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14102285</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>14102285</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>일곱 번째 의뢰인 (총 14화/미완결)
 평점
@@ -3535,155 +3691,155 @@
 어린 탐정 맥스는 아무도 주목하지 않는 도박 업자의 죽음을 조사하라는 의뢰를 받는다. 의뢰인이 용의자로 지목한 도박 업자의 아내 제인. 맥스는 그녀를 향한 의심과 이끌림 사이에서 갈등하는데. 제인은 결백한가, 살인자인..</t>
         </is>
       </c>
-      <c r="Y20" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA20" t="n">
+      <c r="Y21" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA21" t="n">
         <v>105</v>
       </c>
-      <c r="AB20" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
+      <c r="AC21" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD20" t="inlineStr">
+      <c r="AD21" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF20" t="inlineStr"/>
-      <c r="AG20" t="inlineStr"/>
-      <c r="AH20" t="inlineStr">
+      <c r="AE21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI20" t="inlineStr">
+      <c r="AI21" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:56:12</t>
+      <c r="AJ21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>2026-09-07 13:14:01</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="C22" t="n">
         <v>5</v>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>소꿉친구 컴플렉스</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=822640&amp;tab=thu</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>822640</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:16:41</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="b">
-        <v>1</v>
-      </c>
-      <c r="J21" t="inlineStr">
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:25:04</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="b">
+        <v>1</v>
+      </c>
+      <c r="J22" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="N21" t="n">
-        <v>1</v>
-      </c>
-      <c r="O21" t="inlineStr">
+      <c r="N22" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" t="inlineStr">
         <is>
           <t>소꿉친구 컴플렉스</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>소꿉친구 컴플렉스 (총 80화/미완결)</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>총 80화/미완결</t>
         </is>
       </c>
-      <c r="R21" t="n">
+      <c r="R22" t="n">
         <v>80</v>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>평점 9.8 | 은하이 은하이 | 2026.06.17. | 총80화/미완결 | 76화 무료</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>평점 9.8 | 은하이 은하이 | 2026.06.17. | 총80화/미완결 | 76화 무료</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=10851069</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>10851069</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>소꿉친구 컴플렉스 (총 80화/미완결)
 평점
@@ -3691,155 +3847,155 @@
 20살에 20년지기, 평생을 함께한 소꿉친구 하늘과 민철.그런 소꿉친구의 알고 싶지 않은 은밀한 사정을 알아버렸다?!서로를 이성으로 생각한 적이 결코 없는 두사람이지만,오해가 오해를 낳고 착각이 착각을 낳는 상황들 속에..</t>
         </is>
       </c>
-      <c r="Y21" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA21" t="n">
+      <c r="Y22" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA22" t="n">
         <v>105</v>
       </c>
-      <c r="AB21" t="inlineStr">
+      <c r="AB22" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
+      <c r="AC22" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD21" t="inlineStr">
+      <c r="AD22" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE21" t="n">
+      <c r="AE22" t="n">
         <v>3</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
-      <c r="AG21" t="inlineStr"/>
-      <c r="AH21" t="inlineStr">
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI21" t="inlineStr">
+      <c r="AI22" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:56:12</t>
+      <c r="AJ22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>2026-09-07 13:14:01</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="C22" t="n">
+      <c r="C23" t="n">
         <v>6</v>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>럭키비치</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=852498&amp;tab=thu</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>852498</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:16:41</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="b">
-        <v>1</v>
-      </c>
-      <c r="J22" t="inlineStr">
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:25:04</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="b">
+        <v>1</v>
+      </c>
+      <c r="J23" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
         <is>
           <t>thu,sun</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>thu,sun</t>
         </is>
       </c>
-      <c r="N22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O22" t="inlineStr">
+      <c r="N23" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" t="inlineStr">
         <is>
           <t>럭키비치</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>럭키비치 (총 8화/미완결)</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>총 8화/미완결</t>
         </is>
       </c>
-      <c r="R22" t="n">
+      <c r="R23" t="n">
         <v>8</v>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>평점 10.0 | MAJOR, 약수 약수 | 2026.07.18. | 총8화/미완결 | 3화 무료</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>평점 10.0 | MAJOR, 약수 약수 | 2026.07.18. | 총8화/미완결 | 3화 무료</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14424733</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>14424733</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>럭키비치 (총 8화/미완결)
 평점
@@ -3847,155 +4003,155 @@
 “그거 알아? 기는 놈 위에 나는 썅X 있는 거?”불우한 환경과 폐쇄적인 바닷가 촌에서 자라온 소녀 '정임'은,그칠줄 모르는 주변의 부조리와 권태 속에서 결국 폭발,퇴폐업을 하는 고모의 불경한 쌈짓돈을 훔쳐 서울로 상경한..</t>
         </is>
       </c>
-      <c r="Y22" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z22" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA22" t="n">
+      <c r="Y23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA23" t="n">
         <v>105</v>
       </c>
-      <c r="AB22" t="inlineStr">
+      <c r="AB23" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
+      <c r="AC23" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD22" t="inlineStr">
+      <c r="AD23" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF22" t="inlineStr"/>
-      <c r="AG22" t="inlineStr"/>
-      <c r="AH22" t="inlineStr">
+      <c r="AE23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI22" t="inlineStr">
+      <c r="AI23" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:56:12</t>
+      <c r="AJ23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>2026-09-07 13:14:01</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="C23" t="n">
-        <v>18</v>
-      </c>
-      <c r="D23" t="inlineStr">
+      <c r="C24" t="n">
+        <v>9</v>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>나의 경험</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=853278&amp;tab=thu</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>853278</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:16:41</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="b">
-        <v>1</v>
-      </c>
-      <c r="J23" t="inlineStr">
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:25:04</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="b">
+        <v>1</v>
+      </c>
+      <c r="J24" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="N23" t="n">
-        <v>1</v>
-      </c>
-      <c r="O23" t="inlineStr">
+      <c r="N24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" t="inlineStr">
         <is>
           <t>나의 경험</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>나의 경험 (총 6화/미완결)</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>총 6화/미완결</t>
         </is>
       </c>
-      <c r="R23" t="n">
+      <c r="R24" t="n">
         <v>6</v>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>평점 7.0 | 윤박 윤박 | 2026.08.12. | 총6화/미완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>평점 7.0 | 윤박 윤박 | 2026.08.12. | 총6화/미완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14532341</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>14532341</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>나의 경험 (총 6화/미완결)
 평점
@@ -4003,155 +4159,155 @@
 살다 보면 한 번쯤 인연이 물밀듯 밀려 들어오는 순간들이 있다.별다를 것 없던 평범한 스무 살 재우의 일상에도예상치 못한 만남이 하나둘 찾아오기 시작한다.서툴지만 사랑만큼은 누구보다 진심인 재우는 믿는다.이번만큼은 ..</t>
         </is>
       </c>
-      <c r="Y23" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z23" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA23" t="n">
+      <c r="Y24" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA24" t="n">
         <v>105</v>
       </c>
-      <c r="AB23" t="inlineStr">
+      <c r="AB24" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
+      <c r="AC24" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD23" t="inlineStr">
+      <c r="AD24" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF23" t="inlineStr"/>
-      <c r="AG23" t="inlineStr"/>
-      <c r="AH23" t="inlineStr">
+      <c r="AE24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI23" t="inlineStr">
+      <c r="AI24" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:56:12</t>
+      <c r="AJ24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>2026-09-07 13:14:01</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>63</v>
-      </c>
-      <c r="D24" t="inlineStr">
+      <c r="C25" t="n">
+        <v>66</v>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>당신에게 얽힌 채</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=849879&amp;tab=thu</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>849879</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:16:43</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="b">
-        <v>1</v>
-      </c>
-      <c r="J24" t="inlineStr">
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:25:06</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="b">
+        <v>1</v>
+      </c>
+      <c r="J25" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>thu</t>
         </is>
       </c>
-      <c r="N24" t="n">
-        <v>1</v>
-      </c>
-      <c r="O24" t="inlineStr">
+      <c r="N25" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" t="inlineStr">
         <is>
           <t>당신에게 얽힌 채</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>당신에게 얽힌 채 (총 10화/미완결)</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>총 10화/미완결</t>
         </is>
       </c>
-      <c r="R24" t="n">
+      <c r="R25" t="n">
         <v>10</v>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>평점 10.0 | Nicole Knight, 유다 danah789 | 2026.06.17. | 총10화/미완결 | 5화 무료</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>평점 10.0 | Nicole Knight, 유다 danah789 | 2026.06.17. | 총10화/미완결 | 5화 무료</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14041685</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>14041685</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>당신에게 얽힌 채 (총 10화/미완결)
 평점
@@ -4159,155 +4315,155 @@
 상속자가 아닌 복종하는 존재로 길러진 에이바 모레티. 뉴욕에서 가장 강력한 마피아 가문의 막내딸인 그녀는 ‘집안의 사고뭉치’라는 오명을 벗고 자신의 자리를 찾기 위해 분투한다.그러던 어느 날 밤, 낯선 남자와 보낸 뜨..</t>
         </is>
       </c>
-      <c r="Y24" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z24" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA24" t="n">
+      <c r="Y25" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA25" t="n">
         <v>105</v>
       </c>
-      <c r="AB24" t="inlineStr">
+      <c r="AB25" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
+      <c r="AC25" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD24" t="inlineStr">
+      <c r="AD25" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF24" t="inlineStr"/>
-      <c r="AG24" t="inlineStr"/>
-      <c r="AH24" t="inlineStr">
+      <c r="AE25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI24" t="inlineStr">
+      <c r="AI25" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:56:12</t>
+      <c r="AJ25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>2026-09-07 13:14:01</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C25" t="n">
+      <c r="C26" t="n">
         <v>2</v>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>오! 나의 교주님</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=841624&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>841624</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:16:44</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="b">
-        <v>1</v>
-      </c>
-      <c r="J25" t="inlineStr">
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:25:08</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="b">
+        <v>1</v>
+      </c>
+      <c r="J26" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
         <is>
           <t>tue,fri</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>tue,fri</t>
         </is>
       </c>
-      <c r="N25" t="n">
-        <v>1</v>
-      </c>
-      <c r="O25" t="inlineStr">
+      <c r="N26" t="n">
+        <v>1</v>
+      </c>
+      <c r="O26" t="inlineStr">
         <is>
           <t>오! 나의 교주님</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>오! 나의 교주님 (총 94화/미완결)</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>총 94화/미완결</t>
         </is>
       </c>
-      <c r="R25" t="n">
+      <c r="R26" t="n">
         <v>94</v>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>평점 9.4 | 김꿀빨, 김완두 김꿀빨, 김완두 | 2026.06.18. | 총94화/미완결 | 89화 무료</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>평점 9.4 | 김꿀빨, 김완두 김꿀빨, 김완두 | 2026.06.18. | 총94화/미완결 | 89화 무료</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=12998643</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>12998643</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>오! 나의 교주님 (총 94화/미완결)
 평점
@@ -4315,155 +4471,155 @@
 사이비 종교 ‘진천교’에서 태어나 평생을 그곳에서 살아온 한성민. 그는 결국 모든 것을 잃고 홀로 탈출한다.수년 후, 성인이 된 그는 다시 진천교에 잠입해 처절한 복수를 시작하려 한다.“오, 나의 교주님. 제가 보내드릴게..</t>
         </is>
       </c>
-      <c r="Y25" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA25" t="n">
+      <c r="Y26" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA26" t="n">
         <v>105</v>
       </c>
-      <c r="AB25" t="inlineStr">
+      <c r="AB26" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
+      <c r="AC26" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD25" t="inlineStr">
+      <c r="AD26" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF25" t="inlineStr"/>
-      <c r="AG25" t="inlineStr"/>
-      <c r="AH25" t="inlineStr">
+      <c r="AE26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI25" t="inlineStr">
+      <c r="AI26" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:56:12</t>
+      <c r="AJ26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>2026-09-07 13:14:01</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C26" t="n">
+      <c r="C27" t="n">
         <v>9</v>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>두 얼굴</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=845646&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>845646</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:16:45</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="b">
-        <v>1</v>
-      </c>
-      <c r="J26" t="inlineStr">
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:25:08</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="b">
+        <v>1</v>
+      </c>
+      <c r="J27" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="N26" t="n">
-        <v>1</v>
-      </c>
-      <c r="O26" t="inlineStr">
+      <c r="N27" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" t="inlineStr">
         <is>
           <t>두 얼굴의 대표님</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>두 얼굴의 대표님 (총 126화/완결)</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>총 126화/완결</t>
         </is>
       </c>
-      <c r="R26" t="n">
+      <c r="R27" t="n">
         <v>126</v>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>완결</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>평점 6.2 | 1M, KuaiKan, YY 1M, KuaiKan, YY | 2022.10.02. | 총126화/완결 | 3화 무료</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>평점 6.2 | 1M, KuaiKan, YY 1M, KuaiKan, YY | 2022.10.02. | 총126화/완결 | 3화 무료</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=6489984</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>6489984</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>두 얼굴의 대표님 (총 126화/완결)
 평점
@@ -4471,161 +4627,161 @@
 재벌가의 사생아로 태어난 소원은 일찍 엄마를 잃고, 가족들의 멸시 속에서 살아왔다.그러다 언니에게 약혼자까지 뺏기게 되자, 실의에 빠진 소원은 유학을 떠나게 되고, 그곳에서 평범한 남편을 만나 결혼을 하게 된다.1년 후 ..</t>
         </is>
       </c>
-      <c r="Y26" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z26" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA26" t="n">
+      <c r="Y27" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA27" t="n">
         <v>105</v>
       </c>
-      <c r="AB26" t="inlineStr">
+      <c r="AB27" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
+      <c r="AC27" t="inlineStr">
         <is>
           <t>matched</t>
         </is>
       </c>
-      <c r="AD26" t="inlineStr">
+      <c r="AD27" t="inlineStr">
         <is>
           <t>first_non_compilation_numeric_download</t>
         </is>
       </c>
-      <c r="AE26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF26" t="inlineStr">
+      <c r="AE27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF27" t="inlineStr">
         <is>
           <t>157.5만</t>
         </is>
       </c>
-      <c r="AG26" t="n">
+      <c r="AG27" t="n">
         <v>1575000</v>
       </c>
-      <c r="AH26" t="inlineStr">
+      <c r="AH27" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="AI26" t="inlineStr">
+      <c r="AI27" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:56:12</t>
+      <c r="AJ27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>2026-09-07 13:14:01</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C27" t="n">
+      <c r="C28" t="n">
         <v>10</v>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>네가 사는 그 집</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=842465&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>842465</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:16:45</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="b">
-        <v>1</v>
-      </c>
-      <c r="J27" t="inlineStr">
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:25:08</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="b">
+        <v>1</v>
+      </c>
+      <c r="J28" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="N27" t="n">
-        <v>1</v>
-      </c>
-      <c r="O27" t="inlineStr">
+      <c r="N28" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" t="inlineStr">
         <is>
           <t>네가 사는 그 집</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>네가 사는 그 집 (총 47화/미완결)</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>총 47화/미완결</t>
         </is>
       </c>
-      <c r="R27" t="n">
+      <c r="R28" t="n">
         <v>47</v>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>평점 9.7 | 석우 해바다 | 2026.06.18. | 총47화/미완결 | 41화 무료</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>평점 9.7 | 석우 해바다 | 2026.06.18. | 총47화/미완결 | 41화 무료</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13090391</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>13090391</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>네가 사는 그 집 (총 47화/미완결)
 평점
@@ -4633,155 +4789,155 @@
 찢어지게 가난한 집에서 두 아이를 키우며 힘겹게 살아가던 30대 화린.어느날, 자기 첫사랑이었던 부유한 선배와 결혼해 행복하게 사는 친구와 몸이 바뀐다.하지만 부러워하던 삶을 얻은 기쁨도 잠시,그 집의 추악한 비밀이 드..</t>
         </is>
       </c>
-      <c r="Y27" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA27" t="n">
+      <c r="Y28" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA28" t="n">
         <v>105</v>
       </c>
-      <c r="AB27" t="inlineStr">
+      <c r="AB28" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
+      <c r="AC28" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD27" t="inlineStr">
+      <c r="AD28" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF27" t="inlineStr"/>
-      <c r="AG27" t="inlineStr"/>
-      <c r="AH27" t="inlineStr">
+      <c r="AE28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI27" t="inlineStr">
+      <c r="AI28" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:56:12</t>
+      <c r="AJ28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>2026-09-07 13:14:01</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C28" t="n">
-        <v>11</v>
-      </c>
-      <c r="D28" t="inlineStr">
+      <c r="C29" t="n">
+        <v>12</v>
+      </c>
+      <c r="D29" t="inlineStr">
         <is>
           <t>그리디</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=845919&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>845919</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:16:45</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="b">
-        <v>1</v>
-      </c>
-      <c r="J28" t="inlineStr">
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:25:08</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="b">
+        <v>1</v>
+      </c>
+      <c r="J29" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="N28" t="n">
-        <v>1</v>
-      </c>
-      <c r="O28" t="inlineStr">
+      <c r="N29" t="n">
+        <v>1</v>
+      </c>
+      <c r="O29" t="inlineStr">
         <is>
           <t>그리디</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>그리디 (총 31화/미완결)</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>총 31화/미완결</t>
         </is>
       </c>
-      <c r="R28" t="n">
+      <c r="R29" t="n">
         <v>31</v>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>평점 9.9 | 영하 랑라리 | 2026.06.18. | 총31화/미완결 | 25화 무료</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>평점 9.9 | 영하 랑라리 | 2026.06.18. | 총31화/미완결 | 25화 무료</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13530624</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>13530624</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>그리디 (총 31화/미완결)
 평점
@@ -4789,155 +4945,155 @@
 파혼했다. 십년지기 친구와 내가 파혼한 남자가 찍힌 청첩장 한 장.한유주는 그걸 끝으로 서른하나에 사랑도 우정도 다 버렸다. 남은 건 칼럼 한 줄에도 이름을 걸 수 없는 5년짜리 패션지 주니어 에디터 신세뿐.일도 사랑도, 마..</t>
         </is>
       </c>
-      <c r="Y28" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z28" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA28" t="n">
+      <c r="Y29" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA29" t="n">
         <v>105</v>
       </c>
-      <c r="AB28" t="inlineStr">
+      <c r="AB29" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
+      <c r="AC29" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD28" t="inlineStr">
+      <c r="AD29" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF28" t="inlineStr"/>
-      <c r="AG28" t="inlineStr"/>
-      <c r="AH28" t="inlineStr">
+      <c r="AE29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI28" t="inlineStr">
+      <c r="AI29" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:56:12</t>
+      <c r="AJ29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>2026-09-07 13:14:01</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C29" t="n">
-        <v>38</v>
-      </c>
-      <c r="D29" t="inlineStr">
+      <c r="C30" t="n">
+        <v>39</v>
+      </c>
+      <c r="D30" t="inlineStr">
         <is>
           <t>사자의 서</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=823737&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>823737</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:16:45</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="b">
-        <v>1</v>
-      </c>
-      <c r="J29" t="inlineStr">
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:25:09</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="b">
+        <v>1</v>
+      </c>
+      <c r="J30" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr">
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="N29" t="n">
+      <c r="N30" t="n">
         <v>2</v>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>사자의서 [도시정벌 레거시]</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>사자의서 [도시정벌 레거시] (총 219화/완결)</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>총 219화/완결</t>
         </is>
       </c>
-      <c r="R29" t="n">
+      <c r="R30" t="n">
         <v>219</v>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>완결</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>평점 9.2 | 신형빈 신형빈 | 2019.11.06. | 총219화/완결 | 5화 무료</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>평점 9.2 | 신형빈 신형빈 | 2019.11.06. | 총219화/완결 | 5화 무료</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="V30" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=2737090</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>2737090</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>사자의서 [도시정벌 레거시] (총 219화/완결)
 평점
@@ -4945,161 +5101,161 @@
 죽음(死)에서 돌아 온 자. 그가 써내려가는 피의 역사에 도시(都市)가 깨어난다.</t>
         </is>
       </c>
-      <c r="Y29" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA29" t="n">
+      <c r="Y30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA30" t="n">
         <v>100</v>
       </c>
-      <c r="AB29" t="inlineStr">
+      <c r="AB30" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_2</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
+      <c r="AC30" t="inlineStr">
         <is>
           <t>matched</t>
         </is>
       </c>
-      <c r="AD29" t="inlineStr">
+      <c r="AD30" t="inlineStr">
         <is>
           <t>first_non_compilation_numeric_download</t>
         </is>
       </c>
-      <c r="AE29" t="n">
+      <c r="AE30" t="n">
         <v>2</v>
       </c>
-      <c r="AF29" t="inlineStr">
+      <c r="AF30" t="inlineStr">
         <is>
           <t>121.3만</t>
         </is>
       </c>
-      <c r="AG29" t="n">
+      <c r="AG30" t="n">
         <v>1213000</v>
       </c>
-      <c r="AH29" t="inlineStr">
+      <c r="AH30" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="AI29" t="inlineStr">
+      <c r="AI30" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:56:12</t>
+      <c r="AJ30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>2026-09-07 13:14:01</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C30" t="n">
-        <v>58</v>
-      </c>
-      <c r="D30" t="inlineStr">
+      <c r="C31" t="n">
+        <v>59</v>
+      </c>
+      <c r="D31" t="inlineStr">
         <is>
           <t>박제</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=846363&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>846363</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:16:46</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="b">
-        <v>1</v>
-      </c>
-      <c r="J30" t="inlineStr">
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:25:09</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="b">
+        <v>1</v>
+      </c>
+      <c r="J31" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr">
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="N30" t="n">
+      <c r="N31" t="n">
         <v>2</v>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>박제하는 시간</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>박제하는 시간 (총 28화/완결)</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>총 28화/완결</t>
         </is>
       </c>
-      <c r="R30" t="n">
+      <c r="R31" t="n">
         <v>28</v>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>완결</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>평점 10.0 | 이언 | 2024.07.19. | 총28화/완결 | 5화 무료</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>평점 10.0 | 이언 | 2024.07.19. | 총28화/완결 | 5화 무료</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="V31" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=10632769</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
+      <c r="W31" t="inlineStr">
         <is>
           <t>10632769</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>박제하는 시간 (총 28화/완결)
 평점
@@ -5107,161 +5263,161 @@
 박제사 ‘도연’은 죽은 연인의 시체를 빼돌린다.이 과정을 목격한 작가 ‘이명’은 침묵의 대가로 도연의 삶을 소재로 요구해 온다.일주일간의 취재를 허락한 도연. 죽은 연인과 꼭 닮은 이명의 모습에 혼란을 느낀다.숲속의 ..</t>
         </is>
       </c>
-      <c r="Y30" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA30" t="n">
+      <c r="Y31" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA31" t="n">
         <v>100</v>
       </c>
-      <c r="AB30" t="inlineStr">
+      <c r="AB31" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_2</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
+      <c r="AC31" t="inlineStr">
         <is>
           <t>matched</t>
         </is>
       </c>
-      <c r="AD30" t="inlineStr">
+      <c r="AD31" t="inlineStr">
         <is>
           <t>first_non_compilation_numeric_download</t>
         </is>
       </c>
-      <c r="AE30" t="n">
+      <c r="AE31" t="n">
         <v>2</v>
       </c>
-      <c r="AF30" t="inlineStr">
+      <c r="AF31" t="inlineStr">
         <is>
           <t>7.2만</t>
         </is>
       </c>
-      <c r="AG30" t="n">
+      <c r="AG31" t="n">
         <v>72000</v>
       </c>
-      <c r="AH30" t="inlineStr">
+      <c r="AH31" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="AI30" t="inlineStr">
+      <c r="AI31" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:56:12</t>
+      <c r="AJ31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>2026-09-07 13:14:01</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C31" t="n">
-        <v>67</v>
-      </c>
-      <c r="D31" t="inlineStr">
+      <c r="C32" t="n">
+        <v>68</v>
+      </c>
+      <c r="D32" t="inlineStr">
         <is>
           <t>사탄의 순애</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=845378&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>845378</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:16:46</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="b">
-        <v>1</v>
-      </c>
-      <c r="J31" t="inlineStr">
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:25:09</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="b">
+        <v>1</v>
+      </c>
+      <c r="J32" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr">
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="N31" t="n">
-        <v>1</v>
-      </c>
-      <c r="O31" t="inlineStr">
+      <c r="N32" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" t="inlineStr">
         <is>
           <t>사탄의 순애 [독점]</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>사탄의 순애 [독점] (총 35화/미완결)</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>총 35화/미완결</t>
         </is>
       </c>
-      <c r="R31" t="n">
+      <c r="R32" t="n">
         <v>35</v>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>평점 9.8 | 용현 카모모 | 2026.06.18. | 총35화/미완결 | 28화 무료</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>평점 9.8 | 용현 카모모 | 2026.06.18. | 총35화/미완결 | 28화 무료</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13451638</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>13451638</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>사탄의 순애 [독점] (총 35화/미완결)
 평점
@@ -5269,155 +5425,155 @@
 초식동물계 대표주자 호구남 백은우 VS 육식동물계 대표주자 차도녀 범호연.정반대의 두 사람은 어쩌다 사귀게 됐을까?“백은우. 나한테 취업해라. 내 애인인 척 딱 1년. 그럼 10억이야.”업계에서 악마로 소문난 아티스트 레..</t>
         </is>
       </c>
-      <c r="Y31" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z31" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA31" t="n">
+      <c r="Y32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA32" t="n">
         <v>105</v>
       </c>
-      <c r="AB31" t="inlineStr">
+      <c r="AB32" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
+      <c r="AC32" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD31" t="inlineStr">
+      <c r="AD32" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF31" t="inlineStr"/>
-      <c r="AG31" t="inlineStr"/>
-      <c r="AH31" t="inlineStr">
+      <c r="AE32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="inlineStr"/>
+      <c r="AH32" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI31" t="inlineStr">
+      <c r="AI32" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:56:12</t>
+      <c r="AJ32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>2026-09-07 13:14:01</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C32" t="n">
-        <v>71</v>
-      </c>
-      <c r="D32" t="inlineStr">
+      <c r="C33" t="n">
+        <v>69</v>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t>죽여주는 캐스팅</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=843866&amp;tab=fri</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>843866</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:16:47</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="b">
-        <v>1</v>
-      </c>
-      <c r="J32" t="inlineStr">
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:25:09</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="b">
+        <v>1</v>
+      </c>
+      <c r="J33" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr">
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>fri</t>
         </is>
       </c>
-      <c r="N32" t="n">
-        <v>1</v>
-      </c>
-      <c r="O32" t="inlineStr">
+      <c r="N33" t="n">
+        <v>1</v>
+      </c>
+      <c r="O33" t="inlineStr">
         <is>
           <t>죽여주는 캐스팅 [독점]</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>죽여주는 캐스팅 [독점] (총 42화/미완결)</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>총 42화/미완결</t>
         </is>
       </c>
-      <c r="R32" t="n">
+      <c r="R33" t="n">
         <v>42</v>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>평점 9.6 | 영춘 하보 | 2026.06.18. | 총42화/미완결 | 36화 무료</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>평점 9.6 | 영춘 하보 | 2026.06.18. | 총42화/미완결 | 36화 무료</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
+      <c r="V33" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13253015</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr">
+      <c r="W33" t="inlineStr">
         <is>
           <t>13253015</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>죽여주는 캐스팅 [독점] (총 42화/미완결)
 평점
@@ -5425,310 +5581,310 @@
 영화감상 동호회에서 만난 혜수와 강호.성공한 배우를 꿈꾸는 강호는 오디션과 술자리에 몰두하며 혜수에게 기대어 살아간다.그런 강호를 이해하고자 혜수는 연기 수업을 시작하고 점차 자신의 길을 걷기 시작한다.하지만 강..</t>
         </is>
       </c>
-      <c r="Y32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z32" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA32" t="n">
+      <c r="Y33" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA33" t="n">
         <v>105</v>
       </c>
-      <c r="AB32" t="inlineStr">
+      <c r="AB33" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
+      <c r="AC33" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD32" t="inlineStr">
+      <c r="AD33" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF32" t="inlineStr"/>
-      <c r="AG32" t="inlineStr"/>
-      <c r="AH32" t="inlineStr">
+      <c r="AE33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI32" t="inlineStr">
+      <c r="AI33" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:56:12</t>
+      <c r="AJ33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>2026-09-07 13:14:01</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>토</t>
         </is>
       </c>
-      <c r="C33" t="n">
+      <c r="C34" t="n">
         <v>4</v>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>만취남녀</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=846883&amp;tab=sat</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>846883</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:16:48</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="b">
-        <v>1</v>
-      </c>
-      <c r="J33" t="inlineStr">
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:25:11</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="b">
+        <v>1</v>
+      </c>
+      <c r="J34" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr">
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="N33" t="n">
-        <v>1</v>
-      </c>
-      <c r="O33" t="inlineStr">
+      <c r="N34" t="n">
+        <v>1</v>
+      </c>
+      <c r="O34" t="inlineStr">
         <is>
           <t>19금 만취남녀</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>19금 만취남녀 (총 26화/미완결)</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>총 26화/미완결</t>
         </is>
       </c>
-      <c r="R33" t="n">
+      <c r="R34" t="n">
         <v>26</v>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>평점 9.7 | 금 금 | 2026.06.12. | 총26화/미완결 | 21화 무료</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>평점 9.7 | 금 금 | 2026.06.12. | 총26화/미완결 | 21화 무료</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr">
+      <c r="V34" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13646371</t>
         </is>
       </c>
-      <c r="W33" t="inlineStr">
+      <c r="W34" t="inlineStr">
         <is>
           <t>13646371</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>19금 만취남녀 (총 26화/미완결)
 평점
 9.7 | 금 금 | 2026.06.12. | 총26화/미완결 | 21화 무료</t>
         </is>
       </c>
-      <c r="Y33" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z33" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA33" t="n">
+      <c r="Y34" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA34" t="n">
         <v>105</v>
       </c>
-      <c r="AB33" t="inlineStr">
+      <c r="AB34" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
+      <c r="AC34" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD33" t="inlineStr">
+      <c r="AD34" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF33" t="inlineStr"/>
-      <c r="AG33" t="inlineStr"/>
-      <c r="AH33" t="inlineStr">
+      <c r="AE34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI33" t="inlineStr">
+      <c r="AI34" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:56:12</t>
+      <c r="AJ34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>2026-09-07 13:14:01</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>토</t>
         </is>
       </c>
-      <c r="C34" t="n">
+      <c r="C35" t="n">
         <v>5</v>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>시든 꽃에 눈물을</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=827190&amp;tab=sat</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>827190</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:16:48</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="b">
-        <v>1</v>
-      </c>
-      <c r="J34" t="inlineStr">
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:25:11</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="b">
+        <v>1</v>
+      </c>
+      <c r="J35" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr">
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="N34" t="n">
-        <v>1</v>
-      </c>
-      <c r="O34" t="inlineStr">
+      <c r="N35" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" t="inlineStr">
         <is>
           <t>시든 꽃에 눈물을</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>시든 꽃에 눈물을 (총 106화/미완결)</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>총 106화/미완결</t>
         </is>
       </c>
-      <c r="R34" t="n">
+      <c r="R35" t="n">
         <v>106</v>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>평점 9.8 | 개 개 | 2026.06.12. | 총106화/미완결 | 100화 무료</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>평점 9.8 | 개 개 | 2026.06.12. | 총106화/미완결 | 100화 무료</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
+      <c r="V35" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=11253061</t>
         </is>
       </c>
-      <c r="W34" t="inlineStr">
+      <c r="W35" t="inlineStr">
         <is>
           <t>11253061</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>시든 꽃에 눈물을 (총 106화/미완결)
 평점
@@ -5736,155 +5892,155 @@
 남편이 불륜을 저질렀다. 엄청난 빚을 떠안기고, 아이를 잃게 한 것으로 모자라, 한참 어린 여자와 제 눈앞에서 몸을 섞었다. 상처 입은 삶은 볼품 없이 시들어 버려질 예정이었다. 그런데-, "어른의 사랑을 가르쳐 주세요."나해..</t>
         </is>
       </c>
-      <c r="Y34" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z34" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA34" t="n">
+      <c r="Y35" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA35" t="n">
         <v>105</v>
       </c>
-      <c r="AB34" t="inlineStr">
+      <c r="AB35" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
+      <c r="AC35" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD34" t="inlineStr">
+      <c r="AD35" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE34" t="n">
+      <c r="AE35" t="n">
         <v>4</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
-      <c r="AG34" t="inlineStr"/>
-      <c r="AH34" t="inlineStr">
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI34" t="inlineStr">
+      <c r="AI35" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:56:12</t>
+      <c r="AJ35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>2026-09-07 13:14:01</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>토</t>
         </is>
       </c>
-      <c r="C35" t="n">
+      <c r="C36" t="n">
         <v>9</v>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>둘째에게</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=845711&amp;tab=sat</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>845711</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:16:49</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="b">
-        <v>1</v>
-      </c>
-      <c r="J35" t="inlineStr">
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:25:11</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="b">
+        <v>1</v>
+      </c>
+      <c r="J36" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr">
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>sat</t>
         </is>
       </c>
-      <c r="N35" t="n">
-        <v>1</v>
-      </c>
-      <c r="O35" t="inlineStr">
+      <c r="N36" t="n">
+        <v>1</v>
+      </c>
+      <c r="O36" t="inlineStr">
         <is>
           <t>둘째에게</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>둘째에게 (총 32화/미완결)</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>총 32화/미완결</t>
         </is>
       </c>
-      <c r="R35" t="n">
+      <c r="R36" t="n">
         <v>32</v>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>평점 10.0 | 고태호 고태호 | 2026.06.12. | 총32화/미완결 | 27화 무료</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>평점 10.0 | 고태호 고태호 | 2026.06.12. | 총32화/미완결 | 27화 무료</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr">
+      <c r="V36" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13512084</t>
         </is>
       </c>
-      <c r="W35" t="inlineStr">
+      <c r="W36" t="inlineStr">
         <is>
           <t>13512084</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>둘째에게 (총 32화/미완결)
 평점
@@ -5892,162 +6048,6 @@
 슬럼프에 시달리고 있는 작가 '이류진'은 자신의 팬이자 조직폭력배 '둘째'와 우연히 엮이게 되고, 슬럼프를 극복하고 싶은 작가와 글쓰는 법을 배우고 싶어하는 조폭은 필요로 인해 서로 교류를 하게 된다.그렇게 교류를 하며 ..</t>
         </is>
       </c>
-      <c r="Y35" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z35" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>105</v>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>review_needed</t>
-        </is>
-      </c>
-      <c r="AD35" t="inlineStr">
-        <is>
-          <t>non_compilation_but_download_not_ok</t>
-        </is>
-      </c>
-      <c r="AE35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF35" t="inlineStr"/>
-      <c r="AG35" t="inlineStr"/>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:56:12</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>토</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>18</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>데이워커</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=828880&amp;tab=sat</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>828880</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:16:49</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="b">
-        <v>1</v>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="N36" t="n">
-        <v>1</v>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>데이워커</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>데이워커 (총 94화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>총 94화/미완결</t>
-        </is>
-      </c>
-      <c r="R36" t="n">
-        <v>94</v>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>평점 9.6 | MUTE MUTE | 2026.06.12. | 총94화/미완결 | 89화 무료</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>평점 9.6 | MUTE MUTE | 2026.06.12. | 총94화/미완결 | 89화 무료</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=11433164</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>11433164</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>데이워커 (총 94화/미완결)
-평점
-9.6 | MUTE MUTE | 2026.06.12. | 총94화/미완결 | 89화 무료
-국정원 블랙요원 '수혁'은 한국에 약물을 밀매하는 조직 '나나야구미'의 수장 암살 임무를 받는다.그러나 그 수장은 '안나'란 이름의 싸움과는 연관 없을 법한 매력적인 여자였는데... 이 임무 뭔가 이상하다.자신을 배신한 국정..</t>
-        </is>
-      </c>
       <c r="Y36" t="b">
         <v>0</v>
       </c>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>2026-08-31 13:56:12</t>
+          <t>2026-09-07 13:14:01</t>
         </is>
       </c>
     </row>
@@ -6108,7 +6108,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-08-31 13:16:50</t>
+          <t>2026-09-07 12:25:12</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>2026-08-31 13:56:12</t>
+          <t>2026-09-07 13:14:01</t>
         </is>
       </c>
     </row>
@@ -6264,26 +6264,26 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>데스루프</t>
+          <t>초임계지옥</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=852086&amp;tab=sat</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=854340&amp;tab=sat</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>852086</t>
+          <t>854340</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-08-31 13:16:50</t>
+          <t>2026-09-07 12:25:12</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -6311,48 +6311,203 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
+          <t>19금 초임계지옥</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>19금 초임계지옥 (총 4화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>총 4화/미완결</t>
+        </is>
+      </c>
+      <c r="R38" t="n">
+        <v>4</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>평점 10.0 | 김성진 김성진 | 2026.08.28. | 총4화/미완결 | 1화 무료</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>평점 10.0 | 김성진 김성진 | 2026.08.28. | 총4화/미완결 | 1화 무료</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=14649867</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>14649867</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>19금 초임계지옥 (총 4화/미완결)
+평점
+10.0 | 김성진 김성진 | 2026.08.28. | 총4화/미완결 | 1화 무료</t>
+        </is>
+      </c>
+      <c r="Y38" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>non_compilation_but_download_not_ok</t>
+        </is>
+      </c>
+      <c r="AE38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="inlineStr"/>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>2026-09-07 13:14:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>토</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>53</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
           <t>데스루프</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=852086&amp;tab=sat</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>852086</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:25:12</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="b">
+        <v>1</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>데스루프</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
         <is>
           <t>데스루프 (총 6화/미완결)</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr">
+      <c r="Q39" t="inlineStr">
         <is>
           <t>총 6화/미완결</t>
         </is>
       </c>
-      <c r="R38" t="n">
+      <c r="R39" t="n">
         <v>6</v>
       </c>
-      <c r="S38" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr">
+      <c r="T39" t="inlineStr">
         <is>
           <t>평점 8.3 | 은삼 은삼 | 2026.06.26. | 총6화/미완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="U39" t="inlineStr">
         <is>
           <t>평점 8.3 | 은삼 은삼 | 2026.06.26. | 총6화/미완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr">
+      <c r="V39" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=14366954</t>
         </is>
       </c>
-      <c r="W38" t="inlineStr">
+      <c r="W39" t="inlineStr">
         <is>
           <t>14366954</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>데스루프 (총 6화/미완결)
 평점
@@ -6360,161 +6515,6 @@
 정신을 차려 보니 지하 창고에 갇힌 주인공 홍연화.연화는 자신을 가둔 남성에게 여러 번 끔찍한 죽음을 맞이하지만, 계속해서 시간이 반복된다.겨우 그곳을 빠져나오지만 그녀 앞에 마주한 것은 끔찍하게 생긴 괴물.과연 그녀..</t>
         </is>
       </c>
-      <c r="Y38" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z38" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>105</v>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>review_needed</t>
-        </is>
-      </c>
-      <c r="AD38" t="inlineStr">
-        <is>
-          <t>non_compilation_but_download_not_ok</t>
-        </is>
-      </c>
-      <c r="AE38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF38" t="inlineStr"/>
-      <c r="AG38" t="inlineStr"/>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:56:12</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>토</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>53</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>초임계지옥</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=854340&amp;tab=sat</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>854340</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:16:50</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="b">
-        <v>1</v>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="N39" t="n">
-        <v>1</v>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>19금 초임계지옥</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>19금 초임계지옥 (총 4화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>총 4화/미완결</t>
-        </is>
-      </c>
-      <c r="R39" t="n">
-        <v>4</v>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>평점 10.0 | 김성진 김성진 | 2026.08.28. | 총4화/미완결 | 1화 무료</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>평점 10.0 | 김성진 김성진 | 2026.08.28. | 총4화/미완결 | 1화 무료</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=14649867</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>14649867</t>
-        </is>
-      </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>19금 초임계지옥 (총 4화/미완결)
-평점
-10.0 | 김성진 김성진 | 2026.08.28. | 총4화/미완결 | 1화 무료</t>
-        </is>
-      </c>
       <c r="Y39" t="b">
         <v>0</v>
       </c>
@@ -6551,7 +6551,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>searched_series</t>
+          <t>reused_existing_product_no</t>
         </is>
       </c>
       <c r="AJ39" t="b">
@@ -6559,7 +6559,7 @@
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>2026-08-31 13:56:12</t>
+          <t>2026-09-07 13:14:01</t>
         </is>
       </c>
     </row>
@@ -6594,7 +6594,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-08-31 13:16:53</t>
+          <t>2026-09-07 12:25:14</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
@@ -6715,7 +6715,7 @@
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>2026-08-31 13:56:12</t>
+          <t>2026-09-07 13:14:01</t>
         </is>
       </c>
     </row>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-08-31 13:16:53</t>
+          <t>2026-09-07 12:25:15</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -6871,7 +6871,7 @@
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>2026-08-31 13:56:12</t>
+          <t>2026-09-07 13:14:01</t>
         </is>
       </c>
     </row>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-08-31 13:16:53</t>
+          <t>2026-09-07 12:25:15</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
@@ -7027,7 +7027,7 @@
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>2026-08-31 13:56:12</t>
+          <t>2026-09-07 13:14:01</t>
         </is>
       </c>
     </row>
@@ -7062,7 +7062,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-08-31 13:16:53</t>
+          <t>2026-09-07 12:25:15</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
@@ -7182,7 +7182,7 @@
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>2026-08-31 13:56:12</t>
+          <t>2026-09-07 13:14:01</t>
         </is>
       </c>
     </row>
@@ -7198,26 +7198,26 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>서바이브</t>
+          <t>지옥심판</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=838594&amp;tab=sun</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=854096&amp;tab=sun</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>838594</t>
+          <t>854096</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-08-31 13:16:54</t>
+          <t>2026-09-07 12:25:16</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
@@ -7241,52 +7241,208 @@
         </is>
       </c>
       <c r="N44" t="n">
+        <v>1</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>지옥심판</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>지옥심판 (총 7화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>총 7화/미완결</t>
+        </is>
+      </c>
+      <c r="R44" t="n">
+        <v>7</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>평점 9.6 | 가강 주혁 | 2026.08.22. | 총7화/미완결 | 2화 무료</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>평점 9.6 | 가강 주혁 | 2026.08.22. | 총7화/미완결 | 2화 무료</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=14622042</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>14622042</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>지옥심판 (총 7화/미완결)
+평점
+9.6 | 가강 주혁 | 2026.08.22. | 총7화/미완결 | 2화 무료
+죄를 지은 인간은 언젠가 벌을 받게 되어있다. 이승이 아닌 저승에서라도.죄인을 심판하고 지옥으로 인도하는 저승사자 이현의 이야기.</t>
+        </is>
+      </c>
+      <c r="Y44" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z44" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>non_compilation_but_download_not_ok</t>
+        </is>
+      </c>
+      <c r="AE44" t="n">
         <v>2</v>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="inlineStr"/>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>2026-09-07 13:14:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>43</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>서바이브</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=838594&amp;tab=sun</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>838594</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:25:16</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="b">
+        <v>1</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>2</v>
+      </c>
+      <c r="O45" t="inlineStr">
         <is>
           <t>연금술 무인도 서바이브</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>연금술 무인도 서바이브 (총 42화/완결)</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
+      <c r="Q45" t="inlineStr">
         <is>
           <t>총 42화/완결</t>
         </is>
       </c>
-      <c r="R44" t="n">
+      <c r="R45" t="n">
         <v>42</v>
       </c>
-      <c r="S44" t="inlineStr">
+      <c r="S45" t="inlineStr">
         <is>
           <t>완결</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr">
+      <c r="T45" t="inlineStr">
         <is>
           <t>평점 9.9 | 호시 렌지,이구치 콘 호시 렌지 | 2025.02.24. | 총42화/완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="U45" t="inlineStr">
         <is>
           <t>평점 9.9 | 호시 렌지,이구치 콘 호시 렌지 | 2025.02.24. | 총42화/완결 | 1화 무료</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr">
+      <c r="V45" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=10375934</t>
         </is>
       </c>
-      <c r="W44" t="inlineStr">
+      <c r="W45" t="inlineStr">
         <is>
           <t>10375934</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
+      <c r="X45" t="inlineStr">
         <is>
           <t>연금술 무인도 서바이브 (총 42화/완결)
 평점
@@ -7294,200 +7450,44 @@
 항행 중 사고를 당한 연금술사 니코, 요리사 진, 포로남 셋이 표착한 곳은…… 지도에도 표시돼 있지 않은 무인도였다! 「무인도에서 처음으로 해야 할 일은?」, 「물 확보는 어떻게?」, 「식량 수집의 포인트는?」 살아남기 ..</t>
         </is>
       </c>
-      <c r="Y44" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z44" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA44" t="n">
+      <c r="Y45" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z45" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA45" t="n">
         <v>100</v>
       </c>
-      <c r="AB44" t="inlineStr">
+      <c r="AB45" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_2</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
+      <c r="AC45" t="inlineStr">
         <is>
           <t>matched</t>
         </is>
       </c>
-      <c r="AD44" t="inlineStr">
+      <c r="AD45" t="inlineStr">
         <is>
           <t>first_non_compilation_numeric_download</t>
-        </is>
-      </c>
-      <c r="AE44" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF44" t="inlineStr">
-        <is>
-          <t>5.6천</t>
-        </is>
-      </c>
-      <c r="AG44" t="n">
-        <v>5600</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:56:12</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>45</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>지옥심판</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=854096&amp;tab=sun</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>854096</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:16:54</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="b">
-        <v>1</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="N45" t="n">
-        <v>1</v>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>지옥심판</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>지옥심판 (총 7화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>총 7화/미완결</t>
-        </is>
-      </c>
-      <c r="R45" t="n">
-        <v>7</v>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>평점 9.6 | 가강 주혁 | 2026.08.22. | 총7화/미완결 | 2화 무료</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>평점 9.6 | 가강 주혁 | 2026.08.22. | 총7화/미완결 | 2화 무료</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=14622042</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>14622042</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>지옥심판 (총 7화/미완결)
-평점
-9.6 | 가강 주혁 | 2026.08.22. | 총7화/미완결 | 2화 무료
-죄를 지은 인간은 언젠가 벌을 받게 되어있다. 이승이 아닌 저승에서라도.죄인을 심판하고 지옥으로 인도하는 저승사자 이현의 이야기.</t>
-        </is>
-      </c>
-      <c r="Y45" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z45" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>105</v>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>review_needed</t>
-        </is>
-      </c>
-      <c r="AD45" t="inlineStr">
-        <is>
-          <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
       <c r="AE45" t="n">
         <v>2</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
-      <c r="AG45" t="inlineStr"/>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>5.6천</t>
+        </is>
+      </c>
+      <c r="AG45" t="n">
+        <v>5600</v>
+      </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>not_found</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="AI45" t="inlineStr">
@@ -7500,7 +7500,7 @@
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>2026-08-31 13:56:12</t>
+          <t>2026-09-07 13:14:01</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7516,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -7535,7 +7535,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-08-31 13:16:54</t>
+          <t>2026-09-07 12:25:16</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
@@ -7656,7 +7656,7 @@
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>2026-08-31 13:56:12</t>
+          <t>2026-09-07 13:14:01</t>
         </is>
       </c>
     </row>
@@ -7672,7 +7672,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-08-31 13:16:55</t>
+          <t>2026-09-07 12:25:16</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
@@ -7812,7 +7812,7 @@
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>2026-08-31 13:56:12</t>
+          <t>2026-09-07 13:14:01</t>
         </is>
       </c>
     </row>
@@ -7828,26 +7828,26 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>나는 참지 못한다</t>
+          <t>인터뷰</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=823476&amp;tab=sun</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=854396&amp;tab=sun</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>823476</t>
+          <t>854396</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-08-31 13:16:55</t>
+          <t>2026-09-07 12:25:16</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
@@ -7875,48 +7875,366 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
+          <t>살인자와의 인터뷰 [개정판][컬러연재]</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>살인자와의 인터뷰 [개정판][컬러연재] (총 53화/완결)</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>총 53화/완결</t>
+        </is>
+      </c>
+      <c r="R48" t="n">
+        <v>53</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>완결</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>평점 9.9 | KJK KJK | 2019.04.10. | 총53화/완결 | 4화 무료</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>평점 9.9 | KJK KJK | 2019.04.10. | 총53화/완결 | 4화 무료</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=3181357</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>3181357</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>살인자와의 인터뷰 [개정판][컬러연재] (총 53화/완결)
+평점
+9.9 | KJK KJK | 2019.04.10. | 총53화/완결 | 4화 무료
+특종보다는 흥미를 느끼는 취재거리만 찾는 도윤에게 구 남친이 연락해 귀가 솔깃한 제안을 한다.바로 자신의 심리치료 환자인 연쇄 살인범과의 인터뷰를 진행하는 것.자신의 은밀한 사생활(?!)을 유지하고 싶었던 도윤은 이 ..</t>
+        </is>
+      </c>
+      <c r="Y48" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z48" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t>first_non_compilation_numeric_download</t>
+        </is>
+      </c>
+      <c r="AE48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>30.1만</t>
+        </is>
+      </c>
+      <c r="AG48" t="n">
+        <v>301000</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>searched_series</t>
+        </is>
+      </c>
+      <c r="AJ48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>2026-09-07 13:14:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>77</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>나의 비발디</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=854344&amp;tab=sun</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>854344</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:25:16</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="b">
+        <v>1</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>1</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>나의 비발디</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>나의 비발디 (총 6화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>총 6화/미완결</t>
+        </is>
+      </c>
+      <c r="R49" t="n">
+        <v>6</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>평점 10.0 | 배청이 틸다123 | 2026.09.05. | 총6화/미완결 | 1화 무료</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>평점 10.0 | 배청이 틸다123 | 2026.09.05. | 총6화/미완결 | 1화 무료</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=14580181</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>14580181</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>나의 비발디 (총 6화/미완결)
+평점
+10.0 | 배청이 틸다123 | 2026.09.05. | 총6화/미완결 | 1화 무료
+"갖고 싶어... 가르쳐줘, 네 재능."천재의 재능을 훔쳐 정상에 오른 피아니스트 윤설아.그리고 버려진 천재, 우지환.홀로 신곡을 발표한 설아는 추락하고,복수를 결심한 지환은 다시 그녀의 앞에 나타난다.이번엔, 내가 널 가질 차..</t>
+        </is>
+      </c>
+      <c r="Y49" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z49" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>non_compilation_but_download_not_ok</t>
+        </is>
+      </c>
+      <c r="AE49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="inlineStr"/>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>searched_series</t>
+        </is>
+      </c>
+      <c r="AJ49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>2026-09-07 13:14:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>84</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
           <t>나는 참지 못한다</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=823476&amp;tab=sun</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>823476</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:25:17</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="b">
+        <v>1</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>1</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>나는 참지 못한다</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
         <is>
           <t>나는 참지 못한다 (총 115화/미완결)</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
+      <c r="Q50" t="inlineStr">
         <is>
           <t>총 115화/미완결</t>
         </is>
       </c>
-      <c r="R48" t="n">
+      <c r="R50" t="n">
         <v>115</v>
       </c>
-      <c r="S48" t="inlineStr">
+      <c r="S50" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr">
+      <c r="T50" t="inlineStr">
         <is>
           <t>평점 10.0 | 성현 성현 | 2026.06.13. | 총115화/미완결 | 111화 무료</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="U50" t="inlineStr">
         <is>
           <t>평점 10.0 | 성현 성현 | 2026.06.13. | 총115화/미완결 | 111화 무료</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr">
+      <c r="V50" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=10970308</t>
         </is>
       </c>
-      <c r="W48" t="inlineStr">
+      <c r="W50" t="inlineStr">
         <is>
           <t>10970308</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
+      <c r="X50" t="inlineStr">
         <is>
           <t>나는 참지 못한다 (총 115화/미완결)
 평점
@@ -7924,155 +8242,155 @@
 평범한 회사원 김연지는 교통사고 이후 변화를 겪게 된다.스트레스가 폭발하면 아무것도 참지 못하는 상태가 되고 만다.계속 일어나는 통제불능 사건들, 자신에게 접근하는 의문의 남성 민성훈.사건은 커지고 일상은 꼬여만 가..</t>
         </is>
       </c>
-      <c r="Y48" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z48" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA48" t="n">
+      <c r="Y50" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z50" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA50" t="n">
         <v>105</v>
       </c>
-      <c r="AB48" t="inlineStr">
+      <c r="AB50" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
+      <c r="AC50" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD48" t="inlineStr">
+      <c r="AD50" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE48" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF48" t="inlineStr"/>
-      <c r="AG48" t="inlineStr"/>
-      <c r="AH48" t="inlineStr">
+      <c r="AE50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="inlineStr"/>
+      <c r="AH50" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI48" t="inlineStr">
+      <c r="AI50" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:56:12</t>
+      <c r="AJ50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>2026-09-07 13:14:01</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C49" t="n">
-        <v>90</v>
-      </c>
-      <c r="D49" t="inlineStr">
+      <c r="C51" t="n">
+        <v>91</v>
+      </c>
+      <c r="D51" t="inlineStr">
         <is>
           <t>죽거나 혹은 사랑에 빠지거나</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>https://comic.naver.com/webtoon/list?titleId=819696&amp;tab=sun</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>819696</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:16:56</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="b">
-        <v>1</v>
-      </c>
-      <c r="J49" t="inlineStr">
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:25:17</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="b">
+        <v>1</v>
+      </c>
+      <c r="J51" t="inlineStr">
         <is>
           <t>login_or_adult_required</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr">
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="N49" t="n">
-        <v>1</v>
-      </c>
-      <c r="O49" t="inlineStr">
+      <c r="N51" t="n">
+        <v>1</v>
+      </c>
+      <c r="O51" t="inlineStr">
         <is>
           <t>죽거나 혹은 사랑에 빠지거나</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="P51" t="inlineStr">
         <is>
           <t>죽거나 혹은 사랑에 빠지거나 (총 128화/미완결)</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="Q51" t="inlineStr">
         <is>
           <t>총 128화/미완결</t>
         </is>
       </c>
-      <c r="R49" t="n">
+      <c r="R51" t="n">
         <v>128</v>
       </c>
-      <c r="S49" t="inlineStr">
+      <c r="S51" t="inlineStr">
         <is>
           <t>미완결</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr">
+      <c r="T51" t="inlineStr">
         <is>
           <t>평점 9.8 | 허니비 허니비 | 2026.06.13. | 총128화/미완결 | 122화 무료</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr">
+      <c r="U51" t="inlineStr">
         <is>
           <t>평점 9.8 | 허니비 허니비 | 2026.06.13. | 총128화/미완결 | 122화 무료</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr">
+      <c r="V51" t="inlineStr">
         <is>
           <t>https://series.naver.com/comic/detail.series?productNo=10555314</t>
         </is>
       </c>
-      <c r="W49" t="inlineStr">
+      <c r="W51" t="inlineStr">
         <is>
           <t>10555314</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
+      <c r="X51" t="inlineStr">
         <is>
           <t>죽거나 혹은 사랑에 빠지거나 (총 128화/미완결)
 평점
@@ -8080,51 +8398,51 @@
 아름다운 도시 루베른에서 일어나는 의문의 연쇄살인 사건. 조용하고 눈에 띄지 않는 이자벨라에게 살인마의 초대장이 전달되는데.. 목숨을 건 15일간의 내기. 절대 어떤 쾌락과 환상에도 사랑에 빠져서는 안 된다.</t>
         </is>
       </c>
-      <c r="Y49" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z49" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA49" t="n">
+      <c r="Y51" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z51" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA51" t="n">
         <v>105</v>
       </c>
-      <c r="AB49" t="inlineStr">
+      <c r="AB51" t="inlineStr">
         <is>
           <t>title_contains,bonus_total_episode_info,bonus_rank_1</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
+      <c r="AC51" t="inlineStr">
         <is>
           <t>review_needed</t>
         </is>
       </c>
-      <c r="AD49" t="inlineStr">
+      <c r="AD51" t="inlineStr">
         <is>
           <t>non_compilation_but_download_not_ok</t>
         </is>
       </c>
-      <c r="AE49" t="n">
+      <c r="AE51" t="n">
         <v>2</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
-      <c r="AG49" t="inlineStr"/>
-      <c r="AH49" t="inlineStr">
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="inlineStr"/>
+      <c r="AH51" t="inlineStr">
         <is>
           <t>not_found</t>
         </is>
       </c>
-      <c r="AI49" t="inlineStr">
+      <c r="AI51" t="inlineStr">
         <is>
           <t>reused_existing_product_no</t>
         </is>
       </c>
-      <c r="AJ49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:56:12</t>
+      <c r="AJ51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>2026-09-07 13:14:01</t>
         </is>
       </c>
     </row>
